--- a/output/downloads/sofr-forward-curve.xlsx
+++ b/output/downloads/sofr-forward-curve.xlsx
@@ -236,7 +236,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SOFR forward curve, 2026-10-16</a:t>
+              <a:t>SOFR forward curve, 2026-10-19</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="3">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.0389</v>
+        <v>0.0387</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>on 2026-10-15 (NY Fed)</t>
+          <t>on 2026-10-19 (NY Fed)</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 13:28 UTC</t>
+          <t>2026-10-20 17:59 UTC</t>
         </is>
       </c>
     </row>
@@ -855,13 +855,13 @@
         <v>31</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.0389421</v>
+        <v>0.0389413</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>0.0388812</v>
+        <v>0.0388804</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>0.038942</v>
+        <v>0.0389411</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0</v>
@@ -891,13 +891,13 @@
         <v>30</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.0394431</v>
+        <v>0.0394738</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.0393826</v>
+        <v>0.0394132</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>0.039443</v>
+        <v>0.0394737</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.0410883</v>
+        <v>0.04111620000000001</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>0.0410204</v>
+        <v>0.0410482</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0.0410894</v>
+        <v>0.0411171</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>0.01</v>
@@ -963,13 +963,13 @@
         <v>31</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.0418601</v>
+        <v>0.0419154</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.0417901</v>
+        <v>0.0418452</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>0.0418619</v>
+        <v>0.0419171</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>0.02</v>
@@ -999,13 +999,13 @@
         <v>28</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.0425273</v>
+        <v>0.0427757</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.04246229999999999</v>
+        <v>0.0427099</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0.0425314</v>
+        <v>0.0427796</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>0.04</v>
@@ -1035,13 +1035,13 @@
         <v>31</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.0432742</v>
+        <v>0.0435359</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.0431989</v>
+        <v>0.0434597</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0.0432806</v>
+        <v>0.043542</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>0.06</v>
@@ -1071,13 +1071,13 @@
         <v>30</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.04422830000000001</v>
+        <v>0.0445096</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>0.0441519</v>
+        <v>0.04443220000000001</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>0.0442377</v>
+        <v>0.0445186</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>0.09</v>
@@ -1107,13 +1107,13 @@
         <v>31</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.045053</v>
+        <v>0.0453835</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.0449715</v>
+        <v>0.04530090000000001</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.0450659</v>
+        <v>0.04539609999999999</v>
       </c>
       <c r="G19" s="13" t="n">
         <v>0.13</v>
@@ -1143,13 +1143,13 @@
         <v>30</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.04572689999999999</v>
+        <v>0.046054</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>0.0456458</v>
+        <v>0.0459718</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0.0457452</v>
+        <v>0.0460719</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>0.18</v>
@@ -1179,13 +1179,13 @@
         <v>31</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.0460442</v>
+        <v>0.04637260000000001</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.0459591</v>
+        <v>0.0462863</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.0460655</v>
+        <v>0.0463935</v>
       </c>
       <c r="G21" s="13" t="n">
         <v>0.21</v>
@@ -1215,16 +1215,16 @@
         <v>31</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.04627290000000001</v>
+        <v>0.0466261</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.0461862</v>
+        <v>0.0465381</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0.04630049999999999</v>
+        <v>0.0466531</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
@@ -1251,16 +1251,16 @@
         <v>30</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.0464281</v>
+        <v>0.0467797</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.0463445</v>
+        <v>0.0466948</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.0464609</v>
+        <v>0.04681199999999999</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
@@ -1287,16 +1287,16 @@
         <v>31</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.0465874</v>
+        <v>0.0469376</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>0.04650070000000001</v>
+        <v>0.04684960000000001</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0.0466264</v>
+        <v>0.0469761</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
@@ -1323,16 +1323,16 @@
         <v>30</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.046571</v>
+        <v>0.0469217</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.0464867</v>
+        <v>0.0468361</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0.0466167</v>
+        <v>0.0469667</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
@@ -1359,16 +1359,16 @@
         <v>31</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.0464409</v>
+        <v>0.0468024</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.0463542</v>
+        <v>0.0467143</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0.046494</v>
+        <v>0.0468547</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
@@ -1395,16 +1395,16 @@
         <v>31</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.0463868</v>
+        <v>0.0467494</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>0.04630049999999999</v>
+        <v>0.0466617</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0.0464445</v>
+        <v>0.0468063</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
         <v>29</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.0463412</v>
+        <v>0.04669</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>0.046261</v>
+        <v>0.04660859999999999</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>0.0464095</v>
+        <v>0.0467575</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
@@ -1467,16 +1467,16 @@
         <v>31</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.0462487</v>
+        <v>0.04653769999999999</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>0.0461621</v>
+        <v>0.04645</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.0463248</v>
+        <v>0.0466129</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
@@ -1503,16 +1503,16 @@
         <v>30</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>0.0462202</v>
+        <v>0.0464826</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>0.0461375</v>
+        <v>0.046399</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0.0463053</v>
+        <v>0.0465668</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
@@ -1539,16 +1539,16 @@
         <v>31</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>0.0461986</v>
+        <v>0.0464333</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0.0461127</v>
+        <v>0.0463466</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.0462943</v>
+        <v>0.046528</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
@@ -1575,16 +1575,16 @@
         <v>30</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.046176</v>
+        <v>0.04639</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>0.0460932</v>
+        <v>0.0463065</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0.0462819</v>
+        <v>0.0464949</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
@@ -1611,16 +1611,16 @@
         <v>31</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.0461621</v>
+        <v>0.0463646</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>0.0460762</v>
+        <v>0.0462779</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0.046278</v>
+        <v>0.0464794</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
@@ -1647,16 +1647,16 @@
         <v>31</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.04614099999999999</v>
+        <v>0.0463402</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>0.0460548</v>
+        <v>0.0462533</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0.0462687</v>
+        <v>0.0464667</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
@@ -1683,16 +1683,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.0461128</v>
+        <v>0.0463157</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>0.0460305</v>
+        <v>0.04623269999999999</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0.046252</v>
+        <v>0.0464537</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
@@ -1719,16 +1719,16 @@
         <v>31</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>0.0460874</v>
+        <v>0.0462913</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>0.046002</v>
+        <v>0.04620510000000001</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0.0462383</v>
+        <v>0.046441</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
@@ -1755,16 +1755,16 @@
         <v>30</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.0460489</v>
+        <v>0.0462424</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>0.0459662</v>
+        <v>0.046159</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0.0462127</v>
+        <v>0.0464049</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
@@ -1791,16 +1791,16 @@
         <v>31</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>0.0460095</v>
+        <v>0.0461826</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>0.0459249</v>
+        <v>0.0460973</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0.04618629999999999</v>
+        <v>0.0463581</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
@@ -1827,16 +1827,16 @@
         <v>31</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0.0459621</v>
+        <v>0.0461163</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0.0458771</v>
+        <v>0.0460308</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0.0461519</v>
+        <v>0.04630480000000001</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
@@ -1863,16 +1863,16 @@
         <v>28</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>0.0458931</v>
+        <v>0.046041</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>0.0458174</v>
+        <v>0.0459649</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0.046097</v>
+        <v>0.0462436</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>31</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.0458371</v>
+        <v>0.04599669999999999</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.04575249999999999</v>
+        <v>0.0459116</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0.0460552</v>
+        <v>0.0462134</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
@@ -1935,16 +1935,16 @@
         <v>30</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>0.0457698</v>
+        <v>0.04595170000000001</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>0.04568800000000001</v>
+        <v>0.0458692</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0.0460021</v>
+        <v>0.0461824</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         <v>31</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.0457069</v>
+        <v>0.0459136</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.0456229</v>
+        <v>0.0458288</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.0459549</v>
+        <v>0.0461601</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
@@ -2007,16 +2007,16 @@
         <v>30</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.0456487</v>
+        <v>0.0458752</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>0.0455676</v>
+        <v>0.0457933</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0.0459126</v>
+        <v>0.0461375</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
@@ -2043,16 +2043,16 @@
         <v>31</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.0456071</v>
+        <v>0.04584869999999999</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.0455231</v>
+        <v>0.0457637</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0.04588689999999999</v>
+        <v>0.0461269</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
@@ -2079,16 +2079,16 @@
         <v>31</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.04556809999999999</v>
+        <v>0.0458243</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>0.0454841</v>
+        <v>0.0457393</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0.0458652</v>
+        <v>0.04611970000000001</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
@@ -2115,16 +2115,16 @@
         <v>30</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.04553550000000001</v>
+        <v>0.0458052</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.045455</v>
+        <v>0.0457238</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.0458478</v>
+        <v>0.0461158</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
@@ -2151,16 +2151,16 @@
         <v>31</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.0455023</v>
+        <v>0.0457914</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>0.0454191</v>
+        <v>0.045707</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0.0458336</v>
+        <v>0.0461209</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
@@ -2187,16 +2187,16 @@
         <v>30</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.0454613</v>
+        <v>0.0457709</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>0.0453813</v>
+        <v>0.0456898</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0.0458103</v>
+        <v>0.046118</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
@@ -2223,16 +2223,16 @@
         <v>31</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.0454266</v>
+        <v>0.0457556</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>0.04534340000000001</v>
+        <v>0.0456712</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0.0457926</v>
+        <v>0.0461198</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
@@ -2259,16 +2259,16 @@
         <v>31</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.0453907</v>
+        <v>0.0457357</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>0.0453078</v>
+        <v>0.0456515</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>0.04577580000000001</v>
+        <v>0.0461189</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
@@ -2295,16 +2295,16 @@
         <v>28</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.0453614</v>
+        <v>0.045712</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>0.0452874</v>
+        <v>0.0456369</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0.04576590000000001</v>
+        <v>0.0461146</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
@@ -2331,16 +2331,16 @@
         <v>31</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.0453655</v>
+        <v>0.0457139</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.0452827</v>
+        <v>0.0456299</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.0457895</v>
+        <v>0.0461359</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
@@ -2367,16 +2367,16 @@
         <v>30</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>0.0453639</v>
+        <v>0.0457107</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>0.0452841</v>
+        <v>0.04562960000000001</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>0.0458076</v>
+        <v>0.04615230000000001</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
@@ -2403,16 +2403,16 @@
         <v>31</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>0.045364</v>
+        <v>0.0457188</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.0452812</v>
+        <v>0.0456348</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.045828</v>
+        <v>0.0461808</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>4.64</v>
+        <v>4.62</v>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
@@ -2439,16 +2439,16 @@
         <v>30</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>0.0453536</v>
+        <v>0.0457252</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>0.0452736</v>
+        <v>0.0456438</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>0.0458369</v>
+        <v>0.0462064</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>4.83</v>
+        <v>4.81</v>
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
@@ -2475,16 +2475,16 @@
         <v>31</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>0.0453519</v>
+        <v>0.0457434</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.0452688</v>
+        <v>0.0456588</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.0458578</v>
+        <v>0.04624710000000001</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>5.06</v>
+        <v>5.04</v>
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
@@ -2511,16 +2511,16 @@
         <v>31</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>0.0453621</v>
+        <v>0.0457627</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>0.0452789</v>
+        <v>0.0456781</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0.0458894</v>
+        <v>0.0462878</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
@@ -2547,16 +2547,16 @@
         <v>30</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>0.0453832</v>
+        <v>0.0457826</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.0453029</v>
+        <v>0.0457009</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.04593079999999999</v>
+        <v>0.04632799999999999</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>5.48</v>
+        <v>5.45</v>
       </c>
       <c r="H59" s="14" t="inlineStr">
         <is>
@@ -2583,16 +2583,16 @@
         <v>31</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.0454199</v>
+        <v>0.0458172</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>0.0453369</v>
+        <v>0.0457328</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0.0459913</v>
+        <v>0.04638639999999999</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>5.71</v>
+        <v>5.69</v>
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>30</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>0.0454455</v>
+        <v>0.04585</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>0.0453657</v>
+        <v>0.04576889999999999</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0.0460397</v>
+        <v>0.046442</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>5.94</v>
+        <v>5.92</v>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
@@ -2655,16 +2655,16 @@
         <v>31</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>0.0454725</v>
+        <v>0.0458941</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>0.045389</v>
+        <v>0.045809</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0.0460897</v>
+        <v>0.04650890000000001</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>6.17</v>
+        <v>6.15</v>
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
@@ -2691,16 +2691,16 @@
         <v>31</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>0.04549839999999999</v>
+        <v>0.0459397</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>0.0454152</v>
+        <v>0.04585479999999999</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0.0461393</v>
+        <v>0.0465782</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>6.41</v>
+        <v>6.38</v>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
@@ -2727,16 +2727,16 @@
         <v>28</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>0.0455255</v>
+        <v>0.0459786</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>0.0454506</v>
+        <v>0.0459022</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>0.0461888</v>
+        <v>0.0466395</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>6.63</v>
+        <v>6.61</v>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
@@ -2763,16 +2763,16 @@
         <v>31</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>0.0455853</v>
+        <v>0.0460416</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>0.0455013</v>
+        <v>0.045956</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0.0462725</v>
+        <v>0.0467264</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>6.87</v>
+        <v>6.85</v>
       </c>
       <c r="H65" s="14" t="inlineStr">
         <is>
@@ -2799,16 +2799,16 @@
         <v>30</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>0.0456489</v>
+        <v>0.04610159999999999</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>0.04556809999999999</v>
+        <v>0.0460191</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0.0463612</v>
+        <v>0.0468114</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>7.12</v>
+        <v>7.1</v>
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
@@ -2835,16 +2835,16 @@
         <v>31</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>0.045723</v>
+        <v>0.0461717</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>0.0456391</v>
+        <v>0.0460861</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>0.0464597</v>
+        <v>0.0469059</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>7.37</v>
+        <v>7.34</v>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
@@ -2871,16 +2871,16 @@
         <v>30</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>0.0457933</v>
+        <v>0.0462406</v>
       </c>
       <c r="E68" s="12" t="n">
-        <v>0.0457115</v>
+        <v>0.0461573</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0.0465543</v>
+        <v>0.0469991</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>7.61</v>
+        <v>7.58</v>
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
@@ -2907,16 +2907,16 @@
         <v>31</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>0.0458749</v>
+        <v>0.046323</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>0.04579030000000001</v>
+        <v>0.0462367</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0.0466627</v>
+        <v>0.0471082</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>7.88</v>
+        <v>7.85</v>
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
@@ -2943,16 +2943,16 @@
         <v>31</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>0.0459509</v>
+        <v>0.0464</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>0.0458659</v>
+        <v>0.0463134</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>0.0467648</v>
+        <v>0.0472113</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>8.140000000000001</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
@@ -2979,16 +2979,16 @@
         <v>30</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>0.0460203</v>
+        <v>0.0464698</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>0.0459376</v>
+        <v>0.0463854</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0.0468598</v>
+        <v>0.0473066</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>8.4</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H71" s="14" t="inlineStr">
         <is>
@@ -3015,16 +3015,16 @@
         <v>31</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>0.046098</v>
+        <v>0.0465474</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>0.0460125</v>
+        <v>0.0464603</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0.0469653</v>
+        <v>0.047412</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>8.67</v>
+        <v>8.65</v>
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
@@ -3051,16 +3051,16 @@
         <v>30</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>0.0461619</v>
+        <v>0.0466111</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>0.0460793</v>
+        <v>0.0465269</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0.0470545</v>
+        <v>0.0475009</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>8.93</v>
+        <v>8.9</v>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
@@ -3087,16 +3087,16 @@
         <v>31</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>0.046242</v>
+        <v>0.0466912</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>0.0461557</v>
+        <v>0.0466032</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0.047164</v>
+        <v>0.0476104</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>9.220000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
@@ -3123,16 +3123,16 @@
         <v>31</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>0.0463126</v>
+        <v>0.04676179999999999</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>0.0462266</v>
+        <v>0.0466741</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0.0472614</v>
+        <v>0.0477078</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>9.49</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
@@ -3159,16 +3159,16 @@
         <v>29</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>0.0463819</v>
+        <v>0.046831</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>0.0463015</v>
+        <v>0.04674909999999999</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>0.0473583</v>
+        <v>0.0478046</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>9.76</v>
+        <v>9.74</v>
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
@@ -3195,16 +3195,16 @@
         <v>31</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>0.0464652</v>
+        <v>0.0469146</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>0.0463784</v>
+        <v>0.0468261</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0.0474711</v>
+        <v>0.0479175</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>10.06</v>
+        <v>10.03</v>
       </c>
       <c r="H77" s="14" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
         <v>30</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>0.046531</v>
+        <v>0.0469803</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>0.0464464</v>
+        <v>0.04689409999999999</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0.0475652</v>
+        <v>0.0480116</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>10.34</v>
+        <v>10.31</v>
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
@@ -3267,16 +3267,16 @@
         <v>31</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>0.0465876</v>
+        <v>0.047037</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0.0465005</v>
+        <v>0.0469482</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0.047649</v>
+        <v>0.0480955</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>10.61</v>
+        <v>10.58</v>
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
@@ -3303,16 +3303,16 @@
         <v>30</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>0.04663929999999999</v>
+        <v>0.04708859999999999</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>0.0465549</v>
+        <v>0.0470026</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0.0477318</v>
+        <v>0.04817809999999999</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
@@ -3339,16 +3339,16 @@
         <v>31</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>0.046695</v>
+        <v>0.0471444</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>0.0466075</v>
+        <v>0.0470552</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0.0478172</v>
+        <v>0.0482637</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>11.22</v>
+        <v>11.19</v>
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
@@ -3375,16 +3375,16 @@
         <v>31</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>0.0467564</v>
+        <v>0.0472059</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>0.0466679</v>
+        <v>0.0471157</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0.0479077</v>
+        <v>0.0483541</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>11.51</v>
+        <v>11.48</v>
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
@@ -3411,16 +3411,16 @@
         <v>30</v>
       </c>
       <c r="D83" s="12" t="n">
-        <v>0.0468261</v>
+        <v>0.0472755</v>
       </c>
       <c r="E83" s="12" t="n">
-        <v>0.046741</v>
+        <v>0.0471888</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0.0480083</v>
+        <v>0.0484547</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>11.82</v>
+        <v>11.79</v>
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
@@ -3447,16 +3447,16 @@
         <v>31</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>0.0468985</v>
+        <v>0.047348</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>0.0468107</v>
+        <v>0.0472585</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0.04811149999999999</v>
+        <v>0.0485579</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>12.13</v>
+        <v>12.1</v>
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
@@ -3483,16 +3483,16 @@
         <v>30</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>0.0469557</v>
+        <v>0.0474052</v>
       </c>
       <c r="E85" s="12" t="n">
-        <v>0.0468699</v>
+        <v>0.04731779999999999</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>0.0481997</v>
+        <v>0.048646</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>12.44</v>
+        <v>12.41</v>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         <v>31</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>0.0470087</v>
+        <v>0.04745829999999999</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>0.0469198</v>
+        <v>0.0473677</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>0.0482845</v>
+        <v>0.0487308</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>12.76</v>
+        <v>12.73</v>
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
@@ -3555,16 +3555,16 @@
         <v>31</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>0.0470564</v>
+        <v>0.04750600000000001</v>
       </c>
       <c r="E87" s="12" t="n">
-        <v>0.04696760000000001</v>
+        <v>0.0474155</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0.0483619</v>
+        <v>0.0488083</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>13.05</v>
+        <v>13.02</v>
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
@@ -3591,16 +3591,16 @@
         <v>28</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>0.0471114</v>
+        <v>0.0475608</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>0.04703159999999999</v>
+        <v>0.0474796</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0.0484501</v>
+        <v>0.0488964</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>13.39</v>
+        <v>13.36</v>
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>31</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>0.0471912</v>
+        <v>0.04764090000000001</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>0.047101</v>
+        <v>0.047549</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>0.0485623</v>
+        <v>0.0490087</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>13.71</v>
+        <v>13.68</v>
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
@@ -3663,16 +3663,16 @@
         <v>30</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>0.0472549</v>
+        <v>0.0477046</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>0.0471685</v>
+        <v>0.04761650000000001</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0.0486575</v>
+        <v>0.0491039</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>14.03</v>
+        <v>13.99</v>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
@@ -3699,16 +3699,16 @@
         <v>31</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>0.04731150000000001</v>
+        <v>0.0477611</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>0.0472215</v>
+        <v>0.0476694</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>0.0487452</v>
+        <v>0.0491915</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>14.34</v>
+        <v>14.3</v>
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
@@ -3735,16 +3735,16 @@
         <v>30</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>0.0473505</v>
+        <v>0.0478</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>0.0472636</v>
+        <v>0.04771130000000001</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>0.0488174</v>
+        <v>0.0492634</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>14.67</v>
+        <v>14.63</v>
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
@@ -3771,16 +3771,16 @@
         <v>31</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>0.0473864</v>
+        <v>0.0478358</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>0.0472967</v>
+        <v>0.0477444</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>0.0488863</v>
+        <v>0.04933220000000001</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>15</v>
+        <v>14.96</v>
       </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
@@ -3807,16 +3807,16 @@
         <v>31</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>0.0474237</v>
+        <v>0.047873</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>0.0473326</v>
+        <v>0.04778019999999999</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>0.0489574</v>
+        <v>0.0494032</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>15.34</v>
+        <v>15.3</v>
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
@@ -3843,16 +3843,16 @@
         <v>30</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>0.04746590000000001</v>
+        <v>0.0479153</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>0.0473785</v>
+        <v>0.0478262</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>0.0490338</v>
+        <v>0.04947969999999999</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>15.68</v>
+        <v>15.64</v>
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
@@ -3879,16 +3879,16 @@
         <v>31</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>0.04752550000000001</v>
+        <v>0.0479751</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>0.0474349</v>
+        <v>0.0478828</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>0.0491267</v>
+        <v>0.0495728</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>16.01</v>
+        <v>15.98</v>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
@@ -3915,16 +3915,16 @@
         <v>30</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>0.0475995</v>
+        <v>0.0480494</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>0.0475118</v>
+        <v>0.04796</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>0.0492386</v>
+        <v>0.0496849</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>16.39</v>
+        <v>16.36</v>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
@@ -3951,16 +3951,16 @@
         <v>31</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>0.0476769</v>
+        <v>0.04812719999999999</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>0.04758569999999999</v>
+        <v>0.0480342</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>0.0493522</v>
+        <v>0.0497989</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>16.75</v>
+        <v>16.72</v>
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
@@ -3987,16 +3987,16 @@
         <v>31</v>
       </c>
       <c r="D99" s="12" t="n">
-        <v>0.0477259</v>
+        <v>0.04817630000000001</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>0.0476345</v>
+        <v>0.0480832</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>0.0494342</v>
+        <v>0.049881</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>17.08</v>
+        <v>17.05</v>
       </c>
       <c r="H99" s="14" t="inlineStr">
         <is>
@@ -4023,16 +4023,16 @@
         <v>28</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>0.0477332</v>
+        <v>0.0481833</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>0.0476513</v>
+        <v>0.0480999</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>0.0494774</v>
+        <v>0.0499238</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>17.44</v>
+        <v>17.41</v>
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
@@ -4059,16 +4059,16 @@
         <v>31</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>0.0477296</v>
+        <v>0.0481795</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>0.0476374</v>
+        <v>0.0480856</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>0.0495082</v>
+        <v>0.0499545</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>17.79</v>
+        <v>17.75</v>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         <v>30</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>0.047723</v>
+        <v>0.0481726</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>0.0476348</v>
+        <v>0.0480828</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>0.04953299999999999</v>
+        <v>0.0499789</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>18.1</v>
+        <v>18.06</v>
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
         <v>31</v>
       </c>
       <c r="D103" s="12" t="n">
-        <v>0.0477649</v>
+        <v>0.0482144</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>0.0476731</v>
+        <v>0.0481209</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>0.04961280000000001</v>
+        <v>0.0500586</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>18.48</v>
+        <v>18.44</v>
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
@@ -4167,16 +4167,16 @@
         <v>30</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>0.0478382</v>
+        <v>0.0482878</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>0.0477494</v>
+        <v>0.0481973</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>0.0497227</v>
+        <v>0.0501686</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>18.85</v>
+        <v>18.81</v>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
@@ -4203,16 +4203,16 @@
         <v>31</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>0.0479113</v>
+        <v>0.0483611</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>0.0478187</v>
+        <v>0.0482669</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>0.0498314</v>
+        <v>0.0502776</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>19.2</v>
+        <v>19.16</v>
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
@@ -4239,16 +4239,16 @@
         <v>31</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>0.0479439</v>
+        <v>0.04839400000000001</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>0.0478509</v>
+        <v>0.04829920000000001</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>0.0499043</v>
+        <v>0.0503506</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>19.6</v>
+        <v>19.57</v>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         <v>30</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>0.0479218</v>
+        <v>0.0483719</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>0.0478329</v>
+        <v>0.0482813</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>0.0499192</v>
+        <v>0.0503655</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>19.97</v>
+        <v>19.94</v>
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
@@ -4311,16 +4311,16 @@
         <v>31</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>0.0479132</v>
+        <v>0.0483633</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>0.0478208</v>
+        <v>0.04826920000000001</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>0.0499469</v>
+        <v>0.0503932</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>20.34</v>
+        <v>20.3</v>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
@@ -4347,16 +4347,16 @@
         <v>30</v>
       </c>
       <c r="D109" s="12" t="n">
-        <v>0.04796160000000001</v>
+        <v>0.04841160000000001</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>0.0478719</v>
+        <v>0.0483203</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>0.0500337</v>
+        <v>0.0504799</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>20.72</v>
+        <v>20.68</v>
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
@@ -4383,16 +4383,16 @@
         <v>31</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>0.048082</v>
+        <v>0.04853209999999999</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>0.0479896</v>
+        <v>0.048438</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>0.0501922</v>
+        <v>0.0506384</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>21.1</v>
+        <v>21.06</v>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
@@ -4419,16 +4419,16 @@
         <v>31</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0.0482088</v>
+        <v>0.048659</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>0.0481153</v>
+        <v>0.0485637</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>0.050356</v>
+        <v>0.0508022</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
@@ -4455,16 +4455,16 @@
         <v>28</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0.0482785</v>
+        <v>0.04872849999999999</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>0.0481948</v>
+        <v>0.0486432</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>0.050464</v>
+        <v>0.05091</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>21.86</v>
+        <v>21.82</v>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
@@ -4491,16 +4491,16 @@
         <v>31</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.0482944</v>
+        <v>0.0487446</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>0.0482008</v>
+        <v>0.0486493</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>0.0505188</v>
+        <v>0.05096510000000001</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>22.24</v>
+        <v>22.2</v>
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>30</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0.04826399999999999</v>
+        <v>0.0487142</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>0.048173</v>
+        <v>0.0486215</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>0.0505253</v>
+        <v>0.0509715</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>22.61</v>
+        <v>22.57</v>
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
@@ -4563,16 +4563,16 @@
         <v>31</v>
       </c>
       <c r="D115" s="12" t="n">
-        <v>0.048257</v>
+        <v>0.0487073</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>0.0481634</v>
+        <v>0.0486119</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>0.050559</v>
+        <v>0.0510052</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>23.02</v>
+        <v>22.98</v>
       </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
@@ -4599,16 +4599,16 @@
         <v>30</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>0.0482851</v>
+        <v>0.0487353</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>0.0481944</v>
+        <v>0.0486429</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>0.0506266</v>
+        <v>0.0510728</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>23.42</v>
+        <v>23.37</v>
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
@@ -4635,16 +4635,16 @@
         <v>31</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>0.04833999999999999</v>
+        <v>0.0487903</v>
       </c>
       <c r="E117" s="12" t="n">
-        <v>0.0482456</v>
+        <v>0.0486942</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>0.0507209</v>
+        <v>0.0511671</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>23.81</v>
+        <v>23.77</v>
       </c>
       <c r="H117" s="14" t="inlineStr">
         <is>
@@ -4671,16 +4671,16 @@
         <v>31</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>0.0483867</v>
+        <v>0.048837</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>0.0482919</v>
+        <v>0.0487404</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>0.050809</v>
+        <v>0.0512552</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>24.22</v>
+        <v>24.18</v>
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
@@ -4707,16 +4707,16 @@
         <v>30</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>0.0484118</v>
+        <v>0.0488621</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>0.0483209</v>
+        <v>0.0487695</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>0.0508697</v>
+        <v>0.05131579999999999</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>24.58</v>
+        <v>24.54</v>
       </c>
       <c r="H119" s="14" t="inlineStr">
         <is>
@@ -4743,16 +4743,16 @@
         <v>31</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>0.0484647</v>
+        <v>0.0489151</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>0.0483703</v>
+        <v>0.04881890000000001</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>0.0509669</v>
+        <v>0.0514131</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>25.02</v>
+        <v>24.98</v>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
@@ -4779,16 +4779,16 @@
         <v>30</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>0.0485483</v>
+        <v>0.0489986</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>0.0484571</v>
+        <v>0.0489057</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>0.0510905</v>
+        <v>0.0515366</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>25.42</v>
+        <v>25.38</v>
       </c>
       <c r="H121" s="14" t="inlineStr">
         <is>
@@ -4815,16 +4815,16 @@
         <v>31</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.0486668</v>
+        <v>0.0491172</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>0.0485713</v>
+        <v>0.0490199</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>0.0512477</v>
+        <v>0.0516939</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>25.81</v>
+        <v>25.77</v>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
@@ -4851,16 +4851,16 @@
         <v>31</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>0.0487898</v>
+        <v>0.0492402</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>0.0486941</v>
+        <v>0.0491427</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>0.0514133</v>
+        <v>0.05185940000000001</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>26.23</v>
+        <v>26.19</v>
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
@@ -4887,16 +4887,16 @@
         <v>29</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>0.04886</v>
+        <v>0.0493103</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>0.0487709</v>
+        <v>0.0492195</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>0.0515254</v>
+        <v>0.0519714</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>26.65</v>
+        <v>26.61</v>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
@@ -4923,16 +4923,16 @@
         <v>31</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>0.0488794</v>
+        <v>0.0493298</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>0.0487829</v>
+        <v>0.0492315</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>0.051584</v>
+        <v>0.0520301</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>27.05</v>
+        <v>27</v>
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>30</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>0.04884330000000001</v>
+        <v>0.0492937</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>0.0487508</v>
+        <v>0.0491995</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>0.0515911</v>
+        <v>0.0520372</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>27.48</v>
+        <v>27.43</v>
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
@@ -4995,16 +4995,16 @@
         <v>31</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>0.0487928</v>
+        <v>0.0492433</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>0.0486973</v>
+        <v>0.049146</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>0.0515818</v>
+        <v>0.052028</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>27.89</v>
+        <v>27.85</v>
       </c>
       <c r="H127" s="14" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>30</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>0.0487332</v>
+        <v>0.0491836</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>0.04864060000000001</v>
+        <v>0.0490893</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>0.0515613</v>
+        <v>0.0520074</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>28.28</v>
+        <v>28.24</v>
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
@@ -5067,16 +5067,16 @@
         <v>31</v>
       </c>
       <c r="D129" s="18" t="n">
-        <v>0.04873420000000001</v>
+        <v>0.0491847</v>
       </c>
       <c r="E129" s="18" t="n">
-        <v>0.04863870000000001</v>
+        <v>0.0490874</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.051564</v>
+        <v>0.0520102</v>
       </c>
       <c r="G129" s="19" t="n">
-        <v>28.3</v>
+        <v>28.26</v>
       </c>
       <c r="H129" s="20" t="inlineStr">
         <is>
@@ -5103,16 +5103,16 @@
         <v>31</v>
       </c>
       <c r="D130" s="18" t="n">
-        <v>0.04873420000000001</v>
+        <v>0.0491847</v>
       </c>
       <c r="E130" s="18" t="n">
-        <v>0.04863870000000001</v>
+        <v>0.0490874</v>
       </c>
       <c r="F130" s="18" t="n">
-        <v>0.051564</v>
+        <v>0.0520102</v>
       </c>
       <c r="G130" s="19" t="n">
-        <v>28.3</v>
+        <v>28.26</v>
       </c>
       <c r="H130" s="20" t="inlineStr">
         <is>
@@ -5139,16 +5139,16 @@
         <v>30</v>
       </c>
       <c r="D131" s="18" t="n">
-        <v>0.0487314</v>
+        <v>0.0491819</v>
       </c>
       <c r="E131" s="18" t="n">
-        <v>0.04863870000000001</v>
+        <v>0.0490874</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.051561</v>
+        <v>0.0520071</v>
       </c>
       <c r="G131" s="19" t="n">
-        <v>28.3</v>
+        <v>28.25</v>
       </c>
       <c r="H131" s="20" t="inlineStr">
         <is>
@@ -5175,16 +5175,16 @@
         <v>31</v>
       </c>
       <c r="D132" s="18" t="n">
-        <v>0.04873420000000001</v>
+        <v>0.0491847</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>0.04863870000000001</v>
+        <v>0.0490874</v>
       </c>
       <c r="F132" s="18" t="n">
-        <v>0.051564</v>
+        <v>0.0520102</v>
       </c>
       <c r="G132" s="19" t="n">
-        <v>28.3</v>
+        <v>28.26</v>
       </c>
       <c r="H132" s="20" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-16)</t>
+          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-19)</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
         <v>46316</v>
       </c>
       <c r="D4" s="23" t="n">
-        <v>96.2625</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="E4" s="15">
         <f>(100-D4)/100</f>
@@ -5574,13 +5574,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.0373896</v>
+        <v>0.0373861</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>0.146</v>
+        <v>-0.139</v>
       </c>
       <c r="I4" s="25" t="n">
-        <v>20743</v>
+        <v>20741</v>
       </c>
     </row>
     <row r="5">
@@ -5606,13 +5606,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.0383523</v>
+        <v>0.0383578</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>0.023</v>
+        <v>0.078</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>6448</v>
+        <v>6841</v>
       </c>
     </row>
     <row r="6">
@@ -5628,7 +5628,7 @@
         <v>46372</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>96.06</v>
+        <v>96.0575</v>
       </c>
       <c r="E6" s="15">
         <f>(100-D6)/100</f>
@@ -5638,13 +5638,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.0394226</v>
+        <v>0.0394373</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>0.226</v>
+        <v>0.123</v>
       </c>
       <c r="I6" s="25" t="n">
-        <v>1328168</v>
+        <v>1289722</v>
       </c>
     </row>
     <row r="7">
@@ -5670,13 +5670,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.0388812</v>
+        <v>0.0388804</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>-0.188</v>
+        <v>-0.196</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>342282</v>
+        <v>345018</v>
       </c>
     </row>
     <row r="8">
@@ -5692,7 +5692,7 @@
         <v>46407</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>95.94</v>
+        <v>95.9375</v>
       </c>
       <c r="E8" s="15">
         <f>(100-D8)/100</f>
@@ -5702,13 +5702,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.0405791</v>
+        <v>0.0406079</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>-0.209</v>
+        <v>-0.171</v>
       </c>
       <c r="I8" s="25" t="n">
-        <v>5699</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="9">
@@ -5724,7 +5724,7 @@
         <v>46357</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>96.065</v>
+        <v>96.06</v>
       </c>
       <c r="E9" s="15">
         <f>(100-D9)/100</f>
@@ -5734,13 +5734,13 @@
         <v>0</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.0393828</v>
+        <v>0.0394133</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>0.328</v>
+        <v>0.133</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>277312</v>
+        <v>288008</v>
       </c>
     </row>
     <row r="10">
@@ -5756,7 +5756,7 @@
         <v>46435</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>95.845</v>
+        <v>95.8425</v>
       </c>
       <c r="E10" s="15">
         <f>(100-D10)/100</f>
@@ -5766,10 +5766,10 @@
         <v>0.01</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.0415146</v>
+        <v>0.0415914</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.354</v>
+        <v>0.164</v>
       </c>
       <c r="I10" s="25" t="n">
         <v>2587</v>
@@ -5798,13 +5798,13 @@
         <v>0.01</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.0410215</v>
+        <v>0.04104910000000001</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.285</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>216719</v>
+        <v>230370</v>
       </c>
     </row>
     <row r="12">
@@ -5820,7 +5820,7 @@
         <v>46463</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>95.77500000000001</v>
+        <v>95.75</v>
       </c>
       <c r="E12" s="15">
         <f>(100-D12)/100</f>
@@ -5830,13 +5830,13 @@
         <v>0.03</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.04231989999999999</v>
+        <v>0.0424644</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>0.699</v>
+        <v>-0.356</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>1496875</v>
+        <v>1527314</v>
       </c>
     </row>
     <row r="13">
@@ -5852,23 +5852,23 @@
         <v>46419</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>95.81999999999999</v>
+        <v>95.815</v>
       </c>
       <c r="E13" s="15">
         <f>(100-D13)/100</f>
         <v/>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.0417926</v>
+        <v>0.0418475</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>-0.074</v>
+        <v>-0.025</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>177293</v>
+        <v>178423</v>
       </c>
     </row>
     <row r="14">
@@ -5884,7 +5884,7 @@
         <v>46498</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>95.68000000000001</v>
+        <v>95.655</v>
       </c>
       <c r="E14" s="15">
         <f>(100-D14)/100</f>
@@ -5894,13 +5894,13 @@
         <v>0.05</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.0432386</v>
+        <v>0.04348</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.386</v>
+        <v>0.3</v>
       </c>
       <c r="I14" s="25" t="n">
-        <v>1108</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="15">
@@ -5916,7 +5916,7 @@
         <v>46447</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>95.75</v>
+        <v>95.73</v>
       </c>
       <c r="E15" s="15">
         <f>(100-D15)/100</f>
@@ -5926,13 +5926,13 @@
         <v>0.04</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.0424667</v>
+        <v>0.0427141</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.333</v>
+        <v>0.141</v>
       </c>
       <c r="I15" s="25" t="n">
-        <v>106292</v>
+        <v>106075</v>
       </c>
     </row>
     <row r="16">
@@ -5948,7 +5948,7 @@
         <v>46526</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>95.605</v>
+        <v>95.575</v>
       </c>
       <c r="E16" s="15">
         <f>(100-D16)/100</f>
@@ -5958,10 +5958,10 @@
         <v>0.08</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.04401239999999999</v>
+        <v>0.04429420000000001</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>0.624</v>
+        <v>0.442</v>
       </c>
       <c r="I16" s="25" t="n">
         <v>543</v>
@@ -5980,7 +5980,7 @@
         <v>46478</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>95.675</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="E17" s="15">
         <f>(100-D17)/100</f>
@@ -5990,13 +5990,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.0432057</v>
+        <v>0.0434662</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>-0.443</v>
+        <v>-0.338</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>32811</v>
+        <v>33189</v>
       </c>
     </row>
     <row r="18">
@@ -6012,7 +6012,7 @@
         <v>46554</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>95.515</v>
+        <v>95.48</v>
       </c>
       <c r="E18" s="15">
         <f>(100-D18)/100</f>
@@ -6022,13 +6022,13 @@
         <v>0.11</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.04486</v>
+        <v>0.0451669</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>0.1</v>
+        <v>-0.331</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>1315709</v>
+        <v>1324648</v>
       </c>
     </row>
     <row r="19">
@@ -6044,7 +6044,7 @@
         <v>46508</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>95.58</v>
+        <v>95.55500000000001</v>
       </c>
       <c r="E19" s="15">
         <f>(100-D19)/100</f>
@@ -6054,13 +6054,13 @@
         <v>0.1</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.0441618</v>
+        <v>0.0444417</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>-0.382</v>
+        <v>-0.083</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>54556</v>
+        <v>55054</v>
       </c>
     </row>
     <row r="20">
@@ -6076,7 +6076,7 @@
         <v>46539</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>95.5</v>
+        <v>95.47</v>
       </c>
       <c r="E20" s="15">
         <f>(100-D20)/100</f>
@@ -6086,13 +6086,13 @@
         <v>0.13</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.0449849</v>
+        <v>0.0453139</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>-0.151</v>
+        <v>0.139</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>69221</v>
+        <v>69105</v>
       </c>
     </row>
     <row r="21">
@@ -6108,23 +6108,23 @@
         <v>46569</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>95.435</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E21" s="15">
         <f>(100-D21)/100</f>
         <v/>
       </c>
       <c r="F21" s="24" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.0456633</v>
+        <v>0.0459889</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>0.133</v>
+        <v>-0.111</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>21302</v>
+        <v>21236</v>
       </c>
     </row>
     <row r="22">
@@ -6140,7 +6140,7 @@
         <v>46645</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>95.36499999999999</v>
+        <v>95.33</v>
       </c>
       <c r="E22" s="15">
         <f>(100-D22)/100</f>
@@ -6150,13 +6150,13 @@
         <v>0.24</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.0463546</v>
+        <v>0.0466969</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>0.046</v>
+        <v>-0.031</v>
       </c>
       <c r="I22" s="25" t="n">
-        <v>1303344</v>
+        <v>1293215</v>
       </c>
     </row>
     <row r="23">
@@ -6172,7 +6172,7 @@
         <v>46600</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>95.40000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E23" s="15">
         <f>(100-D23)/100</f>
@@ -6182,13 +6182,13 @@
         <v>0.22</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.0459813</v>
+        <v>0.04630799999999999</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>-0.187</v>
+        <v>0.08</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>36906</v>
+        <v>37096</v>
       </c>
     </row>
     <row r="24">
@@ -6204,7 +6204,7 @@
         <v>46631</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>95.38</v>
+        <v>95.345</v>
       </c>
       <c r="E24" s="15">
         <f>(100-D24)/100</f>
@@ -6214,13 +6214,13 @@
         <v>0.27</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.0462136</v>
+        <v>0.0465649</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>0.136</v>
+        <v>0.149</v>
       </c>
       <c r="I24" s="25" t="n">
-        <v>18252</v>
+        <v>18254</v>
       </c>
     </row>
     <row r="25">
@@ -6236,7 +6236,7 @@
         <v>46661</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>95.36</v>
+        <v>95.325</v>
       </c>
       <c r="E25" s="15">
         <f>(100-D25)/100</f>
@@ -6246,13 +6246,13 @@
         <v>0.33</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.0463776</v>
+        <v>0.0467274</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>-0.224</v>
+        <v>-0.226</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>4939</v>
+        <v>4914</v>
       </c>
     </row>
     <row r="26">
@@ -6268,23 +6268,23 @@
         <v>46736</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>95.325</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="E26" s="15">
         <f>(100-D26)/100</f>
         <v/>
       </c>
       <c r="F26" s="24" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.0467889</v>
+        <v>0.0471425</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>0.389</v>
+        <v>0.425</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>1078682</v>
+        <v>1045683</v>
       </c>
     </row>
     <row r="27">
@@ -6300,7 +6300,7 @@
         <v>46692</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>95.345</v>
+        <v>95.31</v>
       </c>
       <c r="E27" s="15">
         <f>(100-D27)/100</f>
@@ -6310,13 +6310,13 @@
         <v>0.39</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.04654</v>
+        <v>0.0468883</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>-0.1</v>
+        <v>-0.117</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>6525</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="28">
@@ -6332,20 +6332,20 @@
         <v>46722</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>95.345</v>
+        <v>95.31</v>
       </c>
       <c r="E28" s="15">
         <f>(100-D28)/100</f>
         <v/>
       </c>
       <c r="F28" s="24" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.0465327</v>
+        <v>0.0468815</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>-0.173</v>
+        <v>-0.185</v>
       </c>
       <c r="I28" s="25" t="n">
         <v>1766</v>
@@ -6364,23 +6364,23 @@
         <v>46827</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>95.34</v>
+        <v>95.30500000000001</v>
       </c>
       <c r="E29" s="15">
         <f>(100-D29)/100</f>
         <v/>
       </c>
       <c r="F29" s="24" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.0465976</v>
+        <v>0.04694689999999999</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>-0.024</v>
+        <v>-0.031</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>1664856</v>
+        <v>1670113</v>
       </c>
     </row>
     <row r="30">
@@ -6396,23 +6396,23 @@
         <v>46925</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>95.34999999999999</v>
+        <v>95.325</v>
       </c>
       <c r="E30" s="15">
         <f>(100-D30)/100</f>
         <v/>
       </c>
       <c r="F30" s="24" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.0465015</v>
+        <v>0.0467511</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="I30" s="25" t="n">
-        <v>813255</v>
+        <v>818076</v>
       </c>
     </row>
     <row r="31">
@@ -6428,23 +6428,23 @@
         <v>47016</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>95.355</v>
+        <v>95.33499999999999</v>
       </c>
       <c r="E31" s="15">
         <f>(100-D31)/100</f>
         <v/>
       </c>
       <c r="F31" s="24" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.0464493</v>
+        <v>0.0466524</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>-0.007</v>
+        <v>0.024</v>
       </c>
       <c r="I31" s="25" t="n">
-        <v>645271</v>
+        <v>639231</v>
       </c>
     </row>
     <row r="32">
@@ -6460,23 +6460,23 @@
         <v>47107</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>95.36</v>
+        <v>95.34</v>
       </c>
       <c r="E32" s="15">
         <f>(100-D32)/100</f>
         <v/>
       </c>
       <c r="F32" s="24" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.0464004</v>
+        <v>0.0465945</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>0.004</v>
+        <v>-0.055</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>670842</v>
+        <v>669558</v>
       </c>
     </row>
     <row r="33">
@@ -6492,23 +6492,23 @@
         <v>47198</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>95.37</v>
+        <v>95.355</v>
       </c>
       <c r="E33" s="15">
         <f>(100-D33)/100</f>
         <v/>
       </c>
       <c r="F33" s="24" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.0462983</v>
+        <v>0.0464541</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>-0.017</v>
+        <v>0.041</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>551719</v>
+        <v>539280</v>
       </c>
     </row>
     <row r="34">
@@ -6524,23 +6524,23 @@
         <v>47289</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>95.38500000000001</v>
+        <v>95.36499999999999</v>
       </c>
       <c r="E34" s="15">
         <f>(100-D34)/100</f>
         <v/>
       </c>
       <c r="F34" s="24" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.0461513</v>
+        <v>0.04634820000000001</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>0.013</v>
+        <v>-0.018</v>
       </c>
       <c r="I34" s="25" t="n">
-        <v>379761</v>
+        <v>382236</v>
       </c>
     </row>
     <row r="35">
@@ -6556,23 +6556,23 @@
         <v>47380</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>95.395</v>
+        <v>95.37</v>
       </c>
       <c r="E35" s="15">
         <f>(100-D35)/100</f>
         <v/>
       </c>
       <c r="F35" s="24" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.04605139999999999</v>
+        <v>0.0463018</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>375406</v>
+        <v>374138</v>
       </c>
     </row>
     <row r="36">
@@ -6588,23 +6588,23 @@
         <v>47471</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>95.40000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E36" s="15">
         <f>(100-D36)/100</f>
         <v/>
       </c>
       <c r="F36" s="24" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.04599610000000001</v>
+        <v>0.0462978</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>-0.039</v>
+        <v>-0.022</v>
       </c>
       <c r="I36" s="25" t="n">
-        <v>296315</v>
+        <v>299423</v>
       </c>
     </row>
     <row r="37">
@@ -6620,23 +6620,23 @@
         <v>47562</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>95.405</v>
+        <v>95.37</v>
       </c>
       <c r="E37" s="15">
         <f>(100-D37)/100</f>
         <v/>
       </c>
       <c r="F37" s="24" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.0459553</v>
+        <v>0.0463014</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>0.053</v>
+        <v>0.014</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>264235</v>
+        <v>245161</v>
       </c>
     </row>
     <row r="38">
@@ -6652,23 +6652,23 @@
         <v>47653</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>95.40000000000001</v>
+        <v>95.36499999999999</v>
       </c>
       <c r="E38" s="15">
         <f>(100-D38)/100</f>
         <v/>
       </c>
       <c r="F38" s="24" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.0459944</v>
+        <v>0.0463496</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>-0.056</v>
+        <v>-0.004</v>
       </c>
       <c r="I38" s="25" t="n">
-        <v>183343</v>
+        <v>179640</v>
       </c>
     </row>
     <row r="39">
@@ -6684,23 +6684,23 @@
         <v>47744</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>95.395</v>
+        <v>95.355</v>
       </c>
       <c r="E39" s="15">
         <f>(100-D39)/100</f>
         <v/>
       </c>
       <c r="F39" s="24" t="n">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.0460555</v>
+        <v>0.04645</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>0.055</v>
+        <v>-0</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>160372</v>
+        <v>159669</v>
       </c>
     </row>
     <row r="40">
@@ -6716,23 +6716,23 @@
         <v>47835</v>
       </c>
       <c r="D40" s="23" t="n">
-        <v>95.38</v>
+        <v>95.34</v>
       </c>
       <c r="E40" s="15">
         <f>(100-D40)/100</f>
         <v/>
       </c>
       <c r="F40" s="24" t="n">
-        <v>5.89</v>
+        <v>5.86</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.0461951</v>
+        <v>0.04660040000000001</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>-0.049</v>
+        <v>0.004</v>
       </c>
       <c r="I40" s="25" t="n">
-        <v>142302</v>
+        <v>139046</v>
       </c>
     </row>
     <row r="41">
@@ -6748,23 +6748,23 @@
         <v>47926</v>
       </c>
       <c r="D41" s="23" t="n">
-        <v>95.36499999999999</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E41" s="15">
         <f>(100-D41)/100</f>
         <v/>
       </c>
       <c r="F41" s="24" t="n">
-        <v>6.58</v>
+        <v>6.56</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.0463532</v>
+        <v>0.0467992</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>0.032</v>
+        <v>-0.008</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>113555</v>
+        <v>114261</v>
       </c>
     </row>
     <row r="42">
@@ -6780,23 +6780,23 @@
         <v>48017</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>95.34</v>
+        <v>95.295</v>
       </c>
       <c r="E42" s="15">
         <f>(100-D42)/100</f>
         <v/>
       </c>
       <c r="F42" s="24" t="n">
-        <v>7.32</v>
+        <v>7.29</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.0465995</v>
+        <v>0.0470514</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>-0.005</v>
+        <v>0.014</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>83586</v>
+        <v>85793</v>
       </c>
     </row>
     <row r="43">
@@ -6812,23 +6812,23 @@
         <v>48108</v>
       </c>
       <c r="D43" s="23" t="n">
-        <v>95.31</v>
+        <v>95.265</v>
       </c>
       <c r="E43" s="15">
         <f>(100-D43)/100</f>
         <v/>
       </c>
       <c r="F43" s="24" t="n">
-        <v>8.08</v>
+        <v>8.06</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.0468995</v>
+        <v>0.0473489</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>-0.005</v>
+        <v>-0.011</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>66369</v>
+        <v>67086</v>
       </c>
     </row>
     <row r="44">
@@ -6844,23 +6844,23 @@
         <v>48199</v>
       </c>
       <c r="D44" s="23" t="n">
-        <v>95.28</v>
+        <v>95.235</v>
       </c>
       <c r="E44" s="15">
         <f>(100-D44)/100</f>
         <v/>
       </c>
       <c r="F44" s="24" t="n">
-        <v>8.880000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.0471997</v>
+        <v>0.04764980000000001</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>31860</v>
+        <v>35026</v>
       </c>
     </row>
     <row r="45">
@@ -6876,23 +6876,23 @@
         <v>48290</v>
       </c>
       <c r="D45" s="23" t="n">
-        <v>95.25</v>
+        <v>95.205</v>
       </c>
       <c r="E45" s="15">
         <f>(100-D45)/100</f>
         <v/>
       </c>
       <c r="F45" s="24" t="n">
-        <v>9.710000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.0475017</v>
+        <v>0.0479517</v>
       </c>
       <c r="H45" s="24" t="n">
         <v>0.017</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>5841</v>
+        <v>5803</v>
       </c>
     </row>
     <row r="46">
@@ -6908,23 +6908,23 @@
         <v>48381</v>
       </c>
       <c r="D46" s="23" t="n">
-        <v>95.22</v>
+        <v>95.175</v>
       </c>
       <c r="E46" s="15">
         <f>(100-D46)/100</f>
         <v/>
       </c>
       <c r="F46" s="24" t="n">
-        <v>10.57</v>
+        <v>10.54</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.0477962</v>
+        <v>0.0482462</v>
       </c>
       <c r="H46" s="24" t="n">
         <v>-0.038</v>
       </c>
       <c r="I46" s="25" t="n">
-        <v>1665</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="47">
@@ -6940,23 +6940,23 @@
         <v>48472</v>
       </c>
       <c r="D47" s="23" t="n">
-        <v>95.19499999999999</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="E47" s="15">
         <f>(100-D47)/100</f>
         <v/>
       </c>
       <c r="F47" s="24" t="n">
-        <v>11.46</v>
+        <v>11.43</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.04805519999999999</v>
+        <v>0.04850520000000001</v>
       </c>
       <c r="H47" s="24" t="n">
         <v>0.052</v>
       </c>
       <c r="I47" s="25" t="n">
-        <v>766</v>
+        <v>813</v>
       </c>
     </row>
     <row r="48">
@@ -6972,23 +6972,23 @@
         <v>48563</v>
       </c>
       <c r="D48" s="23" t="n">
-        <v>95.16500000000001</v>
+        <v>95.12</v>
       </c>
       <c r="E48" s="15">
         <f>(100-D48)/100</f>
         <v/>
       </c>
       <c r="F48" s="24" t="n">
-        <v>12.37</v>
+        <v>12.34</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.0483443</v>
+        <v>0.0487943</v>
       </c>
       <c r="H48" s="24" t="n">
         <v>-0.057</v>
       </c>
       <c r="I48" s="25" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="49">
@@ -7004,20 +7004,20 @@
         <v>48654</v>
       </c>
       <c r="D49" s="23" t="n">
-        <v>95.14</v>
+        <v>95.095</v>
       </c>
       <c r="E49" s="15">
         <f>(100-D49)/100</f>
         <v/>
       </c>
       <c r="F49" s="24" t="n">
-        <v>13.32</v>
+        <v>13.29</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.048606</v>
+        <v>0.04905610000000001</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="I49" s="25" t="n">
         <v>164</v>
@@ -7036,20 +7036,20 @@
         <v>48745</v>
       </c>
       <c r="D50" s="23" t="n">
-        <v>95.11</v>
+        <v>95.065</v>
       </c>
       <c r="E50" s="15">
         <f>(100-D50)/100</f>
         <v/>
       </c>
       <c r="F50" s="24" t="n">
-        <v>14.29</v>
+        <v>14.26</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.0488947</v>
+        <v>0.0493446</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>-0.053</v>
+        <v>-0.054</v>
       </c>
       <c r="I50" s="25" t="n">
         <v>35</v>
@@ -7068,17 +7068,17 @@
         <v>48843</v>
       </c>
       <c r="D51" s="23" t="n">
-        <v>95.08499999999999</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="E51" s="15">
         <f>(100-D51)/100</f>
         <v/>
       </c>
       <c r="F51" s="24" t="n">
-        <v>15.33</v>
+        <v>15.29</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.0491517</v>
+        <v>0.0496017</v>
       </c>
       <c r="H51" s="24" t="n">
         <v>0.017</v>
@@ -7100,17 +7100,17 @@
         <v>48934</v>
       </c>
       <c r="D52" s="23" t="n">
-        <v>95.06</v>
+        <v>95.015</v>
       </c>
       <c r="E52" s="15">
         <f>(100-D52)/100</f>
         <v/>
       </c>
       <c r="F52" s="24" t="n">
-        <v>16.39</v>
+        <v>16.36</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.0494064</v>
+        <v>0.0498564</v>
       </c>
       <c r="H52" s="24" t="n">
         <v>0.064</v>
@@ -7132,20 +7132,20 @@
         <v>49018</v>
       </c>
       <c r="D53" s="23" t="n">
-        <v>95.035</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="E53" s="15">
         <f>(100-D53)/100</f>
         <v/>
       </c>
       <c r="F53" s="24" t="n">
-        <v>17.41</v>
+        <v>17.37</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.0496338</v>
+        <v>0.0500837</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>-0.162</v>
+        <v>-0.163</v>
       </c>
       <c r="I53" s="25" t="n">
         <v>11</v>
@@ -7164,20 +7164,20 @@
         <v>49116</v>
       </c>
       <c r="D54" s="23" t="n">
-        <v>95.02</v>
+        <v>94.97499999999999</v>
       </c>
       <c r="E54" s="15">
         <f>(100-D54)/100</f>
         <v/>
       </c>
       <c r="F54" s="24" t="n">
-        <v>18.48</v>
+        <v>18.44</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.0498229</v>
+        <v>0.05027300000000001</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>0.229</v>
+        <v>0.23</v>
       </c>
       <c r="I54" s="25" t="n">
         <v>0</v>
@@ -7196,20 +7196,20 @@
         <v>49207</v>
       </c>
       <c r="D55" s="23" t="n">
-        <v>94.98999999999999</v>
+        <v>94.94499999999999</v>
       </c>
       <c r="E55" s="15">
         <f>(100-D55)/100</f>
         <v/>
       </c>
       <c r="F55" s="24" t="n">
-        <v>19.62</v>
+        <v>19.59</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.0500714</v>
+        <v>0.0505213</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>-0.286</v>
+        <v>-0.287</v>
       </c>
       <c r="I55" s="25" t="n">
         <v>0</v>
@@ -7228,17 +7228,17 @@
         <v>49298</v>
       </c>
       <c r="D56" s="23" t="n">
-        <v>94.98</v>
+        <v>94.935</v>
       </c>
       <c r="E56" s="15">
         <f>(100-D56)/100</f>
         <v/>
       </c>
       <c r="F56" s="24" t="n">
-        <v>20.75</v>
+        <v>20.71</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.0502337</v>
+        <v>0.0506837</v>
       </c>
       <c r="H56" s="24" t="n">
         <v>0.337</v>
@@ -7260,17 +7260,17 @@
         <v>49389</v>
       </c>
       <c r="D57" s="23" t="n">
-        <v>94.935</v>
+        <v>94.89</v>
       </c>
       <c r="E57" s="15">
         <f>(100-D57)/100</f>
         <v/>
       </c>
       <c r="F57" s="24" t="n">
-        <v>21.89</v>
+        <v>21.86</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.0506186</v>
+        <v>0.0510686</v>
       </c>
       <c r="H57" s="24" t="n">
         <v>-0.314</v>
@@ -7292,17 +7292,17 @@
         <v>49480</v>
       </c>
       <c r="D58" s="23" t="n">
-        <v>94.925</v>
+        <v>94.88</v>
       </c>
       <c r="E58" s="15">
         <f>(100-D58)/100</f>
         <v/>
       </c>
       <c r="F58" s="24" t="n">
-        <v>23.06</v>
+        <v>23.02</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.05077180000000001</v>
+        <v>0.0512218</v>
       </c>
       <c r="H58" s="24" t="n">
         <v>0.218</v>
@@ -7324,17 +7324,17 @@
         <v>49571</v>
       </c>
       <c r="D59" s="23" t="n">
-        <v>94.90000000000001</v>
+        <v>94.855</v>
       </c>
       <c r="E59" s="15">
         <f>(100-D59)/100</f>
         <v/>
       </c>
       <c r="F59" s="24" t="n">
-        <v>24.25</v>
+        <v>24.21</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.0509842</v>
+        <v>0.0514342</v>
       </c>
       <c r="H59" s="24" t="n">
         <v>-0.158</v>
@@ -7356,17 +7356,17 @@
         <v>49662</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>94.875</v>
+        <v>94.83</v>
       </c>
       <c r="E60" s="15">
         <f>(100-D60)/100</f>
         <v/>
       </c>
       <c r="F60" s="24" t="n">
-        <v>25.46</v>
+        <v>25.42</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.0512687</v>
+        <v>0.0517187</v>
       </c>
       <c r="H60" s="24" t="n">
         <v>0.187</v>
@@ -7388,17 +7388,17 @@
         <v>49753</v>
       </c>
       <c r="D61" s="23" t="n">
-        <v>94.83</v>
+        <v>94.785</v>
       </c>
       <c r="E61" s="15">
         <f>(100-D61)/100</f>
         <v/>
       </c>
       <c r="F61" s="24" t="n">
-        <v>26.69</v>
+        <v>26.65</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.0516833</v>
+        <v>0.0521333</v>
       </c>
       <c r="H61" s="24" t="n">
         <v>-0.167</v>
@@ -7420,17 +7420,17 @@
         <v>49844</v>
       </c>
       <c r="D62" s="23" t="n">
-        <v>94.81999999999999</v>
+        <v>94.77500000000001</v>
       </c>
       <c r="E62" s="15">
         <f>(100-D62)/100</f>
         <v/>
       </c>
       <c r="F62" s="24" t="n">
-        <v>27.94</v>
+        <v>27.9</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.0518058</v>
+        <v>0.0522558</v>
       </c>
       <c r="H62" s="24" t="n">
         <v>0.058</v>
@@ -7442,7 +7442,7 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Fit: 59 contracts, RMS residual 0.22 bp, max 0.699 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
+          <t>Fit: 59 contracts, RMS residual 0.17 bp, max 0.442 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
         </is>
       </c>
     </row>
@@ -7457,7 +7457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7485,15 +7485,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="B4" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B5" s="26" t="n">
         <v>0.0388</v>
@@ -7501,7 +7501,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="B6" s="26" t="n">
         <v>0.0389</v>
@@ -7509,79 +7509,79 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="B8" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="B9" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="B10" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="B11" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="B12" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="B13" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B14" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="B15" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B16" s="26" t="n">
         <v>0.039</v>
@@ -7589,55 +7589,55 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="B17" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="B18" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B19" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B20" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B21" s="26" t="n">
-        <v>0.0385</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="B22" s="26" t="n">
-        <v>0.0385</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B23" s="26" t="n">
         <v>0.0385</v>
@@ -7645,23 +7645,23 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B24" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B25" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B26" s="26" t="n">
         <v>0.0362</v>
@@ -7669,15 +7669,15 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B27" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B28" s="26" t="n">
         <v>0.0362</v>
@@ -7685,39 +7685,39 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B29" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B30" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B31" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B32" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B33" s="26" t="n">
         <v>0.0365</v>
@@ -7725,7 +7725,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B34" s="26" t="n">
         <v>0.0366</v>
@@ -7733,111 +7733,111 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B35" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B36" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B37" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B38" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B39" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B40" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B41" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B42" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B43" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B44" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B45" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B48" s="26" t="n">
         <v>0.0362</v>
@@ -7845,63 +7845,63 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B49" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B50" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B51" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B52" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B53" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B54" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B55" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B56" s="26" t="n">
         <v>0.0366</v>
@@ -7909,7 +7909,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B57" s="26" t="n">
         <v>0.0365</v>
@@ -7917,15 +7917,15 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B58" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B59" s="26" t="n">
         <v>0.0365</v>
@@ -7933,23 +7933,23 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B60" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B61" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B62" s="26" t="n">
         <v>0.0364</v>
@@ -7957,159 +7957,159 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B63" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B64" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B65" s="26" t="n">
-        <v>0.0357</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B66" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B67" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0357</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B68" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B69" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B70" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B71" s="26" t="n">
-        <v>0.0355</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B72" s="26" t="n">
-        <v>0.0353</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B73" s="26" t="n">
-        <v>0.0358</v>
+        <v>0.0355</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B74" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B75" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B76" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B77" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B78" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B79" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B80" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B81" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B82" s="26" t="n">
         <v>0.0362</v>
@@ -8117,23 +8117,23 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B83" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B84" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B85" s="26" t="n">
         <v>0.0362</v>
@@ -8141,55 +8141,55 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B86" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B87" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B88" s="26" t="n">
-        <v>0.0369</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B89" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B90" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B91" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B92" s="26" t="n">
         <v>0.036</v>
@@ -8197,55 +8197,55 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B93" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B94" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B95" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B96" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B97" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B98" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B99" s="26" t="n">
         <v>0.0363</v>
@@ -8253,15 +8253,15 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B100" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B101" s="26" t="n">
         <v>0.0363</v>
@@ -8269,34 +8269,26 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B102" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B103" s="26" t="n">
-        <v>0.0355</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B104" s="26" t="n">
-        <v>0.0351</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="n">
-        <v>46162</v>
-      </c>
-      <c r="B105" s="26" t="n">
-        <v>0.035</v>
+        <v>0.0363</v>
       </c>
     </row>
   </sheetData>

--- a/output/downloads/sofr-forward-curve.xlsx
+++ b/output/downloads/sofr-forward-curve.xlsx
@@ -236,7 +236,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SOFR forward curve, 2026-10-19</a:t>
+              <a:t>SOFR forward curve, 2026-10-20</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="3">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>on 2026-10-19 (NY Fed)</t>
+          <t>on 2026-10-20 (NY Fed)</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 17:59 UTC</t>
+          <t>2026-10-21 18:03 UTC</t>
         </is>
       </c>
     </row>
@@ -855,13 +855,13 @@
         <v>31</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.0389413</v>
+        <v>0.038949</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>0.0388804</v>
+        <v>0.0388881</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>0.0389411</v>
+        <v>0.0389488</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0</v>
@@ -891,13 +891,13 @@
         <v>30</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.0394738</v>
+        <v>0.0394398</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.0394132</v>
+        <v>0.0393793</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>0.0394737</v>
+        <v>0.0394396</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.04111620000000001</v>
+        <v>0.04106659999999999</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>0.0410482</v>
+        <v>0.04099879999999999</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0.0411171</v>
+        <v>0.0410675</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>0.01</v>
@@ -963,13 +963,13 @@
         <v>31</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.0419154</v>
+        <v>0.0418666</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.0418452</v>
+        <v>0.04179649999999999</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>0.0419171</v>
+        <v>0.0418682</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>0.02</v>
@@ -999,13 +999,13 @@
         <v>28</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.0427757</v>
+        <v>0.0427749</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.0427099</v>
+        <v>0.0427092</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0.0427796</v>
+        <v>0.0427788</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>0.04</v>
@@ -1035,13 +1035,13 @@
         <v>31</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.0435359</v>
+        <v>0.0435616</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.0434597</v>
+        <v>0.0434853</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0.043542</v>
+        <v>0.0435677</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>0.06</v>
@@ -1071,13 +1071,13 @@
         <v>30</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.0445096</v>
+        <v>0.0445668</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>0.04443220000000001</v>
+        <v>0.0444892</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>0.0445186</v>
+        <v>0.0445758</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>0.09</v>
@@ -1107,16 +1107,16 @@
         <v>31</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.0453835</v>
+        <v>0.0454319</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.04530090000000001</v>
+        <v>0.045349</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.04539609999999999</v>
+        <v>0.0454443</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         <v>30</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.046054</v>
+        <v>0.04615929999999999</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>0.0459718</v>
+        <v>0.0460766</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0.0460719</v>
+        <v>0.0461771</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>0.18</v>
@@ -1179,13 +1179,13 @@
         <v>31</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.04637260000000001</v>
+        <v>0.0465091</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.0462863</v>
+        <v>0.0464223</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.0463935</v>
+        <v>0.0465298</v>
       </c>
       <c r="G21" s="13" t="n">
         <v>0.21</v>
@@ -1215,13 +1215,13 @@
         <v>31</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.0466261</v>
+        <v>0.0468264</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.0465381</v>
+        <v>0.0467376</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0.0466531</v>
+        <v>0.04685330000000001</v>
       </c>
       <c r="G22" s="13" t="n">
         <v>0.27</v>
@@ -1251,13 +1251,13 @@
         <v>30</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.0467797</v>
+        <v>0.0470167</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.0466948</v>
+        <v>0.046931</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.04681199999999999</v>
+        <v>0.0470488</v>
       </c>
       <c r="G23" s="13" t="n">
         <v>0.32</v>
@@ -1287,13 +1287,13 @@
         <v>31</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.0469376</v>
+        <v>0.0472098</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>0.04684960000000001</v>
+        <v>0.0471208</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0.0469761</v>
+        <v>0.047248</v>
       </c>
       <c r="G24" s="13" t="n">
         <v>0.38</v>
@@ -1323,13 +1323,13 @@
         <v>30</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.0469217</v>
+        <v>0.0471833</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.0468361</v>
+        <v>0.0470967</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0.0469667</v>
+        <v>0.0472281</v>
       </c>
       <c r="G25" s="13" t="n">
         <v>0.45</v>
@@ -1359,13 +1359,13 @@
         <v>31</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.0468024</v>
+        <v>0.0471295</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.0467143</v>
+        <v>0.0470402</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0.0468547</v>
+        <v>0.0471816</v>
       </c>
       <c r="G26" s="13" t="n">
         <v>0.52</v>
@@ -1395,13 +1395,13 @@
         <v>31</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.0467494</v>
+        <v>0.0470979</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>0.0466617</v>
+        <v>0.0470089</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0.0468063</v>
+        <v>0.0471546</v>
       </c>
       <c r="G27" s="13" t="n">
         <v>0.57</v>
@@ -1431,13 +1431,13 @@
         <v>29</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.04669</v>
+        <v>0.0470314</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>0.04660859999999999</v>
+        <v>0.0469487</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>0.0467575</v>
+        <v>0.0470985</v>
       </c>
       <c r="G28" s="13" t="n">
         <v>0.67</v>
@@ -1467,13 +1467,13 @@
         <v>31</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.04653769999999999</v>
+        <v>0.046903</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>0.04645</v>
+        <v>0.046814</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.0466129</v>
+        <v>0.0469779</v>
       </c>
       <c r="G29" s="13" t="n">
         <v>0.75</v>
@@ -1503,13 +1503,13 @@
         <v>30</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>0.0464826</v>
+        <v>0.04683760000000001</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>0.046399</v>
+        <v>0.0467527</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0.0465668</v>
+        <v>0.0469215</v>
       </c>
       <c r="G30" s="13" t="n">
         <v>0.84</v>
@@ -1539,16 +1539,16 @@
         <v>31</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>0.0464333</v>
+        <v>0.0467746</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0.0463466</v>
+        <v>0.0466867</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.046528</v>
+        <v>0.04686899999999999</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
@@ -1575,13 +1575,13 @@
         <v>30</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.04639</v>
+        <v>0.0467159</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>0.0463065</v>
+        <v>0.0466313</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0.0464949</v>
+        <v>0.0468205</v>
       </c>
       <c r="G32" s="13" t="n">
         <v>1.05</v>
@@ -1611,16 +1611,16 @@
         <v>31</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.0463646</v>
+        <v>0.0466748</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>0.0462779</v>
+        <v>0.046587</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0.0464794</v>
+        <v>0.04678930000000001</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
@@ -1647,16 +1647,16 @@
         <v>31</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.0463402</v>
+        <v>0.0466324</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>0.0462533</v>
+        <v>0.0465443</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0.0464667</v>
+        <v>0.04675849999999999</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
@@ -1683,13 +1683,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.0463157</v>
+        <v>0.0465911</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>0.04623269999999999</v>
+        <v>0.0465071</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0.0464537</v>
+        <v>0.0467287</v>
       </c>
       <c r="G35" s="13" t="n">
         <v>1.38</v>
@@ -1719,16 +1719,16 @@
         <v>31</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>0.0462913</v>
+        <v>0.0465505</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>0.04620510000000001</v>
+        <v>0.0464633</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0.046441</v>
+        <v>0.0466997</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
@@ -1755,16 +1755,16 @@
         <v>30</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.0462424</v>
+        <v>0.0464836</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>0.046159</v>
+        <v>0.0463993</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0.0464049</v>
+        <v>0.04664570000000001</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
@@ -1791,16 +1791,16 @@
         <v>31</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>0.0461826</v>
+        <v>0.0464064</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>0.0460973</v>
+        <v>0.0463204</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0.0463581</v>
+        <v>0.0465815</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
@@ -1827,16 +1827,16 @@
         <v>31</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0.0461163</v>
+        <v>0.04632500000000001</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0.0460308</v>
+        <v>0.0462387</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0.04630480000000001</v>
+        <v>0.04651309999999999</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
@@ -1863,16 +1863,16 @@
         <v>28</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>0.046041</v>
+        <v>0.0462362</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>0.0459649</v>
+        <v>0.04615929999999999</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0.0462436</v>
+        <v>0.0464382</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>31</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.04599669999999999</v>
+        <v>0.0461794</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.0459116</v>
+        <v>0.0460936</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0.0462134</v>
+        <v>0.0463956</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
@@ -1935,16 +1935,16 @@
         <v>30</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>0.04595170000000001</v>
+        <v>0.0461177</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>0.0458692</v>
+        <v>0.0460346</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0.0461824</v>
+        <v>0.046348</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
@@ -1971,13 +1971,13 @@
         <v>31</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.0459136</v>
+        <v>0.0460523</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.0458288</v>
+        <v>0.045967</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.0461601</v>
+        <v>0.0462983</v>
       </c>
       <c r="G43" s="13" t="n">
         <v>2.46</v>
@@ -2007,13 +2007,13 @@
         <v>30</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.0458752</v>
+        <v>0.0459787</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>0.0457933</v>
+        <v>0.0458965</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0.0461375</v>
+        <v>0.0462405</v>
       </c>
       <c r="G44" s="13" t="n">
         <v>2.62</v>
@@ -2043,13 +2043,13 @@
         <v>31</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.04584869999999999</v>
+        <v>0.0459174</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.0457637</v>
+        <v>0.0458322</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0.0461269</v>
+        <v>0.04619500000000001</v>
       </c>
       <c r="G45" s="13" t="n">
         <v>2.78</v>
@@ -2079,13 +2079,13 @@
         <v>31</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.0458243</v>
+        <v>0.04586369999999999</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>0.0457393</v>
+        <v>0.0457786</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0.04611970000000001</v>
+        <v>0.04615859999999999</v>
       </c>
       <c r="G46" s="13" t="n">
         <v>2.95</v>
@@ -2115,16 +2115,16 @@
         <v>30</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.0458052</v>
+        <v>0.0458282</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.0457238</v>
+        <v>0.0457467</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.0461158</v>
+        <v>0.0461382</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
@@ -2151,16 +2151,16 @@
         <v>31</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.0457914</v>
+        <v>0.04579850000000001</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>0.045707</v>
+        <v>0.0457142</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0.0461209</v>
+        <v>0.0461275</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
@@ -2187,13 +2187,13 @@
         <v>30</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.0457709</v>
+        <v>0.0457618</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>0.0456898</v>
+        <v>0.0456807</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0.046118</v>
+        <v>0.0461083</v>
       </c>
       <c r="G49" s="13" t="n">
         <v>3.47</v>
@@ -2223,13 +2223,13 @@
         <v>31</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.0457556</v>
+        <v>0.0457287</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>0.0456712</v>
+        <v>0.0456444</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0.0461198</v>
+        <v>0.0460923</v>
       </c>
       <c r="G50" s="13" t="n">
         <v>3.64</v>
@@ -2259,13 +2259,13 @@
         <v>31</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.0457357</v>
+        <v>0.045692</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>0.0456515</v>
+        <v>0.045608</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>0.0461189</v>
+        <v>0.0460747</v>
       </c>
       <c r="G51" s="13" t="n">
         <v>3.83</v>
@@ -2295,16 +2295,16 @@
         <v>28</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.045712</v>
+        <v>0.0456608</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>0.0456369</v>
+        <v>0.0455859</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0.0461146</v>
+        <v>0.0460628</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
@@ -2331,16 +2331,16 @@
         <v>31</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.0457139</v>
+        <v>0.045664</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.0456299</v>
+        <v>0.04558010000000001</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.0461359</v>
+        <v>0.0460854</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
@@ -2367,16 +2367,16 @@
         <v>30</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>0.0457107</v>
+        <v>0.0456634</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>0.04562960000000001</v>
+        <v>0.0455825</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>0.04615230000000001</v>
+        <v>0.0461044</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
@@ -2403,16 +2403,16 @@
         <v>31</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>0.0457188</v>
+        <v>0.045667</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.0456348</v>
+        <v>0.04558309999999999</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.0461808</v>
+        <v>0.0461283</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>4.62</v>
+        <v>4.61</v>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
@@ -2439,13 +2439,13 @@
         <v>30</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>0.0457252</v>
+        <v>0.0456601</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>0.0456438</v>
+        <v>0.045579</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>0.0462064</v>
+        <v>0.0461406</v>
       </c>
       <c r="G56" s="13" t="n">
         <v>4.81</v>
@@ -2475,16 +2475,16 @@
         <v>31</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>0.0457434</v>
+        <v>0.0456575</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.0456588</v>
+        <v>0.0455733</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.04624710000000001</v>
+        <v>0.0461606</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
@@ -2511,16 +2511,16 @@
         <v>31</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>0.0457627</v>
+        <v>0.0456575</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>0.0456781</v>
+        <v>0.0455732</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0.0462878</v>
+        <v>0.0461819</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
@@ -2547,13 +2547,13 @@
         <v>30</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>0.0457826</v>
+        <v>0.0456615</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.0457009</v>
+        <v>0.0455802</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.04632799999999999</v>
+        <v>0.0462062</v>
       </c>
       <c r="G59" s="13" t="n">
         <v>5.45</v>
@@ -2583,16 +2583,16 @@
         <v>31</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.0458172</v>
+        <v>0.04567789999999999</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>0.0457328</v>
+        <v>0.045594</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0.04638639999999999</v>
+        <v>0.0462463</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>5.69</v>
+        <v>5.68</v>
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>30</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>0.04585</v>
+        <v>0.0456912</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>0.04576889999999999</v>
+        <v>0.0456106</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0.046442</v>
+        <v>0.0462825</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>5.92</v>
+        <v>5.91</v>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
@@ -2655,16 +2655,16 @@
         <v>31</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>0.0458941</v>
+        <v>0.0457157</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>0.045809</v>
+        <v>0.0456312</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0.04650890000000001</v>
+        <v>0.0463297</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>6.15</v>
+        <v>6.14</v>
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
@@ -2691,13 +2691,13 @@
         <v>31</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>0.0459397</v>
+        <v>0.0457459</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>0.04585479999999999</v>
+        <v>0.0456618</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0.0465782</v>
+        <v>0.0463837</v>
       </c>
       <c r="G63" s="13" t="n">
         <v>6.38</v>
@@ -2727,16 +2727,16 @@
         <v>28</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>0.0459786</v>
+        <v>0.0457797</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>0.0459022</v>
+        <v>0.045704</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>0.0466395</v>
+        <v>0.0464398</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>6.61</v>
+        <v>6.6</v>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
@@ -2763,16 +2763,16 @@
         <v>31</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>0.0460416</v>
+        <v>0.0458446</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>0.045956</v>
+        <v>0.0457597</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0.0467264</v>
+        <v>0.0465286</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>6.85</v>
+        <v>6.84</v>
       </c>
       <c r="H65" s="14" t="inlineStr">
         <is>
@@ -2799,16 +2799,16 @@
         <v>30</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>0.04610159999999999</v>
+        <v>0.0459065</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>0.0460191</v>
+        <v>0.04582480000000001</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0.0468114</v>
+        <v>0.0466155</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
@@ -2835,16 +2835,16 @@
         <v>31</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>0.0461717</v>
+        <v>0.04596910000000001</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>0.0460861</v>
+        <v>0.0458843</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>0.0469059</v>
+        <v>0.0467025</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>7.34</v>
+        <v>7.33</v>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
@@ -2871,13 +2871,13 @@
         <v>30</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>0.0462406</v>
+        <v>0.04602120000000001</v>
       </c>
       <c r="E68" s="12" t="n">
-        <v>0.0461573</v>
+        <v>0.0459386</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0.0469991</v>
+        <v>0.0467788</v>
       </c>
       <c r="G68" s="13" t="n">
         <v>7.58</v>
@@ -2907,16 +2907,16 @@
         <v>31</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>0.046323</v>
+        <v>0.0460835</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>0.0462367</v>
+        <v>0.0459981</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0.0471082</v>
+        <v>0.04686779999999999</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>7.85</v>
+        <v>7.84</v>
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
@@ -2943,13 +2943,13 @@
         <v>31</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>0.0464</v>
+        <v>0.0461482</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>0.0463134</v>
+        <v>0.0460625</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>0.0472113</v>
+        <v>0.0469587</v>
       </c>
       <c r="G70" s="13" t="n">
         <v>8.109999999999999</v>
@@ -2979,16 +2979,16 @@
         <v>30</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>0.0464698</v>
+        <v>0.0462158</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>0.0463854</v>
+        <v>0.0461324</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0.0473066</v>
+        <v>0.0470519</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H71" s="14" t="inlineStr">
         <is>
@@ -3015,16 +3015,16 @@
         <v>31</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>0.0465474</v>
+        <v>0.046297</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>0.0464603</v>
+        <v>0.0462108</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0.047412</v>
+        <v>0.0471607</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
@@ -3051,16 +3051,16 @@
         <v>30</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>0.0466111</v>
+        <v>0.0463641</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>0.0465269</v>
+        <v>0.0462807</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0.0475009</v>
+        <v>0.047253</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
@@ -3087,16 +3087,16 @@
         <v>31</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>0.0466912</v>
+        <v>0.0464456</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>0.0466032</v>
+        <v>0.0463585</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0.0476104</v>
+        <v>0.0473639</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>9.19</v>
+        <v>9.18</v>
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
@@ -3123,16 +3123,16 @@
         <v>31</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>0.04676179999999999</v>
+        <v>0.0465156</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>0.0466741</v>
+        <v>0.0464288</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0.0477078</v>
+        <v>0.04746069999999999</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
@@ -3159,16 +3159,16 @@
         <v>29</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>0.046831</v>
+        <v>0.046584</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>0.04674909999999999</v>
+        <v>0.0465029</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>0.0478046</v>
+        <v>0.0475567</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
@@ -3195,16 +3195,16 @@
         <v>31</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>0.0469146</v>
+        <v>0.0466671</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>0.0468261</v>
+        <v>0.0465795</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0.0479175</v>
+        <v>0.0476691</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
       <c r="H77" s="14" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
         <v>30</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>0.0469803</v>
+        <v>0.046733</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>0.04689409999999999</v>
+        <v>0.0466477</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0.0480116</v>
+        <v>0.0477634</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>10.31</v>
+        <v>10.3</v>
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
@@ -3267,13 +3267,13 @@
         <v>31</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>0.047037</v>
+        <v>0.0467899</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0.0469482</v>
+        <v>0.046702</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0.0480955</v>
+        <v>0.04784740000000001</v>
       </c>
       <c r="G79" s="13" t="n">
         <v>10.58</v>
@@ -3303,13 +3303,13 @@
         <v>30</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>0.04708859999999999</v>
+        <v>0.0468416</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>0.0470026</v>
+        <v>0.0467565</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0.04817809999999999</v>
+        <v>0.04793020000000001</v>
       </c>
       <c r="G80" s="13" t="n">
         <v>10.89</v>
@@ -3339,16 +3339,16 @@
         <v>31</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>0.0471444</v>
+        <v>0.0468974</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>0.0470552</v>
+        <v>0.0468091</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0.0482637</v>
+        <v>0.0480157</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>11.19</v>
+        <v>11.18</v>
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
@@ -3375,16 +3375,16 @@
         <v>31</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>0.0472059</v>
+        <v>0.0469589</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>0.0471157</v>
+        <v>0.0468696</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0.0483541</v>
+        <v>0.0481061</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>11.48</v>
+        <v>11.47</v>
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
@@ -3411,16 +3411,16 @@
         <v>30</v>
       </c>
       <c r="D83" s="12" t="n">
-        <v>0.0472755</v>
+        <v>0.0470285</v>
       </c>
       <c r="E83" s="12" t="n">
-        <v>0.0471888</v>
+        <v>0.0469427</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0.0484547</v>
+        <v>0.0482067</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>11.79</v>
+        <v>11.78</v>
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
@@ -3447,16 +3447,16 @@
         <v>31</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>0.047348</v>
+        <v>0.047101</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>0.0472585</v>
+        <v>0.0470124</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0.0485579</v>
+        <v>0.0483099</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>12.1</v>
+        <v>12.09</v>
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
@@ -3483,16 +3483,16 @@
         <v>30</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>0.0474052</v>
+        <v>0.0471582</v>
       </c>
       <c r="E85" s="12" t="n">
-        <v>0.04731779999999999</v>
+        <v>0.04707169999999999</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>0.048646</v>
+        <v>0.0483981</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>12.41</v>
+        <v>12.4</v>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         <v>31</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>0.04745829999999999</v>
+        <v>0.0472113</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>0.0473677</v>
+        <v>0.0471216</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>0.0487308</v>
+        <v>0.0484829</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>12.73</v>
+        <v>12.72</v>
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
@@ -3555,16 +3555,16 @@
         <v>31</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>0.04750600000000001</v>
+        <v>0.047259</v>
       </c>
       <c r="E87" s="12" t="n">
-        <v>0.0474155</v>
+        <v>0.0471694</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0.0488083</v>
+        <v>0.04856029999999999</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>13.02</v>
+        <v>13.01</v>
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
@@ -3591,16 +3591,16 @@
         <v>28</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>0.0475608</v>
+        <v>0.0473139</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>0.0474796</v>
+        <v>0.0472335</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0.0488964</v>
+        <v>0.0486485</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>13.36</v>
+        <v>13.35</v>
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>31</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>0.04764090000000001</v>
+        <v>0.0473939</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>0.047549</v>
+        <v>0.047303</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>0.0490087</v>
+        <v>0.0487607</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>13.68</v>
+        <v>13.67</v>
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
@@ -3663,16 +3663,16 @@
         <v>30</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>0.0477046</v>
+        <v>0.0474576</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>0.04761650000000001</v>
+        <v>0.0473705</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0.0491039</v>
+        <v>0.04885589999999999</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>13.99</v>
+        <v>13.98</v>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
@@ -3699,16 +3699,16 @@
         <v>31</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>0.0477611</v>
+        <v>0.04751420000000001</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>0.0476694</v>
+        <v>0.0474234</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>0.0491915</v>
+        <v>0.0489436</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>14.3</v>
+        <v>14.29</v>
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
@@ -3735,16 +3735,16 @@
         <v>30</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>0.0478</v>
+        <v>0.0475532</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>0.04771130000000001</v>
+        <v>0.0474655</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>0.0492634</v>
+        <v>0.0490156</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>14.63</v>
+        <v>14.62</v>
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
@@ -3771,16 +3771,16 @@
         <v>31</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>0.0478358</v>
+        <v>0.0475891</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>0.0477444</v>
+        <v>0.0474986</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>0.04933220000000001</v>
+        <v>0.0490845</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>14.96</v>
+        <v>14.95</v>
       </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
@@ -3807,16 +3807,16 @@
         <v>31</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>0.047873</v>
+        <v>0.0476263</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>0.04778019999999999</v>
+        <v>0.0475345</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>0.0494032</v>
+        <v>0.0491555</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>15.3</v>
+        <v>15.29</v>
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
@@ -3843,16 +3843,16 @@
         <v>30</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>0.0479153</v>
+        <v>0.04766860000000001</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>0.0478262</v>
+        <v>0.0475804</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>0.04947969999999999</v>
+        <v>0.049232</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>15.64</v>
+        <v>15.63</v>
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
@@ -3879,16 +3879,16 @@
         <v>31</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>0.0479751</v>
+        <v>0.0477283</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>0.0478828</v>
+        <v>0.0476369</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>0.0495728</v>
+        <v>0.049325</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>15.98</v>
+        <v>15.97</v>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
@@ -3915,16 +3915,16 @@
         <v>30</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>0.0480494</v>
+        <v>0.0478025</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>0.04796</v>
+        <v>0.047714</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>0.0496849</v>
+        <v>0.04943699999999999</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>16.36</v>
+        <v>16.34</v>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
@@ -3951,16 +3951,16 @@
         <v>31</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>0.04812719999999999</v>
+        <v>0.0478801</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>0.0480342</v>
+        <v>0.0477881</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>0.0497989</v>
+        <v>0.0495507</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>16.72</v>
+        <v>16.71</v>
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
@@ -3987,16 +3987,16 @@
         <v>31</v>
       </c>
       <c r="D99" s="12" t="n">
-        <v>0.04817630000000001</v>
+        <v>0.0479292</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>0.0480832</v>
+        <v>0.047837</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>0.049881</v>
+        <v>0.0496328</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>17.05</v>
+        <v>17.04</v>
       </c>
       <c r="H99" s="14" t="inlineStr">
         <is>
@@ -4023,16 +4023,16 @@
         <v>28</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>0.0481833</v>
+        <v>0.0479363</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>0.0480999</v>
+        <v>0.0478538</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>0.0499238</v>
+        <v>0.0496758</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>17.41</v>
+        <v>17.39</v>
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
@@ -4059,16 +4059,16 @@
         <v>31</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>0.0481795</v>
+        <v>0.04793269999999999</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>0.0480856</v>
+        <v>0.0478397</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>0.0499545</v>
+        <v>0.0497066</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>17.75</v>
+        <v>17.74</v>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         <v>30</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>0.0481726</v>
+        <v>0.04792589999999999</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>0.0480828</v>
+        <v>0.0478371</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>0.0499789</v>
+        <v>0.0497312</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>18.06</v>
+        <v>18.05</v>
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
         <v>31</v>
       </c>
       <c r="D103" s="12" t="n">
-        <v>0.0482144</v>
+        <v>0.0479678</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>0.0481209</v>
+        <v>0.0478753</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>0.0500586</v>
+        <v>0.0498109</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>18.44</v>
+        <v>18.43</v>
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
@@ -4167,16 +4167,16 @@
         <v>30</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>0.0482878</v>
+        <v>0.0480412</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>0.0481973</v>
+        <v>0.0479517</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>0.0501686</v>
+        <v>0.0499209</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>18.81</v>
+        <v>18.8</v>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
@@ -4203,16 +4203,16 @@
         <v>31</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>0.0483611</v>
+        <v>0.0481144</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>0.0482669</v>
+        <v>0.0480211</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>0.0502776</v>
+        <v>0.0500297</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>19.16</v>
+        <v>19.15</v>
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
@@ -4239,16 +4239,16 @@
         <v>31</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>0.04839400000000001</v>
+        <v>0.0481472</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>0.04829920000000001</v>
+        <v>0.0480534</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>0.0503506</v>
+        <v>0.0501027</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>19.57</v>
+        <v>19.55</v>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         <v>30</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>0.0483719</v>
+        <v>0.0481251</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>0.0482813</v>
+        <v>0.0480355</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>0.0503655</v>
+        <v>0.0501175</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>19.94</v>
+        <v>19.92</v>
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
@@ -4311,16 +4311,16 @@
         <v>31</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>0.0483633</v>
+        <v>0.0481165</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>0.04826920000000001</v>
+        <v>0.0480234</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>0.0503932</v>
+        <v>0.0501452</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>20.3</v>
+        <v>20.29</v>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
@@ -4347,16 +4347,16 @@
         <v>30</v>
       </c>
       <c r="D109" s="12" t="n">
-        <v>0.04841160000000001</v>
+        <v>0.0481649</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>0.0483203</v>
+        <v>0.0480745</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>0.0504799</v>
+        <v>0.050232</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>20.68</v>
+        <v>20.67</v>
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
@@ -4383,16 +4383,16 @@
         <v>31</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>0.04853209999999999</v>
+        <v>0.0482853</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>0.048438</v>
+        <v>0.0481922</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>0.0506384</v>
+        <v>0.0503905</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>21.06</v>
+        <v>21.05</v>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
@@ -4419,16 +4419,16 @@
         <v>31</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0.048659</v>
+        <v>0.0484122</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>0.0485637</v>
+        <v>0.048318</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>0.0508022</v>
+        <v>0.0505543</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>21.43</v>
+        <v>21.42</v>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
@@ -4455,16 +4455,16 @@
         <v>28</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0.04872849999999999</v>
+        <v>0.04848189999999999</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>0.0486432</v>
+        <v>0.0483974</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>0.05091</v>
+        <v>0.0506623</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>21.82</v>
+        <v>21.8</v>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
@@ -4491,16 +4491,16 @@
         <v>31</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.0487446</v>
+        <v>0.0484979</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>0.0486493</v>
+        <v>0.0484035</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>0.05096510000000001</v>
+        <v>0.0507172</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>22.2</v>
+        <v>22.19</v>
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>30</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0.0487142</v>
+        <v>0.0484675</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>0.0486215</v>
+        <v>0.0483758</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>0.0509715</v>
+        <v>0.0507236</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>22.57</v>
+        <v>22.56</v>
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
@@ -4563,16 +4563,16 @@
         <v>31</v>
       </c>
       <c r="D115" s="12" t="n">
-        <v>0.0487073</v>
+        <v>0.04846059999999999</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>0.0486119</v>
+        <v>0.0483661</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>0.0510052</v>
+        <v>0.0507573</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>22.98</v>
+        <v>22.97</v>
       </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
@@ -4599,16 +4599,16 @@
         <v>30</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>0.0487353</v>
+        <v>0.0484886</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>0.0486429</v>
+        <v>0.0483972</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>0.0510728</v>
+        <v>0.0508249</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>23.37</v>
+        <v>23.36</v>
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
@@ -4635,16 +4635,16 @@
         <v>31</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>0.0487903</v>
+        <v>0.0485436</v>
       </c>
       <c r="E117" s="12" t="n">
-        <v>0.0486942</v>
+        <v>0.0484485</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>0.0511671</v>
+        <v>0.0509192</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>23.77</v>
+        <v>23.76</v>
       </c>
       <c r="H117" s="14" t="inlineStr">
         <is>
@@ -4671,16 +4671,16 @@
         <v>31</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>0.048837</v>
+        <v>0.0485903</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>0.0487404</v>
+        <v>0.0484947</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>0.0512552</v>
+        <v>0.05100730000000001</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>24.18</v>
+        <v>24.17</v>
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
@@ -4707,16 +4707,16 @@
         <v>30</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>0.0488621</v>
+        <v>0.04861550000000001</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>0.0487695</v>
+        <v>0.0485238</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>0.05131579999999999</v>
+        <v>0.051068</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>24.54</v>
+        <v>24.53</v>
       </c>
       <c r="H119" s="14" t="inlineStr">
         <is>
@@ -4743,16 +4743,16 @@
         <v>31</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>0.0489151</v>
+        <v>0.0486684</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>0.04881890000000001</v>
+        <v>0.0485732</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>0.0514131</v>
+        <v>0.0511652</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>24.98</v>
+        <v>24.97</v>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
@@ -4779,16 +4779,16 @@
         <v>30</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>0.0489986</v>
+        <v>0.048752</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>0.0489057</v>
+        <v>0.04865999999999999</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>0.0515366</v>
+        <v>0.0512887</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>25.38</v>
+        <v>25.37</v>
       </c>
       <c r="H121" s="14" t="inlineStr">
         <is>
@@ -4815,16 +4815,16 @@
         <v>31</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.0491172</v>
+        <v>0.0488705</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>0.0490199</v>
+        <v>0.04877430000000001</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>0.0516939</v>
+        <v>0.051446</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>25.77</v>
+        <v>25.75</v>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
@@ -4851,16 +4851,16 @@
         <v>31</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>0.0492402</v>
+        <v>0.0489936</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>0.0491427</v>
+        <v>0.048897</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>0.05185940000000001</v>
+        <v>0.0516116</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>26.19</v>
+        <v>26.18</v>
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
@@ -4887,16 +4887,16 @@
         <v>29</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>0.0493103</v>
+        <v>0.0490638</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>0.0492195</v>
+        <v>0.04897389999999999</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>0.0519714</v>
+        <v>0.0517236</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>26.61</v>
+        <v>26.6</v>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
@@ -4923,16 +4923,16 @@
         <v>31</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>0.0493298</v>
+        <v>0.0490832</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>0.0492315</v>
+        <v>0.04898590000000001</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>0.0520301</v>
+        <v>0.0517823</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>27</v>
+        <v>26.99</v>
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>30</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>0.0492937</v>
+        <v>0.0490472</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>0.0491995</v>
+        <v>0.0489539</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>0.0520372</v>
+        <v>0.0517894</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>27.43</v>
+        <v>27.42</v>
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
@@ -4995,16 +4995,16 @@
         <v>31</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>0.0492433</v>
+        <v>0.0489967</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>0.049146</v>
+        <v>0.0489004</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>0.052028</v>
+        <v>0.0517801</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>27.85</v>
+        <v>27.83</v>
       </c>
       <c r="H127" s="14" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>30</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>0.0491836</v>
+        <v>0.0489371</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>0.0490893</v>
+        <v>0.0488437</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>0.0520074</v>
+        <v>0.0517596</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>28.24</v>
+        <v>28.23</v>
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
@@ -5067,16 +5067,16 @@
         <v>31</v>
       </c>
       <c r="D129" s="18" t="n">
-        <v>0.0491847</v>
+        <v>0.04893810000000001</v>
       </c>
       <c r="E129" s="18" t="n">
-        <v>0.0490874</v>
+        <v>0.0488418</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.0520102</v>
+        <v>0.0517623</v>
       </c>
       <c r="G129" s="19" t="n">
-        <v>28.26</v>
+        <v>28.24</v>
       </c>
       <c r="H129" s="20" t="inlineStr">
         <is>
@@ -5103,16 +5103,16 @@
         <v>31</v>
       </c>
       <c r="D130" s="18" t="n">
-        <v>0.0491847</v>
+        <v>0.04893810000000001</v>
       </c>
       <c r="E130" s="18" t="n">
-        <v>0.0490874</v>
+        <v>0.0488418</v>
       </c>
       <c r="F130" s="18" t="n">
-        <v>0.0520102</v>
+        <v>0.0517623</v>
       </c>
       <c r="G130" s="19" t="n">
-        <v>28.26</v>
+        <v>28.24</v>
       </c>
       <c r="H130" s="20" t="inlineStr">
         <is>
@@ -5139,16 +5139,16 @@
         <v>30</v>
       </c>
       <c r="D131" s="18" t="n">
-        <v>0.0491819</v>
+        <v>0.0489353</v>
       </c>
       <c r="E131" s="18" t="n">
-        <v>0.0490874</v>
+        <v>0.0488418</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.0520071</v>
+        <v>0.0517592</v>
       </c>
       <c r="G131" s="19" t="n">
-        <v>28.25</v>
+        <v>28.24</v>
       </c>
       <c r="H131" s="20" t="inlineStr">
         <is>
@@ -5175,16 +5175,16 @@
         <v>31</v>
       </c>
       <c r="D132" s="18" t="n">
-        <v>0.0491847</v>
+        <v>0.04893810000000001</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>0.0490874</v>
+        <v>0.0488418</v>
       </c>
       <c r="F132" s="18" t="n">
-        <v>0.0520102</v>
+        <v>0.0517623</v>
       </c>
       <c r="G132" s="19" t="n">
-        <v>28.26</v>
+        <v>28.24</v>
       </c>
       <c r="H132" s="20" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5500,7 +5500,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-19)</t>
+          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-20)</t>
         </is>
       </c>
     </row>
@@ -5554,17 +5554,17 @@
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUL 26</t>
+          <t>SR3 AUG 26</t>
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>46218</v>
+        <v>46253</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>46316</v>
+        <v>46344</v>
       </c>
       <c r="D4" s="23" t="n">
-        <v>96.26000000000001</v>
+        <v>96.16500000000001</v>
       </c>
       <c r="E4" s="15">
         <f>(100-D4)/100</f>
@@ -5574,29 +5574,29 @@
         <v>0</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.0373861</v>
+        <v>0.038354</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>-0.139</v>
+        <v>0.04</v>
       </c>
       <c r="I4" s="25" t="n">
-        <v>20741</v>
+        <v>7104</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>SR3 AUG 26</t>
+          <t>SR3 SEP 26</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>46253</v>
+        <v>46281</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>46344</v>
+        <v>46372</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>96.16500000000001</v>
+        <v>96.0575</v>
       </c>
       <c r="E5" s="15">
         <f>(100-D5)/100</f>
@@ -5606,29 +5606,29 @@
         <v>0</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.0383578</v>
+        <v>0.0394216</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>0.078</v>
+        <v>-0.034</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>6841</v>
+        <v>1295273</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 26</t>
+          <t>SR1 OCT 26</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>46281</v>
+        <v>46296</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>46372</v>
+        <v>46327</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>96.0575</v>
+        <v>96.11</v>
       </c>
       <c r="E6" s="15">
         <f>(100-D6)/100</f>
@@ -5638,29 +5638,29 @@
         <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.0394373</v>
+        <v>0.0388881</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>0.123</v>
+        <v>-0.119</v>
       </c>
       <c r="I6" s="25" t="n">
-        <v>1289722</v>
+        <v>344625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>SR1 OCT 26</t>
+          <t>SR3 OCT 26</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>46296</v>
+        <v>46316</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>46327</v>
+        <v>46407</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>96.11</v>
+        <v>95.94</v>
       </c>
       <c r="E7" s="15">
         <f>(100-D7)/100</f>
@@ -5670,29 +5670,29 @@
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.0388804</v>
+        <v>0.0405715</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>-0.196</v>
+        <v>-0.285</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>345018</v>
+        <v>6693</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>SR3 OCT 26</t>
+          <t>SR1 NOV 26</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>46316</v>
+        <v>46327</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>46407</v>
+        <v>46357</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>95.9375</v>
+        <v>96.065</v>
       </c>
       <c r="E8" s="15">
         <f>(100-D8)/100</f>
@@ -5702,61 +5702,61 @@
         <v>0</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.0406079</v>
+        <v>0.0393794</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>-0.171</v>
+        <v>0.294</v>
       </c>
       <c r="I8" s="25" t="n">
-        <v>6393</v>
+        <v>290247</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>SR1 NOV 26</t>
+          <t>SR3 NOV 26</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>46327</v>
+        <v>46344</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>46357</v>
+        <v>46435</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>96.06</v>
+        <v>95.845</v>
       </c>
       <c r="E9" s="15">
         <f>(100-D9)/100</f>
         <v/>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.0394133</v>
+        <v>0.0415526</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>0.133</v>
+        <v>0.026</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>288008</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>SR3 NOV 26</t>
+          <t>SR1 DEC 26</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>46344</v>
+        <v>46357</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>46435</v>
+        <v>46388</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>95.8425</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E10" s="15">
         <f>(100-D10)/100</f>
@@ -5766,762 +5766,762 @@
         <v>0.01</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.0415914</v>
+        <v>0.0409997</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0.164</v>
+        <v>-0.003</v>
       </c>
       <c r="I10" s="25" t="n">
-        <v>2587</v>
+        <v>229671</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>SR1 DEC 26</t>
+          <t>SR3 DEC 26</t>
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>46357</v>
+        <v>46372</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>46388</v>
+        <v>46463</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>95.895</v>
+        <v>95.755</v>
       </c>
       <c r="E11" s="15">
         <f>(100-D11)/100</f>
         <v/>
       </c>
       <c r="F11" s="24" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.04104910000000001</v>
+        <v>0.0424373</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.127</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>230370</v>
+        <v>1555304</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 26</t>
+          <t>SR1 JAN 27</t>
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>46372</v>
+        <v>46388</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>46463</v>
+        <v>46419</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>95.75</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="E12" s="15">
         <f>(100-D12)/100</f>
         <v/>
       </c>
       <c r="F12" s="24" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.0424644</v>
+        <v>0.0417988</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.356</v>
+        <v>-0.012</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>1527314</v>
+        <v>179788</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>SR1 JAN 27</t>
+          <t>SR3 JAN 27</t>
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>46388</v>
+        <v>46407</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>46419</v>
+        <v>46498</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>95.815</v>
+        <v>95.655</v>
       </c>
       <c r="E13" s="15">
         <f>(100-D13)/100</f>
         <v/>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.0418475</v>
+        <v>0.0434964</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>-0.025</v>
+        <v>0.464</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>178423</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>SR3 JAN 27</t>
+          <t>SR1 FEB 27</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>46407</v>
+        <v>46419</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>46498</v>
+        <v>46447</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>95.655</v>
+        <v>95.73</v>
       </c>
       <c r="E14" s="15">
         <f>(100-D14)/100</f>
         <v/>
       </c>
       <c r="F14" s="24" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.04348</v>
+        <v>0.0427133</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.3</v>
+        <v>0.133</v>
       </c>
       <c r="I14" s="25" t="n">
-        <v>1187</v>
+        <v>105993</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>SR1 FEB 27</t>
+          <t>SR3 FEB 27</t>
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>46419</v>
+        <v>46435</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>46447</v>
+        <v>46526</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>95.73</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="E15" s="15">
         <f>(100-D15)/100</f>
         <v/>
       </c>
       <c r="F15" s="24" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.0427141</v>
+        <v>0.0443314</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>0.141</v>
+        <v>0.314</v>
       </c>
       <c r="I15" s="25" t="n">
-        <v>106075</v>
+        <v>543</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>SR3 FEB 27</t>
+          <t>SR1 MAR 27</t>
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>46435</v>
+        <v>46447</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>46526</v>
+        <v>46478</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>95.575</v>
+        <v>95.645</v>
       </c>
       <c r="E16" s="15">
         <f>(100-D16)/100</f>
         <v/>
       </c>
       <c r="F16" s="24" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.04429420000000001</v>
+        <v>0.0434918</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>0.442</v>
+        <v>-0.582</v>
       </c>
       <c r="I16" s="25" t="n">
-        <v>543</v>
+        <v>33926</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>SR1 MAR 27</t>
+          <t>SR3 MAR 27</t>
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>46447</v>
+        <v>46463</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>46478</v>
+        <v>46554</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>95.65000000000001</v>
+        <v>95.47499999999999</v>
       </c>
       <c r="E17" s="15">
         <f>(100-D17)/100</f>
         <v/>
       </c>
       <c r="F17" s="24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.0434662</v>
+        <v>0.0452248</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>-0.338</v>
+        <v>-0.252</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>33189</v>
+        <v>1327865</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 27</t>
+          <t>SR1 APR 27</t>
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>46463</v>
+        <v>46478</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>46554</v>
+        <v>46508</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>95.48</v>
+        <v>95.55</v>
       </c>
       <c r="E18" s="15">
         <f>(100-D18)/100</f>
         <v/>
       </c>
       <c r="F18" s="24" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.0451669</v>
+        <v>0.0444986</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>-0.331</v>
+        <v>-0.014</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>1324648</v>
+        <v>54661</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>SR1 APR 27</t>
+          <t>SR1 MAY 27</t>
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>46478</v>
+        <v>46508</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>46508</v>
+        <v>46539</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>95.55500000000001</v>
+        <v>95.465</v>
       </c>
       <c r="E19" s="15">
         <f>(100-D19)/100</f>
         <v/>
       </c>
       <c r="F19" s="24" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.0444417</v>
+        <v>0.045362</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>-0.083</v>
+        <v>0.12</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>55054</v>
+        <v>69238</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>SR1 MAY 27</t>
+          <t>SR1 JUN 27</t>
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>46508</v>
+        <v>46539</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>46539</v>
+        <v>46569</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>95.47</v>
+        <v>95.39</v>
       </c>
       <c r="E20" s="15">
         <f>(100-D20)/100</f>
         <v/>
       </c>
       <c r="F20" s="24" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.0453139</v>
+        <v>0.0460936</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>0.139</v>
+        <v>-0.064</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>69105</v>
+        <v>21519</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>SR1 JUN 27</t>
+          <t>SR3 JUN 27</t>
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>46539</v>
+        <v>46554</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>46569</v>
+        <v>46645</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>95.40000000000001</v>
+        <v>95.315</v>
       </c>
       <c r="E21" s="15">
         <f>(100-D21)/100</f>
         <v/>
       </c>
       <c r="F21" s="24" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.0459889</v>
+        <v>0.046865</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>-0.111</v>
+        <v>0.15</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>21236</v>
+        <v>1277006</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 27</t>
+          <t>SR1 JUL 27</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>46554</v>
+        <v>46569</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>46645</v>
+        <v>46600</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>95.33</v>
+        <v>95.355</v>
       </c>
       <c r="E22" s="15">
         <f>(100-D22)/100</f>
         <v/>
       </c>
       <c r="F22" s="24" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.0466969</v>
+        <v>0.0464438</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>-0.031</v>
+        <v>-0.062</v>
       </c>
       <c r="I22" s="25" t="n">
-        <v>1293215</v>
+        <v>38743</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>SR1 JUL 27</t>
+          <t>SR1 AUG 27</t>
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>46569</v>
+        <v>46600</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>46600</v>
+        <v>46631</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>95.37</v>
+        <v>95.325</v>
       </c>
       <c r="E23" s="15">
         <f>(100-D23)/100</f>
         <v/>
       </c>
       <c r="F23" s="24" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.04630799999999999</v>
+        <v>0.0467643</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>0.08</v>
+        <v>0.143</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>37096</v>
+        <v>18798</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>SR1 AUG 27</t>
+          <t>SR1 SEP 27</t>
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>46600</v>
+        <v>46631</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>46631</v>
+        <v>46661</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>95.345</v>
+        <v>95.3</v>
       </c>
       <c r="E24" s="15">
         <f>(100-D24)/100</f>
         <v/>
       </c>
       <c r="F24" s="24" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.0465649</v>
+        <v>0.0469633</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>0.149</v>
+        <v>-0.367</v>
       </c>
       <c r="I24" s="25" t="n">
-        <v>18254</v>
+        <v>4936</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>SR1 SEP 27</t>
+          <t>SR3 SEP 27</t>
         </is>
       </c>
       <c r="B25" s="10" t="n">
-        <v>46631</v>
+        <v>46645</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>46661</v>
+        <v>46736</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>95.325</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="E25" s="15">
         <f>(100-D25)/100</f>
         <v/>
       </c>
       <c r="F25" s="24" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.0467274</v>
+        <v>0.0474168</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>-0.226</v>
+        <v>0.168</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>4914</v>
+        <v>1052864</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 27</t>
+          <t>SR1 OCT 27</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>46645</v>
+        <v>46661</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>46736</v>
+        <v>46692</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>95.29000000000001</v>
+        <v>95.285</v>
       </c>
       <c r="E26" s="15">
         <f>(100-D26)/100</f>
         <v/>
       </c>
       <c r="F26" s="24" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.0471425</v>
+        <v>0.0471593</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>0.425</v>
+        <v>0.093</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>1045683</v>
+        <v>6994</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>SR1 OCT 27</t>
+          <t>SR1 NOV 27</t>
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>46661</v>
+        <v>46692</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>46692</v>
+        <v>46722</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>95.31</v>
+        <v>95.285</v>
       </c>
       <c r="E27" s="15">
         <f>(100-D27)/100</f>
         <v/>
       </c>
       <c r="F27" s="24" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.0468883</v>
+        <v>0.0471419</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>-0.117</v>
+        <v>-0.081</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>6970</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>SR1 NOV 27</t>
+          <t>SR3 DEC 27</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>46692</v>
+        <v>46736</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>46722</v>
+        <v>46827</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>95.31</v>
+        <v>95.27</v>
       </c>
       <c r="E28" s="15">
         <f>(100-D28)/100</f>
         <v/>
       </c>
       <c r="F28" s="24" t="n">
-        <v>0.45</v>
+        <v>0.63</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.0468815</v>
+        <v>0.0472984</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>-0.185</v>
+        <v>-0.016</v>
       </c>
       <c r="I28" s="25" t="n">
-        <v>1766</v>
+        <v>1662033</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 27</t>
+          <t>SR3 MAR 28</t>
         </is>
       </c>
       <c r="B29" s="10" t="n">
-        <v>46736</v>
+        <v>46827</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>46827</v>
+        <v>46925</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>95.30500000000001</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="E29" s="15">
         <f>(100-D29)/100</f>
         <v/>
       </c>
       <c r="F29" s="24" t="n">
-        <v>0.63</v>
+        <v>0.91</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.04694689999999999</v>
+        <v>0.0471003</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>-0.031</v>
+        <v>0.003</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>1670113</v>
+        <v>817756</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 28</t>
+          <t>SR3 JUN 28</t>
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>46827</v>
+        <v>46925</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>46925</v>
+        <v>47016</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>95.325</v>
+        <v>95.30500000000001</v>
       </c>
       <c r="E30" s="15">
         <f>(100-D30)/100</f>
         <v/>
       </c>
       <c r="F30" s="24" t="n">
-        <v>0.91</v>
+        <v>1.23</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.0467511</v>
+        <v>0.0469529</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>0.011</v>
+        <v>0.029</v>
       </c>
       <c r="I30" s="25" t="n">
-        <v>818076</v>
+        <v>647741</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 28</t>
+          <t>SR3 SEP 28</t>
         </is>
       </c>
       <c r="B31" s="10" t="n">
-        <v>46925</v>
+        <v>47016</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>47016</v>
+        <v>47107</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>95.33499999999999</v>
+        <v>95.315</v>
       </c>
       <c r="E31" s="15">
         <f>(100-D31)/100</f>
         <v/>
       </c>
       <c r="F31" s="24" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.0466524</v>
+        <v>0.04684389999999999</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>0.024</v>
+        <v>-0.061</v>
       </c>
       <c r="I31" s="25" t="n">
-        <v>639231</v>
+        <v>673706</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 28</t>
+          <t>SR3 DEC 28</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
-        <v>47016</v>
+        <v>47107</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>47107</v>
+        <v>47198</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>95.34</v>
+        <v>95.33499999999999</v>
       </c>
       <c r="E32" s="15">
         <f>(100-D32)/100</f>
         <v/>
       </c>
       <c r="F32" s="24" t="n">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.0465945</v>
+        <v>0.046656</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>-0.055</v>
+        <v>0.06</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>669558</v>
+        <v>550080</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 28</t>
+          <t>SR3 MAR 29</t>
         </is>
       </c>
       <c r="B33" s="10" t="n">
-        <v>47107</v>
+        <v>47198</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>47198</v>
+        <v>47289</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>95.355</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="E33" s="15">
         <f>(100-D33)/100</f>
         <v/>
       </c>
       <c r="F33" s="24" t="n">
-        <v>1.99</v>
+        <v>2.42</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.0464541</v>
+        <v>0.0464945</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>0.041</v>
+        <v>-0.055</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>539280</v>
+        <v>388777</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 29</t>
+          <t>SR3 JUN 29</t>
         </is>
       </c>
       <c r="B34" s="10" t="n">
-        <v>47198</v>
+        <v>47289</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>47289</v>
+        <v>47380</v>
       </c>
       <c r="D34" s="23" t="n">
         <v>95.36499999999999</v>
@@ -6531,29 +6531,29 @@
         <v/>
       </c>
       <c r="F34" s="24" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.04634820000000001</v>
+        <v>0.0463558</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>-0.018</v>
+        <v>0.058</v>
       </c>
       <c r="I34" s="25" t="n">
-        <v>382236</v>
+        <v>379993</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 29</t>
+          <t>SR3 SEP 29</t>
         </is>
       </c>
       <c r="B35" s="10" t="n">
-        <v>47289</v>
+        <v>47380</v>
       </c>
       <c r="C35" s="10" t="n">
-        <v>47380</v>
+        <v>47471</v>
       </c>
       <c r="D35" s="23" t="n">
         <v>95.37</v>
@@ -6563,61 +6563,61 @@
         <v/>
       </c>
       <c r="F35" s="24" t="n">
-        <v>2.91</v>
+        <v>3.42</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.0463018</v>
+        <v>0.0462943</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>0.018</v>
+        <v>-0.057</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>374138</v>
+        <v>302252</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 29</t>
+          <t>SR3 DEC 29</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>47380</v>
+        <v>47471</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>47471</v>
+        <v>47562</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>95.37</v>
+        <v>95.375</v>
       </c>
       <c r="E36" s="15">
         <f>(100-D36)/100</f>
         <v/>
       </c>
       <c r="F36" s="24" t="n">
-        <v>3.42</v>
+        <v>3.97</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.0462978</v>
+        <v>0.04625530000000001</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>-0.022</v>
+        <v>0.053</v>
       </c>
       <c r="I36" s="25" t="n">
-        <v>299423</v>
+        <v>245645</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 29</t>
+          <t>SR3 MAR 30</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>47471</v>
+        <v>47562</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>47562</v>
+        <v>47653</v>
       </c>
       <c r="D37" s="23" t="n">
         <v>95.37</v>
@@ -6627,29 +6627,29 @@
         <v/>
       </c>
       <c r="F37" s="24" t="n">
-        <v>3.98</v>
+        <v>4.56</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.0463014</v>
+        <v>0.046296</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>0.014</v>
+        <v>-0.04</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>245161</v>
+        <v>178997</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 30</t>
+          <t>SR3 JUN 30</t>
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>47562</v>
+        <v>47653</v>
       </c>
       <c r="C38" s="10" t="n">
-        <v>47653</v>
+        <v>47744</v>
       </c>
       <c r="D38" s="23" t="n">
         <v>95.36499999999999</v>
@@ -6659,29 +6659,29 @@
         <v/>
       </c>
       <c r="F38" s="24" t="n">
-        <v>4.57</v>
+        <v>5.19</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.0463496</v>
+        <v>0.0463523</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>-0.004</v>
+        <v>0.023</v>
       </c>
       <c r="I38" s="25" t="n">
-        <v>179640</v>
+        <v>158566</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 30</t>
+          <t>SR3 SEP 30</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
-        <v>47653</v>
+        <v>47744</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>47744</v>
+        <v>47835</v>
       </c>
       <c r="D39" s="23" t="n">
         <v>95.355</v>
@@ -6691,29 +6691,29 @@
         <v/>
       </c>
       <c r="F39" s="24" t="n">
-        <v>5.2</v>
+        <v>5.86</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.04645</v>
+        <v>0.04644790000000001</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>-0</v>
+        <v>-0.021</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>159669</v>
+        <v>138900</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 30</t>
+          <t>SR3 DEC 30</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>47744</v>
+        <v>47835</v>
       </c>
       <c r="C40" s="10" t="n">
-        <v>47835</v>
+        <v>47926</v>
       </c>
       <c r="D40" s="23" t="n">
         <v>95.34</v>
@@ -6723,189 +6723,189 @@
         <v/>
       </c>
       <c r="F40" s="24" t="n">
-        <v>5.86</v>
+        <v>6.55</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.04660040000000001</v>
+        <v>0.0466032</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>0.004</v>
+        <v>0.032</v>
       </c>
       <c r="I40" s="25" t="n">
-        <v>139046</v>
+        <v>113854</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 30</t>
+          <t>SR3 MAR 31</t>
         </is>
       </c>
       <c r="B41" s="10" t="n">
-        <v>47835</v>
+        <v>47926</v>
       </c>
       <c r="C41" s="10" t="n">
-        <v>47926</v>
+        <v>48017</v>
       </c>
       <c r="D41" s="23" t="n">
-        <v>95.31999999999999</v>
+        <v>95.315</v>
       </c>
       <c r="E41" s="15">
         <f>(100-D41)/100</f>
         <v/>
       </c>
       <c r="F41" s="24" t="n">
-        <v>6.56</v>
+        <v>7.28</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.0467992</v>
+        <v>0.0468466</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>-0.008</v>
+        <v>-0.034</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>114261</v>
+        <v>86572</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 31</t>
+          <t>SR3 JUN 31</t>
         </is>
       </c>
       <c r="B42" s="10" t="n">
-        <v>47926</v>
+        <v>48017</v>
       </c>
       <c r="C42" s="10" t="n">
-        <v>48017</v>
+        <v>48108</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>95.295</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="E42" s="15">
         <f>(100-D42)/100</f>
         <v/>
       </c>
       <c r="F42" s="24" t="n">
-        <v>7.29</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.0470514</v>
+        <v>0.0471028</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>0.014</v>
+        <v>0.028</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>85793</v>
+        <v>67769</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 31</t>
+          <t>SR3 SEP 31</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
-        <v>48017</v>
+        <v>48108</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>48108</v>
+        <v>48199</v>
       </c>
       <c r="D43" s="23" t="n">
-        <v>95.265</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="E43" s="15">
         <f>(100-D43)/100</f>
         <v/>
       </c>
       <c r="F43" s="24" t="n">
-        <v>8.06</v>
+        <v>8.84</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.0473489</v>
+        <v>0.047398</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>-0.011</v>
+        <v>-0.02</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>67086</v>
+        <v>34709</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 31</t>
+          <t>SR3 DEC 31</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
-        <v>48108</v>
+        <v>48199</v>
       </c>
       <c r="C44" s="10" t="n">
-        <v>48199</v>
+        <v>48290</v>
       </c>
       <c r="D44" s="23" t="n">
-        <v>95.235</v>
+        <v>95.23</v>
       </c>
       <c r="E44" s="15">
         <f>(100-D44)/100</f>
         <v/>
       </c>
       <c r="F44" s="24" t="n">
-        <v>8.85</v>
+        <v>9.67</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.04764980000000001</v>
+        <v>0.0477022</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>-0.002</v>
+        <v>0.022</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>35026</v>
+        <v>5757</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 31</t>
+          <t>SR3 MAR 32</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
-        <v>48199</v>
+        <v>48290</v>
       </c>
       <c r="C45" s="10" t="n">
-        <v>48290</v>
+        <v>48381</v>
       </c>
       <c r="D45" s="23" t="n">
-        <v>95.205</v>
+        <v>95.2</v>
       </c>
       <c r="E45" s="15">
         <f>(100-D45)/100</f>
         <v/>
       </c>
       <c r="F45" s="24" t="n">
-        <v>9.68</v>
+        <v>10.53</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.0479517</v>
+        <v>0.04799610000000001</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>0.017</v>
+        <v>-0.039</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>5803</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 32</t>
+          <t>SR3 JUN 32</t>
         </is>
       </c>
       <c r="B46" s="10" t="n">
-        <v>48290</v>
+        <v>48381</v>
       </c>
       <c r="C46" s="10" t="n">
-        <v>48381</v>
+        <v>48472</v>
       </c>
       <c r="D46" s="23" t="n">
         <v>95.175</v>
@@ -6915,61 +6915,61 @@
         <v/>
       </c>
       <c r="F46" s="24" t="n">
-        <v>10.54</v>
+        <v>11.42</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.0482462</v>
+        <v>0.0482552</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>-0.038</v>
+        <v>0.052</v>
       </c>
       <c r="I46" s="25" t="n">
-        <v>1755</v>
+        <v>821</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 32</t>
+          <t>SR3 SEP 32</t>
         </is>
       </c>
       <c r="B47" s="10" t="n">
-        <v>48381</v>
+        <v>48472</v>
       </c>
       <c r="C47" s="10" t="n">
-        <v>48472</v>
+        <v>48563</v>
       </c>
       <c r="D47" s="23" t="n">
-        <v>95.15000000000001</v>
+        <v>95.145</v>
       </c>
       <c r="E47" s="15">
         <f>(100-D47)/100</f>
         <v/>
       </c>
       <c r="F47" s="24" t="n">
-        <v>11.43</v>
+        <v>12.33</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.04850520000000001</v>
+        <v>0.0485442</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>0.052</v>
+        <v>-0.058</v>
       </c>
       <c r="I47" s="25" t="n">
-        <v>813</v>
+        <v>576</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 32</t>
+          <t>SR3 DEC 32</t>
         </is>
       </c>
       <c r="B48" s="10" t="n">
-        <v>48472</v>
+        <v>48563</v>
       </c>
       <c r="C48" s="10" t="n">
-        <v>48563</v>
+        <v>48654</v>
       </c>
       <c r="D48" s="23" t="n">
         <v>95.12</v>
@@ -6979,61 +6979,61 @@
         <v/>
       </c>
       <c r="F48" s="24" t="n">
-        <v>12.34</v>
+        <v>13.28</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.0487943</v>
+        <v>0.0488061</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>-0.057</v>
+        <v>0.061</v>
       </c>
       <c r="I48" s="25" t="n">
-        <v>576</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 32</t>
+          <t>SR3 MAR 33</t>
         </is>
       </c>
       <c r="B49" s="10" t="n">
-        <v>48563</v>
+        <v>48654</v>
       </c>
       <c r="C49" s="10" t="n">
-        <v>48654</v>
+        <v>48745</v>
       </c>
       <c r="D49" s="23" t="n">
-        <v>95.095</v>
+        <v>95.09</v>
       </c>
       <c r="E49" s="15">
         <f>(100-D49)/100</f>
         <v/>
       </c>
       <c r="F49" s="24" t="n">
-        <v>13.29</v>
+        <v>14.25</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.04905610000000001</v>
+        <v>0.0490947</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>0.061</v>
+        <v>-0.053</v>
       </c>
       <c r="I49" s="25" t="n">
-        <v>164</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 33</t>
+          <t>SR3 JUN 33</t>
         </is>
       </c>
       <c r="B50" s="10" t="n">
-        <v>48654</v>
+        <v>48745</v>
       </c>
       <c r="C50" s="10" t="n">
-        <v>48745</v>
+        <v>48843</v>
       </c>
       <c r="D50" s="23" t="n">
         <v>95.065</v>
@@ -7043,29 +7043,29 @@
         <v/>
       </c>
       <c r="F50" s="24" t="n">
-        <v>14.26</v>
+        <v>15.28</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.0493446</v>
+        <v>0.04935170000000001</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>-0.054</v>
+        <v>0.017</v>
       </c>
       <c r="I50" s="25" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 33</t>
+          <t>SR3 SEP 33</t>
         </is>
       </c>
       <c r="B51" s="10" t="n">
-        <v>48745</v>
+        <v>48843</v>
       </c>
       <c r="C51" s="10" t="n">
-        <v>48843</v>
+        <v>48934</v>
       </c>
       <c r="D51" s="23" t="n">
         <v>95.04000000000001</v>
@@ -7075,29 +7075,29 @@
         <v/>
       </c>
       <c r="F51" s="24" t="n">
-        <v>15.29</v>
+        <v>16.35</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.0496017</v>
+        <v>0.04960639999999999</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>0.017</v>
+        <v>0.064</v>
       </c>
       <c r="I51" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 33</t>
+          <t>SR3 DEC 33</t>
         </is>
       </c>
       <c r="B52" s="10" t="n">
-        <v>48843</v>
+        <v>48934</v>
       </c>
       <c r="C52" s="10" t="n">
-        <v>48934</v>
+        <v>49018</v>
       </c>
       <c r="D52" s="23" t="n">
         <v>95.015</v>
@@ -7107,77 +7107,77 @@
         <v/>
       </c>
       <c r="F52" s="24" t="n">
-        <v>16.36</v>
+        <v>17.36</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.0498564</v>
+        <v>0.0498337</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>0.064</v>
+        <v>-0.163</v>
       </c>
       <c r="I52" s="25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 33</t>
+          <t>SR3 MAR 34</t>
         </is>
       </c>
       <c r="B53" s="10" t="n">
-        <v>48934</v>
+        <v>49018</v>
       </c>
       <c r="C53" s="10" t="n">
-        <v>49018</v>
+        <v>49116</v>
       </c>
       <c r="D53" s="23" t="n">
-        <v>94.98999999999999</v>
+        <v>95</v>
       </c>
       <c r="E53" s="15">
         <f>(100-D53)/100</f>
         <v/>
       </c>
       <c r="F53" s="24" t="n">
-        <v>17.37</v>
+        <v>18.43</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.0500837</v>
+        <v>0.050023</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>-0.163</v>
+        <v>0.23</v>
       </c>
       <c r="I53" s="25" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 34</t>
+          <t>SR3 JUN 34</t>
         </is>
       </c>
       <c r="B54" s="10" t="n">
-        <v>49018</v>
+        <v>49116</v>
       </c>
       <c r="C54" s="10" t="n">
-        <v>49116</v>
+        <v>49207</v>
       </c>
       <c r="D54" s="23" t="n">
-        <v>94.97499999999999</v>
+        <v>94.97</v>
       </c>
       <c r="E54" s="15">
         <f>(100-D54)/100</f>
         <v/>
       </c>
       <c r="F54" s="24" t="n">
-        <v>18.44</v>
+        <v>19.57</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.05027300000000001</v>
+        <v>0.0502714</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>0.23</v>
+        <v>-0.286</v>
       </c>
       <c r="I54" s="25" t="n">
         <v>0</v>
@@ -7186,30 +7186,30 @@
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 34</t>
+          <t>SR3 SEP 34</t>
         </is>
       </c>
       <c r="B55" s="10" t="n">
-        <v>49116</v>
+        <v>49207</v>
       </c>
       <c r="C55" s="10" t="n">
-        <v>49207</v>
+        <v>49298</v>
       </c>
       <c r="D55" s="23" t="n">
-        <v>94.94499999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="E55" s="15">
         <f>(100-D55)/100</f>
         <v/>
       </c>
       <c r="F55" s="24" t="n">
-        <v>19.59</v>
+        <v>20.7</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.0505213</v>
+        <v>0.0504337</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>-0.287</v>
+        <v>0.337</v>
       </c>
       <c r="I55" s="25" t="n">
         <v>0</v>
@@ -7218,30 +7218,30 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 34</t>
+          <t>SR3 DEC 34</t>
         </is>
       </c>
       <c r="B56" s="10" t="n">
-        <v>49207</v>
+        <v>49298</v>
       </c>
       <c r="C56" s="10" t="n">
-        <v>49298</v>
+        <v>49389</v>
       </c>
       <c r="D56" s="23" t="n">
-        <v>94.935</v>
+        <v>94.91500000000001</v>
       </c>
       <c r="E56" s="15">
         <f>(100-D56)/100</f>
         <v/>
       </c>
       <c r="F56" s="24" t="n">
-        <v>20.71</v>
+        <v>21.84</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.0506837</v>
+        <v>0.0508186</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>0.337</v>
+        <v>-0.314</v>
       </c>
       <c r="I56" s="25" t="n">
         <v>0</v>
@@ -7250,30 +7250,30 @@
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 34</t>
+          <t>SR3 MAR 35</t>
         </is>
       </c>
       <c r="B57" s="10" t="n">
-        <v>49298</v>
+        <v>49389</v>
       </c>
       <c r="C57" s="10" t="n">
-        <v>49389</v>
+        <v>49480</v>
       </c>
       <c r="D57" s="23" t="n">
-        <v>94.89</v>
+        <v>94.905</v>
       </c>
       <c r="E57" s="15">
         <f>(100-D57)/100</f>
         <v/>
       </c>
       <c r="F57" s="24" t="n">
-        <v>21.86</v>
+        <v>23.01</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.0510686</v>
+        <v>0.0509718</v>
       </c>
       <c r="H57" s="24" t="n">
-        <v>-0.314</v>
+        <v>0.218</v>
       </c>
       <c r="I57" s="25" t="n">
         <v>0</v>
@@ -7282,14 +7282,14 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 35</t>
+          <t>SR3 JUN 35</t>
         </is>
       </c>
       <c r="B58" s="10" t="n">
-        <v>49389</v>
+        <v>49480</v>
       </c>
       <c r="C58" s="10" t="n">
-        <v>49480</v>
+        <v>49571</v>
       </c>
       <c r="D58" s="23" t="n">
         <v>94.88</v>
@@ -7299,13 +7299,13 @@
         <v/>
       </c>
       <c r="F58" s="24" t="n">
-        <v>23.02</v>
+        <v>24.2</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.0512218</v>
+        <v>0.05118420000000001</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>0.218</v>
+        <v>-0.158</v>
       </c>
       <c r="I58" s="25" t="n">
         <v>0</v>
@@ -7314,14 +7314,14 @@
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 35</t>
+          <t>SR3 SEP 35</t>
         </is>
       </c>
       <c r="B59" s="10" t="n">
-        <v>49480</v>
+        <v>49571</v>
       </c>
       <c r="C59" s="10" t="n">
-        <v>49571</v>
+        <v>49662</v>
       </c>
       <c r="D59" s="23" t="n">
         <v>94.855</v>
@@ -7331,13 +7331,13 @@
         <v/>
       </c>
       <c r="F59" s="24" t="n">
-        <v>24.21</v>
+        <v>25.41</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.0514342</v>
+        <v>0.0514687</v>
       </c>
       <c r="H59" s="24" t="n">
-        <v>-0.158</v>
+        <v>0.187</v>
       </c>
       <c r="I59" s="25" t="n">
         <v>0</v>
@@ -7346,30 +7346,30 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 35</t>
+          <t>SR3 DEC 35</t>
         </is>
       </c>
       <c r="B60" s="10" t="n">
-        <v>49571</v>
+        <v>49662</v>
       </c>
       <c r="C60" s="10" t="n">
-        <v>49662</v>
+        <v>49753</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>94.83</v>
+        <v>94.81</v>
       </c>
       <c r="E60" s="15">
         <f>(100-D60)/100</f>
         <v/>
       </c>
       <c r="F60" s="24" t="n">
-        <v>25.42</v>
+        <v>26.64</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.0517187</v>
+        <v>0.05188329999999999</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>0.187</v>
+        <v>-0.167</v>
       </c>
       <c r="I60" s="25" t="n">
         <v>0</v>
@@ -7378,71 +7378,39 @@
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 35</t>
+          <t>SR3 MAR 36</t>
         </is>
       </c>
       <c r="B61" s="10" t="n">
-        <v>49662</v>
+        <v>49753</v>
       </c>
       <c r="C61" s="10" t="n">
-        <v>49753</v>
+        <v>49844</v>
       </c>
       <c r="D61" s="23" t="n">
-        <v>94.785</v>
+        <v>94.8</v>
       </c>
       <c r="E61" s="15">
         <f>(100-D61)/100</f>
         <v/>
       </c>
       <c r="F61" s="24" t="n">
-        <v>26.65</v>
+        <v>27.89</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.0521333</v>
+        <v>0.0520058</v>
       </c>
       <c r="H61" s="24" t="n">
-        <v>-0.167</v>
+        <v>0.058</v>
       </c>
       <c r="I61" s="25" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="14" t="inlineStr">
-        <is>
-          <t>SR3 MAR 36</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="n">
-        <v>49753</v>
-      </c>
-      <c r="C62" s="10" t="n">
-        <v>49844</v>
-      </c>
-      <c r="D62" s="23" t="n">
-        <v>94.77500000000001</v>
-      </c>
-      <c r="E62" s="15">
-        <f>(100-D62)/100</f>
-        <v/>
-      </c>
-      <c r="F62" s="24" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="G62" s="12" t="n">
-        <v>0.0522558</v>
-      </c>
-      <c r="H62" s="24" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="I62" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>Fit: 59 contracts, RMS residual 0.17 bp, max 0.442 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Fit: 58 contracts, RMS residual 0.173 bp, max 0.582 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
         </is>
       </c>
     </row>
@@ -7457,7 +7425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7485,55 +7453,55 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B4" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B8" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B9" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B10" s="26" t="n">
         <v>0.0387</v>
@@ -7541,71 +7509,71 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B11" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B12" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B13" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B14" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B15" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B16" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B17" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B18" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B19" s="26" t="n">
         <v>0.039</v>
@@ -7613,23 +7581,23 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B20" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B21" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B22" s="26" t="n">
         <v>0.0387</v>
@@ -7637,15 +7605,15 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B23" s="26" t="n">
-        <v>0.0385</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B24" s="26" t="n">
         <v>0.0385</v>
@@ -7653,7 +7621,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B25" s="26" t="n">
         <v>0.0385</v>
@@ -7661,31 +7629,31 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B26" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B27" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B28" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B29" s="26" t="n">
         <v>0.0362</v>
@@ -7693,7 +7661,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B30" s="26" t="n">
         <v>0.0362</v>
@@ -7701,15 +7669,15 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B31" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B32" s="26" t="n">
         <v>0.0364</v>
@@ -7717,63 +7685,63 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B33" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B34" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B35" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B36" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B37" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B38" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B39" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B40" s="26" t="n">
         <v>0.0364</v>
@@ -7781,23 +7749,23 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B41" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B42" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B43" s="26" t="n">
         <v>0.0365</v>
@@ -7805,47 +7773,47 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B44" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B45" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B48" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B49" s="26" t="n">
         <v>0.0362</v>
@@ -7853,7 +7821,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B50" s="26" t="n">
         <v>0.0362</v>
@@ -7861,79 +7829,79 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B51" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B52" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B53" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B54" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B55" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B56" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B57" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B58" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B59" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B60" s="26" t="n">
         <v>0.0365</v>
@@ -7941,7 +7909,7 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B61" s="26" t="n">
         <v>0.0365</v>
@@ -7949,15 +7917,15 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B62" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B63" s="26" t="n">
         <v>0.0364</v>
@@ -7965,7 +7933,7 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B64" s="26" t="n">
         <v>0.0364</v>
@@ -7973,143 +7941,143 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B65" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B66" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B67" s="26" t="n">
-        <v>0.0357</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B68" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.0357</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B69" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B70" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B71" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B72" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B73" s="26" t="n">
-        <v>0.0355</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B74" s="26" t="n">
-        <v>0.0353</v>
+        <v>0.0355</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B75" s="26" t="n">
-        <v>0.0358</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B76" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B77" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B78" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B79" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B80" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B81" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B82" s="26" t="n">
         <v>0.0362</v>
@@ -8117,23 +8085,23 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B83" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B84" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B85" s="26" t="n">
         <v>0.0362</v>
@@ -8141,31 +8109,31 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B86" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B87" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B88" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B89" s="26" t="n">
         <v>0.0363</v>
@@ -8173,55 +8141,55 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B90" s="26" t="n">
-        <v>0.0369</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B91" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B92" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B93" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B94" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B95" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B96" s="26" t="n">
         <v>0.0363</v>
@@ -8229,65 +8197,73 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B97" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B98" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B99" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B100" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B101" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B102" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B103" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B104" s="26" t="n">
+        <v>0.0363</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="B104" s="26" t="n">
+      <c r="B105" s="26" t="n">
         <v>0.0363</v>
       </c>
     </row>

--- a/output/downloads/sofr-forward-curve.xlsx
+++ b/output/downloads/sofr-forward-curve.xlsx
@@ -236,7 +236,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SOFR forward curve, 2026-10-20</a:t>
+              <a:t>SOFR forward curve, 2026-10-21</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="3">
@@ -731,7 +731,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>on 2026-10-20 (NY Fed)</t>
+          <t>on 2026-10-21 (NY Fed)</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21 18:03 UTC</t>
+          <t>2026-10-22 17:59 UTC</t>
         </is>
       </c>
     </row>
@@ -855,13 +855,13 @@
         <v>31</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.038949</v>
+        <v>0.038938</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>0.0388881</v>
+        <v>0.0388771</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>0.0389488</v>
+        <v>0.0389378</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0</v>
@@ -891,13 +891,13 @@
         <v>30</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.0394398</v>
+        <v>0.0394274</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.0393793</v>
+        <v>0.0393669</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>0.0394396</v>
+        <v>0.0394272</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.04106659999999999</v>
+        <v>0.0410912</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>0.04099879999999999</v>
+        <v>0.04102330000000001</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0.0410675</v>
+        <v>0.041092</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>0.01</v>
@@ -963,13 +963,13 @@
         <v>31</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.0418666</v>
+        <v>0.0419135</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.04179649999999999</v>
+        <v>0.0418433</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>0.0418682</v>
+        <v>0.0419151</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>0.02</v>
@@ -999,13 +999,13 @@
         <v>28</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.0427749</v>
+        <v>0.042871</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.0427092</v>
+        <v>0.04280490000000001</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0.0427788</v>
+        <v>0.0428748</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>0.04</v>
@@ -1035,13 +1035,13 @@
         <v>31</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.0435616</v>
+        <v>0.04368</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.0434853</v>
+        <v>0.0436033</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0.0435677</v>
+        <v>0.043686</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>0.06</v>
@@ -1071,13 +1071,13 @@
         <v>30</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.0445668</v>
+        <v>0.04472019999999999</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>0.0444892</v>
+        <v>0.0446421</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>0.0445758</v>
+        <v>0.04472909999999999</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>0.09</v>
@@ -1107,13 +1107,13 @@
         <v>31</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.0454319</v>
+        <v>0.04569619999999999</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.045349</v>
+        <v>0.0456124</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.0454443</v>
+        <v>0.0457085</v>
       </c>
       <c r="G19" s="13" t="n">
         <v>0.12</v>
@@ -1143,13 +1143,13 @@
         <v>30</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.04615929999999999</v>
+        <v>0.0464663</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>0.0460766</v>
+        <v>0.0463826</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0.0461771</v>
+        <v>0.0464839</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>0.18</v>
@@ -1179,13 +1179,13 @@
         <v>31</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.0465091</v>
+        <v>0.04683760000000001</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.0464223</v>
+        <v>0.0467496</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.0465298</v>
+        <v>0.0468582</v>
       </c>
       <c r="G21" s="13" t="n">
         <v>0.21</v>
@@ -1215,13 +1215,13 @@
         <v>31</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.0468264</v>
+        <v>0.0471845</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.0467376</v>
+        <v>0.0470944</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0.04685330000000001</v>
+        <v>0.0472112</v>
       </c>
       <c r="G22" s="13" t="n">
         <v>0.27</v>
@@ -1251,13 +1251,13 @@
         <v>30</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.0470167</v>
+        <v>0.0474094</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.046931</v>
+        <v>0.0473222</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.0470488</v>
+        <v>0.0474413</v>
       </c>
       <c r="G23" s="13" t="n">
         <v>0.32</v>
@@ -1287,13 +1287,13 @@
         <v>31</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.0472098</v>
+        <v>0.047641</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>0.0471208</v>
+        <v>0.0475504</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0.047248</v>
+        <v>0.047679</v>
       </c>
       <c r="G24" s="13" t="n">
         <v>0.38</v>
@@ -1323,13 +1323,13 @@
         <v>30</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.0471833</v>
+        <v>0.0476404</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.0470967</v>
+        <v>0.0475521</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0.0472281</v>
+        <v>0.04768500000000001</v>
       </c>
       <c r="G25" s="13" t="n">
         <v>0.45</v>
@@ -1359,13 +1359,13 @@
         <v>31</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.0471295</v>
+        <v>0.04756879999999999</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.0470402</v>
+        <v>0.04747779999999999</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0.0471816</v>
+        <v>0.0476206</v>
       </c>
       <c r="G26" s="13" t="n">
         <v>0.52</v>
@@ -1395,16 +1395,16 @@
         <v>31</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.0470979</v>
+        <v>0.0475324</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>0.0470089</v>
+        <v>0.0474418</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0.0471546</v>
+        <v>0.04758880000000001</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
@@ -1431,13 +1431,13 @@
         <v>29</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.0470314</v>
+        <v>0.0474732</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>0.0469487</v>
+        <v>0.047389</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>0.0470985</v>
+        <v>0.0475401</v>
       </c>
       <c r="G28" s="13" t="n">
         <v>0.67</v>
@@ -1467,13 +1467,13 @@
         <v>31</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.046903</v>
+        <v>0.0474113</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>0.046814</v>
+        <v>0.0473203</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.0469779</v>
+        <v>0.0474859</v>
       </c>
       <c r="G29" s="13" t="n">
         <v>0.75</v>
@@ -1503,13 +1503,13 @@
         <v>30</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>0.04683760000000001</v>
+        <v>0.0473399</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>0.0467527</v>
+        <v>0.0472532</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0.0469215</v>
+        <v>0.0474235</v>
       </c>
       <c r="G30" s="13" t="n">
         <v>0.84</v>
@@ -1539,13 +1539,13 @@
         <v>31</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>0.0467746</v>
+        <v>0.04726689999999999</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0.0466867</v>
+        <v>0.0471771</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.04686899999999999</v>
+        <v>0.04736100000000001</v>
       </c>
       <c r="G31" s="13" t="n">
         <v>0.9399999999999999</v>
@@ -1575,16 +1575,16 @@
         <v>30</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.0467159</v>
+        <v>0.047194</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>0.0466313</v>
+        <v>0.0471076</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0.0468205</v>
+        <v>0.0472982</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
@@ -1611,13 +1611,13 @@
         <v>31</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.0466748</v>
+        <v>0.0471356</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>0.046587</v>
+        <v>0.047046</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0.04678930000000001</v>
+        <v>0.0472497</v>
       </c>
       <c r="G33" s="13" t="n">
         <v>1.14</v>
@@ -1647,13 +1647,13 @@
         <v>31</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.0466324</v>
+        <v>0.0470703</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>0.0465443</v>
+        <v>0.0469806</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0.04675849999999999</v>
+        <v>0.0471961</v>
       </c>
       <c r="G34" s="13" t="n">
         <v>1.26</v>
@@ -1683,16 +1683,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.0465911</v>
+        <v>0.04700770000000001</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>0.0465071</v>
+        <v>0.0469222</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0.0467287</v>
+        <v>0.047145</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
@@ -1719,13 +1719,13 @@
         <v>31</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>0.0465505</v>
+        <v>0.0469524</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>0.0464633</v>
+        <v>0.0468637</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0.0466997</v>
+        <v>0.0471012</v>
       </c>
       <c r="G36" s="13" t="n">
         <v>1.49</v>
@@ -1755,13 +1755,13 @@
         <v>30</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.0464836</v>
+        <v>0.0468796</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>0.0463993</v>
+        <v>0.046794</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0.04664570000000001</v>
+        <v>0.0470413</v>
       </c>
       <c r="G37" s="13" t="n">
         <v>1.62</v>
@@ -1791,13 +1791,13 @@
         <v>31</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>0.0464064</v>
+        <v>0.0468051</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>0.0463204</v>
+        <v>0.0467175</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0.0465815</v>
+        <v>0.0469797</v>
       </c>
       <c r="G38" s="13" t="n">
         <v>1.75</v>
@@ -1827,13 +1827,13 @@
         <v>31</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0.04632500000000001</v>
+        <v>0.0467254</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0.0462387</v>
+        <v>0.04663750000000001</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0.04651309999999999</v>
+        <v>0.04691290000000001</v>
       </c>
       <c r="G39" s="13" t="n">
         <v>1.88</v>
@@ -1863,13 +1863,13 @@
         <v>28</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>0.0462362</v>
+        <v>0.0466285</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>0.04615929999999999</v>
+        <v>0.0465504</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0.0464382</v>
+        <v>0.04683010000000001</v>
       </c>
       <c r="G40" s="13" t="n">
         <v>2.02</v>
@@ -1899,13 +1899,13 @@
         <v>31</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.0461794</v>
+        <v>0.0465544</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.0460936</v>
+        <v>0.0464672</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0.0463956</v>
+        <v>0.0467701</v>
       </c>
       <c r="G41" s="13" t="n">
         <v>2.16</v>
@@ -1935,13 +1935,13 @@
         <v>30</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>0.0461177</v>
+        <v>0.0464745</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>0.0460346</v>
+        <v>0.0463901</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0.046348</v>
+        <v>0.0467042</v>
       </c>
       <c r="G42" s="13" t="n">
         <v>2.3</v>
@@ -1971,16 +1971,16 @@
         <v>31</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.0460523</v>
+        <v>0.0463988</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.045967</v>
+        <v>0.0463122</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.0462983</v>
+        <v>0.0466442</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
@@ -2007,16 +2007,16 @@
         <v>30</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.0459787</v>
+        <v>0.0463257</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>0.0458965</v>
+        <v>0.0462422</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0.0462405</v>
+        <v>0.046587</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
@@ -2043,16 +2043,16 @@
         <v>31</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.0459174</v>
+        <v>0.0462665</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.0458322</v>
+        <v>0.04618000000000001</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0.04619500000000001</v>
+        <v>0.0465436</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
@@ -2079,16 +2079,16 @@
         <v>31</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.04586369999999999</v>
+        <v>0.0462059</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>0.0457786</v>
+        <v>0.0461195</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0.04615859999999999</v>
+        <v>0.0465002</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
@@ -2115,16 +2115,16 @@
         <v>30</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.0458282</v>
+        <v>0.0461545</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.0457467</v>
+        <v>0.0460719</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.0461382</v>
+        <v>0.046464</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
@@ -2151,16 +2151,16 @@
         <v>31</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.04579850000000001</v>
+        <v>0.0461045</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>0.0457142</v>
+        <v>0.0460191</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0.0461275</v>
+        <v>0.04643290000000001</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
@@ -2187,16 +2187,16 @@
         <v>30</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.0457618</v>
+        <v>0.0460586</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>0.0456807</v>
+        <v>0.0459765</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0.0461083</v>
+        <v>0.0464046</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
@@ -2223,16 +2223,16 @@
         <v>31</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.0457287</v>
+        <v>0.0460266</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>0.0456444</v>
+        <v>0.0459412</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0.0460923</v>
+        <v>0.0463896</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
@@ -2259,16 +2259,16 @@
         <v>31</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.045692</v>
+        <v>0.04599230000000001</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>0.045608</v>
+        <v>0.0459072</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>0.0460747</v>
+        <v>0.0463743</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
@@ -2295,16 +2295,16 @@
         <v>28</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.0456608</v>
+        <v>0.0459545</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>0.0455859</v>
+        <v>0.0458786</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0.0460628</v>
+        <v>0.0463558</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
@@ -2331,13 +2331,13 @@
         <v>31</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.045664</v>
+        <v>0.0459412</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.04558010000000001</v>
+        <v>0.0458563</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.0460854</v>
+        <v>0.0463619</v>
       </c>
       <c r="G53" s="13" t="n">
         <v>4.21</v>
@@ -2367,16 +2367,16 @@
         <v>30</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>0.0456634</v>
+        <v>0.0459209</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>0.0455825</v>
+        <v>0.0458391</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>0.0461044</v>
+        <v>0.0463612</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
@@ -2403,13 +2403,13 @@
         <v>31</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>0.045667</v>
+        <v>0.0459116</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.04558309999999999</v>
+        <v>0.0458268</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.0461283</v>
+        <v>0.0463721</v>
       </c>
       <c r="G55" s="13" t="n">
         <v>4.61</v>
@@ -2439,16 +2439,16 @@
         <v>30</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>0.0456601</v>
+        <v>0.0459019</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>0.045579</v>
+        <v>0.04582</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>0.0461406</v>
+        <v>0.0463818</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>4.81</v>
+        <v>4.8</v>
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
@@ -2475,16 +2475,16 @@
         <v>31</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>0.0456575</v>
+        <v>0.0459027</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.0455733</v>
+        <v>0.0458176</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.0461606</v>
+        <v>0.0464051</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>5.03</v>
+        <v>5.02</v>
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
@@ -2511,13 +2511,13 @@
         <v>31</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>0.0456575</v>
+        <v>0.0459065</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>0.0455732</v>
+        <v>0.0458213</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0.0461819</v>
+        <v>0.0464302</v>
       </c>
       <c r="G58" s="13" t="n">
         <v>5.24</v>
@@ -2547,16 +2547,16 @@
         <v>30</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>0.0456615</v>
+        <v>0.0459117</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.0455802</v>
+        <v>0.0458296</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.0462062</v>
+        <v>0.0464557</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>5.45</v>
+        <v>5.44</v>
       </c>
       <c r="H59" s="14" t="inlineStr">
         <is>
@@ -2583,13 +2583,13 @@
         <v>31</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.04567789999999999</v>
+        <v>0.04592769999999999</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>0.045594</v>
+        <v>0.0458428</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0.0462463</v>
+        <v>0.0464953</v>
       </c>
       <c r="G60" s="13" t="n">
         <v>5.68</v>
@@ -2619,16 +2619,16 @@
         <v>30</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>0.0456912</v>
+        <v>0.0459403</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>0.0456106</v>
+        <v>0.04585880000000001</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0.0462825</v>
+        <v>0.04653069999999999</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>5.91</v>
+        <v>5.9</v>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
@@ -2655,16 +2655,16 @@
         <v>31</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>0.0457157</v>
+        <v>0.0459646</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>0.0456312</v>
+        <v>0.0458792</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0.0463297</v>
+        <v>0.0465778</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
@@ -2691,16 +2691,16 @@
         <v>31</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>0.0457459</v>
+        <v>0.0459946</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>0.0456618</v>
+        <v>0.04590950000000001</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0.0463837</v>
+        <v>0.0466316</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>6.38</v>
+        <v>6.37</v>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
@@ -2727,16 +2727,16 @@
         <v>28</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>0.0457797</v>
+        <v>0.0460276</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>0.045704</v>
+        <v>0.0459511</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>0.0464398</v>
+        <v>0.0466869</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
@@ -2763,16 +2763,16 @@
         <v>31</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>0.0458446</v>
+        <v>0.046092</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>0.0457597</v>
+        <v>0.0460062</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0.0465286</v>
+        <v>0.0467752</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>6.84</v>
+        <v>6.83</v>
       </c>
       <c r="H65" s="14" t="inlineStr">
         <is>
@@ -2799,16 +2799,16 @@
         <v>30</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>0.0459065</v>
+        <v>0.0461548</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>0.04582480000000001</v>
+        <v>0.0460722</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0.0466155</v>
+        <v>0.046863</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
@@ -2835,13 +2835,13 @@
         <v>31</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>0.04596910000000001</v>
+        <v>0.04622080000000001</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>0.0458843</v>
+        <v>0.0461351</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>0.0467025</v>
+        <v>0.0469534</v>
       </c>
       <c r="G67" s="13" t="n">
         <v>7.33</v>
@@ -2871,16 +2871,16 @@
         <v>30</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>0.04602120000000001</v>
+        <v>0.0462765</v>
       </c>
       <c r="E68" s="12" t="n">
-        <v>0.0459386</v>
+        <v>0.046193</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0.0467788</v>
+        <v>0.0470332</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>7.58</v>
+        <v>7.57</v>
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
@@ -2907,16 +2907,16 @@
         <v>31</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>0.0460835</v>
+        <v>0.0463375</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>0.0459981</v>
+        <v>0.0462511</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0.04686779999999999</v>
+        <v>0.0471209</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>7.84</v>
+        <v>7.83</v>
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
@@ -2943,16 +2943,16 @@
         <v>31</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>0.0461482</v>
+        <v>0.0463913</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>0.0460625</v>
+        <v>0.04630480000000001</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>0.0469587</v>
+        <v>0.04720100000000001</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>8.109999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
@@ -2979,16 +2979,16 @@
         <v>30</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>0.0462158</v>
+        <v>0.0464408</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>0.0461324</v>
+        <v>0.0463566</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0.0470519</v>
+        <v>0.047276</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>8.359999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="H71" s="14" t="inlineStr">
         <is>
@@ -3015,16 +3015,16 @@
         <v>31</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>0.046297</v>
+        <v>0.0465025</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>0.0462108</v>
+        <v>0.0464156</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0.0471607</v>
+        <v>0.0473654</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>8.640000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
@@ -3051,16 +3051,16 @@
         <v>30</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>0.0463641</v>
+        <v>0.0465593</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>0.0462807</v>
+        <v>0.0464752</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0.047253</v>
+        <v>0.0474473</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>8.890000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
@@ -3087,16 +3087,16 @@
         <v>31</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>0.0464456</v>
+        <v>0.0466383</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>0.0463585</v>
+        <v>0.0465505</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0.0473639</v>
+        <v>0.0475557</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>9.18</v>
+        <v>9.17</v>
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
@@ -3123,16 +3123,16 @@
         <v>31</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>0.0465156</v>
+        <v>0.0467118</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>0.0464288</v>
+        <v>0.0466242</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0.04746069999999999</v>
+        <v>0.0476559</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
@@ -3159,16 +3159,16 @@
         <v>29</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>0.046584</v>
+        <v>0.0467837</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>0.0465029</v>
+        <v>0.0467019</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>0.0475567</v>
+        <v>0.0477554</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
@@ -3195,16 +3195,16 @@
         <v>31</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>0.0466671</v>
+        <v>0.0468681</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>0.0465795</v>
+        <v>0.0467797</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0.0476691</v>
+        <v>0.0478692</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
       <c r="H77" s="14" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
         <v>30</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>0.046733</v>
+        <v>0.0469333</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>0.0466477</v>
+        <v>0.04684720000000001</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0.0477634</v>
+        <v>0.0479627</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
@@ -3267,16 +3267,16 @@
         <v>31</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>0.0467899</v>
+        <v>0.0469893</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0.046702</v>
+        <v>0.0469007</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0.04784740000000001</v>
+        <v>0.0480459</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>10.58</v>
+        <v>10.57</v>
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
@@ -3303,16 +3303,16 @@
         <v>30</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>0.0468416</v>
+        <v>0.0470407</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>0.0467565</v>
+        <v>0.0469548</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0.04793020000000001</v>
+        <v>0.0481282</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>10.89</v>
+        <v>10.88</v>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
@@ -3339,16 +3339,16 @@
         <v>31</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>0.0468974</v>
+        <v>0.0470966</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>0.0468091</v>
+        <v>0.0470076</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0.0480157</v>
+        <v>0.0482139</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>11.18</v>
+        <v>11.17</v>
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
@@ -3375,16 +3375,16 @@
         <v>31</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>0.0469589</v>
+        <v>0.04715830000000001</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>0.0468696</v>
+        <v>0.0470682</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0.0481061</v>
+        <v>0.0483045</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>11.47</v>
+        <v>11.46</v>
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
@@ -3411,16 +3411,16 @@
         <v>30</v>
       </c>
       <c r="D83" s="12" t="n">
-        <v>0.0470285</v>
+        <v>0.04722800000000001</v>
       </c>
       <c r="E83" s="12" t="n">
-        <v>0.0469427</v>
+        <v>0.04714140000000001</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0.0482067</v>
+        <v>0.0484051</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>11.78</v>
+        <v>11.77</v>
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
@@ -3447,16 +3447,16 @@
         <v>31</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>0.047101</v>
+        <v>0.0473005</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>0.0470124</v>
+        <v>0.04721110000000001</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0.0483099</v>
+        <v>0.0485084</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>12.09</v>
+        <v>12.08</v>
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
@@ -3483,16 +3483,16 @@
         <v>30</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>0.0471582</v>
+        <v>0.0473576</v>
       </c>
       <c r="E85" s="12" t="n">
-        <v>0.04707169999999999</v>
+        <v>0.0472704</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>0.0483981</v>
+        <v>0.0485964</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>12.4</v>
+        <v>12.39</v>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         <v>31</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>0.0472113</v>
+        <v>0.0474107</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>0.0471216</v>
+        <v>0.0473203</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>0.0484829</v>
+        <v>0.0486812</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>12.72</v>
+        <v>12.71</v>
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
@@ -3555,16 +3555,16 @@
         <v>31</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>0.047259</v>
+        <v>0.0474585</v>
       </c>
       <c r="E87" s="12" t="n">
-        <v>0.0471694</v>
+        <v>0.0473681</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0.04856029999999999</v>
+        <v>0.0487587</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>13.01</v>
+        <v>13</v>
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
@@ -3591,16 +3591,16 @@
         <v>28</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>0.0473139</v>
+        <v>0.0475134</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>0.0472335</v>
+        <v>0.0474322</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0.0486485</v>
+        <v>0.0488468</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>13.35</v>
+        <v>13.33</v>
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>31</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>0.0473939</v>
+        <v>0.0475934</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>0.047303</v>
+        <v>0.0475017</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>0.0487607</v>
+        <v>0.0489591</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>13.67</v>
+        <v>13.66</v>
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
@@ -3663,16 +3663,16 @@
         <v>30</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>0.0474576</v>
+        <v>0.0476571</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>0.0473705</v>
+        <v>0.0475692</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0.04885589999999999</v>
+        <v>0.0490543</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>13.98</v>
+        <v>13.97</v>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
@@ -3699,16 +3699,16 @@
         <v>31</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>0.04751420000000001</v>
+        <v>0.0477137</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>0.0474234</v>
+        <v>0.04762209999999999</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>0.0489436</v>
+        <v>0.0491419</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>14.29</v>
+        <v>14.28</v>
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
@@ -3735,16 +3735,16 @@
         <v>30</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>0.0475532</v>
+        <v>0.04775260000000001</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>0.0474655</v>
+        <v>0.04766409999999999</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>0.0490156</v>
+        <v>0.0492139</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>14.62</v>
+        <v>14.61</v>
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
@@ -3771,16 +3771,16 @@
         <v>31</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>0.0475891</v>
+        <v>0.04778839999999999</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>0.0474986</v>
+        <v>0.0476972</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>0.0490845</v>
+        <v>0.04928270000000001</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>14.95</v>
+        <v>14.94</v>
       </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
@@ -3807,16 +3807,16 @@
         <v>31</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>0.0476263</v>
+        <v>0.0478257</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>0.0475345</v>
+        <v>0.0477331</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>0.0491555</v>
+        <v>0.0493537</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>15.29</v>
+        <v>15.28</v>
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
@@ -3843,16 +3843,16 @@
         <v>30</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>0.04766860000000001</v>
+        <v>0.0478679</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>0.0475804</v>
+        <v>0.0477791</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>0.049232</v>
+        <v>0.0494302</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>15.63</v>
+        <v>15.62</v>
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
@@ -3879,16 +3879,16 @@
         <v>31</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>0.0477283</v>
+        <v>0.04792779999999999</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>0.0476369</v>
+        <v>0.0478356</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>0.049325</v>
+        <v>0.0495233</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>15.97</v>
+        <v>15.95</v>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
@@ -3915,16 +3915,16 @@
         <v>30</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>0.0478025</v>
+        <v>0.048002</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>0.047714</v>
+        <v>0.0479129</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>0.04943699999999999</v>
+        <v>0.04963530000000001</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>16.34</v>
+        <v>16.33</v>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
@@ -3951,16 +3951,16 @@
         <v>31</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>0.0478801</v>
+        <v>0.0480798</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>0.0477881</v>
+        <v>0.0479871</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>0.0495507</v>
+        <v>0.0497492</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>16.71</v>
+        <v>16.69</v>
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
@@ -3987,16 +3987,16 @@
         <v>31</v>
       </c>
       <c r="D99" s="12" t="n">
-        <v>0.0479292</v>
+        <v>0.048129</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>0.047837</v>
+        <v>0.048036</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>0.0496328</v>
+        <v>0.0498314</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>17.04</v>
+        <v>17.02</v>
       </c>
       <c r="H99" s="14" t="inlineStr">
         <is>
@@ -4023,16 +4023,16 @@
         <v>28</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>0.0479363</v>
+        <v>0.048136</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>0.0478538</v>
+        <v>0.0480527</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>0.0496758</v>
+        <v>0.0498742</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>17.39</v>
+        <v>17.38</v>
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
@@ -4059,16 +4059,16 @@
         <v>31</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>0.04793269999999999</v>
+        <v>0.0481323</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>0.0478397</v>
+        <v>0.0480385</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>0.0497066</v>
+        <v>0.0499049</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>17.74</v>
+        <v>17.73</v>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         <v>30</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>0.04792589999999999</v>
+        <v>0.04812540000000001</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>0.0478371</v>
+        <v>0.04803569999999999</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>0.0497312</v>
+        <v>0.0499294</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>18.05</v>
+        <v>18.04</v>
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
         <v>31</v>
       </c>
       <c r="D103" s="12" t="n">
-        <v>0.0479678</v>
+        <v>0.0481672</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>0.0478753</v>
+        <v>0.0480739</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>0.0498109</v>
+        <v>0.0500091</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>18.43</v>
+        <v>18.42</v>
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
@@ -4167,16 +4167,16 @@
         <v>30</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>0.0480412</v>
+        <v>0.0482406</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>0.0479517</v>
+        <v>0.0481503</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>0.0499209</v>
+        <v>0.050119</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>18.8</v>
+        <v>18.78</v>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
@@ -4203,16 +4203,16 @@
         <v>31</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>0.0481144</v>
+        <v>0.048314</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>0.0480211</v>
+        <v>0.0482199</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>0.0500297</v>
+        <v>0.050228</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>19.15</v>
+        <v>19.14</v>
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
@@ -4239,16 +4239,16 @@
         <v>31</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>0.0481472</v>
+        <v>0.0483469</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>0.0480534</v>
+        <v>0.0482522</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>0.0501027</v>
+        <v>0.05030109999999999</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>19.55</v>
+        <v>19.54</v>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         <v>30</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>0.0481251</v>
+        <v>0.0483247</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>0.0480355</v>
+        <v>0.0482344</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>0.0501175</v>
+        <v>0.0503159</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>19.92</v>
+        <v>19.91</v>
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
@@ -4311,16 +4311,16 @@
         <v>31</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>0.0481165</v>
+        <v>0.0483162</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>0.0480234</v>
+        <v>0.0482223</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>0.0501452</v>
+        <v>0.0503436</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>20.29</v>
+        <v>20.27</v>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
@@ -4347,16 +4347,16 @@
         <v>30</v>
       </c>
       <c r="D109" s="12" t="n">
-        <v>0.0481649</v>
+        <v>0.0483645</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>0.0480745</v>
+        <v>0.0482734</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>0.050232</v>
+        <v>0.0504303</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>20.67</v>
+        <v>20.66</v>
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
@@ -4383,16 +4383,16 @@
         <v>31</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>0.0482853</v>
+        <v>0.04848499999999999</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>0.0481922</v>
+        <v>0.0483911</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>0.0503905</v>
+        <v>0.0505888</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>21.05</v>
+        <v>21.04</v>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
@@ -4419,16 +4419,16 @@
         <v>31</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0.0484122</v>
+        <v>0.0486119</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>0.048318</v>
+        <v>0.0485168</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>0.0505543</v>
+        <v>0.0507526</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>21.42</v>
+        <v>21.41</v>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
@@ -4455,16 +4455,16 @@
         <v>28</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0.04848189999999999</v>
+        <v>0.04868140000000001</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>0.0483974</v>
+        <v>0.0485963</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>0.0506623</v>
+        <v>0.0508605</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>21.8</v>
+        <v>21.79</v>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
@@ -4491,16 +4491,16 @@
         <v>31</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.0484979</v>
+        <v>0.0486975</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>0.0484035</v>
+        <v>0.0486024</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>0.0507172</v>
+        <v>0.0509155</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>22.19</v>
+        <v>22.18</v>
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>30</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0.0484675</v>
+        <v>0.0486672</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>0.0483758</v>
+        <v>0.0485747</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>0.0507236</v>
+        <v>0.05092190000000001</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>22.56</v>
+        <v>22.55</v>
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
@@ -4563,16 +4563,16 @@
         <v>31</v>
       </c>
       <c r="D115" s="12" t="n">
-        <v>0.04846059999999999</v>
+        <v>0.0486603</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>0.0483661</v>
+        <v>0.048565</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>0.0507573</v>
+        <v>0.0509556</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>22.97</v>
+        <v>22.95</v>
       </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
@@ -4599,16 +4599,16 @@
         <v>30</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>0.0484886</v>
+        <v>0.0486883</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>0.0483972</v>
+        <v>0.0485961</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>0.0508249</v>
+        <v>0.0510232</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>23.36</v>
+        <v>23.35</v>
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
@@ -4635,16 +4635,16 @@
         <v>31</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>0.0485436</v>
+        <v>0.0487433</v>
       </c>
       <c r="E117" s="12" t="n">
-        <v>0.0484485</v>
+        <v>0.0486474</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>0.0509192</v>
+        <v>0.05111760000000001</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>23.76</v>
+        <v>23.74</v>
       </c>
       <c r="H117" s="14" t="inlineStr">
         <is>
@@ -4671,16 +4671,16 @@
         <v>31</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>0.0485903</v>
+        <v>0.04878999999999999</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>0.0484947</v>
+        <v>0.0486936</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>0.05100730000000001</v>
+        <v>0.0512057</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>24.17</v>
+        <v>24.16</v>
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
@@ -4707,16 +4707,16 @@
         <v>30</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>0.04861550000000001</v>
+        <v>0.04881509999999999</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>0.0485238</v>
+        <v>0.0487227</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>0.051068</v>
+        <v>0.0512662</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>24.53</v>
+        <v>24.51</v>
       </c>
       <c r="H119" s="14" t="inlineStr">
         <is>
@@ -4743,16 +4743,16 @@
         <v>31</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>0.0486684</v>
+        <v>0.0488681</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>0.0485732</v>
+        <v>0.0487721</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>0.0511652</v>
+        <v>0.0513635</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>24.97</v>
+        <v>24.95</v>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
@@ -4779,16 +4779,16 @@
         <v>30</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>0.048752</v>
+        <v>0.0489517</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>0.04865999999999999</v>
+        <v>0.0488589</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>0.0512887</v>
+        <v>0.051487</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>25.37</v>
+        <v>25.35</v>
       </c>
       <c r="H121" s="14" t="inlineStr">
         <is>
@@ -4815,16 +4815,16 @@
         <v>31</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.0488705</v>
+        <v>0.0490702</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>0.04877430000000001</v>
+        <v>0.04897319999999999</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>0.051446</v>
+        <v>0.0516443</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>25.75</v>
+        <v>25.74</v>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
@@ -4851,16 +4851,16 @@
         <v>31</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>0.0489936</v>
+        <v>0.0491933</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>0.048897</v>
+        <v>0.049096</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>0.0516116</v>
+        <v>0.05180990000000001</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>26.18</v>
+        <v>26.17</v>
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
@@ -4887,16 +4887,16 @@
         <v>29</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>0.0490638</v>
+        <v>0.0492635</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>0.04897389999999999</v>
+        <v>0.0491728</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>0.0517236</v>
+        <v>0.0519219</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>26.6</v>
+        <v>26.58</v>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
@@ -4923,16 +4923,16 @@
         <v>31</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>0.0490832</v>
+        <v>0.0492829</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>0.04898590000000001</v>
+        <v>0.0491848</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>0.0517823</v>
+        <v>0.0519806</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>26.99</v>
+        <v>26.98</v>
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>30</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>0.0490472</v>
+        <v>0.0492469</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>0.0489539</v>
+        <v>0.0491528</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>0.0517894</v>
+        <v>0.0519876</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>27.42</v>
+        <v>27.41</v>
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
@@ -4995,16 +4995,16 @@
         <v>31</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>0.0489967</v>
+        <v>0.0491965</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>0.0489004</v>
+        <v>0.04909939999999999</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>0.0517801</v>
+        <v>0.0519784</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>27.83</v>
+        <v>27.82</v>
       </c>
       <c r="H127" s="14" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>30</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>0.0489371</v>
+        <v>0.0491368</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>0.0488437</v>
+        <v>0.0490427</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>0.0517596</v>
+        <v>0.0519578</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>28.23</v>
+        <v>28.21</v>
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
@@ -5067,16 +5067,16 @@
         <v>31</v>
       </c>
       <c r="D129" s="18" t="n">
-        <v>0.04893810000000001</v>
+        <v>0.0491378</v>
       </c>
       <c r="E129" s="18" t="n">
-        <v>0.0488418</v>
+        <v>0.0490408</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.0517623</v>
+        <v>0.0519606</v>
       </c>
       <c r="G129" s="19" t="n">
-        <v>28.24</v>
+        <v>28.23</v>
       </c>
       <c r="H129" s="20" t="inlineStr">
         <is>
@@ -5103,16 +5103,16 @@
         <v>31</v>
       </c>
       <c r="D130" s="18" t="n">
-        <v>0.04893810000000001</v>
+        <v>0.0491378</v>
       </c>
       <c r="E130" s="18" t="n">
-        <v>0.0488418</v>
+        <v>0.0490408</v>
       </c>
       <c r="F130" s="18" t="n">
-        <v>0.0517623</v>
+        <v>0.0519606</v>
       </c>
       <c r="G130" s="19" t="n">
-        <v>28.24</v>
+        <v>28.23</v>
       </c>
       <c r="H130" s="20" t="inlineStr">
         <is>
@@ -5139,16 +5139,16 @@
         <v>30</v>
       </c>
       <c r="D131" s="18" t="n">
-        <v>0.0489353</v>
+        <v>0.04913509999999999</v>
       </c>
       <c r="E131" s="18" t="n">
-        <v>0.0488418</v>
+        <v>0.0490408</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.0517592</v>
+        <v>0.0519575</v>
       </c>
       <c r="G131" s="19" t="n">
-        <v>28.24</v>
+        <v>28.22</v>
       </c>
       <c r="H131" s="20" t="inlineStr">
         <is>
@@ -5175,16 +5175,16 @@
         <v>31</v>
       </c>
       <c r="D132" s="18" t="n">
-        <v>0.04893810000000001</v>
+        <v>0.0491378</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>0.0488418</v>
+        <v>0.0490408</v>
       </c>
       <c r="F132" s="18" t="n">
-        <v>0.0517623</v>
+        <v>0.0519606</v>
       </c>
       <c r="G132" s="19" t="n">
-        <v>28.24</v>
+        <v>28.23</v>
       </c>
       <c r="H132" s="20" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-20)</t>
+          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-21)</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
         <v>46344</v>
       </c>
       <c r="D4" s="23" t="n">
-        <v>96.16500000000001</v>
+        <v>96.16249999999999</v>
       </c>
       <c r="E4" s="15">
         <f>(100-D4)/100</f>
@@ -5574,13 +5574,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.038354</v>
+        <v>0.0383479</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>0.04</v>
+        <v>-0.271</v>
       </c>
       <c r="I4" s="25" t="n">
-        <v>7104</v>
+        <v>7504</v>
       </c>
     </row>
     <row r="5">
@@ -5606,13 +5606,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.0394216</v>
+        <v>0.0394151</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.099</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>1295273</v>
+        <v>1296078</v>
       </c>
     </row>
     <row r="6">
@@ -5638,13 +5638,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.0388881</v>
+        <v>0.0388771</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>-0.119</v>
+        <v>-0.229</v>
       </c>
       <c r="I6" s="25" t="n">
-        <v>344625</v>
+        <v>353941</v>
       </c>
     </row>
     <row r="7">
@@ -5660,7 +5660,7 @@
         <v>46407</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>95.94</v>
+        <v>95.94499999999999</v>
       </c>
       <c r="E7" s="15">
         <f>(100-D7)/100</f>
@@ -5670,13 +5670,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.0405715</v>
+        <v>0.04058029999999999</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>-0.285</v>
+        <v>0.303</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>6693</v>
+        <v>6686</v>
       </c>
     </row>
     <row r="8">
@@ -5702,13 +5702,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.0393794</v>
+        <v>0.039367</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>0.294</v>
+        <v>0.17</v>
       </c>
       <c r="I8" s="25" t="n">
-        <v>290247</v>
+        <v>294896</v>
       </c>
     </row>
     <row r="9">
@@ -5724,7 +5724,7 @@
         <v>46435</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>95.845</v>
+        <v>95.8425</v>
       </c>
       <c r="E9" s="15">
         <f>(100-D9)/100</f>
@@ -5734,13 +5734,13 @@
         <v>0.01</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.0415526</v>
+        <v>0.0415923</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>0.026</v>
+        <v>0.173</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>2590</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="10">
@@ -5756,7 +5756,7 @@
         <v>46388</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>95.90000000000001</v>
+        <v>95.895</v>
       </c>
       <c r="E10" s="15">
         <f>(100-D10)/100</f>
@@ -5766,13 +5766,13 @@
         <v>0.01</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.0409997</v>
+        <v>0.0410242</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.003</v>
+        <v>-0.258</v>
       </c>
       <c r="I10" s="25" t="n">
-        <v>229671</v>
+        <v>230100</v>
       </c>
     </row>
     <row r="11">
@@ -5788,23 +5788,23 @@
         <v>46463</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>95.755</v>
+        <v>95.745</v>
       </c>
       <c r="E11" s="15">
         <f>(100-D11)/100</f>
         <v/>
       </c>
       <c r="F11" s="24" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.0424373</v>
+        <v>0.0425072</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.127</v>
+        <v>-0.428</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>1555304</v>
+        <v>1552541</v>
       </c>
     </row>
     <row r="12">
@@ -5820,7 +5820,7 @@
         <v>46419</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>95.81999999999999</v>
+        <v>95.815</v>
       </c>
       <c r="E12" s="15">
         <f>(100-D12)/100</f>
@@ -5830,13 +5830,13 @@
         <v>0.02</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.0417988</v>
+        <v>0.0418456</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.012</v>
+        <v>-0.044</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>179788</v>
+        <v>181283</v>
       </c>
     </row>
     <row r="13">
@@ -5852,7 +5852,7 @@
         <v>46498</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>95.655</v>
+        <v>95.645</v>
       </c>
       <c r="E13" s="15">
         <f>(100-D13)/100</f>
@@ -5862,13 +5862,13 @@
         <v>0.05</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.0434964</v>
+        <v>0.0436067</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.464</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>1225</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="14">
@@ -5884,7 +5884,7 @@
         <v>46447</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>95.73</v>
+        <v>95.72</v>
       </c>
       <c r="E14" s="15">
         <f>(100-D14)/100</f>
@@ -5894,13 +5894,13 @@
         <v>0.04</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.0427133</v>
+        <v>0.042809</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.133</v>
+        <v>0.09</v>
       </c>
       <c r="I14" s="25" t="n">
-        <v>105993</v>
+        <v>104425</v>
       </c>
     </row>
     <row r="15">
@@ -5916,23 +5916,23 @@
         <v>46526</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>95.56999999999999</v>
+        <v>95.55500000000001</v>
       </c>
       <c r="E15" s="15">
         <f>(100-D15)/100</f>
         <v/>
       </c>
       <c r="F15" s="24" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.0443314</v>
+        <v>0.0444884</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>0.314</v>
+        <v>0.384</v>
       </c>
       <c r="I15" s="25" t="n">
-        <v>543</v>
+        <v>554</v>
       </c>
     </row>
     <row r="16">
@@ -5948,7 +5948,7 @@
         <v>46478</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>95.645</v>
+        <v>95.63500000000001</v>
       </c>
       <c r="E16" s="15">
         <f>(100-D16)/100</f>
@@ -5958,13 +5958,13 @@
         <v>0.06</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.0434918</v>
+        <v>0.0436097</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.582</v>
+        <v>-0.403</v>
       </c>
       <c r="I16" s="25" t="n">
-        <v>33926</v>
+        <v>34879</v>
       </c>
     </row>
     <row r="17">
@@ -5980,23 +5980,23 @@
         <v>46554</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>95.47499999999999</v>
+        <v>95.45</v>
       </c>
       <c r="E17" s="15">
         <f>(100-D17)/100</f>
         <v/>
       </c>
       <c r="F17" s="24" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.0452248</v>
+        <v>0.0454379</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>-0.252</v>
+        <v>-0.621</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>1327865</v>
+        <v>1335306</v>
       </c>
     </row>
     <row r="18">
@@ -6012,7 +6012,7 @@
         <v>46508</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>95.55</v>
+        <v>95.535</v>
       </c>
       <c r="E18" s="15">
         <f>(100-D18)/100</f>
@@ -6022,13 +6022,13 @@
         <v>0.09</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.0444986</v>
+        <v>0.0446514</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>-0.014</v>
+        <v>0.014</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>54661</v>
+        <v>60988</v>
       </c>
     </row>
     <row r="19">
@@ -6044,7 +6044,7 @@
         <v>46539</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>95.465</v>
+        <v>95.44</v>
       </c>
       <c r="E19" s="15">
         <f>(100-D19)/100</f>
@@ -6054,13 +6054,13 @@
         <v>0.13</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.045362</v>
+        <v>0.0456252</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>0.12</v>
+        <v>0.252</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>69238</v>
+        <v>70231</v>
       </c>
     </row>
     <row r="20">
@@ -6076,7 +6076,7 @@
         <v>46569</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>95.39</v>
+        <v>95.36</v>
       </c>
       <c r="E20" s="15">
         <f>(100-D20)/100</f>
@@ -6086,13 +6086,13 @@
         <v>0.17</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.0460936</v>
+        <v>0.0463994</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>-0.064</v>
+        <v>-0.006</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>21519</v>
+        <v>20087</v>
       </c>
     </row>
     <row r="21">
@@ -6108,7 +6108,7 @@
         <v>46645</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>95.315</v>
+        <v>95.27500000000001</v>
       </c>
       <c r="E21" s="15">
         <f>(100-D21)/100</f>
@@ -6118,13 +6118,13 @@
         <v>0.23</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.046865</v>
+        <v>0.0472101</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>0.15</v>
+        <v>-0.399</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>1277006</v>
+        <v>1262304</v>
       </c>
     </row>
     <row r="22">
@@ -6140,23 +6140,23 @@
         <v>46600</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>95.355</v>
+        <v>95.325</v>
       </c>
       <c r="E22" s="15">
         <f>(100-D22)/100</f>
         <v/>
       </c>
       <c r="F22" s="24" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.0464438</v>
+        <v>0.0467709</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>-0.062</v>
+        <v>0.209</v>
       </c>
       <c r="I22" s="25" t="n">
-        <v>38743</v>
+        <v>38733</v>
       </c>
     </row>
     <row r="23">
@@ -6172,7 +6172,7 @@
         <v>46631</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>95.325</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="E23" s="15">
         <f>(100-D23)/100</f>
@@ -6182,13 +6182,13 @@
         <v>0.27</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.0467643</v>
+        <v>0.0471209</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>0.143</v>
+        <v>0.209</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>18798</v>
+        <v>19022</v>
       </c>
     </row>
     <row r="24">
@@ -6204,7 +6204,7 @@
         <v>46661</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>95.3</v>
+        <v>95.265</v>
       </c>
       <c r="E24" s="15">
         <f>(100-D24)/100</f>
@@ -6214,13 +6214,13 @@
         <v>0.32</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.0469633</v>
+        <v>0.0473544</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>-0.367</v>
+        <v>0.044</v>
       </c>
       <c r="I24" s="25" t="n">
-        <v>4936</v>
+        <v>4912</v>
       </c>
     </row>
     <row r="25">
@@ -6236,7 +6236,7 @@
         <v>46736</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>95.26000000000001</v>
+        <v>95.215</v>
       </c>
       <c r="E25" s="15">
         <f>(100-D25)/100</f>
@@ -6246,13 +6246,13 @@
         <v>0.41</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.0474168</v>
+        <v>0.0478608</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>0.168</v>
+        <v>0.108</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>1052864</v>
+        <v>1054765</v>
       </c>
     </row>
     <row r="26">
@@ -6268,7 +6268,7 @@
         <v>46692</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>95.285</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="E26" s="15">
         <f>(100-D26)/100</f>
@@ -6278,13 +6278,13 @@
         <v>0.38</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.0471593</v>
+        <v>0.0475887</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>0.093</v>
+        <v>-0.113</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>6994</v>
+        <v>7001</v>
       </c>
     </row>
     <row r="27">
@@ -6300,7 +6300,7 @@
         <v>46722</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>95.285</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="E27" s="15">
         <f>(100-D27)/100</f>
@@ -6310,13 +6310,13 @@
         <v>0.45</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.0471419</v>
+        <v>0.0475971</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>-0.081</v>
+        <v>-0.029</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>1766</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="28">
@@ -6332,7 +6332,7 @@
         <v>46827</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>95.27</v>
+        <v>95.22499999999999</v>
       </c>
       <c r="E28" s="15">
         <f>(100-D28)/100</f>
@@ -6342,13 +6342,13 @@
         <v>0.63</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.0472984</v>
+        <v>0.0477496</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>-0.016</v>
+        <v>-0.004</v>
       </c>
       <c r="I28" s="25" t="n">
-        <v>1662033</v>
+        <v>1637506</v>
       </c>
     </row>
     <row r="29">
@@ -6364,23 +6364,23 @@
         <v>46925</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>95.29000000000001</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="E29" s="15">
         <f>(100-D29)/100</f>
         <v/>
       </c>
       <c r="F29" s="24" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.0471003</v>
+        <v>0.04759960000000001</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>0.003</v>
+        <v>-0.004</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>817756</v>
+        <v>828142</v>
       </c>
     </row>
     <row r="30">
@@ -6396,7 +6396,7 @@
         <v>47016</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>95.30500000000001</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="E30" s="15">
         <f>(100-D30)/100</f>
@@ -6406,13 +6406,13 @@
         <v>1.23</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.0469529</v>
+        <v>0.04740179999999999</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
       <c r="I30" s="25" t="n">
-        <v>647741</v>
+        <v>643008</v>
       </c>
     </row>
     <row r="31">
@@ -6428,23 +6428,23 @@
         <v>47107</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>95.315</v>
+        <v>95.27500000000001</v>
       </c>
       <c r="E31" s="15">
         <f>(100-D31)/100</f>
         <v/>
       </c>
       <c r="F31" s="24" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.04684389999999999</v>
+        <v>0.0472477</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>-0.061</v>
+        <v>-0.023</v>
       </c>
       <c r="I31" s="25" t="n">
-        <v>673706</v>
+        <v>678274</v>
       </c>
     </row>
     <row r="32">
@@ -6460,7 +6460,7 @@
         <v>47198</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>95.33499999999999</v>
+        <v>95.295</v>
       </c>
       <c r="E32" s="15">
         <f>(100-D32)/100</f>
@@ -6470,13 +6470,13 @@
         <v>1.98</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.046656</v>
+        <v>0.0470507</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>0.06</v>
+        <v>0.007</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>550080</v>
+        <v>551725</v>
       </c>
     </row>
     <row r="33">
@@ -6492,7 +6492,7 @@
         <v>47289</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>95.34999999999999</v>
+        <v>95.315</v>
       </c>
       <c r="E33" s="15">
         <f>(100-D33)/100</f>
@@ -6502,13 +6502,13 @@
         <v>2.42</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.0464945</v>
+        <v>0.04685019999999999</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>-0.055</v>
+        <v>0.002</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>388777</v>
+        <v>380691</v>
       </c>
     </row>
     <row r="34">
@@ -6524,7 +6524,7 @@
         <v>47380</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>95.36499999999999</v>
+        <v>95.33</v>
       </c>
       <c r="E34" s="15">
         <f>(100-D34)/100</f>
@@ -6534,13 +6534,13 @@
         <v>2.9</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.0463558</v>
+        <v>0.0467001</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>0.058</v>
+        <v>0.001</v>
       </c>
       <c r="I34" s="25" t="n">
-        <v>379993</v>
+        <v>378142</v>
       </c>
     </row>
     <row r="35">
@@ -6556,23 +6556,23 @@
         <v>47471</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>95.37</v>
+        <v>95.34</v>
       </c>
       <c r="E35" s="15">
         <f>(100-D35)/100</f>
         <v/>
       </c>
       <c r="F35" s="24" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.0462943</v>
+        <v>0.0465999</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>-0.057</v>
+        <v>-0.001</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>302252</v>
+        <v>303454</v>
       </c>
     </row>
     <row r="36">
@@ -6588,7 +6588,7 @@
         <v>47562</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>95.375</v>
+        <v>95.345</v>
       </c>
       <c r="E36" s="15">
         <f>(100-D36)/100</f>
@@ -6598,13 +6598,13 @@
         <v>3.97</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.04625530000000001</v>
+        <v>0.0465501</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>0.053</v>
+        <v>0.001</v>
       </c>
       <c r="I36" s="25" t="n">
-        <v>245645</v>
+        <v>243437</v>
       </c>
     </row>
     <row r="37">
@@ -6620,7 +6620,7 @@
         <v>47653</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>95.37</v>
+        <v>95.345</v>
       </c>
       <c r="E37" s="15">
         <f>(100-D37)/100</f>
@@ -6630,13 +6630,13 @@
         <v>4.56</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.046296</v>
+        <v>0.0465499</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>-0.04</v>
+        <v>-0.001</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>178997</v>
+        <v>179522</v>
       </c>
     </row>
     <row r="38">
@@ -6652,23 +6652,23 @@
         <v>47744</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>95.36499999999999</v>
+        <v>95.34</v>
       </c>
       <c r="E38" s="15">
         <f>(100-D38)/100</f>
         <v/>
       </c>
       <c r="F38" s="24" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.0463523</v>
+        <v>0.04660040000000001</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>0.023</v>
+        <v>0.004</v>
       </c>
       <c r="I38" s="25" t="n">
-        <v>158566</v>
+        <v>159075</v>
       </c>
     </row>
     <row r="39">
@@ -6684,23 +6684,23 @@
         <v>47835</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>95.355</v>
+        <v>95.33</v>
       </c>
       <c r="E39" s="15">
         <f>(100-D39)/100</f>
         <v/>
       </c>
       <c r="F39" s="24" t="n">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.04644790000000001</v>
+        <v>0.0466986</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>-0.021</v>
+        <v>-0.014</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>138900</v>
+        <v>141748</v>
       </c>
     </row>
     <row r="40">
@@ -6716,7 +6716,7 @@
         <v>47926</v>
       </c>
       <c r="D40" s="23" t="n">
-        <v>95.34</v>
+        <v>95.315</v>
       </c>
       <c r="E40" s="15">
         <f>(100-D40)/100</f>
@@ -6726,13 +6726,13 @@
         <v>6.55</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.0466032</v>
+        <v>0.0468526</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>0.032</v>
+        <v>0.026</v>
       </c>
       <c r="I40" s="25" t="n">
-        <v>113854</v>
+        <v>115058</v>
       </c>
     </row>
     <row r="41">
@@ -6748,7 +6748,7 @@
         <v>48017</v>
       </c>
       <c r="D41" s="23" t="n">
-        <v>95.315</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="E41" s="15">
         <f>(100-D41)/100</f>
@@ -6758,13 +6758,13 @@
         <v>7.28</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.0468466</v>
+        <v>0.0470984</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.016</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>86572</v>
+        <v>88299</v>
       </c>
     </row>
     <row r="42">
@@ -6780,23 +6780,23 @@
         <v>48108</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>95.29000000000001</v>
+        <v>95.265</v>
       </c>
       <c r="E42" s="15">
         <f>(100-D42)/100</f>
         <v/>
       </c>
       <c r="F42" s="24" t="n">
-        <v>8.050000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.0471028</v>
+        <v>0.0473493</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>0.028</v>
+        <v>-0.007</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>67769</v>
+        <v>68749</v>
       </c>
     </row>
     <row r="43">
@@ -6812,7 +6812,7 @@
         <v>48199</v>
       </c>
       <c r="D43" s="23" t="n">
-        <v>95.26000000000001</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="E43" s="15">
         <f>(100-D43)/100</f>
@@ -6822,13 +6822,13 @@
         <v>8.84</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.047398</v>
+        <v>0.0476015</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>-0.02</v>
+        <v>0.015</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>34709</v>
+        <v>35766</v>
       </c>
     </row>
     <row r="44">
@@ -6844,23 +6844,23 @@
         <v>48290</v>
       </c>
       <c r="D44" s="23" t="n">
-        <v>95.23</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="E44" s="15">
         <f>(100-D44)/100</f>
         <v/>
       </c>
       <c r="F44" s="24" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.0477022</v>
+        <v>0.0479004</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>0.022</v>
+        <v>0.004</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>5757</v>
+        <v>5782</v>
       </c>
     </row>
     <row r="45">
@@ -6876,23 +6876,23 @@
         <v>48381</v>
       </c>
       <c r="D45" s="23" t="n">
-        <v>95.2</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="E45" s="15">
         <f>(100-D45)/100</f>
         <v/>
       </c>
       <c r="F45" s="24" t="n">
-        <v>10.53</v>
+        <v>10.52</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.04799610000000001</v>
+        <v>0.0481966</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>-0.039</v>
+        <v>-0.034</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>1769</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="46">
@@ -6908,23 +6908,23 @@
         <v>48472</v>
       </c>
       <c r="D46" s="23" t="n">
-        <v>95.175</v>
+        <v>95.155</v>
       </c>
       <c r="E46" s="15">
         <f>(100-D46)/100</f>
         <v/>
       </c>
       <c r="F46" s="24" t="n">
-        <v>11.42</v>
+        <v>11.41</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.0482552</v>
+        <v>0.0484551</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="I46" s="25" t="n">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="47">
@@ -6940,20 +6940,20 @@
         <v>48563</v>
       </c>
       <c r="D47" s="23" t="n">
-        <v>95.145</v>
+        <v>95.125</v>
       </c>
       <c r="E47" s="15">
         <f>(100-D47)/100</f>
         <v/>
       </c>
       <c r="F47" s="24" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.0485442</v>
+        <v>0.0487443</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>-0.058</v>
+        <v>-0.057</v>
       </c>
       <c r="I47" s="25" t="n">
         <v>576</v>
@@ -6972,17 +6972,17 @@
         <v>48654</v>
       </c>
       <c r="D48" s="23" t="n">
-        <v>95.12</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="E48" s="15">
         <f>(100-D48)/100</f>
         <v/>
       </c>
       <c r="F48" s="24" t="n">
-        <v>13.28</v>
+        <v>13.26</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.0488061</v>
+        <v>0.0490061</v>
       </c>
       <c r="H48" s="24" t="n">
         <v>0.061</v>
@@ -7004,20 +7004,20 @@
         <v>48745</v>
       </c>
       <c r="D49" s="23" t="n">
-        <v>95.09</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="E49" s="15">
         <f>(100-D49)/100</f>
         <v/>
       </c>
       <c r="F49" s="24" t="n">
-        <v>14.25</v>
+        <v>14.24</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.0490947</v>
+        <v>0.04929459999999999</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>-0.053</v>
+        <v>-0.054</v>
       </c>
       <c r="I49" s="25" t="n">
         <v>35</v>
@@ -7036,17 +7036,17 @@
         <v>48843</v>
       </c>
       <c r="D50" s="23" t="n">
-        <v>95.065</v>
+        <v>95.045</v>
       </c>
       <c r="E50" s="15">
         <f>(100-D50)/100</f>
         <v/>
       </c>
       <c r="F50" s="24" t="n">
-        <v>15.28</v>
+        <v>15.27</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.04935170000000001</v>
+        <v>0.0495517</v>
       </c>
       <c r="H50" s="24" t="n">
         <v>0.017</v>
@@ -7068,17 +7068,17 @@
         <v>48934</v>
       </c>
       <c r="D51" s="23" t="n">
-        <v>95.04000000000001</v>
+        <v>95.02</v>
       </c>
       <c r="E51" s="15">
         <f>(100-D51)/100</f>
         <v/>
       </c>
       <c r="F51" s="24" t="n">
-        <v>16.35</v>
+        <v>16.34</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.04960639999999999</v>
+        <v>0.0498064</v>
       </c>
       <c r="H51" s="24" t="n">
         <v>0.064</v>
@@ -7100,17 +7100,17 @@
         <v>49018</v>
       </c>
       <c r="D52" s="23" t="n">
-        <v>95.015</v>
+        <v>94.995</v>
       </c>
       <c r="E52" s="15">
         <f>(100-D52)/100</f>
         <v/>
       </c>
       <c r="F52" s="24" t="n">
-        <v>17.36</v>
+        <v>17.35</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.0498337</v>
+        <v>0.0500337</v>
       </c>
       <c r="H52" s="24" t="n">
         <v>-0.163</v>
@@ -7132,17 +7132,17 @@
         <v>49116</v>
       </c>
       <c r="D53" s="23" t="n">
-        <v>95</v>
+        <v>94.98</v>
       </c>
       <c r="E53" s="15">
         <f>(100-D53)/100</f>
         <v/>
       </c>
       <c r="F53" s="24" t="n">
-        <v>18.43</v>
+        <v>18.42</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.050023</v>
+        <v>0.050223</v>
       </c>
       <c r="H53" s="24" t="n">
         <v>0.23</v>
@@ -7164,17 +7164,17 @@
         <v>49207</v>
       </c>
       <c r="D54" s="23" t="n">
-        <v>94.97</v>
+        <v>94.95</v>
       </c>
       <c r="E54" s="15">
         <f>(100-D54)/100</f>
         <v/>
       </c>
       <c r="F54" s="24" t="n">
-        <v>19.57</v>
+        <v>19.56</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.0502714</v>
+        <v>0.0504714</v>
       </c>
       <c r="H54" s="24" t="n">
         <v>-0.286</v>
@@ -7196,17 +7196,17 @@
         <v>49298</v>
       </c>
       <c r="D55" s="23" t="n">
-        <v>94.95999999999999</v>
+        <v>94.94</v>
       </c>
       <c r="E55" s="15">
         <f>(100-D55)/100</f>
         <v/>
       </c>
       <c r="F55" s="24" t="n">
-        <v>20.7</v>
+        <v>20.69</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.0504337</v>
+        <v>0.0506337</v>
       </c>
       <c r="H55" s="24" t="n">
         <v>0.337</v>
@@ -7228,17 +7228,17 @@
         <v>49389</v>
       </c>
       <c r="D56" s="23" t="n">
-        <v>94.91500000000001</v>
+        <v>94.895</v>
       </c>
       <c r="E56" s="15">
         <f>(100-D56)/100</f>
         <v/>
       </c>
       <c r="F56" s="24" t="n">
-        <v>21.84</v>
+        <v>21.83</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.0508186</v>
+        <v>0.0510186</v>
       </c>
       <c r="H56" s="24" t="n">
         <v>-0.314</v>
@@ -7260,17 +7260,17 @@
         <v>49480</v>
       </c>
       <c r="D57" s="23" t="n">
-        <v>94.905</v>
+        <v>94.88500000000001</v>
       </c>
       <c r="E57" s="15">
         <f>(100-D57)/100</f>
         <v/>
       </c>
       <c r="F57" s="24" t="n">
-        <v>23.01</v>
+        <v>23</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.0509718</v>
+        <v>0.0511718</v>
       </c>
       <c r="H57" s="24" t="n">
         <v>0.218</v>
@@ -7292,17 +7292,17 @@
         <v>49571</v>
       </c>
       <c r="D58" s="23" t="n">
-        <v>94.88</v>
+        <v>94.86</v>
       </c>
       <c r="E58" s="15">
         <f>(100-D58)/100</f>
         <v/>
       </c>
       <c r="F58" s="24" t="n">
-        <v>24.2</v>
+        <v>24.19</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.05118420000000001</v>
+        <v>0.0513842</v>
       </c>
       <c r="H58" s="24" t="n">
         <v>-0.158</v>
@@ -7324,17 +7324,17 @@
         <v>49662</v>
       </c>
       <c r="D59" s="23" t="n">
-        <v>94.855</v>
+        <v>94.83499999999999</v>
       </c>
       <c r="E59" s="15">
         <f>(100-D59)/100</f>
         <v/>
       </c>
       <c r="F59" s="24" t="n">
-        <v>25.41</v>
+        <v>25.4</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.0514687</v>
+        <v>0.0516687</v>
       </c>
       <c r="H59" s="24" t="n">
         <v>0.187</v>
@@ -7356,17 +7356,17 @@
         <v>49753</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>94.81</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="E60" s="15">
         <f>(100-D60)/100</f>
         <v/>
       </c>
       <c r="F60" s="24" t="n">
-        <v>26.64</v>
+        <v>26.62</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.05188329999999999</v>
+        <v>0.0520833</v>
       </c>
       <c r="H60" s="24" t="n">
         <v>-0.167</v>
@@ -7388,17 +7388,17 @@
         <v>49844</v>
       </c>
       <c r="D61" s="23" t="n">
-        <v>94.8</v>
+        <v>94.78</v>
       </c>
       <c r="E61" s="15">
         <f>(100-D61)/100</f>
         <v/>
       </c>
       <c r="F61" s="24" t="n">
-        <v>27.89</v>
+        <v>27.87</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.0520058</v>
+        <v>0.0522058</v>
       </c>
       <c r="H61" s="24" t="n">
         <v>0.058</v>
@@ -7410,7 +7410,7 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Fit: 58 contracts, RMS residual 0.173 bp, max 0.582 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
+          <t>Fit: 58 contracts, RMS residual 0.205 bp, max 0.621 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7453,7 +7453,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B4" s="26" t="n">
         <v>0.0388</v>
@@ -7461,55 +7461,55 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B8" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B9" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B10" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B11" s="26" t="n">
         <v>0.0387</v>
@@ -7517,71 +7517,71 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B12" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B13" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B14" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B15" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B16" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B17" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B18" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B19" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B20" s="26" t="n">
         <v>0.039</v>
@@ -7589,23 +7589,23 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B21" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B22" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B23" s="26" t="n">
         <v>0.0387</v>
@@ -7613,15 +7613,15 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B24" s="26" t="n">
-        <v>0.0385</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B25" s="26" t="n">
         <v>0.0385</v>
@@ -7629,7 +7629,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B26" s="26" t="n">
         <v>0.0385</v>
@@ -7637,31 +7637,31 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B27" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B28" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B29" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B30" s="26" t="n">
         <v>0.0362</v>
@@ -7669,7 +7669,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B31" s="26" t="n">
         <v>0.0362</v>
@@ -7677,15 +7677,15 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B32" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B33" s="26" t="n">
         <v>0.0364</v>
@@ -7693,63 +7693,63 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B34" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B35" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B36" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B37" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B38" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B39" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B40" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B41" s="26" t="n">
         <v>0.0364</v>
@@ -7757,23 +7757,23 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B42" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B43" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B44" s="26" t="n">
         <v>0.0365</v>
@@ -7781,47 +7781,47 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B45" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B48" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B49" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B50" s="26" t="n">
         <v>0.0362</v>
@@ -7829,7 +7829,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B51" s="26" t="n">
         <v>0.0362</v>
@@ -7837,79 +7837,79 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B52" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B53" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B54" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B55" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B56" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B57" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B58" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B59" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B60" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B61" s="26" t="n">
         <v>0.0365</v>
@@ -7917,7 +7917,7 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B62" s="26" t="n">
         <v>0.0365</v>
@@ -7925,15 +7925,15 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B63" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B64" s="26" t="n">
         <v>0.0364</v>
@@ -7941,7 +7941,7 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B65" s="26" t="n">
         <v>0.0364</v>
@@ -7949,143 +7949,143 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B66" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B67" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B68" s="26" t="n">
-        <v>0.0357</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B69" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.0357</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B70" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B71" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B72" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B73" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B74" s="26" t="n">
-        <v>0.0355</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B75" s="26" t="n">
-        <v>0.0353</v>
+        <v>0.0355</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B76" s="26" t="n">
-        <v>0.0358</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B77" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B78" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B79" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B80" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B81" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B82" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B83" s="26" t="n">
         <v>0.0362</v>
@@ -8093,23 +8093,23 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B84" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B85" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B86" s="26" t="n">
         <v>0.0362</v>
@@ -8117,31 +8117,31 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B87" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B88" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B89" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B90" s="26" t="n">
         <v>0.0363</v>
@@ -8149,55 +8149,55 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B91" s="26" t="n">
-        <v>0.0369</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B92" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B93" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B94" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B95" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B96" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B97" s="26" t="n">
         <v>0.0363</v>
@@ -8205,65 +8205,73 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B98" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B99" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B100" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B101" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B102" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B103" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B104" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B105" s="26" t="n">
+        <v>0.0363</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="B105" s="26" t="n">
+      <c r="B106" s="26" t="n">
         <v>0.0363</v>
       </c>
     </row>

--- a/output/downloads/sofr-forward-curve.xlsx
+++ b/output/downloads/sofr-forward-curve.xlsx
@@ -236,7 +236,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SOFR forward curve, 2026-10-21</a:t>
+              <a:t>SOFR forward curve, 2026-10-22</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="3">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>on 2026-10-21 (NY Fed)</t>
+          <t>on 2026-10-22 (NY Fed)</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22 17:59 UTC</t>
+          <t>2026-10-23 17:53 UTC</t>
         </is>
       </c>
     </row>
@@ -855,13 +855,13 @@
         <v>31</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.038938</v>
+        <v>0.0389247</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>0.0388771</v>
+        <v>0.0388639</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>0.0389378</v>
+        <v>0.0389246</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0</v>
@@ -891,13 +891,13 @@
         <v>30</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.0394274</v>
+        <v>0.0392366</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.0393669</v>
+        <v>0.0391767</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>0.0394272</v>
+        <v>0.0392365</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.0410912</v>
+        <v>0.0406874</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>0.04102330000000001</v>
+        <v>0.0406208</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0.041092</v>
+        <v>0.04068819999999999</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>0.01</v>
@@ -963,13 +963,13 @@
         <v>31</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.0419135</v>
+        <v>0.0413587</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.0418433</v>
+        <v>0.0412904</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>0.0419151</v>
+        <v>0.0413603</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>0.02</v>
@@ -999,13 +999,13 @@
         <v>28</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.042871</v>
+        <v>0.0418852</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.04280490000000001</v>
+        <v>0.0418221</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0.0428748</v>
+        <v>0.0418889</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>0.04</v>
@@ -1035,13 +1035,13 @@
         <v>31</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.04368</v>
+        <v>0.042459</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.0436033</v>
+        <v>0.0423865</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0.043686</v>
+        <v>0.0424649</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>0.06</v>
@@ -1071,13 +1071,13 @@
         <v>30</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.04472019999999999</v>
+        <v>0.0431895</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>0.0446421</v>
+        <v>0.0431166</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>0.04472909999999999</v>
+        <v>0.0431982</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>0.09</v>
@@ -1107,13 +1107,13 @@
         <v>31</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.04569619999999999</v>
+        <v>0.0438212</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.0456124</v>
+        <v>0.0437441</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.0457085</v>
+        <v>0.04383339999999999</v>
       </c>
       <c r="G19" s="13" t="n">
         <v>0.12</v>
@@ -1143,16 +1143,16 @@
         <v>30</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.0464663</v>
+        <v>0.04445350000000001</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>0.0463826</v>
+        <v>0.0443768</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0.0464839</v>
+        <v>0.044471</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
@@ -1179,16 +1179,16 @@
         <v>31</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.04683760000000001</v>
+        <v>0.0447606</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.0467496</v>
+        <v>0.0446802</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.0468582</v>
+        <v>0.044781</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
@@ -1215,13 +1215,13 @@
         <v>31</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.0471845</v>
+        <v>0.0450629</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.0470944</v>
+        <v>0.04498070000000001</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0.0472112</v>
+        <v>0.0450894</v>
       </c>
       <c r="G22" s="13" t="n">
         <v>0.27</v>
@@ -1251,13 +1251,13 @@
         <v>30</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.0474094</v>
+        <v>0.0452432</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.0473222</v>
+        <v>0.0451638</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.0474413</v>
+        <v>0.0452749</v>
       </c>
       <c r="G23" s="13" t="n">
         <v>0.32</v>
@@ -1287,13 +1287,13 @@
         <v>31</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.047641</v>
+        <v>0.045429</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>0.0475504</v>
+        <v>0.0453465</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0.047679</v>
+        <v>0.0454668</v>
       </c>
       <c r="G24" s="13" t="n">
         <v>0.38</v>
@@ -1323,16 +1323,16 @@
         <v>30</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.0476404</v>
+        <v>0.0454241</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.0475521</v>
+        <v>0.0453439</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0.04768500000000001</v>
+        <v>0.0454685</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
@@ -1359,13 +1359,13 @@
         <v>31</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.04756879999999999</v>
+        <v>0.0453392</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.04747779999999999</v>
+        <v>0.0452565</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0.0476206</v>
+        <v>0.0453908</v>
       </c>
       <c r="G26" s="13" t="n">
         <v>0.52</v>
@@ -1395,13 +1395,13 @@
         <v>31</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.0475324</v>
+        <v>0.0453007</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>0.0474418</v>
+        <v>0.0452183</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0.04758880000000001</v>
+        <v>0.0453569</v>
       </c>
       <c r="G27" s="13" t="n">
         <v>0.5600000000000001</v>
@@ -1431,13 +1431,13 @@
         <v>29</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.0474732</v>
+        <v>0.0452546</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>0.047389</v>
+        <v>0.0451781</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>0.0475401</v>
+        <v>0.0453213</v>
       </c>
       <c r="G28" s="13" t="n">
         <v>0.67</v>
@@ -1467,16 +1467,16 @@
         <v>31</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.0474113</v>
+        <v>0.0451411</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>0.0473203</v>
+        <v>0.0450586</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.0474859</v>
+        <v>0.0452154</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
@@ -1503,16 +1503,16 @@
         <v>30</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>0.0473399</v>
+        <v>0.04506300000000001</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>0.0472532</v>
+        <v>0.04498440000000001</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0.0474235</v>
+        <v>0.0451463</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
@@ -1539,13 +1539,13 @@
         <v>31</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>0.04726689999999999</v>
+        <v>0.0449843</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0.0471771</v>
+        <v>0.0449029</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.04736100000000001</v>
+        <v>0.0450781</v>
       </c>
       <c r="G31" s="13" t="n">
         <v>0.9399999999999999</v>
@@ -1575,13 +1575,13 @@
         <v>30</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.047194</v>
+        <v>0.0449101</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>0.0471076</v>
+        <v>0.0448318</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0.0472982</v>
+        <v>0.04501400000000001</v>
       </c>
       <c r="G32" s="13" t="n">
         <v>1.04</v>
@@ -1611,13 +1611,13 @@
         <v>31</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.0471356</v>
+        <v>0.0448522</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>0.047046</v>
+        <v>0.04477109999999999</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0.0472497</v>
+        <v>0.044966</v>
       </c>
       <c r="G33" s="13" t="n">
         <v>1.14</v>
@@ -1647,16 +1647,16 @@
         <v>31</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.0470703</v>
+        <v>0.04478869999999999</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>0.0469806</v>
+        <v>0.0447074</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0.0471961</v>
+        <v>0.0449141</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
@@ -1683,13 +1683,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.04700770000000001</v>
+        <v>0.0447276</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>0.0469222</v>
+        <v>0.04465010000000001</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0.047145</v>
+        <v>0.04486449999999999</v>
       </c>
       <c r="G35" s="13" t="n">
         <v>1.37</v>
@@ -1719,13 +1719,13 @@
         <v>31</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>0.0469524</v>
+        <v>0.0446712</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>0.0468637</v>
+        <v>0.0445909</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0.0471012</v>
+        <v>0.0448197</v>
       </c>
       <c r="G36" s="13" t="n">
         <v>1.49</v>
@@ -1755,16 +1755,16 @@
         <v>30</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.0468796</v>
+        <v>0.0445959</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>0.046794</v>
+        <v>0.0445184</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0.0470413</v>
+        <v>0.04475730000000001</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
@@ -1791,16 +1791,16 @@
         <v>31</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>0.0468051</v>
+        <v>0.0445179</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>0.0467175</v>
+        <v>0.0444388</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0.0469797</v>
+        <v>0.0446923</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
@@ -1827,16 +1827,16 @@
         <v>31</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0.0467254</v>
+        <v>0.0444381</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0.04663750000000001</v>
+        <v>0.0443587</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0.04691290000000001</v>
+        <v>0.0446253</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
@@ -1863,16 +1863,16 @@
         <v>28</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>0.0466285</v>
+        <v>0.04434879999999999</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>0.0465504</v>
+        <v>0.0442781</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0.04683010000000001</v>
+        <v>0.04455</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>31</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.0465544</v>
+        <v>0.044288</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.0464672</v>
+        <v>0.0442091</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0.0467701</v>
+        <v>0.0445033</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
@@ -1935,16 +1935,16 @@
         <v>30</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>0.0464745</v>
+        <v>0.0442275</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>0.0463901</v>
+        <v>0.04415110000000001</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0.0467042</v>
+        <v>0.0444569</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
@@ -1971,13 +1971,13 @@
         <v>31</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.0463988</v>
+        <v>0.04417430000000001</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.0463122</v>
+        <v>0.0440958</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.0466442</v>
+        <v>0.0444194</v>
       </c>
       <c r="G43" s="13" t="n">
         <v>2.45</v>
@@ -2007,13 +2007,13 @@
         <v>30</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.0463257</v>
+        <v>0.0441223</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>0.0462422</v>
+        <v>0.0440466</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0.046587</v>
+        <v>0.0443832</v>
       </c>
       <c r="G44" s="13" t="n">
         <v>2.61</v>
@@ -2043,13 +2043,13 @@
         <v>31</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.0462665</v>
+        <v>0.0440786</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.04618000000000001</v>
+        <v>0.0440001</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0.0465436</v>
+        <v>0.0443553</v>
       </c>
       <c r="G45" s="13" t="n">
         <v>2.77</v>
@@ -2079,13 +2079,13 @@
         <v>31</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.0462059</v>
+        <v>0.0440278</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>0.0461195</v>
+        <v>0.0439493</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0.0465002</v>
+        <v>0.0443217</v>
       </c>
       <c r="G46" s="13" t="n">
         <v>2.94</v>
@@ -2115,13 +2115,13 @@
         <v>30</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.0461545</v>
+        <v>0.0439785</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.0460719</v>
+        <v>0.0439034</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.046464</v>
+        <v>0.0442875</v>
       </c>
       <c r="G47" s="13" t="n">
         <v>3.09</v>
@@ -2151,13 +2151,13 @@
         <v>31</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.0461045</v>
+        <v>0.0439247</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>0.0460191</v>
+        <v>0.0438471</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0.04643290000000001</v>
+        <v>0.0442526</v>
       </c>
       <c r="G48" s="13" t="n">
         <v>3.28</v>
@@ -2187,13 +2187,13 @@
         <v>30</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.0460586</v>
+        <v>0.0438727</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>0.0459765</v>
+        <v>0.0437982</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0.0464046</v>
+        <v>0.04421820000000001</v>
       </c>
       <c r="G49" s="13" t="n">
         <v>3.46</v>
@@ -2223,16 +2223,16 @@
         <v>31</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.0460266</v>
+        <v>0.04383600000000001</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>0.0459412</v>
+        <v>0.0437585</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0.0463896</v>
+        <v>0.0441985</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
@@ -2259,13 +2259,13 @@
         <v>31</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.04599230000000001</v>
+        <v>0.0438029</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>0.0459072</v>
+        <v>0.0437257</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>0.0463743</v>
+        <v>0.04418440000000001</v>
       </c>
       <c r="G51" s="13" t="n">
         <v>3.82</v>
@@ -2295,13 +2295,13 @@
         <v>28</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.0459545</v>
+        <v>0.04377710000000001</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>0.0458786</v>
+        <v>0.0437082</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0.0463558</v>
+        <v>0.0441779</v>
       </c>
       <c r="G52" s="13" t="n">
         <v>4.01</v>
@@ -2331,16 +2331,16 @@
         <v>31</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.0459412</v>
+        <v>0.0437813</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.0458563</v>
+        <v>0.0437042</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.0463619</v>
+        <v>0.0442015</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
@@ -2367,13 +2367,13 @@
         <v>30</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>0.0459209</v>
+        <v>0.0437803</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>0.0458391</v>
+        <v>0.0437059</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>0.0463612</v>
+        <v>0.04422010000000001</v>
       </c>
       <c r="G54" s="13" t="n">
         <v>4.4</v>
@@ -2403,16 +2403,16 @@
         <v>31</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>0.0459116</v>
+        <v>0.0437825</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.0458268</v>
+        <v>0.0437054</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.0463721</v>
+        <v>0.0442426</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
@@ -2439,16 +2439,16 @@
         <v>30</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>0.0459019</v>
+        <v>0.0437753</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>0.04582</v>
+        <v>0.0437008</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>0.0463818</v>
+        <v>0.0442547</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
@@ -2475,13 +2475,13 @@
         <v>31</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>0.0459027</v>
+        <v>0.0437727</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.0458176</v>
+        <v>0.0436953</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.0464051</v>
+        <v>0.0442746</v>
       </c>
       <c r="G57" s="13" t="n">
         <v>5.02</v>
@@ -2511,16 +2511,16 @@
         <v>31</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>0.0459065</v>
+        <v>0.0437729</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>0.0458213</v>
+        <v>0.04369550000000001</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0.0464302</v>
+        <v>0.0442961</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
@@ -2547,16 +2547,16 @@
         <v>30</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>0.0459117</v>
+        <v>0.0437773</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.0458296</v>
+        <v>0.0437026</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.0464557</v>
+        <v>0.0443207</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>5.44</v>
+        <v>5.43</v>
       </c>
       <c r="H59" s="14" t="inlineStr">
         <is>
@@ -2583,16 +2583,16 @@
         <v>31</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.04592769999999999</v>
+        <v>0.0437935</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>0.0458428</v>
+        <v>0.0437163</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0.0464953</v>
+        <v>0.0443606</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>5.68</v>
+        <v>5.67</v>
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>30</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>0.0459403</v>
+        <v>0.043807</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>0.04585880000000001</v>
+        <v>0.0437329</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0.04653069999999999</v>
+        <v>0.044397</v>
       </c>
       <c r="G61" s="13" t="n">
         <v>5.9</v>
@@ -2655,13 +2655,13 @@
         <v>31</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>0.0459646</v>
+        <v>0.0438312</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>0.0458792</v>
+        <v>0.0437536</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0.0465778</v>
+        <v>0.044444</v>
       </c>
       <c r="G62" s="13" t="n">
         <v>6.13</v>
@@ -2691,16 +2691,16 @@
         <v>31</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>0.0459946</v>
+        <v>0.0438616</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>0.04590950000000001</v>
+        <v>0.0437842</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0.0466316</v>
+        <v>0.0444979</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>6.37</v>
+        <v>6.36</v>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
@@ -2727,13 +2727,13 @@
         <v>28</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>0.0460276</v>
+        <v>0.043896</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>0.0459511</v>
+        <v>0.0438264</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>0.0466869</v>
+        <v>0.0445548</v>
       </c>
       <c r="G64" s="13" t="n">
         <v>6.59</v>
@@ -2763,13 +2763,13 @@
         <v>31</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>0.046092</v>
+        <v>0.04396029999999999</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>0.0460062</v>
+        <v>0.0438822</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0.0467752</v>
+        <v>0.0446429</v>
       </c>
       <c r="G65" s="13" t="n">
         <v>6.83</v>
@@ -2799,13 +2799,13 @@
         <v>30</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>0.0461548</v>
+        <v>0.04402250000000001</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>0.0460722</v>
+        <v>0.0439473</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0.046863</v>
+        <v>0.0447302</v>
       </c>
       <c r="G66" s="13" t="n">
         <v>7.08</v>
@@ -2835,16 +2835,16 @@
         <v>31</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>0.04622080000000001</v>
+        <v>0.0440849</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>0.0461351</v>
+        <v>0.0440069</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>0.0469534</v>
+        <v>0.04481690000000001</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>7.33</v>
+        <v>7.32</v>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
@@ -2871,16 +2871,16 @@
         <v>30</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>0.0462765</v>
+        <v>0.0441373</v>
       </c>
       <c r="E68" s="12" t="n">
-        <v>0.046193</v>
+        <v>0.0440613</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0.0470332</v>
+        <v>0.0448935</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>7.57</v>
+        <v>7.56</v>
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
@@ -2907,13 +2907,13 @@
         <v>31</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>0.0463375</v>
+        <v>0.04419940000000001</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>0.0462511</v>
+        <v>0.04412079999999999</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0.0471209</v>
+        <v>0.0449823</v>
       </c>
       <c r="G69" s="13" t="n">
         <v>7.83</v>
@@ -2943,16 +2943,16 @@
         <v>31</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>0.0463913</v>
+        <v>0.0442641</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>0.04630480000000001</v>
+        <v>0.0441853</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>0.04720100000000001</v>
+        <v>0.0450732</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>8.1</v>
+        <v>8.09</v>
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
@@ -2979,13 +2979,13 @@
         <v>30</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>0.0464408</v>
+        <v>0.044332</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>0.0463566</v>
+        <v>0.04425519999999999</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0.047276</v>
+        <v>0.0451666</v>
       </c>
       <c r="G71" s="13" t="n">
         <v>8.35</v>
@@ -3015,16 +3015,16 @@
         <v>31</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>0.0465025</v>
+        <v>0.044413</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>0.0464156</v>
+        <v>0.0443337</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0.0473654</v>
+        <v>0.0452753</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>8.630000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
@@ -3051,16 +3051,16 @@
         <v>30</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>0.0465593</v>
+        <v>0.0444804</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>0.0464752</v>
+        <v>0.0444037</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0.0474473</v>
+        <v>0.0453679</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>8.880000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         <v>31</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>0.0466383</v>
+        <v>0.0445617</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>0.0465505</v>
+        <v>0.0444815</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0.0475557</v>
+        <v>0.04547850000000001</v>
       </c>
       <c r="G74" s="13" t="n">
         <v>9.17</v>
@@ -3123,13 +3123,13 @@
         <v>31</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>0.0467118</v>
+        <v>0.04463180000000001</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>0.0466242</v>
+        <v>0.0445518</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0.0476559</v>
+        <v>0.0455753</v>
       </c>
       <c r="G75" s="13" t="n">
         <v>9.44</v>
@@ -3159,16 +3159,16 @@
         <v>29</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>0.0467837</v>
+        <v>0.0447007</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>0.0467019</v>
+        <v>0.044626</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>0.0477554</v>
+        <v>0.0456718</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
@@ -3195,16 +3195,16 @@
         <v>31</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>0.0468681</v>
+        <v>0.0447833</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>0.0467797</v>
+        <v>0.0447027</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0.0478692</v>
+        <v>0.0457838</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="H77" s="14" t="inlineStr">
         <is>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>0.0469333</v>
+        <v>0.04484950000000001</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>0.04684720000000001</v>
+        <v>0.0447709</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0.0479627</v>
+        <v>0.0458784</v>
       </c>
       <c r="G78" s="13" t="n">
         <v>10.29</v>
@@ -3267,16 +3267,16 @@
         <v>31</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>0.0469893</v>
+        <v>0.0449062</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0.0469007</v>
+        <v>0.0448253</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0.0480459</v>
+        <v>0.04596219999999999</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>10.57</v>
+        <v>10.56</v>
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
@@ -3303,16 +3303,16 @@
         <v>30</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>0.0470407</v>
+        <v>0.0449583</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>0.0469548</v>
+        <v>0.0448798</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0.0481282</v>
+        <v>0.0460453</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>10.88</v>
+        <v>10.87</v>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
@@ -3339,13 +3339,13 @@
         <v>31</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>0.0470966</v>
+        <v>0.0450138</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>0.0470076</v>
+        <v>0.0449325</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0.0482139</v>
+        <v>0.0461305</v>
       </c>
       <c r="G81" s="13" t="n">
         <v>11.17</v>
@@ -3375,13 +3375,13 @@
         <v>31</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>0.04715830000000001</v>
+        <v>0.0450753</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>0.0470682</v>
+        <v>0.044993</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0.0483045</v>
+        <v>0.0462209</v>
       </c>
       <c r="G82" s="13" t="n">
         <v>11.46</v>
@@ -3411,13 +3411,13 @@
         <v>30</v>
       </c>
       <c r="D83" s="12" t="n">
-        <v>0.04722800000000001</v>
+        <v>0.0451452</v>
       </c>
       <c r="E83" s="12" t="n">
-        <v>0.04714140000000001</v>
+        <v>0.0450661</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0.0484051</v>
+        <v>0.0463218</v>
       </c>
       <c r="G83" s="13" t="n">
         <v>11.77</v>
@@ -3447,16 +3447,16 @@
         <v>31</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>0.0473005</v>
+        <v>0.0452176</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>0.04721110000000001</v>
+        <v>0.0451359</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0.0485084</v>
+        <v>0.0464249</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>12.08</v>
+        <v>12.07</v>
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
@@ -3483,16 +3483,16 @@
         <v>30</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>0.0473576</v>
+        <v>0.045275</v>
       </c>
       <c r="E85" s="12" t="n">
-        <v>0.0472704</v>
+        <v>0.04519529999999999</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>0.0485964</v>
+        <v>0.0465133</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>12.39</v>
+        <v>12.38</v>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         <v>31</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>0.0474107</v>
+        <v>0.0453279</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>0.0473203</v>
+        <v>0.0452453</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>0.0486812</v>
+        <v>0.0465979</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>12.71</v>
+        <v>12.7</v>
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
@@ -3555,13 +3555,13 @@
         <v>31</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>0.0474585</v>
+        <v>0.0453757</v>
       </c>
       <c r="E87" s="12" t="n">
-        <v>0.0473681</v>
+        <v>0.0452931</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0.0487587</v>
+        <v>0.0466753</v>
       </c>
       <c r="G87" s="13" t="n">
         <v>13</v>
@@ -3591,13 +3591,13 @@
         <v>28</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>0.0475134</v>
+        <v>0.0454312</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>0.0474322</v>
+        <v>0.0453571</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0.0488468</v>
+        <v>0.0467641</v>
       </c>
       <c r="G88" s="13" t="n">
         <v>13.33</v>
@@ -3627,16 +3627,16 @@
         <v>31</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>0.0475934</v>
+        <v>0.0455103</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>0.0475017</v>
+        <v>0.0454265</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>0.0489591</v>
+        <v>0.0468754</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>13.66</v>
+        <v>13.65</v>
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         <v>30</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>0.0476571</v>
+        <v>0.0455745</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>0.0475692</v>
+        <v>0.0454941</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0.0490543</v>
+        <v>0.0469711</v>
       </c>
       <c r="G90" s="13" t="n">
         <v>13.97</v>
@@ -3699,13 +3699,13 @@
         <v>31</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>0.0477137</v>
+        <v>0.0456313</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>0.04762209999999999</v>
+        <v>0.0455475</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>0.0491419</v>
+        <v>0.0470589</v>
       </c>
       <c r="G91" s="13" t="n">
         <v>14.28</v>
@@ -3735,13 +3735,13 @@
         <v>30</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>0.04775260000000001</v>
+        <v>0.0456713</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>0.04766409999999999</v>
+        <v>0.0455904</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>0.0492139</v>
+        <v>0.04713199999999999</v>
       </c>
       <c r="G92" s="13" t="n">
         <v>14.61</v>
@@ -3771,13 +3771,13 @@
         <v>31</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>0.04778839999999999</v>
+        <v>0.0457076</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>0.0476972</v>
+        <v>0.0456241</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>0.04928270000000001</v>
+        <v>0.0472014</v>
       </c>
       <c r="G93" s="13" t="n">
         <v>14.94</v>
@@ -3807,13 +3807,13 @@
         <v>31</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>0.0478257</v>
+        <v>0.0457451</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>0.0477331</v>
+        <v>0.04566029999999999</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>0.0493537</v>
+        <v>0.0472726</v>
       </c>
       <c r="G94" s="13" t="n">
         <v>15.28</v>
@@ -3843,13 +3843,13 @@
         <v>30</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>0.0478679</v>
+        <v>0.0457873</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>0.0477791</v>
+        <v>0.045706</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>0.0494302</v>
+        <v>0.04734910000000001</v>
       </c>
       <c r="G95" s="13" t="n">
         <v>15.62</v>
@@ -3879,13 +3879,13 @@
         <v>31</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>0.04792779999999999</v>
+        <v>0.04584609999999999</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>0.0478356</v>
+        <v>0.0457617</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>0.0495233</v>
+        <v>0.047441</v>
       </c>
       <c r="G96" s="13" t="n">
         <v>15.95</v>
@@ -3915,13 +3915,13 @@
         <v>30</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>0.048002</v>
+        <v>0.0459193</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>0.0479129</v>
+        <v>0.0458377</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>0.04963530000000001</v>
+        <v>0.047552</v>
       </c>
       <c r="G97" s="13" t="n">
         <v>16.33</v>
@@ -3951,13 +3951,13 @@
         <v>31</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>0.0480798</v>
+        <v>0.0459956</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>0.0479871</v>
+        <v>0.0459107</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>0.0497492</v>
+        <v>0.0476644</v>
       </c>
       <c r="G98" s="13" t="n">
         <v>16.69</v>
@@ -3987,13 +3987,13 @@
         <v>31</v>
       </c>
       <c r="D99" s="12" t="n">
-        <v>0.048129</v>
+        <v>0.0460443</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>0.048036</v>
+        <v>0.0459592</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>0.0498314</v>
+        <v>0.0477461</v>
       </c>
       <c r="G99" s="13" t="n">
         <v>17.02</v>
@@ -4023,13 +4023,13 @@
         <v>28</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>0.048136</v>
+        <v>0.0460528</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>0.0480527</v>
+        <v>0.04597660000000001</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>0.0498742</v>
+        <v>0.0477905</v>
       </c>
       <c r="G100" s="13" t="n">
         <v>17.38</v>
@@ -4059,16 +4059,16 @@
         <v>31</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>0.0481323</v>
+        <v>0.0460498</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>0.0480385</v>
+        <v>0.0459639</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>0.0499049</v>
+        <v>0.0478219</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>17.73</v>
+        <v>17.72</v>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
@@ -4095,13 +4095,13 @@
         <v>30</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>0.04812540000000001</v>
+        <v>0.0460447</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>0.04803569999999999</v>
+        <v>0.0459626</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>0.0499294</v>
+        <v>0.0478482</v>
       </c>
       <c r="G102" s="13" t="n">
         <v>18.04</v>
@@ -4131,16 +4131,16 @@
         <v>31</v>
       </c>
       <c r="D103" s="12" t="n">
-        <v>0.0481672</v>
+        <v>0.0460869</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>0.0480739</v>
+        <v>0.0460015</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>0.0500091</v>
+        <v>0.04792830000000001</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>18.42</v>
+        <v>18.41</v>
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
@@ -4167,13 +4167,13 @@
         <v>30</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>0.0482406</v>
+        <v>0.0461602</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>0.0481503</v>
+        <v>0.0460775</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>0.050119</v>
+        <v>0.0480381</v>
       </c>
       <c r="G104" s="13" t="n">
         <v>18.78</v>
@@ -4203,16 +4203,16 @@
         <v>31</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>0.048314</v>
+        <v>0.0462323</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>0.0482199</v>
+        <v>0.0461461</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>0.050228</v>
+        <v>0.0481458</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>19.14</v>
+        <v>19.13</v>
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
@@ -4239,13 +4239,13 @@
         <v>31</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>0.0483469</v>
+        <v>0.0462643</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>0.0482522</v>
+        <v>0.0461776</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>0.05030109999999999</v>
+        <v>0.0482179</v>
       </c>
       <c r="G106" s="13" t="n">
         <v>19.54</v>
@@ -4275,13 +4275,13 @@
         <v>30</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>0.0483247</v>
+        <v>0.0462423</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>0.0482344</v>
+        <v>0.0461595</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>0.0503159</v>
+        <v>0.0482329</v>
       </c>
       <c r="G107" s="13" t="n">
         <v>19.91</v>
@@ -4311,13 +4311,13 @@
         <v>31</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>0.0483162</v>
+        <v>0.0462336</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>0.0482223</v>
+        <v>0.0461477</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>0.0503436</v>
+        <v>0.0482605</v>
       </c>
       <c r="G108" s="13" t="n">
         <v>20.27</v>
@@ -4347,16 +4347,16 @@
         <v>30</v>
       </c>
       <c r="D109" s="12" t="n">
-        <v>0.0483645</v>
+        <v>0.0462825</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>0.0482734</v>
+        <v>0.046199</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>0.0504303</v>
+        <v>0.0483478</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>20.66</v>
+        <v>20.65</v>
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
@@ -4383,16 +4383,16 @@
         <v>31</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>0.04848499999999999</v>
+        <v>0.0464029</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>0.0483911</v>
+        <v>0.04631680000000001</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>0.0505888</v>
+        <v>0.0485062</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>21.04</v>
+        <v>21.03</v>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
@@ -4419,16 +4419,16 @@
         <v>31</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0.0486119</v>
+        <v>0.0465297</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>0.0485168</v>
+        <v>0.0464426</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>0.0507526</v>
+        <v>0.0486699</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>21.41</v>
+        <v>21.4</v>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
@@ -4455,13 +4455,13 @@
         <v>28</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0.04868140000000001</v>
+        <v>0.0466001</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>0.0485963</v>
+        <v>0.04652199999999999</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>0.0508605</v>
+        <v>0.0487786</v>
       </c>
       <c r="G112" s="13" t="n">
         <v>21.79</v>
@@ -4491,16 +4491,16 @@
         <v>31</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.0486975</v>
+        <v>0.0466153</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>0.0486024</v>
+        <v>0.0465281</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>0.0509155</v>
+        <v>0.0488328</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>22.18</v>
+        <v>22.17</v>
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>30</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0.0486672</v>
+        <v>0.0465852</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>0.0485747</v>
+        <v>0.0465004</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>0.05092190000000001</v>
+        <v>0.04883949999999999</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>22.55</v>
+        <v>22.54</v>
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
@@ -4563,13 +4563,13 @@
         <v>31</v>
       </c>
       <c r="D115" s="12" t="n">
-        <v>0.0486603</v>
+        <v>0.0465781</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>0.048565</v>
+        <v>0.0464909</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>0.0509556</v>
+        <v>0.048873</v>
       </c>
       <c r="G115" s="13" t="n">
         <v>22.95</v>
@@ -4599,16 +4599,16 @@
         <v>30</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>0.0486883</v>
+        <v>0.0466064</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>0.0485961</v>
+        <v>0.04652199999999999</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>0.0510232</v>
+        <v>0.0489409</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>23.35</v>
+        <v>23.34</v>
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
@@ -4635,13 +4635,13 @@
         <v>31</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>0.0487433</v>
+        <v>0.0466612</v>
       </c>
       <c r="E117" s="12" t="n">
-        <v>0.0486474</v>
+        <v>0.0465732</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>0.05111760000000001</v>
+        <v>0.0490349</v>
       </c>
       <c r="G117" s="13" t="n">
         <v>23.74</v>
@@ -4671,16 +4671,16 @@
         <v>31</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>0.04878999999999999</v>
+        <v>0.0467079</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>0.0486936</v>
+        <v>0.0466195</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>0.0512057</v>
+        <v>0.049123</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>24.16</v>
+        <v>24.15</v>
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
@@ -4707,13 +4707,13 @@
         <v>30</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>0.04881509999999999</v>
+        <v>0.04673339999999999</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>0.0487227</v>
+        <v>0.0466486</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>0.0512662</v>
+        <v>0.049184</v>
       </c>
       <c r="G119" s="13" t="n">
         <v>24.51</v>
@@ -4743,13 +4743,13 @@
         <v>31</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>0.0488681</v>
+        <v>0.0467861</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>0.0487721</v>
+        <v>0.0466981</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>0.0513635</v>
+        <v>0.049281</v>
       </c>
       <c r="G120" s="13" t="n">
         <v>24.95</v>
@@ -4779,13 +4779,13 @@
         <v>30</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>0.0489517</v>
+        <v>0.04687</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>0.0488589</v>
+        <v>0.04678499999999999</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>0.051487</v>
+        <v>0.04940489999999999</v>
       </c>
       <c r="G121" s="13" t="n">
         <v>25.35</v>
@@ -4815,13 +4815,13 @@
         <v>31</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.0490702</v>
+        <v>0.0469883</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>0.04897319999999999</v>
+        <v>0.0468993</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>0.0516443</v>
+        <v>0.04956190000000001</v>
       </c>
       <c r="G122" s="13" t="n">
         <v>25.74</v>
@@ -4851,16 +4851,16 @@
         <v>31</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>0.0491933</v>
+        <v>0.0471114</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>0.049096</v>
+        <v>0.0470221</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>0.05180990000000001</v>
+        <v>0.04972749999999999</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>26.17</v>
+        <v>26.16</v>
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
@@ -4887,13 +4887,13 @@
         <v>29</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>0.0492635</v>
+        <v>0.0471821</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>0.0491728</v>
+        <v>0.047099</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>0.0519219</v>
+        <v>0.0498401</v>
       </c>
       <c r="G124" s="13" t="n">
         <v>26.58</v>
@@ -4923,16 +4923,16 @@
         <v>31</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>0.0492829</v>
+        <v>0.04720100000000001</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>0.0491848</v>
+        <v>0.047111</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>0.0519806</v>
+        <v>0.0498982</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>26.98</v>
+        <v>26.97</v>
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>30</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>0.0492469</v>
+        <v>0.04716529999999999</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>0.0491528</v>
+        <v>0.047079</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>0.0519876</v>
+        <v>0.0499056</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>27.41</v>
+        <v>27.4</v>
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
@@ -4995,13 +4995,13 @@
         <v>31</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>0.0491965</v>
+        <v>0.0471146</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>0.04909939999999999</v>
+        <v>0.0470255</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>0.0519784</v>
+        <v>0.0498961</v>
       </c>
       <c r="G127" s="13" t="n">
         <v>27.82</v>
@@ -5031,13 +5031,13 @@
         <v>30</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>0.0491368</v>
+        <v>0.0470552</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>0.0490427</v>
+        <v>0.0469689</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>0.0519578</v>
+        <v>0.0498758</v>
       </c>
       <c r="G128" s="13" t="n">
         <v>28.21</v>
@@ -5067,16 +5067,16 @@
         <v>31</v>
       </c>
       <c r="D129" s="18" t="n">
-        <v>0.0491378</v>
+        <v>0.04705599999999999</v>
       </c>
       <c r="E129" s="18" t="n">
-        <v>0.0490408</v>
+        <v>0.04696690000000001</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.0519606</v>
+        <v>0.0498783</v>
       </c>
       <c r="G129" s="19" t="n">
-        <v>28.23</v>
+        <v>28.22</v>
       </c>
       <c r="H129" s="20" t="inlineStr">
         <is>
@@ -5103,16 +5103,16 @@
         <v>31</v>
       </c>
       <c r="D130" s="18" t="n">
-        <v>0.0491378</v>
+        <v>0.04705599999999999</v>
       </c>
       <c r="E130" s="18" t="n">
-        <v>0.0490408</v>
+        <v>0.04696690000000001</v>
       </c>
       <c r="F130" s="18" t="n">
-        <v>0.0519606</v>
+        <v>0.0498783</v>
       </c>
       <c r="G130" s="19" t="n">
-        <v>28.23</v>
+        <v>28.22</v>
       </c>
       <c r="H130" s="20" t="inlineStr">
         <is>
@@ -5139,13 +5139,13 @@
         <v>30</v>
       </c>
       <c r="D131" s="18" t="n">
-        <v>0.04913509999999999</v>
+        <v>0.0470534</v>
       </c>
       <c r="E131" s="18" t="n">
-        <v>0.0490408</v>
+        <v>0.04696690000000001</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.0519575</v>
+        <v>0.0498755</v>
       </c>
       <c r="G131" s="19" t="n">
         <v>28.22</v>
@@ -5175,16 +5175,16 @@
         <v>31</v>
       </c>
       <c r="D132" s="18" t="n">
-        <v>0.0491378</v>
+        <v>0.04705599999999999</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>0.0490408</v>
+        <v>0.04696690000000001</v>
       </c>
       <c r="F132" s="18" t="n">
-        <v>0.0519606</v>
+        <v>0.0498783</v>
       </c>
       <c r="G132" s="19" t="n">
-        <v>28.23</v>
+        <v>28.22</v>
       </c>
       <c r="H132" s="20" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-21)</t>
+          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-22)</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
         <v>46344</v>
       </c>
       <c r="D4" s="23" t="n">
-        <v>96.16249999999999</v>
+        <v>96.1725</v>
       </c>
       <c r="E4" s="15">
         <f>(100-D4)/100</f>
@@ -5574,13 +5574,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.0383479</v>
+        <v>0.0383075</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>-0.271</v>
+        <v>0.325</v>
       </c>
       <c r="I4" s="25" t="n">
-        <v>7504</v>
+        <v>7574</v>
       </c>
     </row>
     <row r="5">
@@ -5596,7 +5596,7 @@
         <v>46372</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>96.0575</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="E5" s="15">
         <f>(100-D5)/100</f>
@@ -5606,13 +5606,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.0394151</v>
+        <v>0.0392957</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>-0.099</v>
+        <v>-0.043</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>1296078</v>
+        <v>1303679</v>
       </c>
     </row>
     <row r="6">
@@ -5638,13 +5638,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.0388771</v>
+        <v>0.0388639</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>-0.229</v>
+        <v>-0.361</v>
       </c>
       <c r="I6" s="25" t="n">
-        <v>353941</v>
+        <v>353705</v>
       </c>
     </row>
     <row r="7">
@@ -5660,7 +5660,7 @@
         <v>46407</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>95.94499999999999</v>
+        <v>95.9725</v>
       </c>
       <c r="E7" s="15">
         <f>(100-D7)/100</f>
@@ -5670,13 +5670,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.04058029999999999</v>
+        <v>0.0402708</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>0.303</v>
+        <v>-0.042</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>6686</v>
+        <v>7233</v>
       </c>
     </row>
     <row r="8">
@@ -5692,7 +5692,7 @@
         <v>46357</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>96.065</v>
+        <v>96.08499999999999</v>
       </c>
       <c r="E8" s="15">
         <f>(100-D8)/100</f>
@@ -5702,13 +5702,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.039367</v>
+        <v>0.0391769</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>0.17</v>
+        <v>0.269</v>
       </c>
       <c r="I8" s="25" t="n">
-        <v>294896</v>
+        <v>296856</v>
       </c>
     </row>
     <row r="9">
@@ -5724,7 +5724,7 @@
         <v>46435</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>95.8425</v>
+        <v>95.8925</v>
       </c>
       <c r="E9" s="15">
         <f>(100-D9)/100</f>
@@ -5734,10 +5734,10 @@
         <v>0.01</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.0415923</v>
+        <v>0.0410614</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>0.173</v>
+        <v>-0.136</v>
       </c>
       <c r="I9" s="25" t="n">
         <v>2585</v>
@@ -5756,7 +5756,7 @@
         <v>46388</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>95.895</v>
+        <v>95.935</v>
       </c>
       <c r="E10" s="15">
         <f>(100-D10)/100</f>
@@ -5766,13 +5766,13 @@
         <v>0.01</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.0410242</v>
+        <v>0.0406217</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.258</v>
+        <v>-0.283</v>
       </c>
       <c r="I10" s="25" t="n">
-        <v>230100</v>
+        <v>232198</v>
       </c>
     </row>
     <row r="11">
@@ -5788,7 +5788,7 @@
         <v>46463</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>95.745</v>
+        <v>95.83</v>
       </c>
       <c r="E11" s="15">
         <f>(100-D11)/100</f>
@@ -5798,13 +5798,13 @@
         <v>0.02</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.0425072</v>
+        <v>0.0417497</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.428</v>
+        <v>0.497</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>1552541</v>
+        <v>1566590</v>
       </c>
     </row>
     <row r="12">
@@ -5820,7 +5820,7 @@
         <v>46419</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>95.815</v>
+        <v>95.87</v>
       </c>
       <c r="E12" s="15">
         <f>(100-D12)/100</f>
@@ -5830,13 +5830,13 @@
         <v>0.02</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.0418456</v>
+        <v>0.0412925</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.044</v>
+        <v>-0.075</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>181283</v>
+        <v>183605</v>
       </c>
     </row>
     <row r="13">
@@ -5852,7 +5852,7 @@
         <v>46498</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>95.645</v>
+        <v>95.75</v>
       </c>
       <c r="E13" s="15">
         <f>(100-D13)/100</f>
@@ -5862,13 +5862,13 @@
         <v>0.05</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.0436067</v>
+        <v>0.0424615</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.5669999999999999</v>
+        <v>-0.385</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>1230</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="14">
@@ -5884,7 +5884,7 @@
         <v>46447</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>95.72</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="E14" s="15">
         <f>(100-D14)/100</f>
@@ -5894,13 +5894,13 @@
         <v>0.04</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.042809</v>
+        <v>0.0418261</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.09</v>
+        <v>0.261</v>
       </c>
       <c r="I14" s="25" t="n">
-        <v>104425</v>
+        <v>103380</v>
       </c>
     </row>
     <row r="15">
@@ -5916,7 +5916,7 @@
         <v>46526</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>95.55500000000001</v>
+        <v>95.69</v>
       </c>
       <c r="E15" s="15">
         <f>(100-D15)/100</f>
@@ -5926,13 +5926,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.0444884</v>
+        <v>0.0430563</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>0.384</v>
+        <v>-0.437</v>
       </c>
       <c r="I15" s="25" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
     </row>
     <row r="16">
@@ -5948,7 +5948,7 @@
         <v>46478</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>95.63500000000001</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="E16" s="15">
         <f>(100-D16)/100</f>
@@ -5958,13 +5958,13 @@
         <v>0.06</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.0436097</v>
+        <v>0.0423928</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.403</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="I16" s="25" t="n">
-        <v>34879</v>
+        <v>34419</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>46554</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>95.45</v>
+        <v>95.63</v>
       </c>
       <c r="E17" s="15">
         <f>(100-D17)/100</f>
@@ -5990,13 +5990,13 @@
         <v>0.1</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.0454379</v>
+        <v>0.0437171</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>-0.621</v>
+        <v>0.171</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>1335306</v>
+        <v>1359464</v>
       </c>
     </row>
     <row r="18">
@@ -6012,7 +6012,7 @@
         <v>46508</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>95.535</v>
+        <v>95.69</v>
       </c>
       <c r="E18" s="15">
         <f>(100-D18)/100</f>
@@ -6022,13 +6022,13 @@
         <v>0.09</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.0446514</v>
+        <v>0.0431258</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>0.014</v>
+        <v>0.258</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>60988</v>
+        <v>60743</v>
       </c>
     </row>
     <row r="19">
@@ -6044,7 +6044,7 @@
         <v>46539</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>95.44</v>
+        <v>95.625</v>
       </c>
       <c r="E19" s="15">
         <f>(100-D19)/100</f>
@@ -6054,13 +6054,13 @@
         <v>0.13</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.0456252</v>
+        <v>0.0437568</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>0.252</v>
+        <v>0.068</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>70231</v>
+        <v>70319</v>
       </c>
     </row>
     <row r="20">
@@ -6076,7 +6076,7 @@
         <v>46569</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>95.36</v>
+        <v>95.56</v>
       </c>
       <c r="E20" s="15">
         <f>(100-D20)/100</f>
@@ -6086,13 +6086,13 @@
         <v>0.17</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.0463994</v>
+        <v>0.0443935</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>-0.006</v>
+        <v>-0.065</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>20087</v>
+        <v>20020</v>
       </c>
     </row>
     <row r="21">
@@ -6108,7 +6108,7 @@
         <v>46645</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>95.27500000000001</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="E21" s="15">
         <f>(100-D21)/100</f>
@@ -6118,13 +6118,13 @@
         <v>0.23</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.0472101</v>
+        <v>0.04509559999999999</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>-0.399</v>
+        <v>-0.044</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>1262304</v>
+        <v>1260932</v>
       </c>
     </row>
     <row r="22">
@@ -6140,7 +6140,7 @@
         <v>46600</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>95.325</v>
+        <v>95.53</v>
       </c>
       <c r="E22" s="15">
         <f>(100-D22)/100</f>
@@ -6150,13 +6150,13 @@
         <v>0.21</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.0467709</v>
+        <v>0.0447014</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>0.209</v>
+        <v>0.014</v>
       </c>
       <c r="I22" s="25" t="n">
-        <v>38733</v>
+        <v>38412</v>
       </c>
     </row>
     <row r="23">
@@ -6172,23 +6172,23 @@
         <v>46631</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>95.29000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="E23" s="15">
         <f>(100-D23)/100</f>
         <v/>
       </c>
       <c r="F23" s="24" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.0471209</v>
+        <v>0.045007</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>0.209</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>19022</v>
+        <v>19917</v>
       </c>
     </row>
     <row r="24">
@@ -6204,7 +6204,7 @@
         <v>46661</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>95.265</v>
+        <v>95.48</v>
       </c>
       <c r="E24" s="15">
         <f>(100-D24)/100</f>
@@ -6214,13 +6214,13 @@
         <v>0.32</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.0473544</v>
+        <v>0.0451957</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>0.044</v>
+        <v>-0.043</v>
       </c>
       <c r="I24" s="25" t="n">
-        <v>4912</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="25">
@@ -6236,23 +6236,23 @@
         <v>46736</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>95.215</v>
+        <v>95.44</v>
       </c>
       <c r="E25" s="15">
         <f>(100-D25)/100</f>
         <v/>
       </c>
       <c r="F25" s="24" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.0478608</v>
+        <v>0.0456291</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>0.108</v>
+        <v>0.291</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>1054765</v>
+        <v>1070636</v>
       </c>
     </row>
     <row r="26">
@@ -6268,7 +6268,7 @@
         <v>46692</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="E26" s="15">
         <f>(100-D26)/100</f>
@@ -6278,13 +6278,13 @@
         <v>0.38</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.0475887</v>
+        <v>0.0453846</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>-0.113</v>
+        <v>-0.154</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>7001</v>
+        <v>7003</v>
       </c>
     </row>
     <row r="27">
@@ -6300,7 +6300,7 @@
         <v>46722</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="E27" s="15">
         <f>(100-D27)/100</f>
@@ -6310,10 +6310,10 @@
         <v>0.45</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.0475971</v>
+        <v>0.04538859999999999</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>-0.029</v>
+        <v>-0.114</v>
       </c>
       <c r="I27" s="25" t="n">
         <v>1769</v>
@@ -6332,23 +6332,23 @@
         <v>46827</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>95.22499999999999</v>
+        <v>95.45</v>
       </c>
       <c r="E28" s="15">
         <f>(100-D28)/100</f>
         <v/>
       </c>
       <c r="F28" s="24" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.0477496</v>
+        <v>0.045498</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>-0.004</v>
+        <v>-0.02</v>
       </c>
       <c r="I28" s="25" t="n">
-        <v>1637506</v>
+        <v>1651579</v>
       </c>
     </row>
     <row r="29">
@@ -6364,7 +6364,7 @@
         <v>46925</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>95.23999999999999</v>
+        <v>95.47</v>
       </c>
       <c r="E29" s="15">
         <f>(100-D29)/100</f>
@@ -6374,13 +6374,13 @@
         <v>0.9</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.04759960000000001</v>
+        <v>0.0453006</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>828142</v>
+        <v>831516</v>
       </c>
     </row>
     <row r="30">
@@ -6396,23 +6396,23 @@
         <v>47016</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>95.26000000000001</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="E30" s="15">
         <f>(100-D30)/100</f>
         <v/>
       </c>
       <c r="F30" s="24" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.04740179999999999</v>
+        <v>0.0451016</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="I30" s="25" t="n">
-        <v>643008</v>
+        <v>636471</v>
       </c>
     </row>
     <row r="31">
@@ -6428,7 +6428,7 @@
         <v>47107</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>95.27500000000001</v>
+        <v>95.505</v>
       </c>
       <c r="E31" s="15">
         <f>(100-D31)/100</f>
@@ -6438,13 +6438,13 @@
         <v>1.58</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.0472477</v>
+        <v>0.0449466</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>-0.023</v>
+        <v>-0.034</v>
       </c>
       <c r="I31" s="25" t="n">
-        <v>678274</v>
+        <v>676741</v>
       </c>
     </row>
     <row r="32">
@@ -6460,7 +6460,7 @@
         <v>47198</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>95.295</v>
+        <v>95.52500000000001</v>
       </c>
       <c r="E32" s="15">
         <f>(100-D32)/100</f>
@@ -6470,13 +6470,13 @@
         <v>1.98</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.0470507</v>
+        <v>0.0447524</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>0.007</v>
+        <v>0.024</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>551725</v>
+        <v>542344</v>
       </c>
     </row>
     <row r="33">
@@ -6492,23 +6492,23 @@
         <v>47289</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>95.315</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="E33" s="15">
         <f>(100-D33)/100</f>
         <v/>
       </c>
       <c r="F33" s="24" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.04685019999999999</v>
+        <v>0.0446001</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>380691</v>
+        <v>382026</v>
       </c>
     </row>
     <row r="34">
@@ -6524,23 +6524,23 @@
         <v>47380</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>95.33</v>
+        <v>95.55</v>
       </c>
       <c r="E34" s="15">
         <f>(100-D34)/100</f>
         <v/>
       </c>
       <c r="F34" s="24" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.0467001</v>
+        <v>0.0444989</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>0.001</v>
+        <v>-0.011</v>
       </c>
       <c r="I34" s="25" t="n">
-        <v>378142</v>
+        <v>382203</v>
       </c>
     </row>
     <row r="35">
@@ -6556,7 +6556,7 @@
         <v>47471</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>95.34</v>
+        <v>95.56</v>
       </c>
       <c r="E35" s="15">
         <f>(100-D35)/100</f>
@@ -6566,13 +6566,13 @@
         <v>3.41</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.0465999</v>
+        <v>0.0443994</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>-0.001</v>
+        <v>-0.006</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>303454</v>
+        <v>318885</v>
       </c>
     </row>
     <row r="36">
@@ -6588,23 +6588,23 @@
         <v>47562</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>95.345</v>
+        <v>95.565</v>
       </c>
       <c r="E36" s="15">
         <f>(100-D36)/100</f>
         <v/>
       </c>
       <c r="F36" s="24" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.0465501</v>
+        <v>0.04435310000000001</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>0.001</v>
+        <v>0.031</v>
       </c>
       <c r="I36" s="25" t="n">
-        <v>243437</v>
+        <v>241835</v>
       </c>
     </row>
     <row r="37">
@@ -6620,23 +6620,23 @@
         <v>47653</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>95.345</v>
+        <v>95.56</v>
       </c>
       <c r="E37" s="15">
         <f>(100-D37)/100</f>
         <v/>
       </c>
       <c r="F37" s="24" t="n">
-        <v>4.56</v>
+        <v>4.55</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.0465499</v>
+        <v>0.0443966</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>-0.001</v>
+        <v>-0.034</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>179522</v>
+        <v>177899</v>
       </c>
     </row>
     <row r="38">
@@ -6652,7 +6652,7 @@
         <v>47744</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>95.34</v>
+        <v>95.55500000000001</v>
       </c>
       <c r="E38" s="15">
         <f>(100-D38)/100</f>
@@ -6662,13 +6662,13 @@
         <v>5.18</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.04660040000000001</v>
+        <v>0.0444521</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>0.004</v>
+        <v>0.021</v>
       </c>
       <c r="I38" s="25" t="n">
-        <v>159075</v>
+        <v>157777</v>
       </c>
     </row>
     <row r="39">
@@ -6684,23 +6684,23 @@
         <v>47835</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>95.33</v>
+        <v>95.545</v>
       </c>
       <c r="E39" s="15">
         <f>(100-D39)/100</f>
         <v/>
       </c>
       <c r="F39" s="24" t="n">
-        <v>5.85</v>
+        <v>5.84</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.0466986</v>
+        <v>0.044548</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>-0.014</v>
+        <v>-0.02</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>141748</v>
+        <v>143895</v>
       </c>
     </row>
     <row r="40">
@@ -6716,23 +6716,23 @@
         <v>47926</v>
       </c>
       <c r="D40" s="23" t="n">
-        <v>95.315</v>
+        <v>95.53</v>
       </c>
       <c r="E40" s="15">
         <f>(100-D40)/100</f>
         <v/>
       </c>
       <c r="F40" s="24" t="n">
-        <v>6.55</v>
+        <v>6.54</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.0468526</v>
+        <v>0.0447032</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>0.026</v>
+        <v>0.032</v>
       </c>
       <c r="I40" s="25" t="n">
-        <v>115058</v>
+        <v>116482</v>
       </c>
     </row>
     <row r="41">
@@ -6748,23 +6748,23 @@
         <v>48017</v>
       </c>
       <c r="D41" s="23" t="n">
-        <v>95.29000000000001</v>
+        <v>95.505</v>
       </c>
       <c r="E41" s="15">
         <f>(100-D41)/100</f>
         <v/>
       </c>
       <c r="F41" s="24" t="n">
-        <v>7.28</v>
+        <v>7.27</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.0470984</v>
+        <v>0.0449466</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>-0.016</v>
+        <v>-0.034</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>88299</v>
+        <v>92312</v>
       </c>
     </row>
     <row r="42">
@@ -6780,23 +6780,23 @@
         <v>48108</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>95.265</v>
+        <v>95.48</v>
       </c>
       <c r="E42" s="15">
         <f>(100-D42)/100</f>
         <v/>
       </c>
       <c r="F42" s="24" t="n">
-        <v>8.039999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.0473493</v>
+        <v>0.04520279999999999</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>-0.007</v>
+        <v>0.028</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>68749</v>
+        <v>69978</v>
       </c>
     </row>
     <row r="43">
@@ -6812,23 +6812,23 @@
         <v>48199</v>
       </c>
       <c r="D43" s="23" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="E43" s="15">
         <f>(100-D43)/100</f>
         <v/>
       </c>
       <c r="F43" s="24" t="n">
-        <v>8.84</v>
+        <v>8.83</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.0476015</v>
+        <v>0.045498</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>0.015</v>
+        <v>-0.02</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>35766</v>
+        <v>35785</v>
       </c>
     </row>
     <row r="44">
@@ -6844,23 +6844,23 @@
         <v>48290</v>
       </c>
       <c r="D44" s="23" t="n">
-        <v>95.20999999999999</v>
+        <v>95.42</v>
       </c>
       <c r="E44" s="15">
         <f>(100-D44)/100</f>
         <v/>
       </c>
       <c r="F44" s="24" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.0479004</v>
+        <v>0.04580219999999999</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>0.004</v>
+        <v>0.022</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>5782</v>
+        <v>8183</v>
       </c>
     </row>
     <row r="45">
@@ -6876,23 +6876,23 @@
         <v>48381</v>
       </c>
       <c r="D45" s="23" t="n">
-        <v>95.18000000000001</v>
+        <v>95.39</v>
       </c>
       <c r="E45" s="15">
         <f>(100-D45)/100</f>
         <v/>
       </c>
       <c r="F45" s="24" t="n">
-        <v>10.52</v>
+        <v>10.51</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.0481966</v>
+        <v>0.0460961</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.039</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>1771</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="46">
@@ -6908,20 +6908,20 @@
         <v>48472</v>
       </c>
       <c r="D46" s="23" t="n">
-        <v>95.155</v>
+        <v>95.36499999999999</v>
       </c>
       <c r="E46" s="15">
         <f>(100-D46)/100</f>
         <v/>
       </c>
       <c r="F46" s="24" t="n">
-        <v>11.41</v>
+        <v>11.4</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.0484551</v>
+        <v>0.0463552</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="I46" s="25" t="n">
         <v>823</v>
@@ -6940,17 +6940,17 @@
         <v>48563</v>
       </c>
       <c r="D47" s="23" t="n">
-        <v>95.125</v>
+        <v>95.33499999999999</v>
       </c>
       <c r="E47" s="15">
         <f>(100-D47)/100</f>
         <v/>
       </c>
       <c r="F47" s="24" t="n">
-        <v>12.32</v>
+        <v>12.31</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.0487443</v>
+        <v>0.0466443</v>
       </c>
       <c r="H47" s="24" t="n">
         <v>-0.057</v>
@@ -6972,20 +6972,20 @@
         <v>48654</v>
       </c>
       <c r="D48" s="23" t="n">
-        <v>95.09999999999999</v>
+        <v>95.31</v>
       </c>
       <c r="E48" s="15">
         <f>(100-D48)/100</f>
         <v/>
       </c>
       <c r="F48" s="24" t="n">
-        <v>13.26</v>
+        <v>13.25</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.0490061</v>
+        <v>0.046906</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="I48" s="25" t="n">
         <v>164</v>
@@ -7004,20 +7004,20 @@
         <v>48745</v>
       </c>
       <c r="D49" s="23" t="n">
-        <v>95.06999999999999</v>
+        <v>95.28</v>
       </c>
       <c r="E49" s="15">
         <f>(100-D49)/100</f>
         <v/>
       </c>
       <c r="F49" s="24" t="n">
-        <v>14.24</v>
+        <v>14.23</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.04929459999999999</v>
+        <v>0.0471948</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>-0.054</v>
+        <v>-0.052</v>
       </c>
       <c r="I49" s="25" t="n">
         <v>35</v>
@@ -7036,20 +7036,20 @@
         <v>48843</v>
       </c>
       <c r="D50" s="23" t="n">
-        <v>95.045</v>
+        <v>95.255</v>
       </c>
       <c r="E50" s="15">
         <f>(100-D50)/100</f>
         <v/>
       </c>
       <c r="F50" s="24" t="n">
-        <v>15.27</v>
+        <v>15.26</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.0495517</v>
+        <v>0.0474516</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="I50" s="25" t="n">
         <v>1</v>
@@ -7068,20 +7068,20 @@
         <v>48934</v>
       </c>
       <c r="D51" s="23" t="n">
-        <v>95.02</v>
+        <v>95.23</v>
       </c>
       <c r="E51" s="15">
         <f>(100-D51)/100</f>
         <v/>
       </c>
       <c r="F51" s="24" t="n">
-        <v>16.34</v>
+        <v>16.33</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.0498064</v>
+        <v>0.0477063</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="I51" s="25" t="n">
         <v>0</v>
@@ -7100,20 +7100,20 @@
         <v>49018</v>
       </c>
       <c r="D52" s="23" t="n">
-        <v>94.995</v>
+        <v>95.205</v>
       </c>
       <c r="E52" s="15">
         <f>(100-D52)/100</f>
         <v/>
       </c>
       <c r="F52" s="24" t="n">
-        <v>17.35</v>
+        <v>17.34</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.0500337</v>
+        <v>0.0479341</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>-0.163</v>
+        <v>-0.159</v>
       </c>
       <c r="I52" s="25" t="n">
         <v>11</v>
@@ -7132,20 +7132,20 @@
         <v>49116</v>
       </c>
       <c r="D53" s="23" t="n">
-        <v>94.98</v>
+        <v>95.19</v>
       </c>
       <c r="E53" s="15">
         <f>(100-D53)/100</f>
         <v/>
       </c>
       <c r="F53" s="24" t="n">
-        <v>18.42</v>
+        <v>18.41</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.050223</v>
+        <v>0.0481226</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>0.23</v>
+        <v>0.226</v>
       </c>
       <c r="I53" s="25" t="n">
         <v>0</v>
@@ -7164,20 +7164,20 @@
         <v>49207</v>
       </c>
       <c r="D54" s="23" t="n">
-        <v>94.95</v>
+        <v>95.16</v>
       </c>
       <c r="E54" s="15">
         <f>(100-D54)/100</f>
         <v/>
       </c>
       <c r="F54" s="24" t="n">
-        <v>19.56</v>
+        <v>19.55</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.0504714</v>
+        <v>0.0483716</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>-0.286</v>
+        <v>-0.284</v>
       </c>
       <c r="I54" s="25" t="n">
         <v>0</v>
@@ -7196,20 +7196,20 @@
         <v>49298</v>
       </c>
       <c r="D55" s="23" t="n">
-        <v>94.94</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="E55" s="15">
         <f>(100-D55)/100</f>
         <v/>
       </c>
       <c r="F55" s="24" t="n">
-        <v>20.69</v>
+        <v>20.67</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.0506337</v>
+        <v>0.0485336</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>0.337</v>
+        <v>0.336</v>
       </c>
       <c r="I55" s="25" t="n">
         <v>0</v>
@@ -7228,17 +7228,17 @@
         <v>49389</v>
       </c>
       <c r="D56" s="23" t="n">
-        <v>94.895</v>
+        <v>95.105</v>
       </c>
       <c r="E56" s="15">
         <f>(100-D56)/100</f>
         <v/>
       </c>
       <c r="F56" s="24" t="n">
-        <v>21.83</v>
+        <v>21.82</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.0510186</v>
+        <v>0.04891860000000001</v>
       </c>
       <c r="H56" s="24" t="n">
         <v>-0.314</v>
@@ -7260,17 +7260,17 @@
         <v>49480</v>
       </c>
       <c r="D57" s="23" t="n">
-        <v>94.88500000000001</v>
+        <v>95.095</v>
       </c>
       <c r="E57" s="15">
         <f>(100-D57)/100</f>
         <v/>
       </c>
       <c r="F57" s="24" t="n">
-        <v>23</v>
+        <v>22.98</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.0511718</v>
+        <v>0.04907180000000001</v>
       </c>
       <c r="H57" s="24" t="n">
         <v>0.218</v>
@@ -7292,20 +7292,20 @@
         <v>49571</v>
       </c>
       <c r="D58" s="23" t="n">
-        <v>94.86</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="E58" s="15">
         <f>(100-D58)/100</f>
         <v/>
       </c>
       <c r="F58" s="24" t="n">
-        <v>24.19</v>
+        <v>24.17</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.0513842</v>
+        <v>0.0492841</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>-0.158</v>
+        <v>-0.159</v>
       </c>
       <c r="I58" s="25" t="n">
         <v>0</v>
@@ -7324,17 +7324,17 @@
         <v>49662</v>
       </c>
       <c r="D59" s="23" t="n">
-        <v>94.83499999999999</v>
+        <v>95.045</v>
       </c>
       <c r="E59" s="15">
         <f>(100-D59)/100</f>
         <v/>
       </c>
       <c r="F59" s="24" t="n">
-        <v>25.4</v>
+        <v>25.38</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.0516687</v>
+        <v>0.0495687</v>
       </c>
       <c r="H59" s="24" t="n">
         <v>0.187</v>
@@ -7356,17 +7356,17 @@
         <v>49753</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>94.79000000000001</v>
+        <v>95</v>
       </c>
       <c r="E60" s="15">
         <f>(100-D60)/100</f>
         <v/>
       </c>
       <c r="F60" s="24" t="n">
-        <v>26.62</v>
+        <v>26.61</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.0520833</v>
+        <v>0.0499833</v>
       </c>
       <c r="H60" s="24" t="n">
         <v>-0.167</v>
@@ -7388,17 +7388,17 @@
         <v>49844</v>
       </c>
       <c r="D61" s="23" t="n">
-        <v>94.78</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="E61" s="15">
         <f>(100-D61)/100</f>
         <v/>
       </c>
       <c r="F61" s="24" t="n">
-        <v>27.87</v>
+        <v>27.86</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.0522058</v>
+        <v>0.0501058</v>
       </c>
       <c r="H61" s="24" t="n">
         <v>0.058</v>
@@ -7410,7 +7410,7 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Fit: 58 contracts, RMS residual 0.205 bp, max 0.621 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
+          <t>Fit: 58 contracts, RMS residual 0.178 bp, max 0.497 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7453,15 +7453,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B4" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B5" s="26" t="n">
         <v>0.0388</v>
@@ -7469,55 +7469,55 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B8" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B9" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B10" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B11" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B12" s="26" t="n">
         <v>0.0387</v>
@@ -7525,71 +7525,71 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B13" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B14" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B15" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B16" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B17" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B18" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B19" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B20" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B21" s="26" t="n">
         <v>0.039</v>
@@ -7597,23 +7597,23 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B22" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B23" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B24" s="26" t="n">
         <v>0.0387</v>
@@ -7621,15 +7621,15 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B25" s="26" t="n">
-        <v>0.0385</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B26" s="26" t="n">
         <v>0.0385</v>
@@ -7637,7 +7637,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B27" s="26" t="n">
         <v>0.0385</v>
@@ -7645,31 +7645,31 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B28" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B29" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B30" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B31" s="26" t="n">
         <v>0.0362</v>
@@ -7677,7 +7677,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B32" s="26" t="n">
         <v>0.0362</v>
@@ -7685,15 +7685,15 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B33" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B34" s="26" t="n">
         <v>0.0364</v>
@@ -7701,63 +7701,63 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B35" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B36" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B37" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B38" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B39" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B40" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B41" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B42" s="26" t="n">
         <v>0.0364</v>
@@ -7765,23 +7765,23 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B43" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B44" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B45" s="26" t="n">
         <v>0.0365</v>
@@ -7789,47 +7789,47 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B48" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B49" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B50" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B51" s="26" t="n">
         <v>0.0362</v>
@@ -7837,7 +7837,7 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B52" s="26" t="n">
         <v>0.0362</v>
@@ -7845,79 +7845,79 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B53" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B54" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B55" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B56" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B57" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B58" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B59" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B60" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B61" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B62" s="26" t="n">
         <v>0.0365</v>
@@ -7925,7 +7925,7 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B63" s="26" t="n">
         <v>0.0365</v>
@@ -7933,15 +7933,15 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B64" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B65" s="26" t="n">
         <v>0.0364</v>
@@ -7949,7 +7949,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B66" s="26" t="n">
         <v>0.0364</v>
@@ -7957,143 +7957,143 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B67" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B68" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B69" s="26" t="n">
-        <v>0.0357</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B70" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.0357</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B71" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B72" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B73" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B74" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B75" s="26" t="n">
-        <v>0.0355</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B76" s="26" t="n">
-        <v>0.0353</v>
+        <v>0.0355</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B77" s="26" t="n">
-        <v>0.0358</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B78" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B79" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B80" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B81" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B82" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B83" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B84" s="26" t="n">
         <v>0.0362</v>
@@ -8101,23 +8101,23 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B85" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B86" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B87" s="26" t="n">
         <v>0.0362</v>
@@ -8125,31 +8125,31 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B88" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B89" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B90" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B91" s="26" t="n">
         <v>0.0363</v>
@@ -8157,55 +8157,55 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B92" s="26" t="n">
-        <v>0.0369</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B93" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B94" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B95" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B96" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B97" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B98" s="26" t="n">
         <v>0.0363</v>
@@ -8213,65 +8213,73 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B99" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B100" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B101" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B102" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B103" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B104" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B105" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B106" s="26" t="n">
+        <v>0.0363</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="B106" s="26" t="n">
+      <c r="B107" s="26" t="n">
         <v>0.0363</v>
       </c>
     </row>

--- a/output/downloads/sofr-forward-curve.xlsx
+++ b/output/downloads/sofr-forward-curve.xlsx
@@ -236,7 +236,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SOFR forward curve, 2026-10-22</a:t>
+              <a:t>SOFR forward curve, 2026-10-23</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="3">
@@ -743,7 +743,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23 17:53 UTC</t>
+          <t>2026-10-24 16:35 UTC</t>
         </is>
       </c>
     </row>
@@ -855,13 +855,13 @@
         <v>31</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.0389247</v>
+        <v>0.038972</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>0.0388639</v>
+        <v>0.038911</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>0.0389246</v>
+        <v>0.0389719</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0</v>
@@ -891,13 +891,13 @@
         <v>30</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.0392366</v>
+        <v>0.039333</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.0391767</v>
+        <v>0.0392728</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>0.0392365</v>
+        <v>0.0393329</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.0406874</v>
+        <v>0.0407256</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>0.0406208</v>
+        <v>0.0406589</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0.04068819999999999</v>
+        <v>0.0407264</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>0.01</v>
@@ -963,13 +963,13 @@
         <v>31</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.0413587</v>
+        <v>0.04138219999999999</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.0412904</v>
+        <v>0.0413138</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>0.0413603</v>
+        <v>0.0413837</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>0.02</v>
@@ -999,13 +999,13 @@
         <v>28</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.0418852</v>
+        <v>0.0419707</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.0418221</v>
+        <v>0.0419074</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0.0418889</v>
+        <v>0.0419743</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>0.04</v>
@@ -1035,13 +1035,13 @@
         <v>31</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.042459</v>
+        <v>0.0426272</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.0423865</v>
+        <v>0.0425541</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0.0424649</v>
+        <v>0.042633</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>0.06</v>
@@ -1071,13 +1071,13 @@
         <v>30</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.0431895</v>
+        <v>0.0434672</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>0.0431166</v>
+        <v>0.0433933</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>0.0431982</v>
+        <v>0.0434758</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>0.09</v>
@@ -1107,13 +1107,13 @@
         <v>31</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.0438212</v>
+        <v>0.0442254</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.0437441</v>
+        <v>0.0441469</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.04383339999999999</v>
+        <v>0.0442374</v>
       </c>
       <c r="G19" s="13" t="n">
         <v>0.12</v>
@@ -1143,13 +1143,13 @@
         <v>30</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.04445350000000001</v>
+        <v>0.0449175</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>0.0443768</v>
+        <v>0.0448393</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0.044471</v>
+        <v>0.04493490000000001</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>0.17</v>
@@ -1179,13 +1179,13 @@
         <v>31</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.0447606</v>
+        <v>0.0452529</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.0446802</v>
+        <v>0.0451708</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.044781</v>
+        <v>0.04527319999999999</v>
       </c>
       <c r="G21" s="13" t="n">
         <v>0.2</v>
@@ -1215,16 +1215,16 @@
         <v>31</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.0450629</v>
+        <v>0.0455792</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.04498070000000001</v>
+        <v>0.045495</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0.0450894</v>
+        <v>0.0456055</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
@@ -1251,16 +1251,16 @@
         <v>30</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.0452432</v>
+        <v>0.0457608</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.0451638</v>
+        <v>0.0456795</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.0452749</v>
+        <v>0.0457923</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
@@ -1287,13 +1287,13 @@
         <v>31</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.045429</v>
+        <v>0.045945</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>0.0453465</v>
+        <v>0.0458606</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0.0454668</v>
+        <v>0.0459825</v>
       </c>
       <c r="G24" s="13" t="n">
         <v>0.38</v>
@@ -1323,13 +1323,13 @@
         <v>30</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.0454241</v>
+        <v>0.0459196</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.0453439</v>
+        <v>0.0458376</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0.0454685</v>
+        <v>0.0459638</v>
       </c>
       <c r="G25" s="13" t="n">
         <v>0.44</v>
@@ -1359,16 +1359,16 @@
         <v>31</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.0453392</v>
+        <v>0.0458384</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.0452565</v>
+        <v>0.04575389999999999</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0.0453908</v>
+        <v>0.0458898</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         <v>31</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.0453007</v>
+        <v>0.0458021</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>0.0452183</v>
+        <v>0.0457179</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0.0453569</v>
+        <v>0.045858</v>
       </c>
       <c r="G27" s="13" t="n">
         <v>0.5600000000000001</v>
@@ -1431,16 +1431,16 @@
         <v>29</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.0452546</v>
+        <v>0.0457603</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>0.0451781</v>
+        <v>0.0456821</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>0.0453213</v>
+        <v>0.0458266</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
@@ -1467,13 +1467,13 @@
         <v>31</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.0451411</v>
+        <v>0.0455943</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>0.0450586</v>
+        <v>0.0455102</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.0452154</v>
+        <v>0.0456684</v>
       </c>
       <c r="G29" s="13" t="n">
         <v>0.74</v>
@@ -1503,13 +1503,13 @@
         <v>30</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>0.04506300000000001</v>
+        <v>0.0455113</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>0.04498440000000001</v>
+        <v>0.0454311</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0.0451463</v>
+        <v>0.0455943</v>
       </c>
       <c r="G30" s="13" t="n">
         <v>0.83</v>
@@ -1539,16 +1539,16 @@
         <v>31</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>0.0449843</v>
+        <v>0.0454295</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0.0449029</v>
+        <v>0.0453465</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.0450781</v>
+        <v>0.04552290000000001</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
@@ -1575,13 +1575,13 @@
         <v>30</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.0449101</v>
+        <v>0.045355</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>0.0448318</v>
+        <v>0.0452752</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0.04501400000000001</v>
+        <v>0.0454585</v>
       </c>
       <c r="G32" s="13" t="n">
         <v>1.04</v>
@@ -1611,16 +1611,16 @@
         <v>31</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.0448522</v>
+        <v>0.0452981</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>0.04477109999999999</v>
+        <v>0.0452154</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0.044966</v>
+        <v>0.0454115</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
@@ -1647,13 +1647,13 @@
         <v>31</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.04478869999999999</v>
+        <v>0.0452352</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>0.0447074</v>
+        <v>0.0451524</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0.0449141</v>
+        <v>0.0453603</v>
       </c>
       <c r="G34" s="13" t="n">
         <v>1.25</v>
@@ -1683,13 +1683,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.0447276</v>
+        <v>0.0451739</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>0.04465010000000001</v>
+        <v>0.04509490000000001</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0.04486449999999999</v>
+        <v>0.0453104</v>
       </c>
       <c r="G35" s="13" t="n">
         <v>1.37</v>
@@ -1719,16 +1719,16 @@
         <v>31</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>0.0446712</v>
+        <v>0.0451179</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>0.0445909</v>
+        <v>0.04503599999999999</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0.0448197</v>
+        <v>0.045266</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
@@ -1755,13 +1755,13 @@
         <v>30</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.0445959</v>
+        <v>0.0450446</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>0.0445184</v>
+        <v>0.0449655</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0.04475730000000001</v>
+        <v>0.0452055</v>
       </c>
       <c r="G37" s="13" t="n">
         <v>1.61</v>
@@ -1791,13 +1791,13 @@
         <v>31</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>0.0445179</v>
+        <v>0.0449695</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>0.0444388</v>
+        <v>0.0448887</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0.0446923</v>
+        <v>0.0451433</v>
       </c>
       <c r="G38" s="13" t="n">
         <v>1.74</v>
@@ -1827,13 +1827,13 @@
         <v>31</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0.0444381</v>
+        <v>0.04489</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0.0443587</v>
+        <v>0.044809</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0.0446253</v>
+        <v>0.0450768</v>
       </c>
       <c r="G39" s="13" t="n">
         <v>1.87</v>
@@ -1863,13 +1863,13 @@
         <v>28</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>0.04434879999999999</v>
+        <v>0.0447949</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>0.0442781</v>
+        <v>0.04472279999999999</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0.04455</v>
+        <v>0.0449956</v>
       </c>
       <c r="G40" s="13" t="n">
         <v>2.01</v>
@@ -1899,13 +1899,13 @@
         <v>31</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.044288</v>
+        <v>0.04472089999999999</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.0442091</v>
+        <v>0.0446404</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0.0445033</v>
+        <v>0.0449357</v>
       </c>
       <c r="G41" s="13" t="n">
         <v>2.15</v>
@@ -1935,13 +1935,13 @@
         <v>30</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>0.0442275</v>
+        <v>0.0446403</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>0.04415110000000001</v>
+        <v>0.0445625</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0.0444569</v>
+        <v>0.0448692</v>
       </c>
       <c r="G42" s="13" t="n">
         <v>2.29</v>
@@ -1971,13 +1971,13 @@
         <v>31</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.04417430000000001</v>
+        <v>0.0445611</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.0440958</v>
+        <v>0.04448120000000001</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.0444194</v>
+        <v>0.04480559999999999</v>
       </c>
       <c r="G43" s="13" t="n">
         <v>2.45</v>
@@ -2007,16 +2007,16 @@
         <v>30</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.0441223</v>
+        <v>0.0444845</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>0.0440466</v>
+        <v>0.0444075</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0.0443832</v>
+        <v>0.0447448</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
@@ -2043,16 +2043,16 @@
         <v>31</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.0440786</v>
+        <v>0.0444263</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.0440001</v>
+        <v>0.0443466</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0.0443553</v>
+        <v>0.0447025</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
@@ -2079,16 +2079,16 @@
         <v>31</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.0440278</v>
+        <v>0.0443768</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>0.0439493</v>
+        <v>0.0442971</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0.0443217</v>
+        <v>0.0446701</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
@@ -2115,16 +2115,16 @@
         <v>30</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.0439785</v>
+        <v>0.0443428</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.0439034</v>
+        <v>0.04426650000000001</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.0442875</v>
+        <v>0.0446512</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
@@ -2151,16 +2151,16 @@
         <v>31</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.0439247</v>
+        <v>0.0443124</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>0.0438471</v>
+        <v>0.0442334</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0.0442526</v>
+        <v>0.0446398</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
@@ -2187,16 +2187,16 @@
         <v>30</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.0438727</v>
+        <v>0.0442748</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>0.0437982</v>
+        <v>0.0441989</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0.04421820000000001</v>
+        <v>0.0446197</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
@@ -2223,13 +2223,13 @@
         <v>31</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.04383600000000001</v>
+        <v>0.044241</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>0.0437585</v>
+        <v>0.0441621</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0.0441985</v>
+        <v>0.04460289999999999</v>
       </c>
       <c r="G50" s="13" t="n">
         <v>3.62</v>
@@ -2259,16 +2259,16 @@
         <v>31</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.0438029</v>
+        <v>0.0442047</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>0.0437257</v>
+        <v>0.0441261</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>0.04418440000000001</v>
+        <v>0.0445856</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
@@ -2295,16 +2295,16 @@
         <v>28</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.04377710000000001</v>
+        <v>0.0441752</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>0.0437082</v>
+        <v>0.0441051</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0.0441779</v>
+        <v>0.0445754</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
@@ -2331,13 +2331,13 @@
         <v>31</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.0437813</v>
+        <v>0.0441786</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.0437042</v>
+        <v>0.0441001</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.0442015</v>
+        <v>0.0445982</v>
       </c>
       <c r="G53" s="13" t="n">
         <v>4.2</v>
@@ -2367,16 +2367,16 @@
         <v>30</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>0.0437803</v>
+        <v>0.04417740000000001</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>0.0437059</v>
+        <v>0.0441017</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>0.04422010000000001</v>
+        <v>0.0446165</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
@@ -2403,16 +2403,16 @@
         <v>31</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>0.0437825</v>
+        <v>0.0441775</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.0437054</v>
+        <v>0.04409900000000001</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.0442426</v>
+        <v>0.0446369</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>4.6</v>
+        <v>4.59</v>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
@@ -2439,13 +2439,13 @@
         <v>30</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>0.0437753</v>
+        <v>0.0441674</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>0.0437008</v>
+        <v>0.04409150000000001</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>0.0442547</v>
+        <v>0.044646</v>
       </c>
       <c r="G56" s="13" t="n">
         <v>4.79</v>
@@ -2475,16 +2475,16 @@
         <v>31</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>0.0437727</v>
+        <v>0.0441657</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.0436953</v>
+        <v>0.0440869</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.0442746</v>
+        <v>0.0446668</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
@@ -2511,16 +2511,16 @@
         <v>31</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>0.0437729</v>
+        <v>0.04417620000000001</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>0.04369550000000001</v>
+        <v>0.0440973</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0.0442961</v>
+        <v>0.0446987</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>5.23</v>
+        <v>5.22</v>
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
@@ -2547,13 +2547,13 @@
         <v>30</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>0.0437773</v>
+        <v>0.0441977</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.0437026</v>
+        <v>0.04412149999999999</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.0443207</v>
+        <v>0.0447403</v>
       </c>
       <c r="G59" s="13" t="n">
         <v>5.43</v>
@@ -2583,16 +2583,16 @@
         <v>31</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.0437935</v>
+        <v>0.04423390000000001</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>0.0437163</v>
+        <v>0.0441552</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0.0443606</v>
+        <v>0.0448003</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>5.67</v>
+        <v>5.66</v>
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>30</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>0.043807</v>
+        <v>0.0442587</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>0.0437329</v>
+        <v>0.0441831</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0.044397</v>
+        <v>0.0448479</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>5.9</v>
+        <v>5.89</v>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
@@ -2655,16 +2655,16 @@
         <v>31</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>0.0438312</v>
+        <v>0.04428480000000001</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>0.0437536</v>
+        <v>0.0442056</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0.044444</v>
+        <v>0.0448968</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
@@ -2691,13 +2691,13 @@
         <v>31</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>0.0438616</v>
+        <v>0.0443122</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>0.0437842</v>
+        <v>0.0442332</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0.0444979</v>
+        <v>0.0449478</v>
       </c>
       <c r="G63" s="13" t="n">
         <v>6.36</v>
@@ -2727,16 +2727,16 @@
         <v>28</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>0.043896</v>
+        <v>0.044344</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>0.0438264</v>
+        <v>0.044273</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>0.0445548</v>
+        <v>0.0450019</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
@@ -2763,16 +2763,16 @@
         <v>31</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>0.04396029999999999</v>
+        <v>0.0444078</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>0.0438822</v>
+        <v>0.0443281</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0.0446429</v>
+        <v>0.0450896</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>6.83</v>
+        <v>6.82</v>
       </c>
       <c r="H65" s="14" t="inlineStr">
         <is>
@@ -2799,16 +2799,16 @@
         <v>30</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>0.04402250000000001</v>
+        <v>0.0444696</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>0.0439473</v>
+        <v>0.0443929</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0.0447302</v>
+        <v>0.0451764</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>7.08</v>
+        <v>7.07</v>
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
@@ -2835,16 +2835,16 @@
         <v>31</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>0.0440849</v>
+        <v>0.0445296</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>0.0440069</v>
+        <v>0.04445</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>0.04481690000000001</v>
+        <v>0.0452608</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>7.32</v>
+        <v>7.31</v>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
@@ -2871,16 +2871,16 @@
         <v>30</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>0.0441373</v>
+        <v>0.0445787</v>
       </c>
       <c r="E68" s="12" t="n">
-        <v>0.0440613</v>
+        <v>0.04450129999999999</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0.0448935</v>
+        <v>0.0453341</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>7.56</v>
+        <v>7.55</v>
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
@@ -2907,16 +2907,16 @@
         <v>31</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>0.04419940000000001</v>
+        <v>0.044642</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>0.04412079999999999</v>
+        <v>0.0445619</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0.0449823</v>
+        <v>0.045424</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>7.83</v>
+        <v>7.82</v>
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
@@ -2943,16 +2943,16 @@
         <v>31</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>0.0442641</v>
+        <v>0.0447173</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>0.0441853</v>
+        <v>0.0446368</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>0.0450732</v>
+        <v>0.04552539999999999</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>8.09</v>
+        <v>8.08</v>
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
@@ -2979,16 +2979,16 @@
         <v>30</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>0.044332</v>
+        <v>0.044803</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>0.04425519999999999</v>
+        <v>0.0447246</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0.0451666</v>
+        <v>0.0456366</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>8.35</v>
+        <v>8.34</v>
       </c>
       <c r="H71" s="14" t="inlineStr">
         <is>
@@ -3015,16 +3015,16 @@
         <v>31</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>0.044413</v>
+        <v>0.0449039</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>0.0443337</v>
+        <v>0.0448228</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0.0452753</v>
+        <v>0.0457653</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>8.619999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
@@ -3051,16 +3051,16 @@
         <v>30</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>0.0444804</v>
+        <v>0.04498249999999999</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>0.0444037</v>
+        <v>0.044904</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0.0453679</v>
+        <v>0.045869</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>8.869999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
@@ -3087,16 +3087,16 @@
         <v>31</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>0.0445617</v>
+        <v>0.04506719999999999</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>0.0444815</v>
+        <v>0.04498509999999999</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0.04547850000000001</v>
+        <v>0.045983</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>9.17</v>
+        <v>9.16</v>
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
@@ -3123,16 +3123,16 @@
         <v>31</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>0.04463180000000001</v>
+        <v>0.04513259999999999</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>0.0445518</v>
+        <v>0.0450509</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0.0455753</v>
+        <v>0.0460752</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>9.44</v>
+        <v>9.43</v>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
@@ -3159,16 +3159,16 @@
         <v>29</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>0.0447007</v>
+        <v>0.0451943</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>0.044626</v>
+        <v>0.045118</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>0.0456718</v>
+        <v>0.0461644</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>9.710000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
@@ -3195,16 +3195,16 @@
         <v>31</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>0.0447833</v>
+        <v>0.0452722</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>0.0447027</v>
+        <v>0.04518970000000001</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0.0457838</v>
+        <v>0.0462717</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="H77" s="14" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
         <v>30</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>0.04484950000000001</v>
+        <v>0.0453409</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>0.0447709</v>
+        <v>0.0452606</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0.0458784</v>
+        <v>0.0463687</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>10.29</v>
+        <v>10.28</v>
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
@@ -3267,16 +3267,16 @@
         <v>31</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>0.0449062</v>
+        <v>0.0454091</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0.0448253</v>
+        <v>0.0453264</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0.04596219999999999</v>
+        <v>0.0464641</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>10.56</v>
+        <v>10.55</v>
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
@@ -3303,16 +3303,16 @@
         <v>30</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>0.0449583</v>
+        <v>0.045481</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>0.0448798</v>
+        <v>0.0454008</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0.0460453</v>
+        <v>0.046567</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>10.87</v>
+        <v>10.86</v>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
@@ -3339,16 +3339,16 @@
         <v>31</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>0.0450138</v>
+        <v>0.0455551</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>0.0449325</v>
+        <v>0.0454718</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0.0461305</v>
+        <v>0.0466707</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>11.17</v>
+        <v>11.16</v>
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
@@ -3375,16 +3375,16 @@
         <v>31</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>0.0450753</v>
+        <v>0.0456268</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>0.044993</v>
+        <v>0.0455425</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0.0462209</v>
+        <v>0.0467714</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>11.46</v>
+        <v>11.45</v>
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
@@ -3411,16 +3411,16 @@
         <v>30</v>
       </c>
       <c r="D83" s="12" t="n">
-        <v>0.0451452</v>
+        <v>0.0456985</v>
       </c>
       <c r="E83" s="12" t="n">
-        <v>0.0450661</v>
+        <v>0.0456174</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0.0463218</v>
+        <v>0.0468739</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>11.77</v>
+        <v>11.75</v>
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
@@ -3447,16 +3447,16 @@
         <v>31</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>0.0452176</v>
+        <v>0.0457673</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>0.0451359</v>
+        <v>0.0456836</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0.0464249</v>
+        <v>0.0469735</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>12.07</v>
+        <v>12.06</v>
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
@@ -3483,16 +3483,16 @@
         <v>30</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>0.045275</v>
+        <v>0.0458213</v>
       </c>
       <c r="E85" s="12" t="n">
-        <v>0.04519529999999999</v>
+        <v>0.0457397</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>0.0465133</v>
+        <v>0.0470584</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>12.38</v>
+        <v>12.37</v>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         <v>31</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>0.0453279</v>
+        <v>0.0458733</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>0.0452453</v>
+        <v>0.0457887</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>0.0465979</v>
+        <v>0.04714209999999999</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>12.7</v>
+        <v>12.69</v>
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
@@ -3555,16 +3555,16 @@
         <v>31</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>0.0453757</v>
+        <v>0.0459217</v>
       </c>
       <c r="E87" s="12" t="n">
-        <v>0.0452931</v>
+        <v>0.0458371</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0.0466753</v>
+        <v>0.0472202</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>13</v>
+        <v>12.98</v>
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
@@ -3591,16 +3591,16 @@
         <v>28</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>0.0454312</v>
+        <v>0.045978</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>0.0453571</v>
+        <v>0.04590200000000001</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0.0467641</v>
+        <v>0.0473097</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>13.33</v>
+        <v>13.32</v>
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>31</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>0.0455103</v>
+        <v>0.0460576</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>0.0454265</v>
+        <v>0.0459718</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>0.0468754</v>
+        <v>0.0474216</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>13.65</v>
+        <v>13.64</v>
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
@@ -3663,16 +3663,16 @@
         <v>30</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>0.0455745</v>
+        <v>0.04612160000000001</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>0.0454941</v>
+        <v>0.0460392</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0.0469711</v>
+        <v>0.047517</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>13.97</v>
+        <v>13.95</v>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
@@ -3699,16 +3699,16 @@
         <v>31</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>0.0456313</v>
+        <v>0.04617810000000001</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>0.0455475</v>
+        <v>0.0460924</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>0.0470589</v>
+        <v>0.0476046</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>14.28</v>
+        <v>14.26</v>
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
@@ -3735,16 +3735,16 @@
         <v>30</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>0.0456713</v>
+        <v>0.0462177</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>0.0455904</v>
+        <v>0.0461349</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>0.04713199999999999</v>
+        <v>0.04767730000000001</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>14.61</v>
+        <v>14.6</v>
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
@@ -3771,16 +3771,16 @@
         <v>31</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>0.0457076</v>
+        <v>0.046254</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>0.0456241</v>
+        <v>0.0461685</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>0.0472014</v>
+        <v>0.0477465</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>14.94</v>
+        <v>14.93</v>
       </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
@@ -3807,16 +3807,16 @@
         <v>31</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>0.0457451</v>
+        <v>0.0462915</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>0.04566029999999999</v>
+        <v>0.0462047</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>0.0472726</v>
+        <v>0.0478177</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>15.28</v>
+        <v>15.26</v>
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
@@ -3843,16 +3843,16 @@
         <v>30</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>0.0457873</v>
+        <v>0.04633370000000001</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>0.045706</v>
+        <v>0.0462505</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>0.04734910000000001</v>
+        <v>0.0478942</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>15.62</v>
+        <v>15.6</v>
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
@@ -3879,16 +3879,16 @@
         <v>31</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>0.04584609999999999</v>
+        <v>0.0463928</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>0.0457617</v>
+        <v>0.0463064</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>0.047441</v>
+        <v>0.0479864</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>15.95</v>
+        <v>15.94</v>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
@@ -3915,16 +3915,16 @@
         <v>30</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>0.0459193</v>
+        <v>0.0464663</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>0.0458377</v>
+        <v>0.04638270000000001</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>0.047552</v>
+        <v>0.0480977</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>16.33</v>
+        <v>16.31</v>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
@@ -3951,16 +3951,16 @@
         <v>31</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>0.0459956</v>
+        <v>0.046543</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>0.0459107</v>
+        <v>0.046456</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>0.0476644</v>
+        <v>0.0482105</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>16.69</v>
+        <v>16.67</v>
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
@@ -3987,16 +3987,16 @@
         <v>31</v>
       </c>
       <c r="D99" s="12" t="n">
-        <v>0.0460443</v>
+        <v>0.0465918</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>0.0459592</v>
+        <v>0.0465047</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>0.0477461</v>
+        <v>0.0482923</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>17.02</v>
+        <v>17</v>
       </c>
       <c r="H99" s="14" t="inlineStr">
         <is>
@@ -4023,16 +4023,16 @@
         <v>28</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>0.0460528</v>
+        <v>0.0465999</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>0.04597660000000001</v>
+        <v>0.0465219</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>0.0477905</v>
+        <v>0.04833630000000001</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>17.38</v>
+        <v>17.36</v>
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
@@ -4059,16 +4059,16 @@
         <v>31</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>0.0460498</v>
+        <v>0.0465968</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>0.0459639</v>
+        <v>0.04650890000000001</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>0.0478219</v>
+        <v>0.0483675</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>17.72</v>
+        <v>17.71</v>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         <v>30</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>0.0460447</v>
+        <v>0.0465912</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>0.0459626</v>
+        <v>0.0465072</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>0.0478482</v>
+        <v>0.0483933</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>18.04</v>
+        <v>18.02</v>
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
         <v>31</v>
       </c>
       <c r="D103" s="12" t="n">
-        <v>0.0460869</v>
+        <v>0.0466333</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>0.0460015</v>
+        <v>0.0465459</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>0.04792830000000001</v>
+        <v>0.0484734</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>18.41</v>
+        <v>18.4</v>
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
@@ -4167,16 +4167,16 @@
         <v>30</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>0.0461602</v>
+        <v>0.0467066</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>0.0460775</v>
+        <v>0.046622</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>0.0480381</v>
+        <v>0.0485832</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>18.78</v>
+        <v>18.77</v>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
@@ -4203,16 +4203,16 @@
         <v>31</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>0.0462323</v>
+        <v>0.0467791</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>0.0461461</v>
+        <v>0.0466909</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>0.0481458</v>
+        <v>0.0486912</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>19.13</v>
+        <v>19.12</v>
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
@@ -4239,16 +4239,16 @@
         <v>31</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>0.0462643</v>
+        <v>0.04681129999999999</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>0.0461776</v>
+        <v>0.0467226</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>0.0482179</v>
+        <v>0.0487636</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>19.54</v>
+        <v>19.52</v>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         <v>30</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>0.0462423</v>
+        <v>0.04678930000000001</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>0.0461595</v>
+        <v>0.04670460000000001</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>0.0482329</v>
+        <v>0.0487785</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>19.91</v>
+        <v>19.89</v>
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
@@ -4311,16 +4311,16 @@
         <v>31</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>0.0462336</v>
+        <v>0.0467807</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>0.0461477</v>
+        <v>0.0466927</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>0.0482605</v>
+        <v>0.0488061</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>20.27</v>
+        <v>20.25</v>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
@@ -4347,16 +4347,16 @@
         <v>30</v>
       </c>
       <c r="D109" s="12" t="n">
-        <v>0.0462825</v>
+        <v>0.0468294</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>0.046199</v>
+        <v>0.0467439</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>0.0483478</v>
+        <v>0.0488933</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>20.65</v>
+        <v>20.64</v>
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
@@ -4383,16 +4383,16 @@
         <v>31</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>0.0464029</v>
+        <v>0.0469498</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>0.04631680000000001</v>
+        <v>0.0468618</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>0.0485062</v>
+        <v>0.0490517</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>21.03</v>
+        <v>21.02</v>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
@@ -4419,16 +4419,16 @@
         <v>31</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0.0465297</v>
+        <v>0.0470767</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>0.0464426</v>
+        <v>0.0469875</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>0.0486699</v>
+        <v>0.0492155</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>21.4</v>
+        <v>21.39</v>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
@@ -4455,16 +4455,16 @@
         <v>28</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0.0466001</v>
+        <v>0.0471469</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>0.04652199999999999</v>
+        <v>0.047067</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>0.0487786</v>
+        <v>0.04932400000000001</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>21.79</v>
+        <v>21.77</v>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
@@ -4491,16 +4491,16 @@
         <v>31</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.0466153</v>
+        <v>0.0471624</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>0.0465281</v>
+        <v>0.0470731</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>0.0488328</v>
+        <v>0.0493783</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>22.17</v>
+        <v>22.16</v>
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>30</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0.0465852</v>
+        <v>0.0471322</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>0.0465004</v>
+        <v>0.04704539999999999</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>0.04883949999999999</v>
+        <v>0.0493849</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>22.54</v>
+        <v>22.53</v>
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
@@ -4563,16 +4563,16 @@
         <v>31</v>
       </c>
       <c r="D115" s="12" t="n">
-        <v>0.0465781</v>
+        <v>0.0471251</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>0.0464909</v>
+        <v>0.0470358</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>0.048873</v>
+        <v>0.0494185</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>22.95</v>
+        <v>22.93</v>
       </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
@@ -4599,16 +4599,16 @@
         <v>30</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>0.0466064</v>
+        <v>0.04715340000000001</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>0.04652199999999999</v>
+        <v>0.0470669</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>0.0489409</v>
+        <v>0.0494863</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>23.34</v>
+        <v>23.33</v>
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
@@ -4635,16 +4635,16 @@
         <v>31</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>0.0466612</v>
+        <v>0.0472082</v>
       </c>
       <c r="E117" s="12" t="n">
-        <v>0.0465732</v>
+        <v>0.04711820000000001</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>0.0490349</v>
+        <v>0.0495805</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>23.74</v>
+        <v>23.72</v>
       </c>
       <c r="H117" s="14" t="inlineStr">
         <is>
@@ -4671,16 +4671,16 @@
         <v>31</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>0.0467079</v>
+        <v>0.0472549</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>0.0466195</v>
+        <v>0.0471645</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>0.049123</v>
+        <v>0.04966859999999999</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>24.15</v>
+        <v>24.14</v>
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
@@ -4707,16 +4707,16 @@
         <v>30</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>0.04673339999999999</v>
+        <v>0.0472803</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>0.0466486</v>
+        <v>0.0471936</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>0.049184</v>
+        <v>0.04972940000000001</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>24.51</v>
+        <v>24.49</v>
       </c>
       <c r="H119" s="14" t="inlineStr">
         <is>
@@ -4743,16 +4743,16 @@
         <v>31</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>0.0467861</v>
+        <v>0.0473331</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>0.0466981</v>
+        <v>0.04724300000000001</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>0.049281</v>
+        <v>0.0498265</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>24.95</v>
+        <v>24.93</v>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
@@ -4779,16 +4779,16 @@
         <v>30</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>0.04687</v>
+        <v>0.0474169</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>0.04678499999999999</v>
+        <v>0.0473299</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>0.04940489999999999</v>
+        <v>0.0499503</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>25.35</v>
+        <v>25.33</v>
       </c>
       <c r="H121" s="14" t="inlineStr">
         <is>
@@ -4815,16 +4815,16 @@
         <v>31</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.0469883</v>
+        <v>0.0475353</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>0.0468993</v>
+        <v>0.0474442</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>0.04956190000000001</v>
+        <v>0.05010729999999999</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>25.74</v>
+        <v>25.72</v>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
@@ -4851,16 +4851,16 @@
         <v>31</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>0.0471114</v>
+        <v>0.0476584</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>0.0470221</v>
+        <v>0.04756700000000001</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>0.04972749999999999</v>
+        <v>0.05027300000000001</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>26.16</v>
+        <v>26.15</v>
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
@@ -4887,16 +4887,16 @@
         <v>29</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>0.0471821</v>
+        <v>0.047729</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>0.047099</v>
+        <v>0.0476439</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>0.0498401</v>
+        <v>0.0503854</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>26.58</v>
+        <v>26.56</v>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
@@ -4923,16 +4923,16 @@
         <v>31</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>0.04720100000000001</v>
+        <v>0.0477481</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>0.047111</v>
+        <v>0.047656</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>0.0498982</v>
+        <v>0.0504437</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>26.97</v>
+        <v>26.96</v>
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>30</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>0.04716529999999999</v>
+        <v>0.0477123</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>0.047079</v>
+        <v>0.04762400000000001</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>0.0499056</v>
+        <v>0.050451</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>27.4</v>
+        <v>27.39</v>
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
@@ -4995,16 +4995,16 @@
         <v>31</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>0.0471146</v>
+        <v>0.0476617</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>0.0470255</v>
+        <v>0.04757049999999999</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>0.0498961</v>
+        <v>0.0504416</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>27.82</v>
+        <v>27.8</v>
       </c>
       <c r="H127" s="14" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>30</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>0.0470552</v>
+        <v>0.0476022</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>0.0469689</v>
+        <v>0.0475139</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>0.0498758</v>
+        <v>0.0504212</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>28.21</v>
+        <v>28.19</v>
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
@@ -5067,16 +5067,16 @@
         <v>31</v>
       </c>
       <c r="D129" s="18" t="n">
-        <v>0.04705599999999999</v>
+        <v>0.0476031</v>
       </c>
       <c r="E129" s="18" t="n">
-        <v>0.04696690000000001</v>
+        <v>0.0475119</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.0498783</v>
+        <v>0.0504238</v>
       </c>
       <c r="G129" s="19" t="n">
-        <v>28.22</v>
+        <v>28.21</v>
       </c>
       <c r="H129" s="20" t="inlineStr">
         <is>
@@ -5103,16 +5103,16 @@
         <v>31</v>
       </c>
       <c r="D130" s="18" t="n">
-        <v>0.04705599999999999</v>
+        <v>0.0476031</v>
       </c>
       <c r="E130" s="18" t="n">
-        <v>0.04696690000000001</v>
+        <v>0.0475119</v>
       </c>
       <c r="F130" s="18" t="n">
-        <v>0.0498783</v>
+        <v>0.0504238</v>
       </c>
       <c r="G130" s="19" t="n">
-        <v>28.22</v>
+        <v>28.21</v>
       </c>
       <c r="H130" s="20" t="inlineStr">
         <is>
@@ -5139,16 +5139,16 @@
         <v>30</v>
       </c>
       <c r="D131" s="18" t="n">
-        <v>0.0470534</v>
+        <v>0.0476004</v>
       </c>
       <c r="E131" s="18" t="n">
-        <v>0.04696690000000001</v>
+        <v>0.0475119</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.0498755</v>
+        <v>0.0504208</v>
       </c>
       <c r="G131" s="19" t="n">
-        <v>28.22</v>
+        <v>28.2</v>
       </c>
       <c r="H131" s="20" t="inlineStr">
         <is>
@@ -5175,16 +5175,16 @@
         <v>31</v>
       </c>
       <c r="D132" s="18" t="n">
-        <v>0.04705599999999999</v>
+        <v>0.0476031</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>0.04696690000000001</v>
+        <v>0.0475119</v>
       </c>
       <c r="F132" s="18" t="n">
-        <v>0.0498783</v>
+        <v>0.0504238</v>
       </c>
       <c r="G132" s="19" t="n">
-        <v>28.22</v>
+        <v>28.21</v>
       </c>
       <c r="H132" s="20" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-22)</t>
+          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-23)</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
         <v>46344</v>
       </c>
       <c r="D4" s="23" t="n">
-        <v>96.1725</v>
+        <v>96.1675</v>
       </c>
       <c r="E4" s="15">
         <f>(100-D4)/100</f>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.0383075</v>
+        <v>0.0383419</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>0.325</v>
+        <v>0.169</v>
       </c>
       <c r="I4" s="25" t="n">
         <v>7574</v>
@@ -5596,7 +5596,7 @@
         <v>46372</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>96.06999999999999</v>
+        <v>96.065</v>
       </c>
       <c r="E5" s="15">
         <f>(100-D5)/100</f>
@@ -5606,13 +5606,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.0392957</v>
+        <v>0.0393544</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>-0.043</v>
+        <v>0.044</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>1303679</v>
+        <v>1315971</v>
       </c>
     </row>
     <row r="6">
@@ -5628,7 +5628,7 @@
         <v>46327</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>96.11</v>
+        <v>96.105</v>
       </c>
       <c r="E6" s="15">
         <f>(100-D6)/100</f>
@@ -5638,13 +5638,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.0388639</v>
+        <v>0.038911</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>-0.361</v>
+        <v>-0.39</v>
       </c>
       <c r="I6" s="25" t="n">
-        <v>353705</v>
+        <v>361918</v>
       </c>
     </row>
     <row r="7">
@@ -5660,7 +5660,7 @@
         <v>46407</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>95.9725</v>
+        <v>95.9675</v>
       </c>
       <c r="E7" s="15">
         <f>(100-D7)/100</f>
@@ -5670,13 +5670,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.0402708</v>
+        <v>0.0403352</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>-0.042</v>
+        <v>0.102</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>7233</v>
+        <v>7222</v>
       </c>
     </row>
     <row r="8">
@@ -5692,7 +5692,7 @@
         <v>46357</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>96.08499999999999</v>
+        <v>96.075</v>
       </c>
       <c r="E8" s="15">
         <f>(100-D8)/100</f>
@@ -5702,13 +5702,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.0391769</v>
+        <v>0.0392729</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>0.269</v>
+        <v>0.229</v>
       </c>
       <c r="I8" s="25" t="n">
-        <v>296856</v>
+        <v>289356</v>
       </c>
     </row>
     <row r="9">
@@ -5724,7 +5724,7 @@
         <v>46435</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>95.8925</v>
+        <v>95.8875</v>
       </c>
       <c r="E9" s="15">
         <f>(100-D9)/100</f>
@@ -5734,13 +5734,13 @@
         <v>0.01</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.0410614</v>
+        <v>0.0411115</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.136</v>
+        <v>-0.135</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>2585</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="10">
@@ -5756,7 +5756,7 @@
         <v>46388</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>95.935</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="E10" s="15">
         <f>(100-D10)/100</f>
@@ -5766,13 +5766,13 @@
         <v>0.01</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.0406217</v>
+        <v>0.0406597</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.283</v>
+        <v>-0.403</v>
       </c>
       <c r="I10" s="25" t="n">
-        <v>232198</v>
+        <v>239346</v>
       </c>
     </row>
     <row r="11">
@@ -5788,7 +5788,7 @@
         <v>46463</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>95.83</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="E11" s="15">
         <f>(100-D11)/100</f>
@@ -5798,13 +5798,13 @@
         <v>0.02</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.0417497</v>
+        <v>0.0418019</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>0.497</v>
+        <v>0.019</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>1566590</v>
+        <v>1573564</v>
       </c>
     </row>
     <row r="12">
@@ -5830,13 +5830,13 @@
         <v>0.02</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.0412925</v>
+        <v>0.0413159</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.075</v>
+        <v>0.159</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>183605</v>
+        <v>186854</v>
       </c>
     </row>
     <row r="13">
@@ -5852,7 +5852,7 @@
         <v>46498</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>95.75</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="E13" s="15">
         <f>(100-D13)/100</f>
@@ -5862,13 +5862,13 @@
         <v>0.05</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.0424615</v>
+        <v>0.0426102</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>-0.385</v>
+        <v>0.102</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>1233</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="14">
@@ -5884,7 +5884,7 @@
         <v>46447</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>95.81999999999999</v>
+        <v>95.81</v>
       </c>
       <c r="E14" s="15">
         <f>(100-D14)/100</f>
@@ -5894,13 +5894,13 @@
         <v>0.04</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.0418261</v>
+        <v>0.04191130000000001</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.261</v>
+        <v>0.113</v>
       </c>
       <c r="I14" s="25" t="n">
-        <v>103380</v>
+        <v>100934</v>
       </c>
     </row>
     <row r="15">
@@ -5916,7 +5916,7 @@
         <v>46526</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>95.69</v>
+        <v>95.675</v>
       </c>
       <c r="E15" s="15">
         <f>(100-D15)/100</f>
@@ -5926,13 +5926,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.0430563</v>
+        <v>0.043298</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.437</v>
+        <v>0.48</v>
       </c>
       <c r="I15" s="25" t="n">
-        <v>559</v>
+        <v>554</v>
       </c>
     </row>
     <row r="16">
@@ -5948,7 +5948,7 @@
         <v>46478</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>95.76000000000001</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="E16" s="15">
         <f>(100-D16)/100</f>
@@ -5958,13 +5958,13 @@
         <v>0.06</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.0423928</v>
+        <v>0.0425603</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.397</v>
       </c>
       <c r="I16" s="25" t="n">
-        <v>34419</v>
+        <v>35762</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>46554</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>95.63</v>
+        <v>95.59</v>
       </c>
       <c r="E17" s="15">
         <f>(100-D17)/100</f>
@@ -5990,13 +5990,13 @@
         <v>0.1</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.0437171</v>
+        <v>0.0440632</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.171</v>
+        <v>-0.368</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>1359464</v>
+        <v>1334265</v>
       </c>
     </row>
     <row r="18">
@@ -6012,7 +6012,7 @@
         <v>46508</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>95.69</v>
+        <v>95.66</v>
       </c>
       <c r="E18" s="15">
         <f>(100-D18)/100</f>
@@ -6022,13 +6022,13 @@
         <v>0.09</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.0431258</v>
+        <v>0.04340239999999999</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>0.258</v>
+        <v>0.024</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>60743</v>
+        <v>69216</v>
       </c>
     </row>
     <row r="19">
@@ -6044,7 +6044,7 @@
         <v>46539</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>95.625</v>
+        <v>95.58499999999999</v>
       </c>
       <c r="E19" s="15">
         <f>(100-D19)/100</f>
@@ -6054,13 +6054,13 @@
         <v>0.13</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.0437568</v>
+        <v>0.0441594</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>0.068</v>
+        <v>0.094</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>70319</v>
+        <v>71683</v>
       </c>
     </row>
     <row r="20">
@@ -6076,7 +6076,7 @@
         <v>46569</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>95.56</v>
+        <v>95.515</v>
       </c>
       <c r="E20" s="15">
         <f>(100-D20)/100</f>
@@ -6086,13 +6086,13 @@
         <v>0.17</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.0443935</v>
+        <v>0.04485579999999999</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>-0.065</v>
+        <v>0.058</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>20020</v>
+        <v>21182</v>
       </c>
     </row>
     <row r="21">
@@ -6108,7 +6108,7 @@
         <v>46645</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>95.48999999999999</v>
+        <v>95.44</v>
       </c>
       <c r="E21" s="15">
         <f>(100-D21)/100</f>
@@ -6118,13 +6118,13 @@
         <v>0.23</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.04509559999999999</v>
+        <v>0.045603</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>-0.044</v>
+        <v>0.03</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>1260932</v>
+        <v>1238896</v>
       </c>
     </row>
     <row r="22">
@@ -6140,7 +6140,7 @@
         <v>46600</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>95.53</v>
+        <v>95.48</v>
       </c>
       <c r="E22" s="15">
         <f>(100-D22)/100</f>
@@ -6150,10 +6150,10 @@
         <v>0.21</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.0447014</v>
+        <v>0.0451918</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>0.014</v>
+        <v>-0.082</v>
       </c>
       <c r="I22" s="25" t="n">
         <v>38412</v>
@@ -6172,7 +6172,7 @@
         <v>46631</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>95.5</v>
+        <v>95.45</v>
       </c>
       <c r="E23" s="15">
         <f>(100-D23)/100</f>
@@ -6182,13 +6182,13 @@
         <v>0.26</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.045007</v>
+        <v>0.0455212</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.212</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>19917</v>
+        <v>19872</v>
       </c>
     </row>
     <row r="24">
@@ -6204,7 +6204,7 @@
         <v>46661</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>95.48</v>
+        <v>95.425</v>
       </c>
       <c r="E24" s="15">
         <f>(100-D24)/100</f>
@@ -6214,13 +6214,13 @@
         <v>0.32</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.0451957</v>
+        <v>0.0457113</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>-0.043</v>
+        <v>-0.387</v>
       </c>
       <c r="I24" s="25" t="n">
-        <v>4910</v>
+        <v>5238</v>
       </c>
     </row>
     <row r="25">
@@ -6236,7 +6236,7 @@
         <v>46736</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>95.44</v>
+        <v>95.39</v>
       </c>
       <c r="E25" s="15">
         <f>(100-D25)/100</f>
@@ -6246,13 +6246,13 @@
         <v>0.4</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.0456291</v>
+        <v>0.0461397</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>0.291</v>
+        <v>0.397</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>1070636</v>
+        <v>1071479</v>
       </c>
     </row>
     <row r="26">
@@ -6268,7 +6268,7 @@
         <v>46692</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>95.45999999999999</v>
+        <v>95.41</v>
       </c>
       <c r="E26" s="15">
         <f>(100-D26)/100</f>
@@ -6278,13 +6278,13 @@
         <v>0.38</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.0453846</v>
+        <v>0.0458985</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>-0.154</v>
+        <v>-0.015</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>7003</v>
+        <v>7666</v>
       </c>
     </row>
     <row r="27">
@@ -6300,20 +6300,20 @@
         <v>46722</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>95.45999999999999</v>
+        <v>95.41</v>
       </c>
       <c r="E27" s="15">
         <f>(100-D27)/100</f>
         <v/>
       </c>
       <c r="F27" s="24" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.04538859999999999</v>
+        <v>0.0458821</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>-0.114</v>
+        <v>-0.179</v>
       </c>
       <c r="I27" s="25" t="n">
         <v>1769</v>
@@ -6332,7 +6332,7 @@
         <v>46827</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>95.45</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E28" s="15">
         <f>(100-D28)/100</f>
@@ -6342,13 +6342,13 @@
         <v>0.62</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.045498</v>
+        <v>0.04599669999999999</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>-0.02</v>
+        <v>-0.033</v>
       </c>
       <c r="I28" s="25" t="n">
-        <v>1651579</v>
+        <v>1618719</v>
       </c>
     </row>
     <row r="29">
@@ -6364,7 +6364,7 @@
         <v>46925</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>95.47</v>
+        <v>95.425</v>
       </c>
       <c r="E29" s="15">
         <f>(100-D29)/100</f>
@@ -6374,13 +6374,13 @@
         <v>0.9</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.0453006</v>
+        <v>0.0457515</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>831516</v>
+        <v>830047</v>
       </c>
     </row>
     <row r="30">
@@ -6396,7 +6396,7 @@
         <v>47016</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>95.48999999999999</v>
+        <v>95.44499999999999</v>
       </c>
       <c r="E30" s="15">
         <f>(100-D30)/100</f>
@@ -6406,13 +6406,13 @@
         <v>1.22</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.0451016</v>
+        <v>0.0455507</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="I30" s="25" t="n">
-        <v>636471</v>
+        <v>659097</v>
       </c>
     </row>
     <row r="31">
@@ -6428,23 +6428,23 @@
         <v>47107</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>95.505</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="E31" s="15">
         <f>(100-D31)/100</f>
         <v/>
       </c>
       <c r="F31" s="24" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.0449466</v>
+        <v>0.0453979</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.021</v>
       </c>
       <c r="I31" s="25" t="n">
-        <v>676741</v>
+        <v>678440</v>
       </c>
     </row>
     <row r="32">
@@ -6460,23 +6460,23 @@
         <v>47198</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>95.52500000000001</v>
+        <v>95.48</v>
       </c>
       <c r="E32" s="15">
         <f>(100-D32)/100</f>
         <v/>
       </c>
       <c r="F32" s="24" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.0447524</v>
+        <v>0.0452012</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>0.024</v>
+        <v>0.012</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>542344</v>
+        <v>552076</v>
       </c>
     </row>
     <row r="33">
@@ -6492,7 +6492,7 @@
         <v>47289</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>95.54000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="E33" s="15">
         <f>(100-D33)/100</f>
@@ -6502,13 +6502,13 @@
         <v>2.41</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.0446001</v>
+        <v>0.0449984</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>0.001</v>
+        <v>-0.016</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>382026</v>
+        <v>381514</v>
       </c>
     </row>
     <row r="34">
@@ -6524,23 +6524,23 @@
         <v>47380</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>95.55</v>
+        <v>95.515</v>
       </c>
       <c r="E34" s="15">
         <f>(100-D34)/100</f>
         <v/>
       </c>
       <c r="F34" s="24" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.0444989</v>
+        <v>0.044854</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>-0.011</v>
+        <v>0.04</v>
       </c>
       <c r="I34" s="25" t="n">
-        <v>382203</v>
+        <v>391934</v>
       </c>
     </row>
     <row r="35">
@@ -6556,23 +6556,23 @@
         <v>47471</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>95.56</v>
+        <v>95.52</v>
       </c>
       <c r="E35" s="15">
         <f>(100-D35)/100</f>
         <v/>
       </c>
       <c r="F35" s="24" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.0443994</v>
+        <v>0.0447947</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>-0.006</v>
+        <v>-0.053</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>318885</v>
+        <v>303902</v>
       </c>
     </row>
     <row r="36">
@@ -6588,23 +6588,23 @@
         <v>47562</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>95.565</v>
+        <v>95.52500000000001</v>
       </c>
       <c r="E36" s="15">
         <f>(100-D36)/100</f>
         <v/>
       </c>
       <c r="F36" s="24" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.04435310000000001</v>
+        <v>0.0447557</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>0.031</v>
+        <v>0.057</v>
       </c>
       <c r="I36" s="25" t="n">
-        <v>241835</v>
+        <v>244481</v>
       </c>
     </row>
     <row r="37">
@@ -6620,23 +6620,23 @@
         <v>47653</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>95.56</v>
+        <v>95.52</v>
       </c>
       <c r="E37" s="15">
         <f>(100-D37)/100</f>
         <v/>
       </c>
       <c r="F37" s="24" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.0443966</v>
+        <v>0.0447943</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.057</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>177899</v>
+        <v>180561</v>
       </c>
     </row>
     <row r="38">
@@ -6652,23 +6652,23 @@
         <v>47744</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>95.55500000000001</v>
+        <v>95.515</v>
       </c>
       <c r="E38" s="15">
         <f>(100-D38)/100</f>
         <v/>
       </c>
       <c r="F38" s="24" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.0444521</v>
+        <v>0.0448556</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>0.021</v>
+        <v>0.056</v>
       </c>
       <c r="I38" s="25" t="n">
-        <v>157777</v>
+        <v>157616</v>
       </c>
     </row>
     <row r="39">
@@ -6684,23 +6684,23 @@
         <v>47835</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>95.545</v>
+        <v>95.5</v>
       </c>
       <c r="E39" s="15">
         <f>(100-D39)/100</f>
         <v/>
       </c>
       <c r="F39" s="24" t="n">
-        <v>5.84</v>
+        <v>5.83</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.044548</v>
+        <v>0.0449944</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>-0.02</v>
+        <v>-0.056</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>143895</v>
+        <v>148421</v>
       </c>
     </row>
     <row r="40">
@@ -6716,23 +6716,23 @@
         <v>47926</v>
       </c>
       <c r="D40" s="23" t="n">
-        <v>95.53</v>
+        <v>95.485</v>
       </c>
       <c r="E40" s="15">
         <f>(100-D40)/100</f>
         <v/>
       </c>
       <c r="F40" s="24" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.0447032</v>
+        <v>0.0451554</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>0.032</v>
+        <v>0.054</v>
       </c>
       <c r="I40" s="25" t="n">
-        <v>116482</v>
+        <v>116344</v>
       </c>
     </row>
     <row r="41">
@@ -6748,23 +6748,23 @@
         <v>48017</v>
       </c>
       <c r="D41" s="23" t="n">
-        <v>95.505</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="E41" s="15">
         <f>(100-D41)/100</f>
         <v/>
       </c>
       <c r="F41" s="24" t="n">
-        <v>7.27</v>
+        <v>7.26</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.0449466</v>
+        <v>0.0453944</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.056</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>92312</v>
+        <v>87263</v>
       </c>
     </row>
     <row r="42">
@@ -6780,23 +6780,23 @@
         <v>48108</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>95.48</v>
+        <v>95.435</v>
       </c>
       <c r="E42" s="15">
         <f>(100-D42)/100</f>
         <v/>
       </c>
       <c r="F42" s="24" t="n">
-        <v>8.029999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.04520279999999999</v>
+        <v>0.0456562</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>0.028</v>
+        <v>0.062</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>69978</v>
+        <v>72512</v>
       </c>
     </row>
     <row r="43">
@@ -6812,23 +6812,23 @@
         <v>48199</v>
       </c>
       <c r="D43" s="23" t="n">
-        <v>95.45</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E43" s="15">
         <f>(100-D43)/100</f>
         <v/>
       </c>
       <c r="F43" s="24" t="n">
-        <v>8.83</v>
+        <v>8.82</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.045498</v>
+        <v>0.045995</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>35785</v>
+        <v>38592</v>
       </c>
     </row>
     <row r="44">
@@ -6844,23 +6844,23 @@
         <v>48290</v>
       </c>
       <c r="D44" s="23" t="n">
-        <v>95.42</v>
+        <v>95.37</v>
       </c>
       <c r="E44" s="15">
         <f>(100-D44)/100</f>
         <v/>
       </c>
       <c r="F44" s="24" t="n">
-        <v>9.65</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.04580219999999999</v>
+        <v>0.0463023</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>8183</v>
+        <v>7219</v>
       </c>
     </row>
     <row r="45">
@@ -6876,23 +6876,23 @@
         <v>48381</v>
       </c>
       <c r="D45" s="23" t="n">
-        <v>95.39</v>
+        <v>95.34</v>
       </c>
       <c r="E45" s="15">
         <f>(100-D45)/100</f>
         <v/>
       </c>
       <c r="F45" s="24" t="n">
-        <v>10.51</v>
+        <v>10.5</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.0460961</v>
+        <v>0.046599</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>-0.039</v>
+        <v>-0.01</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>2008</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="46">
@@ -6908,23 +6908,23 @@
         <v>48472</v>
       </c>
       <c r="D46" s="23" t="n">
-        <v>95.36499999999999</v>
+        <v>95.31</v>
       </c>
       <c r="E46" s="15">
         <f>(100-D46)/100</f>
         <v/>
       </c>
       <c r="F46" s="24" t="n">
-        <v>11.4</v>
+        <v>11.39</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.0463552</v>
+        <v>0.046902</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>0.052</v>
+        <v>0.02</v>
       </c>
       <c r="I46" s="25" t="n">
-        <v>823</v>
+        <v>905</v>
       </c>
     </row>
     <row r="47">
@@ -6940,23 +6940,23 @@
         <v>48563</v>
       </c>
       <c r="D47" s="23" t="n">
-        <v>95.33499999999999</v>
+        <v>95.28</v>
       </c>
       <c r="E47" s="15">
         <f>(100-D47)/100</f>
         <v/>
       </c>
       <c r="F47" s="24" t="n">
-        <v>12.31</v>
+        <v>12.3</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.0466443</v>
+        <v>0.04719599999999999</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>-0.057</v>
+        <v>-0.04</v>
       </c>
       <c r="I47" s="25" t="n">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="48">
@@ -6972,20 +6972,20 @@
         <v>48654</v>
       </c>
       <c r="D48" s="23" t="n">
-        <v>95.31</v>
+        <v>95.255</v>
       </c>
       <c r="E48" s="15">
         <f>(100-D48)/100</f>
         <v/>
       </c>
       <c r="F48" s="24" t="n">
-        <v>13.25</v>
+        <v>13.24</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.046906</v>
+        <v>0.0474555</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="I48" s="25" t="n">
         <v>164</v>
@@ -7004,20 +7004,20 @@
         <v>48745</v>
       </c>
       <c r="D49" s="23" t="n">
-        <v>95.28</v>
+        <v>95.22499999999999</v>
       </c>
       <c r="E49" s="15">
         <f>(100-D49)/100</f>
         <v/>
       </c>
       <c r="F49" s="24" t="n">
-        <v>14.23</v>
+        <v>14.21</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.0471948</v>
+        <v>0.0477449</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>-0.052</v>
+        <v>-0.051</v>
       </c>
       <c r="I49" s="25" t="n">
         <v>35</v>
@@ -7036,17 +7036,17 @@
         <v>48843</v>
       </c>
       <c r="D50" s="23" t="n">
-        <v>95.255</v>
+        <v>95.2</v>
       </c>
       <c r="E50" s="15">
         <f>(100-D50)/100</f>
         <v/>
       </c>
       <c r="F50" s="24" t="n">
-        <v>15.26</v>
+        <v>15.25</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.0474516</v>
+        <v>0.0480016</v>
       </c>
       <c r="H50" s="24" t="n">
         <v>0.016</v>
@@ -7068,17 +7068,17 @@
         <v>48934</v>
       </c>
       <c r="D51" s="23" t="n">
-        <v>95.23</v>
+        <v>95.175</v>
       </c>
       <c r="E51" s="15">
         <f>(100-D51)/100</f>
         <v/>
       </c>
       <c r="F51" s="24" t="n">
-        <v>16.33</v>
+        <v>16.31</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.0477063</v>
+        <v>0.0482563</v>
       </c>
       <c r="H51" s="24" t="n">
         <v>0.063</v>
@@ -7100,20 +7100,20 @@
         <v>49018</v>
       </c>
       <c r="D52" s="23" t="n">
-        <v>95.205</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="E52" s="15">
         <f>(100-D52)/100</f>
         <v/>
       </c>
       <c r="F52" s="24" t="n">
-        <v>17.34</v>
+        <v>17.32</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.0479341</v>
+        <v>0.048484</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>-0.159</v>
+        <v>-0.16</v>
       </c>
       <c r="I52" s="25" t="n">
         <v>11</v>
@@ -7132,20 +7132,20 @@
         <v>49116</v>
       </c>
       <c r="D53" s="23" t="n">
-        <v>95.19</v>
+        <v>95.13500000000001</v>
       </c>
       <c r="E53" s="15">
         <f>(100-D53)/100</f>
         <v/>
       </c>
       <c r="F53" s="24" t="n">
-        <v>18.41</v>
+        <v>18.4</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.0481226</v>
+        <v>0.04867270000000001</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="I53" s="25" t="n">
         <v>0</v>
@@ -7164,20 +7164,20 @@
         <v>49207</v>
       </c>
       <c r="D54" s="23" t="n">
-        <v>95.16</v>
+        <v>95.105</v>
       </c>
       <c r="E54" s="15">
         <f>(100-D54)/100</f>
         <v/>
       </c>
       <c r="F54" s="24" t="n">
-        <v>19.55</v>
+        <v>19.54</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.0483716</v>
+        <v>0.0489215</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>-0.284</v>
+        <v>-0.285</v>
       </c>
       <c r="I54" s="25" t="n">
         <v>0</v>
@@ -7196,20 +7196,20 @@
         <v>49298</v>
       </c>
       <c r="D55" s="23" t="n">
-        <v>95.15000000000001</v>
+        <v>95.095</v>
       </c>
       <c r="E55" s="15">
         <f>(100-D55)/100</f>
         <v/>
       </c>
       <c r="F55" s="24" t="n">
-        <v>20.67</v>
+        <v>20.66</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.0485336</v>
+        <v>0.04908369999999999</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="I55" s="25" t="n">
         <v>0</v>
@@ -7228,17 +7228,17 @@
         <v>49389</v>
       </c>
       <c r="D56" s="23" t="n">
-        <v>95.105</v>
+        <v>95.05</v>
       </c>
       <c r="E56" s="15">
         <f>(100-D56)/100</f>
         <v/>
       </c>
       <c r="F56" s="24" t="n">
-        <v>21.82</v>
+        <v>21.8</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.04891860000000001</v>
+        <v>0.0494686</v>
       </c>
       <c r="H56" s="24" t="n">
         <v>-0.314</v>
@@ -7260,17 +7260,17 @@
         <v>49480</v>
       </c>
       <c r="D57" s="23" t="n">
-        <v>95.095</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="E57" s="15">
         <f>(100-D57)/100</f>
         <v/>
       </c>
       <c r="F57" s="24" t="n">
-        <v>22.98</v>
+        <v>22.97</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.04907180000000001</v>
+        <v>0.0496218</v>
       </c>
       <c r="H57" s="24" t="n">
         <v>0.218</v>
@@ -7292,20 +7292,20 @@
         <v>49571</v>
       </c>
       <c r="D58" s="23" t="n">
-        <v>95.06999999999999</v>
+        <v>95.015</v>
       </c>
       <c r="E58" s="15">
         <f>(100-D58)/100</f>
         <v/>
       </c>
       <c r="F58" s="24" t="n">
-        <v>24.17</v>
+        <v>24.16</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.0492841</v>
+        <v>0.0498342</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>-0.159</v>
+        <v>-0.158</v>
       </c>
       <c r="I58" s="25" t="n">
         <v>0</v>
@@ -7324,17 +7324,17 @@
         <v>49662</v>
       </c>
       <c r="D59" s="23" t="n">
-        <v>95.045</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="E59" s="15">
         <f>(100-D59)/100</f>
         <v/>
       </c>
       <c r="F59" s="24" t="n">
-        <v>25.38</v>
+        <v>25.37</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.0495687</v>
+        <v>0.0501187</v>
       </c>
       <c r="H59" s="24" t="n">
         <v>0.187</v>
@@ -7356,17 +7356,17 @@
         <v>49753</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>95</v>
+        <v>94.94499999999999</v>
       </c>
       <c r="E60" s="15">
         <f>(100-D60)/100</f>
         <v/>
       </c>
       <c r="F60" s="24" t="n">
-        <v>26.61</v>
+        <v>26.6</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.0499833</v>
+        <v>0.0505333</v>
       </c>
       <c r="H60" s="24" t="n">
         <v>-0.167</v>
@@ -7388,17 +7388,17 @@
         <v>49844</v>
       </c>
       <c r="D61" s="23" t="n">
-        <v>94.98999999999999</v>
+        <v>94.935</v>
       </c>
       <c r="E61" s="15">
         <f>(100-D61)/100</f>
         <v/>
       </c>
       <c r="F61" s="24" t="n">
-        <v>27.86</v>
+        <v>27.85</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.0501058</v>
+        <v>0.0506558</v>
       </c>
       <c r="H61" s="24" t="n">
         <v>0.058</v>
@@ -7410,7 +7410,7 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Fit: 58 contracts, RMS residual 0.178 bp, max 0.497 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
+          <t>Fit: 58 contracts, RMS residual 0.184 bp, max 0.48 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8272,14 +8272,6 @@
         <v>46169</v>
       </c>
       <c r="B106" s="26" t="n">
-        <v>0.0363</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="n">
-        <v>46168</v>
-      </c>
-      <c r="B107" s="26" t="n">
         <v>0.0363</v>
       </c>
     </row>

--- a/output/downloads/sofr-forward-curve.xlsx
+++ b/output/downloads/sofr-forward-curve.xlsx
@@ -236,7 +236,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SOFR forward curve, 2026-10-23</a:t>
+              <a:t>SOFR forward curve, 2026-10-26</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="3">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.039</v>
+        <v>0.0393</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>on 2026-10-22 (NY Fed)</t>
+          <t>on 2026-10-26 (NY Fed)</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24 16:35 UTC</t>
+          <t>2026-10-27 18:42 UTC</t>
         </is>
       </c>
     </row>
@@ -855,13 +855,13 @@
         <v>31</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.038972</v>
+        <v>0.0389663</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>0.038911</v>
+        <v>0.0389053</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>0.0389719</v>
+        <v>0.0389662</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0</v>
@@ -891,13 +891,13 @@
         <v>30</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.039333</v>
+        <v>0.0393875</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.0392728</v>
+        <v>0.0393271</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>0.0393329</v>
+        <v>0.0393873</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.0407256</v>
+        <v>0.0408613</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>0.0406589</v>
+        <v>0.0407941</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0.0407264</v>
+        <v>0.040862</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>0.01</v>
@@ -963,16 +963,16 @@
         <v>31</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.04138219999999999</v>
+        <v>0.0415602</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.0413138</v>
+        <v>0.0414912</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>0.0413837</v>
+        <v>0.0415615</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
@@ -999,16 +999,16 @@
         <v>28</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.0419707</v>
+        <v>0.04220939999999999</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.0419074</v>
+        <v>0.04214540000000001</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0.0419743</v>
+        <v>0.0422129</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
@@ -1035,13 +1035,13 @@
         <v>31</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.0426272</v>
+        <v>0.0429475</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.0425541</v>
+        <v>0.0428733</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0.042633</v>
+        <v>0.04295309999999999</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>0.06</v>
@@ -1071,16 +1071,16 @@
         <v>30</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.0434672</v>
+        <v>0.0438907</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>0.0433933</v>
+        <v>0.0438155</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>0.0434758</v>
+        <v>0.043899</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>31</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.0442254</v>
+        <v>0.0447104</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.0441469</v>
+        <v>0.0446302</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.0442374</v>
+        <v>0.04472209999999999</v>
       </c>
       <c r="G19" s="13" t="n">
         <v>0.12</v>
@@ -1143,13 +1143,13 @@
         <v>30</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.0449175</v>
+        <v>0.0454124</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>0.0448393</v>
+        <v>0.0453325</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0.04493490000000001</v>
+        <v>0.04542939999999999</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>0.17</v>
@@ -1179,13 +1179,13 @@
         <v>31</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.0452529</v>
+        <v>0.0457461</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.0451708</v>
+        <v>0.0456621</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.04527319999999999</v>
+        <v>0.04576590000000001</v>
       </c>
       <c r="G21" s="13" t="n">
         <v>0.2</v>
@@ -1215,13 +1215,13 @@
         <v>31</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.0455792</v>
+        <v>0.0460157</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.045495</v>
+        <v>0.04593</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0.0456055</v>
+        <v>0.0460416</v>
       </c>
       <c r="G22" s="13" t="n">
         <v>0.26</v>
@@ -1251,13 +1251,13 @@
         <v>30</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.0457608</v>
+        <v>0.04617549999999999</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.0456795</v>
+        <v>0.0460928</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.0457923</v>
+        <v>0.0462064</v>
       </c>
       <c r="G23" s="13" t="n">
         <v>0.31</v>
@@ -1287,16 +1287,16 @@
         <v>31</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.045945</v>
+        <v>0.0463397</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>0.0458606</v>
+        <v>0.046254</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0.0459825</v>
+        <v>0.0463767</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
@@ -1323,16 +1323,16 @@
         <v>30</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.0459196</v>
+        <v>0.0463263</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.0458376</v>
+        <v>0.0462428</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0.0459638</v>
+        <v>0.04636949999999999</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
@@ -1359,16 +1359,16 @@
         <v>31</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.0458384</v>
+        <v>0.0462203</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.04575389999999999</v>
+        <v>0.0461344</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0.0458898</v>
+        <v>0.0462727</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
@@ -1395,16 +1395,16 @@
         <v>31</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.0458021</v>
+        <v>0.046135</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>0.0457179</v>
+        <v>0.0460496</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0.045858</v>
+        <v>0.0461921</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
         <v>29</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.0457603</v>
+        <v>0.0458833</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>0.0456821</v>
+        <v>0.0458046</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>0.0458266</v>
+        <v>0.0459483</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
@@ -1467,16 +1467,16 @@
         <v>31</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.0455943</v>
+        <v>0.04579220000000001</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>0.0455102</v>
+        <v>0.0457073</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.0456684</v>
+        <v>0.045864</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
@@ -1503,16 +1503,16 @@
         <v>30</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>0.0455113</v>
+        <v>0.0457128</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>0.0454311</v>
+        <v>0.0456319</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0.0455943</v>
+        <v>0.0457944</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
@@ -1539,13 +1539,13 @@
         <v>31</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>0.0454295</v>
+        <v>0.04562770000000001</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0.0453465</v>
+        <v>0.045544</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.04552290000000001</v>
+        <v>0.0457205</v>
       </c>
       <c r="G31" s="13" t="n">
         <v>0.93</v>
@@ -1575,16 +1575,16 @@
         <v>30</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.045355</v>
+        <v>0.0455401</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>0.0452752</v>
+        <v>0.0454596</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0.0454585</v>
+        <v>0.0456431</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
@@ -1611,13 +1611,13 @@
         <v>31</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.0452981</v>
+        <v>0.0454641</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>0.0452154</v>
+        <v>0.0453808</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0.0454115</v>
+        <v>0.0455767</v>
       </c>
       <c r="G33" s="13" t="n">
         <v>1.13</v>
@@ -1647,16 +1647,16 @@
         <v>31</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.0452352</v>
+        <v>0.0453769</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>0.0451524</v>
+        <v>0.0452935</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0.0453603</v>
+        <v>0.0455009</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
@@ -1683,16 +1683,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.0451739</v>
+        <v>0.0452943</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>0.04509490000000001</v>
+        <v>0.0452149</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0.0453104</v>
+        <v>0.0454296</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
@@ -1719,16 +1719,16 @@
         <v>31</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>0.0451179</v>
+        <v>0.0452231</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>0.04503599999999999</v>
+        <v>0.0451408</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0.045266</v>
+        <v>0.0453699</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
@@ -1755,16 +1755,16 @@
         <v>30</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.0450446</v>
+        <v>0.0451412</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>0.0449655</v>
+        <v>0.0450618</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0.0452055</v>
+        <v>0.04530090000000001</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
@@ -1791,16 +1791,16 @@
         <v>31</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>0.0449695</v>
+        <v>0.045065</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>0.0448887</v>
+        <v>0.04498389999999999</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0.0451433</v>
+        <v>0.0452376</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
@@ -1827,16 +1827,16 @@
         <v>31</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0.04489</v>
+        <v>0.044988</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0.044809</v>
+        <v>0.0449066</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0.0450768</v>
+        <v>0.04517350000000001</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
@@ -1863,16 +1863,16 @@
         <v>28</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>0.0447949</v>
+        <v>0.0448949</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>0.04472279999999999</v>
+        <v>0.04482249999999999</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0.0449956</v>
+        <v>0.0450943</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>31</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.04472089999999999</v>
+        <v>0.04482129999999999</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.0446404</v>
+        <v>0.0447405</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0.0449357</v>
+        <v>0.0450347</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
@@ -1935,16 +1935,16 @@
         <v>30</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>0.0446403</v>
+        <v>0.0447412</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>0.0445625</v>
+        <v>0.044663</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0.0448692</v>
+        <v>0.0449686</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         <v>31</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.0445611</v>
+        <v>0.0446646</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.04448120000000001</v>
+        <v>0.0445843</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.04480559999999999</v>
+        <v>0.0449076</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
@@ -2007,16 +2007,16 @@
         <v>30</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.0444845</v>
+        <v>0.0445914</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>0.0444075</v>
+        <v>0.0445141</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0.0447448</v>
+        <v>0.0448501</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
@@ -2043,16 +2043,16 @@
         <v>31</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.0444263</v>
+        <v>0.04453210000000001</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.0443466</v>
+        <v>0.044452</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0.0447025</v>
+        <v>0.0448066</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
@@ -2079,16 +2079,16 @@
         <v>31</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.0443768</v>
+        <v>0.0444717</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>0.0442971</v>
+        <v>0.0443916</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0.0446701</v>
+        <v>0.0447634</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
@@ -2115,16 +2115,16 @@
         <v>30</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.0443428</v>
+        <v>0.0444207</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.04426650000000001</v>
+        <v>0.0443442</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.0446512</v>
+        <v>0.0447275</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
@@ -2151,16 +2151,16 @@
         <v>31</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.0443124</v>
+        <v>0.0443706</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>0.0442334</v>
+        <v>0.0442914</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0.0446398</v>
+        <v>0.0446962</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
@@ -2187,16 +2187,16 @@
         <v>30</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.0442748</v>
+        <v>0.04432489999999999</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>0.0441989</v>
+        <v>0.0442488</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0.0446197</v>
+        <v>0.044668</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
@@ -2223,16 +2223,16 @@
         <v>31</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.044241</v>
+        <v>0.0442927</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>0.0441621</v>
+        <v>0.0442136</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0.04460289999999999</v>
+        <v>0.0446527</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
@@ -2259,16 +2259,16 @@
         <v>31</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.0442047</v>
+        <v>0.0442584</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>0.0441261</v>
+        <v>0.0441796</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>0.0445856</v>
+        <v>0.04463739999999999</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
@@ -2295,16 +2295,16 @@
         <v>28</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.0441752</v>
+        <v>0.0442213</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>0.0441051</v>
+        <v>0.04415110000000001</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0.0445754</v>
+        <v>0.0446196</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
@@ -2331,16 +2331,16 @@
         <v>31</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.0441786</v>
+        <v>0.0442074</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.0441001</v>
+        <v>0.0441288</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.0445982</v>
+        <v>0.044625</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
@@ -2367,16 +2367,16 @@
         <v>30</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>0.04417740000000001</v>
+        <v>0.0441875</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>0.0441017</v>
+        <v>0.0441117</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>0.0446165</v>
+        <v>0.0446246</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
@@ -2403,16 +2403,16 @@
         <v>31</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>0.0441775</v>
+        <v>0.0441781</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.04409900000000001</v>
+        <v>0.0440996</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.0446369</v>
+        <v>0.04463549999999999</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
@@ -2439,16 +2439,16 @@
         <v>30</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>0.0441674</v>
+        <v>0.0441689</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>0.04409150000000001</v>
+        <v>0.044093</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>0.044646</v>
+        <v>0.0446455</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
@@ -2475,16 +2475,16 @@
         <v>31</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>0.0441657</v>
+        <v>0.04416929999999999</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.0440869</v>
+        <v>0.0440905</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.0446668</v>
+        <v>0.0446683</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>5.01</v>
+        <v>4.99</v>
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
@@ -2511,16 +2511,16 @@
         <v>31</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>0.04417620000000001</v>
+        <v>0.0441723</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>0.0440973</v>
+        <v>0.0440935</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0.0446987</v>
+        <v>0.0446927</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
@@ -2547,16 +2547,16 @@
         <v>30</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>0.0441977</v>
+        <v>0.0441772</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.04412149999999999</v>
+        <v>0.0441011</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.0447403</v>
+        <v>0.0447177</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>5.43</v>
+        <v>5.4</v>
       </c>
       <c r="H59" s="14" t="inlineStr">
         <is>
@@ -2583,16 +2583,16 @@
         <v>31</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.04423390000000001</v>
+        <v>0.0441939</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>0.0441552</v>
+        <v>0.0441153</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0.0448003</v>
+        <v>0.04475799999999999</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>5.66</v>
+        <v>5.64</v>
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>30</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>0.0442587</v>
+        <v>0.04421</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>0.0441831</v>
+        <v>0.0441345</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0.0448479</v>
+        <v>0.0447969</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>5.89</v>
+        <v>5.87</v>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
@@ -2655,16 +2655,16 @@
         <v>31</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>0.04428480000000001</v>
+        <v>0.0442374</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>0.0442056</v>
+        <v>0.0441583</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0.0448968</v>
+        <v>0.044847</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>6.12</v>
+        <v>6.1</v>
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
@@ -2691,16 +2691,16 @@
         <v>31</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>0.0443122</v>
+        <v>0.0442664</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>0.0442332</v>
+        <v>0.0441876</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0.0449478</v>
+        <v>0.04489969999999999</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>6.36</v>
+        <v>6.33</v>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
@@ -2727,16 +2727,16 @@
         <v>28</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>0.044344</v>
+        <v>0.0442909</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>0.044273</v>
+        <v>0.04422010000000001</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>0.0450019</v>
+        <v>0.0449465</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>6.58</v>
+        <v>6.56</v>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
@@ -2763,16 +2763,16 @@
         <v>31</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>0.0444078</v>
+        <v>0.0443377</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>0.0443281</v>
+        <v>0.0442583</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0.0450896</v>
+        <v>0.0450171</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>6.82</v>
+        <v>6.79</v>
       </c>
       <c r="H65" s="14" t="inlineStr">
         <is>
@@ -2799,16 +2799,16 @@
         <v>30</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>0.0444696</v>
+        <v>0.0443802</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>0.0443929</v>
+        <v>0.0443038</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0.0451764</v>
+        <v>0.0450845</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>7.07</v>
+        <v>7.04</v>
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
@@ -2835,16 +2835,16 @@
         <v>31</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>0.0445296</v>
+        <v>0.0444312</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>0.04445</v>
+        <v>0.044352</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>0.0452608</v>
+        <v>0.0451599</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
@@ -2871,16 +2871,16 @@
         <v>30</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>0.0445787</v>
+        <v>0.0444815</v>
       </c>
       <c r="E68" s="12" t="n">
-        <v>0.04450129999999999</v>
+        <v>0.0444044</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0.0453341</v>
+        <v>0.0452344</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>7.55</v>
+        <v>7.53</v>
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
@@ -2907,16 +2907,16 @@
         <v>31</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>0.044642</v>
+        <v>0.0445469</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>0.0445619</v>
+        <v>0.0444671</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0.045424</v>
+        <v>0.0453264</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>7.82</v>
+        <v>7.79</v>
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
@@ -2943,16 +2943,16 @@
         <v>31</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>0.0447173</v>
+        <v>0.0446151</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>0.0446368</v>
+        <v>0.044535</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>0.04552539999999999</v>
+        <v>0.0454207</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>8.08</v>
+        <v>8.06</v>
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
@@ -2979,16 +2979,16 @@
         <v>30</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>0.044803</v>
+        <v>0.04468390000000001</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>0.0447246</v>
+        <v>0.0446059</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0.0456366</v>
+        <v>0.045515</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>8.34</v>
+        <v>8.31</v>
       </c>
       <c r="H71" s="14" t="inlineStr">
         <is>
@@ -3015,16 +3015,16 @@
         <v>31</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>0.0449039</v>
+        <v>0.04476479999999999</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>0.0448228</v>
+        <v>0.0446842</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0.0457653</v>
+        <v>0.0456235</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>8.609999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
@@ -3051,16 +3051,16 @@
         <v>30</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>0.04498249999999999</v>
+        <v>0.0448323</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>0.044904</v>
+        <v>0.0447543</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0.045869</v>
+        <v>0.0457161</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>8.859999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
@@ -3087,16 +3087,16 @@
         <v>31</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>0.04506719999999999</v>
+        <v>0.044914</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>0.04498509999999999</v>
+        <v>0.0448325</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0.045983</v>
+        <v>0.0458272</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>9.16</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
@@ -3123,16 +3123,16 @@
         <v>31</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>0.04513259999999999</v>
+        <v>0.0449831</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>0.0450509</v>
+        <v>0.0449019</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0.0460752</v>
+        <v>0.0459229</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>9.43</v>
+        <v>9.4</v>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
@@ -3159,16 +3159,16 @@
         <v>29</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>0.0451943</v>
+        <v>0.0450486</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>0.045118</v>
+        <v>0.0449727</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>0.0461644</v>
+        <v>0.0460159</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
@@ -3195,16 +3195,16 @@
         <v>31</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>0.0452722</v>
+        <v>0.0451278</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>0.04518970000000001</v>
+        <v>0.0450459</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0.0462717</v>
+        <v>0.0461245</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>9.99</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H77" s="14" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
         <v>30</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>0.0453409</v>
+        <v>0.0451958</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>0.0452606</v>
+        <v>0.045116</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0.0463687</v>
+        <v>0.04622080000000001</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>10.28</v>
+        <v>10.25</v>
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
@@ -3267,16 +3267,16 @@
         <v>31</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>0.0454091</v>
+        <v>0.0452632</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0.0453264</v>
+        <v>0.0451809</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0.0464641</v>
+        <v>0.0463153</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>10.55</v>
+        <v>10.52</v>
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
@@ -3303,16 +3303,16 @@
         <v>30</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>0.045481</v>
+        <v>0.04533470000000001</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>0.0454008</v>
+        <v>0.045255</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0.046567</v>
+        <v>0.0464178</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>10.86</v>
+        <v>10.83</v>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
@@ -3339,16 +3339,16 @@
         <v>31</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>0.0455551</v>
+        <v>0.0454089</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>0.0454718</v>
+        <v>0.0453262</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0.0466707</v>
+        <v>0.0465217</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>11.16</v>
+        <v>11.13</v>
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
@@ -3375,16 +3375,16 @@
         <v>31</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>0.0456268</v>
+        <v>0.0454809</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>0.0455425</v>
+        <v>0.0453971</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0.0467714</v>
+        <v>0.0466225</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>11.45</v>
+        <v>11.42</v>
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
@@ -3411,16 +3411,16 @@
         <v>30</v>
       </c>
       <c r="D83" s="12" t="n">
-        <v>0.0456985</v>
+        <v>0.0455527</v>
       </c>
       <c r="E83" s="12" t="n">
-        <v>0.0456174</v>
+        <v>0.0454722</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0.0468739</v>
+        <v>0.04672519999999999</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>11.75</v>
+        <v>11.73</v>
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
@@ -3447,16 +3447,16 @@
         <v>31</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>0.0457673</v>
+        <v>0.0456215</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>0.0456836</v>
+        <v>0.0455384</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0.0469735</v>
+        <v>0.0468247</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>12.06</v>
+        <v>12.03</v>
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
@@ -3483,16 +3483,16 @@
         <v>30</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>0.0458213</v>
+        <v>0.0456755</v>
       </c>
       <c r="E85" s="12" t="n">
-        <v>0.0457397</v>
+        <v>0.04559440000000001</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>0.0470584</v>
+        <v>0.0469096</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>12.37</v>
+        <v>12.34</v>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         <v>31</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>0.0458733</v>
+        <v>0.0457275</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>0.0457887</v>
+        <v>0.04564339999999999</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>0.04714209999999999</v>
+        <v>0.04699329999999999</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>12.69</v>
+        <v>12.66</v>
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
@@ -3555,16 +3555,16 @@
         <v>31</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>0.0459217</v>
+        <v>0.045776</v>
       </c>
       <c r="E87" s="12" t="n">
-        <v>0.0458371</v>
+        <v>0.0456919</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0.0472202</v>
+        <v>0.0470713</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>12.98</v>
+        <v>12.95</v>
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
@@ -3591,16 +3591,16 @@
         <v>28</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>0.045978</v>
+        <v>0.04583230000000001</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>0.04590200000000001</v>
+        <v>0.0457569</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0.0473097</v>
+        <v>0.04716090000000001</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>13.32</v>
+        <v>13.29</v>
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>31</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>0.0460576</v>
+        <v>0.0459119</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>0.0459718</v>
+        <v>0.0458266</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>0.0474216</v>
+        <v>0.0472727</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>13.64</v>
+        <v>13.61</v>
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
@@ -3663,16 +3663,16 @@
         <v>30</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>0.04612160000000001</v>
+        <v>0.0459759</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>0.0460392</v>
+        <v>0.0458941</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0.047517</v>
+        <v>0.0473681</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>13.95</v>
+        <v>13.92</v>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
@@ -3699,16 +3699,16 @@
         <v>31</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>0.04617810000000001</v>
+        <v>0.0460325</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>0.0460924</v>
+        <v>0.0459473</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>0.0476046</v>
+        <v>0.04745580000000001</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>14.26</v>
+        <v>14.23</v>
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
@@ -3735,16 +3735,16 @@
         <v>30</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>0.0462177</v>
+        <v>0.0460723</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>0.0461349</v>
+        <v>0.0459899</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>0.04767730000000001</v>
+        <v>0.0475286</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>14.6</v>
+        <v>14.56</v>
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
@@ -3771,16 +3771,16 @@
         <v>31</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>0.046254</v>
+        <v>0.0461086</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>0.0461685</v>
+        <v>0.0460236</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>0.0477465</v>
+        <v>0.0475978</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>14.93</v>
+        <v>14.89</v>
       </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
@@ -3807,16 +3807,16 @@
         <v>31</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>0.0462915</v>
+        <v>0.0461461</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>0.0462047</v>
+        <v>0.0460598</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>0.0478177</v>
+        <v>0.047669</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>15.26</v>
+        <v>15.23</v>
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
@@ -3843,16 +3843,16 @@
         <v>30</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>0.04633370000000001</v>
+        <v>0.0461884</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>0.0462505</v>
+        <v>0.0461056</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>0.0478942</v>
+        <v>0.0477455</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>15.6</v>
+        <v>15.57</v>
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
@@ -3879,16 +3879,16 @@
         <v>31</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>0.0463928</v>
+        <v>0.0462474</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>0.0463064</v>
+        <v>0.0461615</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>0.0479864</v>
+        <v>0.0478377</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>15.94</v>
+        <v>15.9</v>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
@@ -3915,16 +3915,16 @@
         <v>30</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>0.0464663</v>
+        <v>0.0463208</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>0.04638270000000001</v>
+        <v>0.0462378</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>0.0480977</v>
+        <v>0.0479489</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>16.31</v>
+        <v>16.28</v>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
@@ -3951,16 +3951,16 @@
         <v>31</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>0.046543</v>
+        <v>0.0463974</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>0.046456</v>
+        <v>0.046311</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>0.0482105</v>
+        <v>0.0480615</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>16.67</v>
+        <v>16.64</v>
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
@@ -3987,16 +3987,16 @@
         <v>31</v>
       </c>
       <c r="D99" s="12" t="n">
-        <v>0.0465918</v>
+        <v>0.0464463</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>0.0465047</v>
+        <v>0.0463597</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>0.0482923</v>
+        <v>0.0481433</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>17</v>
+        <v>16.97</v>
       </c>
       <c r="H99" s="14" t="inlineStr">
         <is>
@@ -4023,16 +4023,16 @@
         <v>28</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>0.0465999</v>
+        <v>0.0464545</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>0.0465219</v>
+        <v>0.04637699999999999</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>0.04833630000000001</v>
+        <v>0.0481874</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>17.36</v>
+        <v>17.33</v>
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
@@ -4059,16 +4059,16 @@
         <v>31</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>0.0465968</v>
+        <v>0.0464514</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>0.04650890000000001</v>
+        <v>0.0463641</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>0.0483675</v>
+        <v>0.0482187</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>17.71</v>
+        <v>17.67</v>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         <v>30</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>0.0465912</v>
+        <v>0.04644599999999999</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>0.0465072</v>
+        <v>0.0463625</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>0.0483933</v>
+        <v>0.0482447</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>18.02</v>
+        <v>17.99</v>
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
         <v>31</v>
       </c>
       <c r="D103" s="12" t="n">
-        <v>0.0466333</v>
+        <v>0.0464882</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>0.0465459</v>
+        <v>0.0464013</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>0.0484734</v>
+        <v>0.0483247</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>18.4</v>
+        <v>18.36</v>
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
@@ -4167,16 +4167,16 @@
         <v>30</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>0.0467066</v>
+        <v>0.04656150000000001</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>0.046622</v>
+        <v>0.0464774</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>0.0485832</v>
+        <v>0.0484345</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>18.77</v>
+        <v>18.73</v>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
@@ -4203,16 +4203,16 @@
         <v>31</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>0.0467791</v>
+        <v>0.0466339</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>0.0466909</v>
+        <v>0.0465462</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>0.0486912</v>
+        <v>0.0485425</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>19.12</v>
+        <v>19.09</v>
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
@@ -4239,16 +4239,16 @@
         <v>31</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>0.04681129999999999</v>
+        <v>0.0466661</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>0.0467226</v>
+        <v>0.04657790000000001</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>0.0487636</v>
+        <v>0.0486148</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>19.52</v>
+        <v>19.49</v>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         <v>30</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>0.04678930000000001</v>
+        <v>0.0466441</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>0.04670460000000001</v>
+        <v>0.0465599</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>0.0487785</v>
+        <v>0.0486297</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>19.89</v>
+        <v>19.86</v>
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
@@ -4311,16 +4311,16 @@
         <v>31</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>0.0467807</v>
+        <v>0.0466355</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>0.0466927</v>
+        <v>0.0465481</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>0.0488061</v>
+        <v>0.0486573</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>20.25</v>
+        <v>20.22</v>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
@@ -4347,16 +4347,16 @@
         <v>30</v>
       </c>
       <c r="D109" s="12" t="n">
-        <v>0.0468294</v>
+        <v>0.0466843</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>0.0467439</v>
+        <v>0.0465994</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>0.0488933</v>
+        <v>0.0487445</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>20.64</v>
+        <v>20.6</v>
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
@@ -4383,16 +4383,16 @@
         <v>31</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>0.0469498</v>
+        <v>0.0468047</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>0.0468618</v>
+        <v>0.04671719999999999</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>0.0490517</v>
+        <v>0.048903</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>21.02</v>
+        <v>20.98</v>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
@@ -4419,16 +4419,16 @@
         <v>31</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0.0470767</v>
+        <v>0.0469316</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>0.0469875</v>
+        <v>0.046843</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>0.0492155</v>
+        <v>0.0490667</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>21.39</v>
+        <v>21.35</v>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
@@ -4455,16 +4455,16 @@
         <v>28</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0.0471469</v>
+        <v>0.0470019</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>0.047067</v>
+        <v>0.0469225</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>0.04932400000000001</v>
+        <v>0.0491752</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>21.77</v>
+        <v>21.73</v>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
@@ -4491,16 +4491,16 @@
         <v>31</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.0471624</v>
+        <v>0.0470173</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>0.0470731</v>
+        <v>0.04692859999999999</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>0.0493783</v>
+        <v>0.0492295</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>22.16</v>
+        <v>22.12</v>
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>30</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0.0471322</v>
+        <v>0.0469872</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>0.04704539999999999</v>
+        <v>0.0469009</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>0.0493849</v>
+        <v>0.04923619999999999</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>22.53</v>
+        <v>22.49</v>
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
@@ -4563,16 +4563,16 @@
         <v>31</v>
       </c>
       <c r="D115" s="12" t="n">
-        <v>0.0471251</v>
+        <v>0.0469802</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>0.0470358</v>
+        <v>0.0468914</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>0.0494185</v>
+        <v>0.0492697</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>22.93</v>
+        <v>22.9</v>
       </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
@@ -4599,16 +4599,16 @@
         <v>30</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>0.04715340000000001</v>
+        <v>0.0470085</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>0.0470669</v>
+        <v>0.0469225</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>0.0494863</v>
+        <v>0.0493376</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>23.33</v>
+        <v>23.29</v>
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
@@ -4635,16 +4635,16 @@
         <v>31</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>0.0472082</v>
+        <v>0.0470633</v>
       </c>
       <c r="E117" s="12" t="n">
-        <v>0.04711820000000001</v>
+        <v>0.0469738</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>0.0495805</v>
+        <v>0.0494317</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>23.72</v>
+        <v>23.68</v>
       </c>
       <c r="H117" s="14" t="inlineStr">
         <is>
@@ -4671,16 +4671,16 @@
         <v>31</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>0.0472549</v>
+        <v>0.04711000000000001</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>0.0471645</v>
+        <v>0.0470201</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>0.04966859999999999</v>
+        <v>0.0495198</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>24.14</v>
+        <v>24.1</v>
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
@@ -4707,16 +4707,16 @@
         <v>30</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>0.0472803</v>
+        <v>0.0471355</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>0.0471936</v>
+        <v>0.0470493</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>0.04972940000000001</v>
+        <v>0.04958070000000001</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>24.49</v>
+        <v>24.45</v>
       </c>
       <c r="H119" s="14" t="inlineStr">
         <is>
@@ -4743,16 +4743,16 @@
         <v>31</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>0.0473331</v>
+        <v>0.0471883</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>0.04724300000000001</v>
+        <v>0.04709869999999999</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>0.0498265</v>
+        <v>0.0496777</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>24.93</v>
+        <v>24.89</v>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
@@ -4779,16 +4779,16 @@
         <v>30</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>0.0474169</v>
+        <v>0.0472721</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>0.0473299</v>
+        <v>0.0471857</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>0.0499503</v>
+        <v>0.0498015</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>25.33</v>
+        <v>25.29</v>
       </c>
       <c r="H121" s="14" t="inlineStr">
         <is>
@@ -4815,16 +4815,16 @@
         <v>31</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.0475353</v>
+        <v>0.0473905</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>0.0474442</v>
+        <v>0.0473</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>0.05010729999999999</v>
+        <v>0.04995860000000001</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>25.72</v>
+        <v>25.68</v>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
@@ -4851,16 +4851,16 @@
         <v>31</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>0.0476584</v>
+        <v>0.0475136</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>0.04756700000000001</v>
+        <v>0.0474228</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>0.05027300000000001</v>
+        <v>0.05012419999999999</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>26.15</v>
+        <v>26.11</v>
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
@@ -4887,16 +4887,16 @@
         <v>29</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>0.047729</v>
+        <v>0.0475843</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>0.0476439</v>
+        <v>0.04749970000000001</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>0.0503854</v>
+        <v>0.0502367</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>26.56</v>
+        <v>26.52</v>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
@@ -4923,16 +4923,16 @@
         <v>31</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>0.0477481</v>
+        <v>0.04760329999999999</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>0.047656</v>
+        <v>0.0475118</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>0.0504437</v>
+        <v>0.0502949</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>26.96</v>
+        <v>26.92</v>
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>30</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>0.0477123</v>
+        <v>0.0475676</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>0.04762400000000001</v>
+        <v>0.0474798</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>0.050451</v>
+        <v>0.0503022</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>27.39</v>
+        <v>27.35</v>
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
@@ -4995,16 +4995,16 @@
         <v>31</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>0.0476617</v>
+        <v>0.047517</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>0.04757049999999999</v>
+        <v>0.0474264</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>0.0504416</v>
+        <v>0.0502928</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>27.8</v>
+        <v>27.76</v>
       </c>
       <c r="H127" s="14" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>30</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>0.0476022</v>
+        <v>0.0474575</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>0.0475139</v>
+        <v>0.0473698</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>0.0504212</v>
+        <v>0.0502725</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>28.19</v>
+        <v>28.15</v>
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
@@ -5067,16 +5067,16 @@
         <v>31</v>
       </c>
       <c r="D129" s="18" t="n">
-        <v>0.0476031</v>
+        <v>0.0474584</v>
       </c>
       <c r="E129" s="18" t="n">
-        <v>0.0475119</v>
+        <v>0.0473678</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.0504238</v>
+        <v>0.050275</v>
       </c>
       <c r="G129" s="19" t="n">
-        <v>28.21</v>
+        <v>28.17</v>
       </c>
       <c r="H129" s="20" t="inlineStr">
         <is>
@@ -5103,16 +5103,16 @@
         <v>31</v>
       </c>
       <c r="D130" s="18" t="n">
-        <v>0.0476031</v>
+        <v>0.0474584</v>
       </c>
       <c r="E130" s="18" t="n">
-        <v>0.0475119</v>
+        <v>0.0473678</v>
       </c>
       <c r="F130" s="18" t="n">
-        <v>0.0504238</v>
+        <v>0.050275</v>
       </c>
       <c r="G130" s="19" t="n">
-        <v>28.21</v>
+        <v>28.17</v>
       </c>
       <c r="H130" s="20" t="inlineStr">
         <is>
@@ -5139,16 +5139,16 @@
         <v>30</v>
       </c>
       <c r="D131" s="18" t="n">
-        <v>0.0476004</v>
+        <v>0.04745580000000001</v>
       </c>
       <c r="E131" s="18" t="n">
-        <v>0.0475119</v>
+        <v>0.0473678</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.0504208</v>
+        <v>0.0502721</v>
       </c>
       <c r="G131" s="19" t="n">
-        <v>28.2</v>
+        <v>28.16</v>
       </c>
       <c r="H131" s="20" t="inlineStr">
         <is>
@@ -5175,16 +5175,16 @@
         <v>31</v>
       </c>
       <c r="D132" s="18" t="n">
-        <v>0.0476031</v>
+        <v>0.0474584</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>0.0475119</v>
+        <v>0.0473678</v>
       </c>
       <c r="F132" s="18" t="n">
-        <v>0.0504238</v>
+        <v>0.050275</v>
       </c>
       <c r="G132" s="19" t="n">
-        <v>28.21</v>
+        <v>28.17</v>
       </c>
       <c r="H132" s="20" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5500,7 +5500,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-23)</t>
+          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
         <v>46344</v>
       </c>
       <c r="D4" s="23" t="n">
-        <v>96.1675</v>
+        <v>96.16249999999999</v>
       </c>
       <c r="E4" s="15">
         <f>(100-D4)/100</f>
@@ -5574,13 +5574,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.0383419</v>
+        <v>0.0383501</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>0.169</v>
+        <v>-0.249</v>
       </c>
       <c r="I4" s="25" t="n">
-        <v>7574</v>
+        <v>7744</v>
       </c>
     </row>
     <row r="5">
@@ -5596,7 +5596,7 @@
         <v>46372</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>96.065</v>
+        <v>96.06</v>
       </c>
       <c r="E5" s="15">
         <f>(100-D5)/100</f>
@@ -5606,13 +5606,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.0393544</v>
+        <v>0.0393872</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>0.044</v>
+        <v>-0.128</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>1315971</v>
+        <v>1309996</v>
       </c>
     </row>
     <row r="6">
@@ -5628,7 +5628,7 @@
         <v>46327</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>96.105</v>
+        <v>96.10250000000001</v>
       </c>
       <c r="E6" s="15">
         <f>(100-D6)/100</f>
@@ -5638,13 +5638,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.038911</v>
+        <v>0.0389053</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>-0.39</v>
+        <v>-0.697</v>
       </c>
       <c r="I6" s="25" t="n">
-        <v>361918</v>
+        <v>340840</v>
       </c>
     </row>
     <row r="7">
@@ -5660,7 +5660,7 @@
         <v>46407</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>95.9675</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="E7" s="15">
         <f>(100-D7)/100</f>
@@ -5670,13 +5670,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.0403352</v>
+        <v>0.0404333</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>0.102</v>
+        <v>0.333</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>7222</v>
+        <v>7722</v>
       </c>
     </row>
     <row r="8">
@@ -5692,7 +5692,7 @@
         <v>46357</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>96.075</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="E8" s="15">
         <f>(100-D8)/100</f>
@@ -5702,13 +5702,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.0392729</v>
+        <v>0.0393272</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>0.229</v>
+        <v>0.272</v>
       </c>
       <c r="I8" s="25" t="n">
-        <v>289356</v>
+        <v>297603</v>
       </c>
     </row>
     <row r="9">
@@ -5724,7 +5724,7 @@
         <v>46435</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>95.8875</v>
+        <v>95.875</v>
       </c>
       <c r="E9" s="15">
         <f>(100-D9)/100</f>
@@ -5734,13 +5734,13 @@
         <v>0.01</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.0411115</v>
+        <v>0.0412691</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.135</v>
+        <v>0.191</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>2035</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="10">
@@ -5756,7 +5756,7 @@
         <v>46388</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>95.93000000000001</v>
+        <v>95.91500000000001</v>
       </c>
       <c r="E10" s="15">
         <f>(100-D10)/100</f>
@@ -5766,13 +5766,13 @@
         <v>0.01</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.0406597</v>
+        <v>0.0407948</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.403</v>
+        <v>-0.552</v>
       </c>
       <c r="I10" s="25" t="n">
-        <v>239346</v>
+        <v>241428</v>
       </c>
     </row>
     <row r="11">
@@ -5788,7 +5788,7 @@
         <v>46463</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>95.81999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="E11" s="15">
         <f>(100-D11)/100</f>
@@ -5798,13 +5798,13 @@
         <v>0.02</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.0418019</v>
+        <v>0.042009</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>0.019</v>
+        <v>0.09</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>1573564</v>
+        <v>1574834</v>
       </c>
     </row>
     <row r="12">
@@ -5820,7 +5820,7 @@
         <v>46419</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>95.87</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="E12" s="15">
         <f>(100-D12)/100</f>
@@ -5830,13 +5830,13 @@
         <v>0.02</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.0413159</v>
+        <v>0.0414931</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>0.159</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>186854</v>
+        <v>190690</v>
       </c>
     </row>
     <row r="13">
@@ -5852,7 +5852,7 @@
         <v>46498</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>95.73999999999999</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="E13" s="15">
         <f>(100-D13)/100</f>
@@ -5862,13 +5862,13 @@
         <v>0.05</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.0426102</v>
+        <v>0.0429122</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.102</v>
+        <v>0.122</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>1409</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="14">
@@ -5884,7 +5884,7 @@
         <v>46447</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>95.81</v>
+        <v>95.785</v>
       </c>
       <c r="E14" s="15">
         <f>(100-D14)/100</f>
@@ -5894,13 +5894,13 @@
         <v>0.04</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.04191130000000001</v>
+        <v>0.04214909999999999</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.113</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="I14" s="25" t="n">
-        <v>100934</v>
+        <v>101983</v>
       </c>
     </row>
     <row r="15">
@@ -5916,7 +5916,7 @@
         <v>46526</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>95.675</v>
+        <v>95.63500000000001</v>
       </c>
       <c r="E15" s="15">
         <f>(100-D15)/100</f>
@@ -5926,10 +5926,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.043298</v>
+        <v>0.04367670000000001</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>0.48</v>
+        <v>0.267</v>
       </c>
       <c r="I15" s="25" t="n">
         <v>554</v>
@@ -5948,7 +5948,7 @@
         <v>46478</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>95.73999999999999</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="E16" s="15">
         <f>(100-D16)/100</f>
@@ -5958,13 +5958,13 @@
         <v>0.06</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.0425603</v>
+        <v>0.0428793</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.397</v>
+        <v>-0.207</v>
       </c>
       <c r="I16" s="25" t="n">
-        <v>35762</v>
+        <v>35644</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>46554</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>95.59</v>
+        <v>95.55</v>
       </c>
       <c r="E17" s="15">
         <f>(100-D17)/100</f>
@@ -5990,13 +5990,13 @@
         <v>0.1</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.0440632</v>
+        <v>0.0445192</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>-0.368</v>
+        <v>0.192</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>1334265</v>
+        <v>1324243</v>
       </c>
     </row>
     <row r="18">
@@ -6012,7 +6012,7 @@
         <v>46508</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>95.66</v>
+        <v>95.61499999999999</v>
       </c>
       <c r="E18" s="15">
         <f>(100-D18)/100</f>
@@ -6022,13 +6022,13 @@
         <v>0.09</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.04340239999999999</v>
+        <v>0.0438243</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>0.024</v>
+        <v>-0.257</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>69216</v>
+        <v>68394</v>
       </c>
     </row>
     <row r="19">
@@ -6044,23 +6044,23 @@
         <v>46539</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>95.58499999999999</v>
+        <v>95.535</v>
       </c>
       <c r="E19" s="15">
         <f>(100-D19)/100</f>
         <v/>
       </c>
       <c r="F19" s="24" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.0441594</v>
+        <v>0.0446424</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>0.094</v>
+        <v>-0.076</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>71683</v>
+        <v>71874</v>
       </c>
     </row>
     <row r="20">
@@ -6076,23 +6076,23 @@
         <v>46569</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>95.515</v>
+        <v>95.465</v>
       </c>
       <c r="E20" s="15">
         <f>(100-D20)/100</f>
         <v/>
       </c>
       <c r="F20" s="24" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.04485579999999999</v>
+        <v>0.0453486</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>0.058</v>
+        <v>-0.014</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>21182</v>
+        <v>21272</v>
       </c>
     </row>
     <row r="21">
@@ -6108,23 +6108,23 @@
         <v>46645</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>95.44</v>
+        <v>95.395</v>
       </c>
       <c r="E21" s="15">
         <f>(100-D21)/100</f>
         <v/>
       </c>
       <c r="F21" s="24" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.045603</v>
+        <v>0.0460722</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>0.03</v>
+        <v>0.222</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>1238896</v>
+        <v>1244435</v>
       </c>
     </row>
     <row r="22">
@@ -6140,7 +6140,7 @@
         <v>46600</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>95.48</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="E22" s="15">
         <f>(100-D22)/100</f>
@@ -6150,13 +6150,13 @@
         <v>0.21</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.0451918</v>
+        <v>0.0456827</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>-0.082</v>
+        <v>-0.173</v>
       </c>
       <c r="I22" s="25" t="n">
-        <v>38412</v>
+        <v>38126</v>
       </c>
     </row>
     <row r="23">
@@ -6172,7 +6172,7 @@
         <v>46631</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>95.45</v>
+        <v>95.405</v>
       </c>
       <c r="E23" s="15">
         <f>(100-D23)/100</f>
@@ -6182,13 +6182,13 @@
         <v>0.26</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.0455212</v>
+        <v>0.0459557</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>0.212</v>
+        <v>0.057</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>19872</v>
+        <v>20213</v>
       </c>
     </row>
     <row r="24">
@@ -6204,23 +6204,23 @@
         <v>46661</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>95.425</v>
+        <v>95.38500000000001</v>
       </c>
       <c r="E24" s="15">
         <f>(100-D24)/100</f>
         <v/>
       </c>
       <c r="F24" s="24" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.0457113</v>
+        <v>0.046124</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>-0.387</v>
+        <v>-0.26</v>
       </c>
       <c r="I24" s="25" t="n">
-        <v>5238</v>
+        <v>5231</v>
       </c>
     </row>
     <row r="25">
@@ -6236,7 +6236,7 @@
         <v>46736</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>95.39</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="E25" s="15">
         <f>(100-D25)/100</f>
@@ -6246,13 +6246,13 @@
         <v>0.4</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.0461397</v>
+        <v>0.0465406</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>0.397</v>
+        <v>0.406</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>1071479</v>
+        <v>1081152</v>
       </c>
     </row>
     <row r="26">
@@ -6268,23 +6268,23 @@
         <v>46692</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>95.41</v>
+        <v>95.37</v>
       </c>
       <c r="E26" s="15">
         <f>(100-D26)/100</f>
         <v/>
       </c>
       <c r="F26" s="24" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.0458985</v>
+        <v>0.0462912</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>-0.015</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>7666</v>
+        <v>7808</v>
       </c>
     </row>
     <row r="27">
@@ -6300,7 +6300,7 @@
         <v>46722</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>95.41</v>
+        <v>95.37</v>
       </c>
       <c r="E27" s="15">
         <f>(100-D27)/100</f>
@@ -6310,842 +6310,842 @@
         <v>0.44</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.0458821</v>
+        <v>0.0462866</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>-0.179</v>
+        <v>-0.134</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>1769</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 27</t>
+          <t>SR1 DEC 27</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>46736</v>
+        <v>46722</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>46827</v>
+        <v>46753</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>95.40000000000001</v>
+        <v>95.38</v>
       </c>
       <c r="E28" s="15">
         <f>(100-D28)/100</f>
         <v/>
       </c>
       <c r="F28" s="24" t="n">
-        <v>0.62</v>
+        <v>0.51</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.04599669999999999</v>
+        <v>0.0461853</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>-0.033</v>
+        <v>-0.147</v>
       </c>
       <c r="I28" s="25" t="n">
-        <v>1618719</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 28</t>
+          <t>SR3 DEC 27</t>
         </is>
       </c>
       <c r="B29" s="10" t="n">
+        <v>46736</v>
+      </c>
+      <c r="C29" s="10" t="n">
         <v>46827</v>
       </c>
-      <c r="C29" s="10" t="n">
-        <v>46925</v>
-      </c>
       <c r="D29" s="23" t="n">
-        <v>95.425</v>
+        <v>95.375</v>
       </c>
       <c r="E29" s="15">
         <f>(100-D29)/100</f>
         <v/>
       </c>
       <c r="F29" s="24" t="n">
-        <v>0.9</v>
+        <v>0.61</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.0457515</v>
+        <v>0.0462506</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>0.015</v>
+        <v>0.006</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>830047</v>
+        <v>1627781</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 28</t>
+          <t>SR1 JAN 28</t>
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>46925</v>
+        <v>46753</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>47016</v>
+        <v>46784</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>95.44499999999999</v>
+        <v>95.39</v>
       </c>
       <c r="E30" s="15">
         <f>(100-D30)/100</f>
         <v/>
       </c>
       <c r="F30" s="24" t="n">
-        <v>1.22</v>
+        <v>0.59</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.0455507</v>
+        <v>0.0461082</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>0.007</v>
+        <v>0.082</v>
       </c>
       <c r="I30" s="25" t="n">
-        <v>659097</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 28</t>
+          <t>SR3 MAR 28</t>
         </is>
       </c>
       <c r="B31" s="10" t="n">
-        <v>47016</v>
+        <v>46827</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>47107</v>
+        <v>46925</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>95.45999999999999</v>
+        <v>95.405</v>
       </c>
       <c r="E31" s="15">
         <f>(100-D31)/100</f>
         <v/>
       </c>
       <c r="F31" s="24" t="n">
-        <v>1.57</v>
+        <v>0.89</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.0453979</v>
+        <v>0.0459488</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>-0.021</v>
+        <v>-0.012</v>
       </c>
       <c r="I31" s="25" t="n">
-        <v>678440</v>
+        <v>826033</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 28</t>
+          <t>SR3 JUN 28</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
-        <v>47107</v>
+        <v>46925</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>47198</v>
+        <v>47016</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>95.48</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="E32" s="15">
         <f>(100-D32)/100</f>
         <v/>
       </c>
       <c r="F32" s="24" t="n">
-        <v>1.97</v>
+        <v>1.21</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.0452012</v>
+        <v>0.04570109999999999</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>552076</v>
+        <v>646307</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 29</t>
+          <t>SR3 SEP 28</t>
         </is>
       </c>
       <c r="B33" s="10" t="n">
-        <v>47198</v>
+        <v>47016</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>47289</v>
+        <v>47107</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>95.5</v>
+        <v>95.45</v>
       </c>
       <c r="E33" s="15">
         <f>(100-D33)/100</f>
         <v/>
       </c>
       <c r="F33" s="24" t="n">
-        <v>2.41</v>
+        <v>1.56</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.0449984</v>
+        <v>0.04549959999999999</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>-0.016</v>
+        <v>-0.004</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>381514</v>
+        <v>678096</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 29</t>
+          <t>SR3 DEC 28</t>
         </is>
       </c>
       <c r="B34" s="10" t="n">
-        <v>47289</v>
+        <v>47107</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>47380</v>
+        <v>47198</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>95.515</v>
+        <v>95.47</v>
       </c>
       <c r="E34" s="15">
         <f>(100-D34)/100</f>
         <v/>
       </c>
       <c r="F34" s="24" t="n">
-        <v>2.88</v>
+        <v>1.96</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.044854</v>
+        <v>0.0452994</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>0.04</v>
+        <v>-0.006</v>
       </c>
       <c r="I34" s="25" t="n">
-        <v>391934</v>
+        <v>553406</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 29</t>
+          <t>SR3 MAR 29</t>
         </is>
       </c>
       <c r="B35" s="10" t="n">
-        <v>47380</v>
+        <v>47198</v>
       </c>
       <c r="C35" s="10" t="n">
-        <v>47471</v>
+        <v>47289</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>95.52</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="E35" s="15">
         <f>(100-D35)/100</f>
         <v/>
       </c>
       <c r="F35" s="24" t="n">
-        <v>3.4</v>
+        <v>2.39</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.0447947</v>
+        <v>0.0451006</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>-0.053</v>
+        <v>0.006</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>303902</v>
+        <v>385197</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 29</t>
+          <t>SR3 JUN 29</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>47471</v>
+        <v>47289</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>47562</v>
+        <v>47380</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>95.52500000000001</v>
+        <v>95.505</v>
       </c>
       <c r="E36" s="15">
         <f>(100-D36)/100</f>
         <v/>
       </c>
       <c r="F36" s="24" t="n">
-        <v>3.95</v>
+        <v>2.87</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.0447557</v>
+        <v>0.04495</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="I36" s="25" t="n">
-        <v>244481</v>
+        <v>391297</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 30</t>
+          <t>SR3 SEP 29</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>47562</v>
+        <v>47380</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>47653</v>
+        <v>47471</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>95.52</v>
+        <v>95.515</v>
       </c>
       <c r="E37" s="15">
         <f>(100-D37)/100</f>
         <v/>
       </c>
       <c r="F37" s="24" t="n">
-        <v>4.54</v>
+        <v>3.38</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.0447943</v>
+        <v>0.0448499</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>-0.057</v>
+        <v>-0.001</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>180561</v>
+        <v>306915</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 30</t>
+          <t>SR3 DEC 29</t>
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>47653</v>
+        <v>47471</v>
       </c>
       <c r="C38" s="10" t="n">
-        <v>47744</v>
+        <v>47562</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>95.515</v>
+        <v>95.52</v>
       </c>
       <c r="E38" s="15">
         <f>(100-D38)/100</f>
         <v/>
       </c>
       <c r="F38" s="24" t="n">
-        <v>5.17</v>
+        <v>3.93</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.0448556</v>
+        <v>0.0448001</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>0.056</v>
+        <v>0.001</v>
       </c>
       <c r="I38" s="25" t="n">
-        <v>157616</v>
+        <v>246472</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 30</t>
+          <t>SR3 MAR 30</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
-        <v>47744</v>
+        <v>47562</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>47835</v>
+        <v>47653</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>95.5</v>
+        <v>95.52</v>
       </c>
       <c r="E39" s="15">
         <f>(100-D39)/100</f>
         <v/>
       </c>
       <c r="F39" s="24" t="n">
-        <v>5.83</v>
+        <v>4.52</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.0449944</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>-0.056</v>
+        <v>-0</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>148421</v>
+        <v>179275</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 30</t>
+          <t>SR3 JUN 30</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>47835</v>
+        <v>47653</v>
       </c>
       <c r="C40" s="10" t="n">
-        <v>47926</v>
+        <v>47744</v>
       </c>
       <c r="D40" s="23" t="n">
-        <v>95.485</v>
+        <v>95.515</v>
       </c>
       <c r="E40" s="15">
         <f>(100-D40)/100</f>
         <v/>
       </c>
       <c r="F40" s="24" t="n">
-        <v>6.53</v>
+        <v>5.15</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.0451554</v>
+        <v>0.04485</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>0.054</v>
+        <v>-0</v>
       </c>
       <c r="I40" s="25" t="n">
-        <v>116344</v>
+        <v>155229</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 31</t>
+          <t>SR3 SEP 30</t>
         </is>
       </c>
       <c r="B41" s="10" t="n">
-        <v>47926</v>
+        <v>47744</v>
       </c>
       <c r="C41" s="10" t="n">
-        <v>48017</v>
+        <v>47835</v>
       </c>
       <c r="D41" s="23" t="n">
-        <v>95.45999999999999</v>
+        <v>95.505</v>
       </c>
       <c r="E41" s="15">
         <f>(100-D41)/100</f>
         <v/>
       </c>
       <c r="F41" s="24" t="n">
-        <v>7.26</v>
+        <v>5.81</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.0453944</v>
+        <v>0.0449502</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>-0.056</v>
+        <v>0.002</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>87263</v>
+        <v>149374</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 31</t>
+          <t>SR3 DEC 30</t>
         </is>
       </c>
       <c r="B42" s="10" t="n">
-        <v>48017</v>
+        <v>47835</v>
       </c>
       <c r="C42" s="10" t="n">
-        <v>48108</v>
+        <v>47926</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>95.435</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="E42" s="15">
         <f>(100-D42)/100</f>
         <v/>
       </c>
       <c r="F42" s="24" t="n">
-        <v>8.02</v>
+        <v>6.51</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.0456562</v>
+        <v>0.0450998</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>0.062</v>
+        <v>-0.002</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>72512</v>
+        <v>117178</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 31</t>
+          <t>SR3 MAR 31</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
-        <v>48108</v>
+        <v>47926</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>48199</v>
+        <v>48017</v>
       </c>
       <c r="D43" s="23" t="n">
-        <v>95.40000000000001</v>
+        <v>95.47</v>
       </c>
       <c r="E43" s="15">
         <f>(100-D43)/100</f>
         <v/>
       </c>
       <c r="F43" s="24" t="n">
-        <v>8.82</v>
+        <v>7.23</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.045995</v>
+        <v>0.0452999</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>-0.05</v>
+        <v>-0.001</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>38592</v>
+        <v>86402</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 31</t>
+          <t>SR3 JUN 31</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
-        <v>48199</v>
+        <v>48017</v>
       </c>
       <c r="C44" s="10" t="n">
-        <v>48290</v>
+        <v>48108</v>
       </c>
       <c r="D44" s="23" t="n">
-        <v>95.37</v>
+        <v>95.44499999999999</v>
       </c>
       <c r="E44" s="15">
         <f>(100-D44)/100</f>
         <v/>
       </c>
       <c r="F44" s="24" t="n">
-        <v>9.640000000000001</v>
+        <v>8</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.0463023</v>
+        <v>0.0455509</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>0.023</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>7219</v>
+        <v>72371</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 32</t>
+          <t>SR3 SEP 31</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
-        <v>48290</v>
+        <v>48108</v>
       </c>
       <c r="C45" s="10" t="n">
-        <v>48381</v>
+        <v>48199</v>
       </c>
       <c r="D45" s="23" t="n">
-        <v>95.34</v>
+        <v>95.41500000000001</v>
       </c>
       <c r="E45" s="15">
         <f>(100-D45)/100</f>
         <v/>
       </c>
       <c r="F45" s="24" t="n">
-        <v>10.5</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.046599</v>
+        <v>0.045849</v>
       </c>
       <c r="H45" s="24" t="n">
         <v>-0.01</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>2675</v>
+        <v>38653</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 32</t>
+          <t>SR3 DEC 31</t>
         </is>
       </c>
       <c r="B46" s="10" t="n">
-        <v>48381</v>
+        <v>48199</v>
       </c>
       <c r="C46" s="10" t="n">
-        <v>48472</v>
+        <v>48290</v>
       </c>
       <c r="D46" s="23" t="n">
-        <v>95.31</v>
+        <v>95.38500000000001</v>
       </c>
       <c r="E46" s="15">
         <f>(100-D46)/100</f>
         <v/>
       </c>
       <c r="F46" s="24" t="n">
-        <v>11.39</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.046902</v>
+        <v>0.0461503</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>0.02</v>
+        <v>0.003</v>
       </c>
       <c r="I46" s="25" t="n">
-        <v>905</v>
+        <v>7521</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 32</t>
+          <t>SR3 MAR 32</t>
         </is>
       </c>
       <c r="B47" s="10" t="n">
-        <v>48472</v>
+        <v>48290</v>
       </c>
       <c r="C47" s="10" t="n">
-        <v>48563</v>
+        <v>48381</v>
       </c>
       <c r="D47" s="23" t="n">
-        <v>95.28</v>
+        <v>95.355</v>
       </c>
       <c r="E47" s="15">
         <f>(100-D47)/100</f>
         <v/>
       </c>
       <c r="F47" s="24" t="n">
-        <v>12.3</v>
+        <v>10.47</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.04719599999999999</v>
+        <v>0.0464495</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>-0.04</v>
+        <v>-0.005</v>
       </c>
       <c r="I47" s="25" t="n">
-        <v>574</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 32</t>
+          <t>SR3 JUN 32</t>
         </is>
       </c>
       <c r="B48" s="10" t="n">
-        <v>48563</v>
+        <v>48381</v>
       </c>
       <c r="C48" s="10" t="n">
-        <v>48654</v>
+        <v>48472</v>
       </c>
       <c r="D48" s="23" t="n">
-        <v>95.255</v>
+        <v>95.325</v>
       </c>
       <c r="E48" s="15">
         <f>(100-D48)/100</f>
         <v/>
       </c>
       <c r="F48" s="24" t="n">
-        <v>13.24</v>
+        <v>11.36</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.0474555</v>
+        <v>0.0467518</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>0.055</v>
+        <v>0.018</v>
       </c>
       <c r="I48" s="25" t="n">
-        <v>164</v>
+        <v>722</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 33</t>
+          <t>SR3 SEP 32</t>
         </is>
       </c>
       <c r="B49" s="10" t="n">
-        <v>48654</v>
+        <v>48472</v>
       </c>
       <c r="C49" s="10" t="n">
-        <v>48745</v>
+        <v>48563</v>
       </c>
       <c r="D49" s="23" t="n">
-        <v>95.22499999999999</v>
+        <v>95.295</v>
       </c>
       <c r="E49" s="15">
         <f>(100-D49)/100</f>
         <v/>
       </c>
       <c r="F49" s="24" t="n">
-        <v>14.21</v>
+        <v>12.27</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.0477449</v>
+        <v>0.047046</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>-0.051</v>
+        <v>-0.04</v>
       </c>
       <c r="I49" s="25" t="n">
-        <v>35</v>
+        <v>434</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 33</t>
+          <t>SR3 DEC 32</t>
         </is>
       </c>
       <c r="B50" s="10" t="n">
-        <v>48745</v>
+        <v>48563</v>
       </c>
       <c r="C50" s="10" t="n">
-        <v>48843</v>
+        <v>48654</v>
       </c>
       <c r="D50" s="23" t="n">
-        <v>95.2</v>
+        <v>95.27</v>
       </c>
       <c r="E50" s="15">
         <f>(100-D50)/100</f>
         <v/>
       </c>
       <c r="F50" s="24" t="n">
-        <v>15.25</v>
+        <v>13.21</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.0480016</v>
+        <v>0.0473055</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>0.016</v>
+        <v>0.055</v>
       </c>
       <c r="I50" s="25" t="n">
-        <v>1</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 33</t>
+          <t>SR3 MAR 33</t>
         </is>
       </c>
       <c r="B51" s="10" t="n">
-        <v>48843</v>
+        <v>48654</v>
       </c>
       <c r="C51" s="10" t="n">
-        <v>48934</v>
+        <v>48745</v>
       </c>
       <c r="D51" s="23" t="n">
-        <v>95.175</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="E51" s="15">
         <f>(100-D51)/100</f>
         <v/>
       </c>
       <c r="F51" s="24" t="n">
-        <v>16.31</v>
+        <v>14.18</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.0482563</v>
+        <v>0.0475949</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>0.063</v>
+        <v>-0.051</v>
       </c>
       <c r="I51" s="25" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 33</t>
+          <t>SR3 JUN 33</t>
         </is>
       </c>
       <c r="B52" s="10" t="n">
-        <v>48934</v>
+        <v>48745</v>
       </c>
       <c r="C52" s="10" t="n">
-        <v>49018</v>
+        <v>48843</v>
       </c>
       <c r="D52" s="23" t="n">
-        <v>95.15000000000001</v>
+        <v>95.215</v>
       </c>
       <c r="E52" s="15">
         <f>(100-D52)/100</f>
         <v/>
       </c>
       <c r="F52" s="24" t="n">
-        <v>17.32</v>
+        <v>15.22</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.048484</v>
+        <v>0.0478516</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>-0.16</v>
+        <v>0.016</v>
       </c>
       <c r="I52" s="25" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 34</t>
+          <t>SR3 SEP 33</t>
         </is>
       </c>
       <c r="B53" s="10" t="n">
-        <v>49018</v>
+        <v>48843</v>
       </c>
       <c r="C53" s="10" t="n">
-        <v>49116</v>
+        <v>48934</v>
       </c>
       <c r="D53" s="23" t="n">
-        <v>95.13500000000001</v>
+        <v>95.19</v>
       </c>
       <c r="E53" s="15">
         <f>(100-D53)/100</f>
         <v/>
       </c>
       <c r="F53" s="24" t="n">
-        <v>18.4</v>
+        <v>16.28</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.04867270000000001</v>
+        <v>0.0481063</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>0.227</v>
+        <v>0.063</v>
       </c>
       <c r="I53" s="25" t="n">
         <v>0</v>
@@ -7154,62 +7154,62 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 34</t>
+          <t>SR3 DEC 33</t>
         </is>
       </c>
       <c r="B54" s="10" t="n">
-        <v>49116</v>
+        <v>48934</v>
       </c>
       <c r="C54" s="10" t="n">
-        <v>49207</v>
+        <v>49018</v>
       </c>
       <c r="D54" s="23" t="n">
-        <v>95.105</v>
+        <v>95.16500000000001</v>
       </c>
       <c r="E54" s="15">
         <f>(100-D54)/100</f>
         <v/>
       </c>
       <c r="F54" s="24" t="n">
-        <v>19.54</v>
+        <v>17.29</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.0489215</v>
+        <v>0.048334</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>-0.285</v>
+        <v>-0.16</v>
       </c>
       <c r="I54" s="25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 34</t>
+          <t>SR3 MAR 34</t>
         </is>
       </c>
       <c r="B55" s="10" t="n">
-        <v>49207</v>
+        <v>49018</v>
       </c>
       <c r="C55" s="10" t="n">
-        <v>49298</v>
+        <v>49116</v>
       </c>
       <c r="D55" s="23" t="n">
-        <v>95.095</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="E55" s="15">
         <f>(100-D55)/100</f>
         <v/>
       </c>
       <c r="F55" s="24" t="n">
-        <v>20.66</v>
+        <v>18.36</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.04908369999999999</v>
+        <v>0.0485227</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>0.337</v>
+        <v>0.227</v>
       </c>
       <c r="I55" s="25" t="n">
         <v>0</v>
@@ -7218,30 +7218,30 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 34</t>
+          <t>SR3 JUN 34</t>
         </is>
       </c>
       <c r="B56" s="10" t="n">
-        <v>49298</v>
+        <v>49116</v>
       </c>
       <c r="C56" s="10" t="n">
-        <v>49389</v>
+        <v>49207</v>
       </c>
       <c r="D56" s="23" t="n">
-        <v>95.05</v>
+        <v>95.12</v>
       </c>
       <c r="E56" s="15">
         <f>(100-D56)/100</f>
         <v/>
       </c>
       <c r="F56" s="24" t="n">
-        <v>21.8</v>
+        <v>19.5</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.0494686</v>
+        <v>0.0487716</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>-0.314</v>
+        <v>-0.284</v>
       </c>
       <c r="I56" s="25" t="n">
         <v>0</v>
@@ -7250,30 +7250,30 @@
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 35</t>
+          <t>SR3 SEP 34</t>
         </is>
       </c>
       <c r="B57" s="10" t="n">
-        <v>49389</v>
+        <v>49207</v>
       </c>
       <c r="C57" s="10" t="n">
-        <v>49480</v>
+        <v>49298</v>
       </c>
       <c r="D57" s="23" t="n">
-        <v>95.04000000000001</v>
+        <v>95.11</v>
       </c>
       <c r="E57" s="15">
         <f>(100-D57)/100</f>
         <v/>
       </c>
       <c r="F57" s="24" t="n">
-        <v>22.97</v>
+        <v>20.62</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.0496218</v>
+        <v>0.0489337</v>
       </c>
       <c r="H57" s="24" t="n">
-        <v>0.218</v>
+        <v>0.337</v>
       </c>
       <c r="I57" s="25" t="n">
         <v>0</v>
@@ -7282,30 +7282,30 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 35</t>
+          <t>SR3 DEC 34</t>
         </is>
       </c>
       <c r="B58" s="10" t="n">
-        <v>49480</v>
+        <v>49298</v>
       </c>
       <c r="C58" s="10" t="n">
-        <v>49571</v>
+        <v>49389</v>
       </c>
       <c r="D58" s="23" t="n">
-        <v>95.015</v>
+        <v>95.065</v>
       </c>
       <c r="E58" s="15">
         <f>(100-D58)/100</f>
         <v/>
       </c>
       <c r="F58" s="24" t="n">
-        <v>24.16</v>
+        <v>21.77</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.0498342</v>
+        <v>0.0493186</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>-0.158</v>
+        <v>-0.314</v>
       </c>
       <c r="I58" s="25" t="n">
         <v>0</v>
@@ -7314,30 +7314,30 @@
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 35</t>
+          <t>SR3 MAR 35</t>
         </is>
       </c>
       <c r="B59" s="10" t="n">
-        <v>49571</v>
+        <v>49389</v>
       </c>
       <c r="C59" s="10" t="n">
-        <v>49662</v>
+        <v>49480</v>
       </c>
       <c r="D59" s="23" t="n">
-        <v>94.98999999999999</v>
+        <v>95.05500000000001</v>
       </c>
       <c r="E59" s="15">
         <f>(100-D59)/100</f>
         <v/>
       </c>
       <c r="F59" s="24" t="n">
-        <v>25.37</v>
+        <v>22.93</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.0501187</v>
+        <v>0.0494718</v>
       </c>
       <c r="H59" s="24" t="n">
-        <v>0.187</v>
+        <v>0.218</v>
       </c>
       <c r="I59" s="25" t="n">
         <v>0</v>
@@ -7346,30 +7346,30 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 35</t>
+          <t>SR3 JUN 35</t>
         </is>
       </c>
       <c r="B60" s="10" t="n">
-        <v>49662</v>
+        <v>49480</v>
       </c>
       <c r="C60" s="10" t="n">
-        <v>49753</v>
+        <v>49571</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>94.94499999999999</v>
+        <v>95.03</v>
       </c>
       <c r="E60" s="15">
         <f>(100-D60)/100</f>
         <v/>
       </c>
       <c r="F60" s="24" t="n">
-        <v>26.6</v>
+        <v>24.12</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.0505333</v>
+        <v>0.0496842</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>-0.167</v>
+        <v>-0.158</v>
       </c>
       <c r="I60" s="25" t="n">
         <v>0</v>
@@ -7378,39 +7378,103 @@
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 36</t>
+          <t>SR3 SEP 35</t>
         </is>
       </c>
       <c r="B61" s="10" t="n">
-        <v>49753</v>
+        <v>49571</v>
       </c>
       <c r="C61" s="10" t="n">
-        <v>49844</v>
+        <v>49662</v>
       </c>
       <c r="D61" s="23" t="n">
-        <v>94.935</v>
+        <v>95.005</v>
       </c>
       <c r="E61" s="15">
         <f>(100-D61)/100</f>
         <v/>
       </c>
       <c r="F61" s="24" t="n">
-        <v>27.85</v>
+        <v>25.33</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.0506558</v>
+        <v>0.0499687</v>
       </c>
       <c r="H61" s="24" t="n">
-        <v>0.058</v>
+        <v>0.187</v>
       </c>
       <c r="I61" s="25" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>SR3 DEC 35</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n">
+        <v>49662</v>
+      </c>
+      <c r="C62" s="10" t="n">
+        <v>49753</v>
+      </c>
+      <c r="D62" s="23" t="n">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="E62" s="15">
+        <f>(100-D62)/100</f>
+        <v/>
+      </c>
+      <c r="F62" s="24" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>0.0503833</v>
+      </c>
+      <c r="H62" s="24" t="n">
+        <v>-0.167</v>
+      </c>
+      <c r="I62" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>Fit: 58 contracts, RMS residual 0.184 bp, max 0.48 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>SR3 MAR 36</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="n">
+        <v>49753</v>
+      </c>
+      <c r="C63" s="10" t="n">
+        <v>49844</v>
+      </c>
+      <c r="D63" s="23" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="E63" s="15">
+        <f>(100-D63)/100</f>
+        <v/>
+      </c>
+      <c r="F63" s="24" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>0.0505058</v>
+      </c>
+      <c r="H63" s="24" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I63" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Fit: 60 contracts, RMS residual 0.193 bp, max 0.697 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7453,39 +7517,39 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46317</v>
+        <v>46321</v>
       </c>
       <c r="B4" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0393</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="B8" s="26" t="n">
         <v>0.0388</v>
@@ -7493,15 +7557,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="B9" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B10" s="26" t="n">
         <v>0.0388</v>
@@ -7509,7 +7573,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="B11" s="26" t="n">
         <v>0.0389</v>
@@ -7517,79 +7581,79 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="B12" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="B13" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="B14" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="B15" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="B16" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="B17" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="B18" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B19" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="B20" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B21" s="26" t="n">
         <v>0.039</v>
@@ -7597,55 +7661,55 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="B22" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="B23" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B24" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B25" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B26" s="26" t="n">
-        <v>0.0385</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="B27" s="26" t="n">
-        <v>0.0385</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B28" s="26" t="n">
         <v>0.0385</v>
@@ -7653,23 +7717,23 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B29" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B30" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B31" s="26" t="n">
         <v>0.0362</v>
@@ -7677,15 +7741,15 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B32" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B33" s="26" t="n">
         <v>0.0362</v>
@@ -7693,39 +7757,39 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B34" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B35" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B36" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B37" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B38" s="26" t="n">
         <v>0.0365</v>
@@ -7733,7 +7797,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B39" s="26" t="n">
         <v>0.0366</v>
@@ -7741,111 +7805,111 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B40" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B41" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B42" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B43" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B44" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B45" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B48" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B49" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B50" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B51" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B52" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B53" s="26" t="n">
         <v>0.0362</v>
@@ -7853,63 +7917,63 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B54" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B55" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B56" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B57" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B58" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B59" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B60" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B61" s="26" t="n">
         <v>0.0366</v>
@@ -7917,7 +7981,7 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B62" s="26" t="n">
         <v>0.0365</v>
@@ -7925,15 +7989,15 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B63" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B64" s="26" t="n">
         <v>0.0365</v>
@@ -7941,23 +8005,23 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B65" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B66" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B67" s="26" t="n">
         <v>0.0364</v>
@@ -7965,159 +8029,159 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B68" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B69" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B70" s="26" t="n">
-        <v>0.0357</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B71" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B72" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0357</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B73" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B74" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B75" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B76" s="26" t="n">
-        <v>0.0355</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B77" s="26" t="n">
-        <v>0.0353</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B78" s="26" t="n">
-        <v>0.0358</v>
+        <v>0.0355</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B79" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B80" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B81" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B82" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B83" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B84" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B85" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B86" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B87" s="26" t="n">
         <v>0.0362</v>
@@ -8125,23 +8189,23 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B88" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B89" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B90" s="26" t="n">
         <v>0.0362</v>
@@ -8149,55 +8213,55 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B91" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B92" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B93" s="26" t="n">
-        <v>0.0369</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B94" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B95" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B96" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B97" s="26" t="n">
         <v>0.036</v>
@@ -8205,55 +8269,55 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B98" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B99" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B100" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B101" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B102" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B103" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B104" s="26" t="n">
         <v>0.0363</v>
@@ -8261,18 +8325,10 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B105" s="26" t="n">
-        <v>0.0362</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="n">
-        <v>46169</v>
-      </c>
-      <c r="B106" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0365</v>
       </c>
     </row>
   </sheetData>

--- a/output/downloads/sofr-forward-curve.xlsx
+++ b/output/downloads/sofr-forward-curve.xlsx
@@ -236,7 +236,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SOFR forward curve, 2026-10-26</a:t>
+              <a:t>SOFR forward curve, 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="3">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.0393</v>
+        <v>0.0395</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>on 2026-10-26 (NY Fed)</t>
+          <t>on 2026-10-27 (NY Fed)</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27 18:42 UTC</t>
+          <t>2026-10-28 18:52 UTC</t>
         </is>
       </c>
     </row>
@@ -855,13 +855,13 @@
         <v>31</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.0389663</v>
+        <v>0.0389578</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>0.0389053</v>
+        <v>0.0388969</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>0.0389662</v>
+        <v>0.0389577</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0</v>
@@ -891,13 +891,13 @@
         <v>30</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.0393875</v>
+        <v>0.0392515</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.0393271</v>
+        <v>0.0391915</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>0.0393873</v>
+        <v>0.0392513</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.0408613</v>
+        <v>0.0407753</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>0.0407941</v>
+        <v>0.0407084</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0.040862</v>
+        <v>0.0407759</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>0.01</v>
@@ -963,13 +963,13 @@
         <v>31</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.0415602</v>
+        <v>0.0415104</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.0414912</v>
+        <v>0.0414416</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>0.0415615</v>
+        <v>0.0415118</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>0.01</v>
@@ -999,13 +999,13 @@
         <v>28</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.04220939999999999</v>
+        <v>0.042266</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.04214540000000001</v>
+        <v>0.0422018</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0.0422129</v>
+        <v>0.0422694</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>0.03</v>
@@ -1035,16 +1035,16 @@
         <v>31</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.0429475</v>
+        <v>0.0430513</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.0428733</v>
+        <v>0.0429768</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0.04295309999999999</v>
+        <v>0.0430568</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
@@ -1071,13 +1071,13 @@
         <v>30</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.0438907</v>
+        <v>0.0440598</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>0.0438155</v>
+        <v>0.0439839</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>0.043899</v>
+        <v>0.0440679</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>0.08</v>
@@ -1107,16 +1107,16 @@
         <v>31</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.0447104</v>
+        <v>0.0449906</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.0446302</v>
+        <v>0.0449094</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.04472209999999999</v>
+        <v>0.04500200000000001</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         <v>30</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.0454124</v>
+        <v>0.04571310000000001</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>0.0453325</v>
+        <v>0.045632</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0.04542939999999999</v>
+        <v>0.0457297</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>0.17</v>
@@ -1179,13 +1179,13 @@
         <v>31</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.0457461</v>
+        <v>0.0460596</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.0456621</v>
+        <v>0.0459744</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.04576590000000001</v>
+        <v>0.0460791</v>
       </c>
       <c r="G21" s="13" t="n">
         <v>0.2</v>
@@ -1215,13 +1215,13 @@
         <v>31</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.0460157</v>
+        <v>0.0463663</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.04593</v>
+        <v>0.04627919999999999</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0.0460416</v>
+        <v>0.046392</v>
       </c>
       <c r="G22" s="13" t="n">
         <v>0.26</v>
@@ -1251,13 +1251,13 @@
         <v>30</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.04617549999999999</v>
+        <v>0.0465441</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.0460928</v>
+        <v>0.04646</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.0462064</v>
+        <v>0.0465748</v>
       </c>
       <c r="G23" s="13" t="n">
         <v>0.31</v>
@@ -1287,13 +1287,13 @@
         <v>31</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.0463397</v>
+        <v>0.0467213</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>0.046254</v>
+        <v>0.0466341</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0.0463767</v>
+        <v>0.04675799999999999</v>
       </c>
       <c r="G24" s="13" t="n">
         <v>0.37</v>
@@ -1323,13 +1323,13 @@
         <v>30</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.0463263</v>
+        <v>0.0466737</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.0462428</v>
+        <v>0.0465889</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0.04636949999999999</v>
+        <v>0.0467166</v>
       </c>
       <c r="G25" s="13" t="n">
         <v>0.43</v>
@@ -1359,13 +1359,13 @@
         <v>31</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.0462203</v>
+        <v>0.0465657</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.0461344</v>
+        <v>0.0464785</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0.0462727</v>
+        <v>0.0466179</v>
       </c>
       <c r="G26" s="13" t="n">
         <v>0.52</v>
@@ -1395,13 +1395,13 @@
         <v>31</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.046135</v>
+        <v>0.0464957</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>0.0460496</v>
+        <v>0.0464089</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0.0461921</v>
+        <v>0.0465525</v>
       </c>
       <c r="G27" s="13" t="n">
         <v>0.57</v>
@@ -1431,13 +1431,13 @@
         <v>29</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.0458833</v>
+        <v>0.046327</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>0.0458046</v>
+        <v>0.0462468</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>0.0459483</v>
+        <v>0.0463918</v>
       </c>
       <c r="G28" s="13" t="n">
         <v>0.65</v>
@@ -1467,16 +1467,16 @@
         <v>31</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.04579220000000001</v>
+        <v>0.04619239999999999</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>0.0457073</v>
+        <v>0.046106</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.045864</v>
+        <v>0.0462639</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
@@ -1503,16 +1503,16 @@
         <v>30</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>0.0457128</v>
+        <v>0.04607770000000001</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>0.0456319</v>
+        <v>0.0459956</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0.0457944</v>
+        <v>0.0461591</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
@@ -1539,16 +1539,16 @@
         <v>31</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>0.04562770000000001</v>
+        <v>0.0459587</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0.045544</v>
+        <v>0.04587379999999999</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.0457205</v>
+        <v>0.0460512</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
@@ -1575,13 +1575,13 @@
         <v>30</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.0455401</v>
+        <v>0.0458494</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>0.0454596</v>
+        <v>0.0457678</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0.0456431</v>
+        <v>0.045952</v>
       </c>
       <c r="G32" s="13" t="n">
         <v>1.03</v>
@@ -1611,16 +1611,16 @@
         <v>31</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.0454641</v>
+        <v>0.0457632</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>0.0453808</v>
+        <v>0.0456788</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0.0455767</v>
+        <v>0.0458755</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
@@ -1647,13 +1647,13 @@
         <v>31</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.0453769</v>
+        <v>0.04567350000000001</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>0.0452935</v>
+        <v>0.0455891</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0.0455009</v>
+        <v>0.04579710000000001</v>
       </c>
       <c r="G34" s="13" t="n">
         <v>1.24</v>
@@ -1683,13 +1683,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.0452943</v>
+        <v>0.0455941</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>0.0452149</v>
+        <v>0.0455137</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0.0454296</v>
+        <v>0.045729</v>
       </c>
       <c r="G35" s="13" t="n">
         <v>1.35</v>
@@ -1719,16 +1719,16 @@
         <v>31</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>0.0452231</v>
+        <v>0.0455246</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>0.0451408</v>
+        <v>0.0454413</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0.0453699</v>
+        <v>0.04567109999999999</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
@@ -1755,16 +1755,16 @@
         <v>30</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.0451412</v>
+        <v>0.04543700000000001</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>0.0450618</v>
+        <v>0.0453565</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0.04530090000000001</v>
+        <v>0.0455962</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
@@ -1791,16 +1791,16 @@
         <v>31</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>0.045065</v>
+        <v>0.0453463</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>0.04498389999999999</v>
+        <v>0.0452641</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0.0452376</v>
+        <v>0.0455184</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
@@ -1827,13 +1827,13 @@
         <v>31</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0.044988</v>
+        <v>0.0452504</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0.0449066</v>
+        <v>0.0451681</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0.04517350000000001</v>
+        <v>0.0454354</v>
       </c>
       <c r="G39" s="13" t="n">
         <v>1.85</v>
@@ -1863,13 +1863,13 @@
         <v>28</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>0.0448949</v>
+        <v>0.04513760000000001</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>0.04482249999999999</v>
+        <v>0.0450644</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0.0450943</v>
+        <v>0.04533649999999999</v>
       </c>
       <c r="G40" s="13" t="n">
         <v>1.99</v>
@@ -1899,13 +1899,13 @@
         <v>31</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.04482129999999999</v>
+        <v>0.0450471</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.0447405</v>
+        <v>0.0449655</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0.0450347</v>
+        <v>0.04525999999999999</v>
       </c>
       <c r="G41" s="13" t="n">
         <v>2.13</v>
@@ -1935,13 +1935,13 @@
         <v>30</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>0.0447412</v>
+        <v>0.0449508</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>0.044663</v>
+        <v>0.0448718</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0.0449686</v>
+        <v>0.04517769999999999</v>
       </c>
       <c r="G42" s="13" t="n">
         <v>2.27</v>
@@ -1971,16 +1971,16 @@
         <v>31</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.0446646</v>
+        <v>0.04485459999999999</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.0445843</v>
+        <v>0.0447737</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.0449076</v>
+        <v>0.0450971</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
@@ -2007,16 +2007,16 @@
         <v>30</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.0445914</v>
+        <v>0.0447613</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>0.0445141</v>
+        <v>0.04468340000000001</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0.0448501</v>
+        <v>0.0450195</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
@@ -2043,16 +2043,16 @@
         <v>31</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.04453210000000001</v>
+        <v>0.0446868</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.044452</v>
+        <v>0.0446062</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0.0448066</v>
+        <v>0.0449608</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
@@ -2079,16 +2079,16 @@
         <v>31</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.0444717</v>
+        <v>0.04462</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>0.0443916</v>
+        <v>0.0445394</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0.0447634</v>
+        <v>0.0449111</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
@@ -2115,16 +2115,16 @@
         <v>30</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.0444207</v>
+        <v>0.0445711</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.0443442</v>
+        <v>0.044494</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.0447275</v>
+        <v>0.04487720000000001</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
@@ -2151,16 +2151,16 @@
         <v>31</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.0443706</v>
+        <v>0.0445226</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>0.0442914</v>
+        <v>0.04444289999999999</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0.0446962</v>
+        <v>0.0448477</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
@@ -2187,13 +2187,13 @@
         <v>30</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.04432489999999999</v>
+        <v>0.0444685</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>0.0442488</v>
+        <v>0.04439199999999999</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0.044668</v>
+        <v>0.0448111</v>
       </c>
       <c r="G49" s="13" t="n">
         <v>3.43</v>
@@ -2223,16 +2223,16 @@
         <v>31</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.0442927</v>
+        <v>0.0444194</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>0.0442136</v>
+        <v>0.0443398</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0.0446527</v>
+        <v>0.0447788</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
@@ -2259,16 +2259,16 @@
         <v>31</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.0442584</v>
+        <v>0.0443661</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>0.0441796</v>
+        <v>0.0442869</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>0.04463739999999999</v>
+        <v>0.0447445</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
@@ -2295,13 +2295,13 @@
         <v>28</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.0442213</v>
+        <v>0.0443195</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>0.04415110000000001</v>
+        <v>0.04424890000000001</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0.0446196</v>
+        <v>0.0447171</v>
       </c>
       <c r="G52" s="13" t="n">
         <v>3.98</v>
@@ -2331,16 +2331,16 @@
         <v>31</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.0442074</v>
+        <v>0.04430659999999999</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.0441288</v>
+        <v>0.04422760000000001</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.044625</v>
+        <v>0.0447235</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
@@ -2367,13 +2367,13 @@
         <v>30</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>0.0441875</v>
+        <v>0.0442889</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>0.0441117</v>
+        <v>0.0442128</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>0.0446246</v>
+        <v>0.04472540000000001</v>
       </c>
       <c r="G54" s="13" t="n">
         <v>4.37</v>
@@ -2403,13 +2403,13 @@
         <v>31</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>0.0441781</v>
+        <v>0.0442726</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.0440996</v>
+        <v>0.0441937</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.04463549999999999</v>
+        <v>0.0447292</v>
       </c>
       <c r="G55" s="13" t="n">
         <v>4.57</v>
@@ -2439,16 +2439,16 @@
         <v>30</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>0.0441689</v>
+        <v>0.0442469</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>0.044093</v>
+        <v>0.0441708</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>0.0446455</v>
+        <v>0.04472279999999999</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>4.77</v>
+        <v>4.76</v>
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
@@ -2475,16 +2475,16 @@
         <v>31</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>0.04416929999999999</v>
+        <v>0.0442274</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.0440905</v>
+        <v>0.0441484</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.0446683</v>
+        <v>0.0447258</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>4.99</v>
+        <v>4.98</v>
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
@@ -2511,13 +2511,13 @@
         <v>31</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>0.0441723</v>
+        <v>0.0442212</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>0.0440935</v>
+        <v>0.0441422</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0.0446927</v>
+        <v>0.0447408</v>
       </c>
       <c r="G58" s="13" t="n">
         <v>5.2</v>
@@ -2547,13 +2547,13 @@
         <v>30</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>0.0441772</v>
+        <v>0.0442272</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.0441011</v>
+        <v>0.0441509</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.0447177</v>
+        <v>0.0447669</v>
       </c>
       <c r="G59" s="13" t="n">
         <v>5.4</v>
@@ -2583,16 +2583,16 @@
         <v>31</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.0441939</v>
+        <v>0.044246</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>0.0441153</v>
+        <v>0.0441673</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0.04475799999999999</v>
+        <v>0.0448095</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>5.64</v>
+        <v>5.63</v>
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>30</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>0.04421</v>
+        <v>0.044255</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>0.0441345</v>
+        <v>0.0441793</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0.0447969</v>
+        <v>0.0448411</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>5.87</v>
+        <v>5.86</v>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
@@ -2655,16 +2655,16 @@
         <v>31</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>0.0442374</v>
+        <v>0.0442654</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>0.0441583</v>
+        <v>0.0441863</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0.044847</v>
+        <v>0.0448743</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
@@ -2691,16 +2691,16 @@
         <v>31</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>0.0442664</v>
+        <v>0.0442749</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>0.0441876</v>
+        <v>0.044196</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0.04489969999999999</v>
+        <v>0.0449074</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>6.33</v>
+        <v>6.32</v>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
@@ -2727,16 +2727,16 @@
         <v>28</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>0.0442909</v>
+        <v>0.0442874</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>0.04422010000000001</v>
+        <v>0.0442165</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>0.0449465</v>
+        <v>0.0449422</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>6.56</v>
+        <v>6.55</v>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
@@ -2763,13 +2763,13 @@
         <v>31</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>0.0443377</v>
+        <v>0.04433119999999999</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>0.0442583</v>
+        <v>0.0442518</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0.0450171</v>
+        <v>0.0450097</v>
       </c>
       <c r="G65" s="13" t="n">
         <v>6.79</v>
@@ -2799,13 +2799,13 @@
         <v>30</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>0.0443802</v>
+        <v>0.0443773</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>0.0443038</v>
+        <v>0.0443009</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0.0450845</v>
+        <v>0.0450809</v>
       </c>
       <c r="G66" s="13" t="n">
         <v>7.04</v>
@@ -2835,16 +2835,16 @@
         <v>31</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>0.0444312</v>
+        <v>0.0444324</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>0.044352</v>
+        <v>0.0443532</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>0.0451599</v>
+        <v>0.0451603</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>7.29</v>
+        <v>7.28</v>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
@@ -2871,16 +2871,16 @@
         <v>30</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>0.0444815</v>
+        <v>0.044484</v>
       </c>
       <c r="E68" s="12" t="n">
-        <v>0.0444044</v>
+        <v>0.0444069</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0.0452344</v>
+        <v>0.045236</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>7.53</v>
+        <v>7.52</v>
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
@@ -2907,13 +2907,13 @@
         <v>31</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>0.0445469</v>
+        <v>0.0445488</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>0.0444671</v>
+        <v>0.044469</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0.0453264</v>
+        <v>0.0453274</v>
       </c>
       <c r="G69" s="13" t="n">
         <v>7.79</v>
@@ -2943,16 +2943,16 @@
         <v>31</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>0.0446151</v>
+        <v>0.0446159</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>0.044535</v>
+        <v>0.0445359</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>0.0454207</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>8.06</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
@@ -2979,16 +2979,16 @@
         <v>30</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>0.04468390000000001</v>
+        <v>0.0446844</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>0.0446059</v>
+        <v>0.0446064</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0.045515</v>
+        <v>0.0455146</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>8.31</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H71" s="14" t="inlineStr">
         <is>
@@ -3015,16 +3015,16 @@
         <v>31</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>0.04476479999999999</v>
+        <v>0.0447654</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>0.0446842</v>
+        <v>0.0446848</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0.0456235</v>
+        <v>0.04562330000000001</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>8.59</v>
+        <v>8.58</v>
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
@@ -3051,16 +3051,16 @@
         <v>30</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>0.0448323</v>
+        <v>0.0448332</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>0.0447543</v>
+        <v>0.0447552</v>
       </c>
       <c r="F73" s="12" t="n">
         <v>0.0457161</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>8.84</v>
+        <v>8.83</v>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
@@ -3087,16 +3087,16 @@
         <v>31</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>0.044914</v>
+        <v>0.0449151</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>0.0448325</v>
+        <v>0.0448336</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0.0458272</v>
+        <v>0.04582729999999999</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>9.130000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
@@ -3123,16 +3123,16 @@
         <v>31</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>0.0449831</v>
+        <v>0.044984</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>0.0449019</v>
+        <v>0.0449028</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0.0459229</v>
+        <v>0.045923</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>9.4</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
@@ -3159,16 +3159,16 @@
         <v>29</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>0.0450486</v>
+        <v>0.0450493</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>0.0449727</v>
+        <v>0.0449734</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>0.0460159</v>
+        <v>0.0460157</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
@@ -3195,16 +3195,16 @@
         <v>31</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>0.0451278</v>
+        <v>0.0451283</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>0.0450459</v>
+        <v>0.0450464</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0.0461245</v>
+        <v>0.04612409999999999</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="H77" s="14" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
         <v>30</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>0.0451958</v>
+        <v>0.0451967</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>0.045116</v>
+        <v>0.04511689999999999</v>
       </c>
       <c r="F78" s="12" t="n">
         <v>0.04622080000000001</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
@@ -3267,16 +3267,16 @@
         <v>31</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>0.0452632</v>
+        <v>0.04526500000000001</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0.0451809</v>
+        <v>0.0451828</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0.0463153</v>
+        <v>0.0463161</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>10.52</v>
+        <v>10.51</v>
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
@@ -3303,16 +3303,16 @@
         <v>30</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>0.04533470000000001</v>
+        <v>0.0453373</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>0.045255</v>
+        <v>0.04525750000000001</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0.0464178</v>
+        <v>0.0464194</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
@@ -3339,16 +3339,16 @@
         <v>31</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>0.0454089</v>
+        <v>0.0454103</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>0.0453262</v>
+        <v>0.0453275</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0.0465217</v>
+        <v>0.04652199999999999</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>11.13</v>
+        <v>11.12</v>
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
@@ -3375,16 +3375,16 @@
         <v>31</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>0.0454809</v>
+        <v>0.0454786</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>0.0453971</v>
+        <v>0.04539489999999999</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0.0466225</v>
+        <v>0.0466193</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>11.42</v>
+        <v>11.41</v>
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
@@ -3411,16 +3411,16 @@
         <v>30</v>
       </c>
       <c r="D83" s="12" t="n">
-        <v>0.0455527</v>
+        <v>0.0455467</v>
       </c>
       <c r="E83" s="12" t="n">
-        <v>0.0454722</v>
+        <v>0.0454662</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0.04672519999999999</v>
+        <v>0.0467183</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>11.73</v>
+        <v>11.72</v>
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
@@ -3447,16 +3447,16 @@
         <v>31</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>0.0456215</v>
+        <v>0.0456178</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>0.0455384</v>
+        <v>0.0455346</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0.0468247</v>
+        <v>0.0468199</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>12.03</v>
+        <v>12.02</v>
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
@@ -3483,16 +3483,16 @@
         <v>30</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>0.0456755</v>
+        <v>0.0456836</v>
       </c>
       <c r="E85" s="12" t="n">
-        <v>0.04559440000000001</v>
+        <v>0.0456024</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>0.0469096</v>
+        <v>0.04691670000000001</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>12.34</v>
+        <v>12.33</v>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         <v>31</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>0.0457275</v>
+        <v>0.0457548</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>0.04564339999999999</v>
+        <v>0.0456706</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>0.04699329999999999</v>
+        <v>0.0470195</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>12.66</v>
+        <v>12.65</v>
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
@@ -3555,16 +3555,16 @@
         <v>31</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>0.045776</v>
+        <v>0.0458205</v>
       </c>
       <c r="E87" s="12" t="n">
-        <v>0.0456919</v>
+        <v>0.04573629999999999</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0.0470713</v>
+        <v>0.0471149</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>12.95</v>
+        <v>12.94</v>
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
@@ -3591,16 +3591,16 @@
         <v>28</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>0.04583230000000001</v>
+        <v>0.0458887</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>0.0457569</v>
+        <v>0.045813</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0.04716090000000001</v>
+        <v>0.0472162</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>13.29</v>
+        <v>13.28</v>
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>31</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>0.0459119</v>
+        <v>0.0459696</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>0.0458266</v>
+        <v>0.0458841</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>0.0472727</v>
+        <v>0.0473293</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>13.61</v>
+        <v>13.6</v>
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
@@ -3663,16 +3663,16 @@
         <v>30</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>0.0459759</v>
+        <v>0.0460297</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>0.0458941</v>
+        <v>0.04594769999999999</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0.0473681</v>
+        <v>0.0474208</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>13.92</v>
+        <v>13.91</v>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
@@ -3699,16 +3699,16 @@
         <v>31</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>0.0460325</v>
+        <v>0.0460827</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>0.0459473</v>
+        <v>0.0459973</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>0.04745580000000001</v>
+        <v>0.04750479999999999</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>14.23</v>
+        <v>14.22</v>
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
@@ -3735,16 +3735,16 @@
         <v>30</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>0.0460723</v>
+        <v>0.0461212</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>0.0459899</v>
+        <v>0.0460386</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>0.0475286</v>
+        <v>0.0475764</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>14.56</v>
+        <v>14.55</v>
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
@@ -3771,16 +3771,16 @@
         <v>31</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>0.0461086</v>
+        <v>0.0461582</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>0.0460236</v>
+        <v>0.0460731</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>0.0475978</v>
+        <v>0.0476464</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>14.89</v>
+        <v>14.88</v>
       </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
@@ -3807,16 +3807,16 @@
         <v>31</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>0.0461461</v>
+        <v>0.0461967</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>0.0460598</v>
+        <v>0.04611030000000001</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>0.047669</v>
+        <v>0.0477186</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>15.23</v>
+        <v>15.22</v>
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
@@ -3843,16 +3843,16 @@
         <v>30</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>0.0461884</v>
+        <v>0.0462395</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>0.0461056</v>
+        <v>0.0461565</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>0.0477455</v>
+        <v>0.0477955</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>15.57</v>
+        <v>15.56</v>
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
@@ -3879,16 +3879,16 @@
         <v>31</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>0.0462474</v>
+        <v>0.0462984</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>0.0461615</v>
+        <v>0.0462124</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>0.0478377</v>
+        <v>0.0478875</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>15.9</v>
+        <v>15.89</v>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
@@ -3915,16 +3915,16 @@
         <v>30</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>0.0463208</v>
+        <v>0.0463716</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>0.0462378</v>
+        <v>0.0462884</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>0.0479489</v>
+        <v>0.0479985</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>16.28</v>
+        <v>16.27</v>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
@@ -3951,16 +3951,16 @@
         <v>31</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>0.0463974</v>
+        <v>0.0464481</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>0.046311</v>
+        <v>0.0463616</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>0.0480615</v>
+        <v>0.0481111</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>16.64</v>
+        <v>16.63</v>
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
@@ -3987,16 +3987,16 @@
         <v>31</v>
       </c>
       <c r="D99" s="12" t="n">
-        <v>0.0464463</v>
+        <v>0.046497</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>0.0463597</v>
+        <v>0.04641029999999999</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>0.0481433</v>
+        <v>0.0481929</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>16.97</v>
+        <v>16.96</v>
       </c>
       <c r="H99" s="14" t="inlineStr">
         <is>
@@ -4023,16 +4023,16 @@
         <v>28</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>0.0464545</v>
+        <v>0.0465053</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>0.04637699999999999</v>
+        <v>0.0464276</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>0.0481874</v>
+        <v>0.0482371</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>17.33</v>
+        <v>17.32</v>
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
@@ -4059,16 +4059,16 @@
         <v>31</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>0.0464514</v>
+        <v>0.0465022</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>0.0463641</v>
+        <v>0.0464147</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>0.0482187</v>
+        <v>0.0482683</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>17.67</v>
+        <v>17.66</v>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         <v>30</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>0.04644599999999999</v>
+        <v>0.0464967</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>0.0463625</v>
+        <v>0.0464131</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>0.0482447</v>
+        <v>0.0482942</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>17.99</v>
+        <v>17.97</v>
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
         <v>31</v>
       </c>
       <c r="D103" s="12" t="n">
-        <v>0.0464882</v>
+        <v>0.046539</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>0.0464013</v>
+        <v>0.0464519</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>0.0483247</v>
+        <v>0.0483743</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>18.36</v>
+        <v>18.35</v>
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
@@ -4167,16 +4167,16 @@
         <v>30</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>0.04656150000000001</v>
+        <v>0.0466123</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>0.0464774</v>
+        <v>0.046528</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>0.0484345</v>
+        <v>0.0484841</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>18.73</v>
+        <v>18.72</v>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
@@ -4203,16 +4203,16 @@
         <v>31</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>0.0466339</v>
+        <v>0.0466847</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>0.0465462</v>
+        <v>0.0465969</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>0.0485425</v>
+        <v>0.048592</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>19.09</v>
+        <v>19.07</v>
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
@@ -4239,16 +4239,16 @@
         <v>31</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>0.0466661</v>
+        <v>0.0467169</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>0.04657790000000001</v>
+        <v>0.0466286</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>0.0486148</v>
+        <v>0.0486644</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>19.49</v>
+        <v>19.47</v>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         <v>30</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>0.0466441</v>
+        <v>0.046695</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>0.0465599</v>
+        <v>0.0466106</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>0.0486297</v>
+        <v>0.0486793</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>19.86</v>
+        <v>19.84</v>
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
@@ -4311,16 +4311,16 @@
         <v>31</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>0.0466355</v>
+        <v>0.0466864</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>0.0465481</v>
+        <v>0.0465987</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>0.0486573</v>
+        <v>0.0487069</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>20.22</v>
+        <v>20.21</v>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
@@ -4347,16 +4347,16 @@
         <v>30</v>
       </c>
       <c r="D109" s="12" t="n">
-        <v>0.0466843</v>
+        <v>0.0467352</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>0.0465994</v>
+        <v>0.04665</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>0.0487445</v>
+        <v>0.0487941</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>20.6</v>
+        <v>20.59</v>
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
@@ -4383,16 +4383,16 @@
         <v>31</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>0.0468047</v>
+        <v>0.0468556</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>0.04671719999999999</v>
+        <v>0.04676789999999999</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>0.048903</v>
+        <v>0.0489525</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>20.98</v>
+        <v>20.97</v>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
@@ -4419,16 +4419,16 @@
         <v>31</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0.0469316</v>
+        <v>0.0469825</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>0.046843</v>
+        <v>0.0468937</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>0.0490667</v>
+        <v>0.04911629999999999</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>21.35</v>
+        <v>21.34</v>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
@@ -4455,16 +4455,16 @@
         <v>28</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0.0470019</v>
+        <v>0.0470527</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>0.0469225</v>
+        <v>0.04697320000000001</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>0.0491752</v>
+        <v>0.0492248</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>21.73</v>
+        <v>21.72</v>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
@@ -4491,16 +4491,16 @@
         <v>31</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.0470173</v>
+        <v>0.0470682</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>0.04692859999999999</v>
+        <v>0.0469793</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>0.0492295</v>
+        <v>0.0492791</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>22.12</v>
+        <v>22.11</v>
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>30</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0.0469872</v>
+        <v>0.0470381</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>0.0469009</v>
+        <v>0.0469516</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>0.04923619999999999</v>
+        <v>0.0492858</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>22.49</v>
+        <v>22.48</v>
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
@@ -4563,16 +4563,16 @@
         <v>31</v>
       </c>
       <c r="D115" s="12" t="n">
-        <v>0.0469802</v>
+        <v>0.0470311</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>0.0468914</v>
+        <v>0.0469421</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>0.0492697</v>
+        <v>0.0493193</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>22.9</v>
+        <v>22.88</v>
       </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
@@ -4599,16 +4599,16 @@
         <v>30</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>0.0470085</v>
+        <v>0.0470594</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>0.0469225</v>
+        <v>0.04697320000000001</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>0.0493376</v>
+        <v>0.0493872</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>23.29</v>
+        <v>23.28</v>
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
@@ -4635,16 +4635,16 @@
         <v>31</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>0.0470633</v>
+        <v>0.0471142</v>
       </c>
       <c r="E117" s="12" t="n">
-        <v>0.0469738</v>
+        <v>0.0470245</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>0.0494317</v>
+        <v>0.0494813</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>23.68</v>
+        <v>23.67</v>
       </c>
       <c r="H117" s="14" t="inlineStr">
         <is>
@@ -4671,16 +4671,16 @@
         <v>31</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>0.04711000000000001</v>
+        <v>0.04716090000000001</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>0.0470201</v>
+        <v>0.0470709</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>0.0495198</v>
+        <v>0.04956940000000001</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>24.1</v>
+        <v>24.08</v>
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
@@ -4707,16 +4707,16 @@
         <v>30</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>0.0471355</v>
+        <v>0.0471864</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>0.0470493</v>
+        <v>0.0471</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>0.04958070000000001</v>
+        <v>0.0496303</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>24.45</v>
+        <v>24.44</v>
       </c>
       <c r="H119" s="14" t="inlineStr">
         <is>
@@ -4743,16 +4743,16 @@
         <v>31</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>0.0471883</v>
+        <v>0.0472392</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>0.04709869999999999</v>
+        <v>0.0471495</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>0.0496777</v>
+        <v>0.0497273</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>24.89</v>
+        <v>24.88</v>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
@@ -4779,16 +4779,16 @@
         <v>30</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>0.0472721</v>
+        <v>0.0473231</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>0.0471857</v>
+        <v>0.0472364</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>0.0498015</v>
+        <v>0.0498511</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>25.29</v>
+        <v>25.28</v>
       </c>
       <c r="H121" s="14" t="inlineStr">
         <is>
@@ -4815,16 +4815,16 @@
         <v>31</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.0473905</v>
+        <v>0.04744139999999999</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>0.0473</v>
+        <v>0.0473507</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>0.04995860000000001</v>
+        <v>0.0500082</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>25.68</v>
+        <v>25.67</v>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
@@ -4851,16 +4851,16 @@
         <v>31</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>0.0475136</v>
+        <v>0.0475646</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>0.0474228</v>
+        <v>0.0474736</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>0.05012419999999999</v>
+        <v>0.0501738</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>26.11</v>
+        <v>26.09</v>
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
@@ -4887,16 +4887,16 @@
         <v>29</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>0.0475843</v>
+        <v>0.04763530000000001</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>0.04749970000000001</v>
+        <v>0.0475505</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>0.0502367</v>
+        <v>0.0502863</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>26.52</v>
+        <v>26.51</v>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
@@ -4923,16 +4923,16 @@
         <v>31</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>0.04760329999999999</v>
+        <v>0.0476543</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>0.0475118</v>
+        <v>0.0475626</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>0.0502949</v>
+        <v>0.05034449999999999</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>26.92</v>
+        <v>26.9</v>
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>30</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>0.0475676</v>
+        <v>0.0476185</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>0.0474798</v>
+        <v>0.0475306</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>0.0503022</v>
+        <v>0.0503518</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>27.35</v>
+        <v>27.33</v>
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
@@ -4995,16 +4995,16 @@
         <v>31</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>0.047517</v>
+        <v>0.047568</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>0.0474264</v>
+        <v>0.0474772</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>0.0502928</v>
+        <v>0.0503424</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>27.76</v>
+        <v>27.74</v>
       </c>
       <c r="H127" s="14" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>30</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>0.0474575</v>
+        <v>0.0475085</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>0.0473698</v>
+        <v>0.0474205</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>0.0502725</v>
+        <v>0.0503221</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>28.15</v>
+        <v>28.14</v>
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
@@ -5067,16 +5067,16 @@
         <v>31</v>
       </c>
       <c r="D129" s="18" t="n">
-        <v>0.0474584</v>
+        <v>0.0475094</v>
       </c>
       <c r="E129" s="18" t="n">
-        <v>0.0473678</v>
+        <v>0.0474186</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.050275</v>
+        <v>0.0503246</v>
       </c>
       <c r="G129" s="19" t="n">
-        <v>28.17</v>
+        <v>28.15</v>
       </c>
       <c r="H129" s="20" t="inlineStr">
         <is>
@@ -5103,16 +5103,16 @@
         <v>31</v>
       </c>
       <c r="D130" s="18" t="n">
-        <v>0.0474584</v>
+        <v>0.0475094</v>
       </c>
       <c r="E130" s="18" t="n">
-        <v>0.0473678</v>
+        <v>0.0474186</v>
       </c>
       <c r="F130" s="18" t="n">
-        <v>0.050275</v>
+        <v>0.0503246</v>
       </c>
       <c r="G130" s="19" t="n">
-        <v>28.17</v>
+        <v>28.15</v>
       </c>
       <c r="H130" s="20" t="inlineStr">
         <is>
@@ -5139,16 +5139,16 @@
         <v>30</v>
       </c>
       <c r="D131" s="18" t="n">
-        <v>0.04745580000000001</v>
+        <v>0.0475068</v>
       </c>
       <c r="E131" s="18" t="n">
-        <v>0.0473678</v>
+        <v>0.0474186</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.0502721</v>
+        <v>0.0503217</v>
       </c>
       <c r="G131" s="19" t="n">
-        <v>28.16</v>
+        <v>28.15</v>
       </c>
       <c r="H131" s="20" t="inlineStr">
         <is>
@@ -5175,16 +5175,16 @@
         <v>31</v>
       </c>
       <c r="D132" s="18" t="n">
-        <v>0.0474584</v>
+        <v>0.0475094</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>0.0473678</v>
+        <v>0.0474186</v>
       </c>
       <c r="F132" s="18" t="n">
-        <v>0.050275</v>
+        <v>0.0503246</v>
       </c>
       <c r="G132" s="19" t="n">
-        <v>28.17</v>
+        <v>28.15</v>
       </c>
       <c r="H132" s="20" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5500,7 +5500,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-26)</t>
+          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-27)</t>
         </is>
       </c>
     </row>
@@ -5574,13 +5574,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.0383501</v>
+        <v>0.0383217</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>-0.249</v>
+        <v>-0.533</v>
       </c>
       <c r="I4" s="25" t="n">
-        <v>7744</v>
+        <v>7844</v>
       </c>
     </row>
     <row r="5">
@@ -5596,7 +5596,7 @@
         <v>46372</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>96.06</v>
+        <v>96.065</v>
       </c>
       <c r="E5" s="15">
         <f>(100-D5)/100</f>
@@ -5606,13 +5606,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.0393872</v>
+        <v>0.0393212</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>-0.128</v>
+        <v>-0.288</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>1309996</v>
+        <v>1308389</v>
       </c>
     </row>
     <row r="6">
@@ -5638,13 +5638,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.0389053</v>
+        <v>0.0388969</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>-0.697</v>
+        <v>-0.781</v>
       </c>
       <c r="I6" s="25" t="n">
-        <v>340840</v>
+        <v>339910</v>
       </c>
     </row>
     <row r="7">
@@ -5660,7 +5660,7 @@
         <v>46407</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>95.95999999999999</v>
+        <v>95.965</v>
       </c>
       <c r="E7" s="15">
         <f>(100-D7)/100</f>
@@ -5670,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.0404333</v>
+        <v>0.040342</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>0.333</v>
+        <v>-0.08</v>
       </c>
       <c r="I7" s="25" t="n">
         <v>7722</v>
@@ -5692,7 +5692,7 @@
         <v>46357</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>96.06999999999999</v>
+        <v>96.08499999999999</v>
       </c>
       <c r="E8" s="15">
         <f>(100-D8)/100</f>
@@ -5702,13 +5702,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.0393272</v>
+        <v>0.0391916</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>0.272</v>
+        <v>0.416</v>
       </c>
       <c r="I8" s="25" t="n">
-        <v>297603</v>
+        <v>315657</v>
       </c>
     </row>
     <row r="9">
@@ -5724,7 +5724,7 @@
         <v>46435</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>95.875</v>
+        <v>95.88</v>
       </c>
       <c r="E9" s="15">
         <f>(100-D9)/100</f>
@@ -5734,13 +5734,13 @@
         <v>0.01</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.0412691</v>
+        <v>0.041213</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>0.191</v>
+        <v>0.13</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>2028</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="10">
@@ -5756,7 +5756,7 @@
         <v>46388</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>95.91500000000001</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="E10" s="15">
         <f>(100-D10)/100</f>
@@ -5766,13 +5766,13 @@
         <v>0.01</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.0407948</v>
+        <v>0.0407091</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.552</v>
+        <v>0.091</v>
       </c>
       <c r="I10" s="25" t="n">
-        <v>241428</v>
+        <v>244021</v>
       </c>
     </row>
     <row r="11">
@@ -5788,7 +5788,7 @@
         <v>46463</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>95.8</v>
+        <v>95.795</v>
       </c>
       <c r="E11" s="15">
         <f>(100-D11)/100</f>
@@ -5798,13 +5798,13 @@
         <v>0.02</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.042009</v>
+        <v>0.0420078</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>0.09</v>
+        <v>-0.422</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>1574834</v>
+        <v>1596096</v>
       </c>
     </row>
     <row r="12">
@@ -5820,7 +5820,7 @@
         <v>46419</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>95.84999999999999</v>
+        <v>95.855</v>
       </c>
       <c r="E12" s="15">
         <f>(100-D12)/100</f>
@@ -5830,13 +5830,13 @@
         <v>0.02</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.0414931</v>
+        <v>0.0414435</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.065</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>190690</v>
+        <v>193502</v>
       </c>
     </row>
     <row r="13">
@@ -5852,23 +5852,23 @@
         <v>46498</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>95.70999999999999</v>
+        <v>95.705</v>
       </c>
       <c r="E13" s="15">
         <f>(100-D13)/100</f>
         <v/>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.0429122</v>
+        <v>0.0429976</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.122</v>
+        <v>0.476</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>1358</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="14">
@@ -5884,7 +5884,7 @@
         <v>46447</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>95.785</v>
+        <v>95.78</v>
       </c>
       <c r="E14" s="15">
         <f>(100-D14)/100</f>
@@ -5894,13 +5894,13 @@
         <v>0.04</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.04214909999999999</v>
+        <v>0.0422055</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.055</v>
       </c>
       <c r="I14" s="25" t="n">
-        <v>101983</v>
+        <v>111680</v>
       </c>
     </row>
     <row r="15">
@@ -5916,7 +5916,7 @@
         <v>46526</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>95.63500000000001</v>
+        <v>95.62</v>
       </c>
       <c r="E15" s="15">
         <f>(100-D15)/100</f>
@@ -5926,10 +5926,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.04367670000000001</v>
+        <v>0.0438317</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>0.267</v>
+        <v>0.317</v>
       </c>
       <c r="I15" s="25" t="n">
         <v>554</v>
@@ -5948,7 +5948,7 @@
         <v>46478</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>95.70999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="E16" s="15">
         <f>(100-D16)/100</f>
@@ -5958,13 +5958,13 @@
         <v>0.06</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.0428793</v>
+        <v>0.0429826</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.207</v>
+        <v>-0.174</v>
       </c>
       <c r="I16" s="25" t="n">
-        <v>35644</v>
+        <v>36442</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>46554</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>95.55</v>
+        <v>95.52</v>
       </c>
       <c r="E17" s="15">
         <f>(100-D17)/100</f>
@@ -5990,13 +5990,13 @@
         <v>0.1</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.0445192</v>
+        <v>0.0447454</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.192</v>
+        <v>-0.546</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>1324243</v>
+        <v>1311471</v>
       </c>
     </row>
     <row r="18">
@@ -6012,7 +6012,7 @@
         <v>46508</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>95.61499999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="E18" s="15">
         <f>(100-D18)/100</f>
@@ -6022,218 +6022,218 @@
         <v>0.09</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.0438243</v>
+        <v>0.0439926</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>-0.257</v>
+        <v>-0.074</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>68394</v>
+        <v>70063</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>SR1 MAY 27</t>
+          <t>SR3 APR 27</t>
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>46508</v>
+        <v>46498</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>46539</v>
+        <v>46589</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>95.535</v>
+        <v>95.44499999999999</v>
       </c>
       <c r="E19" s="15">
         <f>(100-D19)/100</f>
         <v/>
       </c>
       <c r="F19" s="24" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.0446424</v>
+        <v>0.0455556</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>-0.076</v>
+        <v>0.056</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>71874</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>SR1 JUN 27</t>
+          <t>SR1 MAY 27</t>
         </is>
       </c>
       <c r="B20" s="10" t="n">
+        <v>46508</v>
+      </c>
+      <c r="C20" s="10" t="n">
         <v>46539</v>
       </c>
-      <c r="C20" s="10" t="n">
-        <v>46569</v>
-      </c>
       <c r="D20" s="23" t="n">
-        <v>95.465</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="E20" s="15">
         <f>(100-D20)/100</f>
         <v/>
       </c>
       <c r="F20" s="24" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.0453486</v>
+        <v>0.0449214</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>-0.014</v>
+        <v>0.214</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>21272</v>
+        <v>71981</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 27</t>
+          <t>SR1 JUN 27</t>
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>46554</v>
+        <v>46539</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>46645</v>
+        <v>46569</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>95.395</v>
+        <v>95.435</v>
       </c>
       <c r="E21" s="15">
         <f>(100-D21)/100</f>
         <v/>
       </c>
       <c r="F21" s="24" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.0460722</v>
+        <v>0.045648</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>0.222</v>
+        <v>-0.02</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>1244435</v>
+        <v>21197</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>SR1 JUL 27</t>
+          <t>SR3 JUN 27</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>46569</v>
+        <v>46554</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>46600</v>
+        <v>46645</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>95.43000000000001</v>
+        <v>95.36</v>
       </c>
       <c r="E22" s="15">
         <f>(100-D22)/100</f>
         <v/>
       </c>
       <c r="F22" s="24" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.0456827</v>
+        <v>0.0464058</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>-0.173</v>
+        <v>0.058</v>
       </c>
       <c r="I22" s="25" t="n">
-        <v>38126</v>
+        <v>1244193</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>SR1 AUG 27</t>
+          <t>SR1 JUL 27</t>
         </is>
       </c>
       <c r="B23" s="10" t="n">
+        <v>46569</v>
+      </c>
+      <c r="C23" s="10" t="n">
         <v>46600</v>
       </c>
-      <c r="C23" s="10" t="n">
-        <v>46631</v>
-      </c>
       <c r="D23" s="23" t="n">
-        <v>95.405</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E23" s="15">
         <f>(100-D23)/100</f>
         <v/>
       </c>
       <c r="F23" s="24" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.0459557</v>
+        <v>0.0459948</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>0.057</v>
+        <v>-0.052</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>20213</v>
+        <v>38111</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>SR1 SEP 27</t>
+          <t>SR1 AUG 27</t>
         </is>
       </c>
       <c r="B24" s="10" t="n">
+        <v>46600</v>
+      </c>
+      <c r="C24" s="10" t="n">
         <v>46631</v>
       </c>
-      <c r="C24" s="10" t="n">
-        <v>46661</v>
-      </c>
       <c r="D24" s="23" t="n">
-        <v>95.38500000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E24" s="15">
         <f>(100-D24)/100</f>
         <v/>
       </c>
       <c r="F24" s="24" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.046124</v>
+        <v>0.0463047</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>-0.26</v>
+        <v>0.047</v>
       </c>
       <c r="I24" s="25" t="n">
-        <v>5231</v>
+        <v>20521</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 27</t>
+          <t>SR1 SEP 27</t>
         </is>
       </c>
       <c r="B25" s="10" t="n">
-        <v>46645</v>
+        <v>46631</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>46736</v>
+        <v>46661</v>
       </c>
       <c r="D25" s="23" t="n">
         <v>95.34999999999999</v>
@@ -6243,1005 +6243,1005 @@
         <v/>
       </c>
       <c r="F25" s="24" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.0465406</v>
+        <v>0.046491</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>0.406</v>
+        <v>-0.09</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>1081152</v>
+        <v>5161</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>SR1 OCT 27</t>
+          <t>SR3 SEP 27</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>46661</v>
+        <v>46645</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>46692</v>
+        <v>46736</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>95.37</v>
+        <v>95.315</v>
       </c>
       <c r="E26" s="15">
         <f>(100-D26)/100</f>
         <v/>
       </c>
       <c r="F26" s="24" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.0462912</v>
+        <v>0.04690859999999999</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0.586</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>7808</v>
+        <v>1076373</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>SR1 NOV 27</t>
+          <t>SR1 OCT 27</t>
         </is>
       </c>
       <c r="B27" s="10" t="n">
+        <v>46661</v>
+      </c>
+      <c r="C27" s="10" t="n">
         <v>46692</v>
       </c>
-      <c r="C27" s="10" t="n">
-        <v>46722</v>
-      </c>
       <c r="D27" s="23" t="n">
-        <v>95.37</v>
+        <v>95.33</v>
       </c>
       <c r="E27" s="15">
         <f>(100-D27)/100</f>
         <v/>
       </c>
       <c r="F27" s="24" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.0462866</v>
+        <v>0.0466711</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>-0.134</v>
+        <v>-0.289</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>1742</v>
+        <v>8027</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>SR1 DEC 27</t>
+          <t>SR1 NOV 27</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
+        <v>46692</v>
+      </c>
+      <c r="C28" s="10" t="n">
         <v>46722</v>
       </c>
-      <c r="C28" s="10" t="n">
-        <v>46753</v>
-      </c>
       <c r="D28" s="23" t="n">
-        <v>95.38</v>
+        <v>95.33499999999999</v>
       </c>
       <c r="E28" s="15">
         <f>(100-D28)/100</f>
         <v/>
       </c>
       <c r="F28" s="24" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.0461853</v>
+        <v>0.04663249999999999</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>-0.147</v>
+        <v>-0.175</v>
       </c>
       <c r="I28" s="25" t="n">
-        <v>20</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 27</t>
+          <t>SR1 DEC 27</t>
         </is>
       </c>
       <c r="B29" s="10" t="n">
-        <v>46736</v>
+        <v>46722</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>46827</v>
+        <v>46753</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>95.375</v>
+        <v>95.345</v>
       </c>
       <c r="E29" s="15">
         <f>(100-D29)/100</f>
         <v/>
       </c>
       <c r="F29" s="24" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.0462506</v>
+        <v>0.0465291</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>0.006</v>
+        <v>-0.209</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>1627781</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>SR1 JAN 28</t>
+          <t>SR3 DEC 27</t>
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>46753</v>
+        <v>46736</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>46784</v>
+        <v>46827</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>95.39</v>
+        <v>95.33499999999999</v>
       </c>
       <c r="E30" s="15">
         <f>(100-D30)/100</f>
         <v/>
       </c>
       <c r="F30" s="24" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.0461082</v>
+        <v>0.0466436</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>0.082</v>
+        <v>-0.064</v>
       </c>
       <c r="I30" s="25" t="n">
-        <v>1</v>
+        <v>1608233</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 28</t>
+          <t>SR1 JAN 28</t>
         </is>
       </c>
       <c r="B31" s="10" t="n">
-        <v>46827</v>
+        <v>46753</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>46925</v>
+        <v>46784</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>95.405</v>
+        <v>95.355</v>
       </c>
       <c r="E31" s="15">
         <f>(100-D31)/100</f>
         <v/>
       </c>
       <c r="F31" s="24" t="n">
-        <v>0.89</v>
+        <v>0.58</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.0459488</v>
+        <v>0.0464673</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>-0.012</v>
+        <v>0.173</v>
       </c>
       <c r="I31" s="25" t="n">
-        <v>826033</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 28</t>
+          <t>SR3 MAR 28</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
+        <v>46827</v>
+      </c>
+      <c r="C32" s="10" t="n">
         <v>46925</v>
       </c>
-      <c r="C32" s="10" t="n">
-        <v>47016</v>
-      </c>
       <c r="D32" s="23" t="n">
-        <v>95.43000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E32" s="15">
         <f>(100-D32)/100</f>
         <v/>
       </c>
       <c r="F32" s="24" t="n">
-        <v>1.21</v>
+        <v>0.88</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.04570109999999999</v>
+        <v>0.0463004</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>646307</v>
+        <v>833821</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 28</t>
+          <t>SR3 JUN 28</t>
         </is>
       </c>
       <c r="B33" s="10" t="n">
+        <v>46925</v>
+      </c>
+      <c r="C33" s="10" t="n">
         <v>47016</v>
       </c>
-      <c r="C33" s="10" t="n">
-        <v>47107</v>
-      </c>
       <c r="D33" s="23" t="n">
-        <v>95.45</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E33" s="15">
         <f>(100-D33)/100</f>
         <v/>
       </c>
       <c r="F33" s="24" t="n">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.04549959999999999</v>
+        <v>0.0460025</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>-0.004</v>
+        <v>0.025</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>678096</v>
+        <v>646762</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 28</t>
+          <t>SR3 SEP 28</t>
         </is>
       </c>
       <c r="B34" s="10" t="n">
+        <v>47016</v>
+      </c>
+      <c r="C34" s="10" t="n">
         <v>47107</v>
       </c>
-      <c r="C34" s="10" t="n">
-        <v>47198</v>
-      </c>
       <c r="D34" s="23" t="n">
-        <v>95.47</v>
+        <v>95.42</v>
       </c>
       <c r="E34" s="15">
         <f>(100-D34)/100</f>
         <v/>
       </c>
       <c r="F34" s="24" t="n">
-        <v>1.96</v>
+        <v>1.56</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.0452994</v>
+        <v>0.04579659999999999</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>-0.006</v>
+        <v>-0.034</v>
       </c>
       <c r="I34" s="25" t="n">
-        <v>553406</v>
+        <v>672641</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 29</t>
+          <t>SR3 DEC 28</t>
         </is>
       </c>
       <c r="B35" s="10" t="n">
+        <v>47107</v>
+      </c>
+      <c r="C35" s="10" t="n">
         <v>47198</v>
       </c>
-      <c r="C35" s="10" t="n">
-        <v>47289</v>
-      </c>
       <c r="D35" s="23" t="n">
-        <v>95.48999999999999</v>
+        <v>95.44499999999999</v>
       </c>
       <c r="E35" s="15">
         <f>(100-D35)/100</f>
         <v/>
       </c>
       <c r="F35" s="24" t="n">
-        <v>2.39</v>
+        <v>1.95</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.0451006</v>
+        <v>0.0455516</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>0.006</v>
+        <v>0.016</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>385197</v>
+        <v>551465</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 29</t>
+          <t>SR3 MAR 29</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
+        <v>47198</v>
+      </c>
+      <c r="C36" s="10" t="n">
         <v>47289</v>
       </c>
-      <c r="C36" s="10" t="n">
-        <v>47380</v>
-      </c>
       <c r="D36" s="23" t="n">
-        <v>95.505</v>
+        <v>95.47</v>
       </c>
       <c r="E36" s="15">
         <f>(100-D36)/100</f>
         <v/>
       </c>
       <c r="F36" s="24" t="n">
-        <v>2.87</v>
+        <v>2.39</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.04495</v>
+        <v>0.0452982</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="I36" s="25" t="n">
-        <v>391297</v>
+        <v>385342</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 29</t>
+          <t>SR3 JUN 29</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
+        <v>47289</v>
+      </c>
+      <c r="C37" s="10" t="n">
         <v>47380</v>
       </c>
-      <c r="C37" s="10" t="n">
-        <v>47471</v>
-      </c>
       <c r="D37" s="23" t="n">
-        <v>95.515</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="E37" s="15">
         <f>(100-D37)/100</f>
         <v/>
       </c>
       <c r="F37" s="24" t="n">
-        <v>3.38</v>
+        <v>2.86</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.0448499</v>
+        <v>0.0451041</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>-0.001</v>
+        <v>0.041</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>306915</v>
+        <v>391038</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 29</t>
+          <t>SR3 SEP 29</t>
         </is>
       </c>
       <c r="B38" s="10" t="n">
+        <v>47380</v>
+      </c>
+      <c r="C38" s="10" t="n">
         <v>47471</v>
       </c>
-      <c r="C38" s="10" t="n">
-        <v>47562</v>
-      </c>
       <c r="D38" s="23" t="n">
-        <v>95.52</v>
+        <v>95.5</v>
       </c>
       <c r="E38" s="15">
         <f>(100-D38)/100</f>
         <v/>
       </c>
       <c r="F38" s="24" t="n">
-        <v>3.93</v>
+        <v>3.38</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.0448001</v>
+        <v>0.0449946</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>0.001</v>
+        <v>-0.054</v>
       </c>
       <c r="I38" s="25" t="n">
-        <v>246472</v>
+        <v>309038</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 30</t>
+          <t>SR3 DEC 29</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
+        <v>47471</v>
+      </c>
+      <c r="C39" s="10" t="n">
         <v>47562</v>
       </c>
-      <c r="C39" s="10" t="n">
-        <v>47653</v>
-      </c>
       <c r="D39" s="23" t="n">
-        <v>95.52</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="E39" s="15">
         <f>(100-D39)/100</f>
         <v/>
       </c>
       <c r="F39" s="24" t="n">
-        <v>4.52</v>
+        <v>3.93</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.0449057</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>-0</v>
+        <v>0.057</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>179275</v>
+        <v>250351</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 30</t>
+          <t>SR3 MAR 30</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
+        <v>47562</v>
+      </c>
+      <c r="C40" s="10" t="n">
         <v>47653</v>
       </c>
-      <c r="C40" s="10" t="n">
-        <v>47744</v>
-      </c>
       <c r="D40" s="23" t="n">
-        <v>95.515</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="E40" s="15">
         <f>(100-D40)/100</f>
         <v/>
       </c>
       <c r="F40" s="24" t="n">
-        <v>5.15</v>
+        <v>4.52</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.04485</v>
+        <v>0.0448943</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>-0</v>
+        <v>-0.057</v>
       </c>
       <c r="I40" s="25" t="n">
-        <v>155229</v>
+        <v>181620</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 30</t>
+          <t>SR3 JUN 30</t>
         </is>
       </c>
       <c r="B41" s="10" t="n">
+        <v>47653</v>
+      </c>
+      <c r="C41" s="10" t="n">
         <v>47744</v>
       </c>
-      <c r="C41" s="10" t="n">
-        <v>47835</v>
-      </c>
       <c r="D41" s="23" t="n">
-        <v>95.505</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="E41" s="15">
         <f>(100-D41)/100</f>
         <v/>
       </c>
       <c r="F41" s="24" t="n">
-        <v>5.81</v>
+        <v>5.14</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.0449502</v>
+        <v>0.0449056</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>0.002</v>
+        <v>0.056</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>149374</v>
+        <v>157168</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 30</t>
+          <t>SR3 SEP 30</t>
         </is>
       </c>
       <c r="B42" s="10" t="n">
+        <v>47744</v>
+      </c>
+      <c r="C42" s="10" t="n">
         <v>47835</v>
       </c>
-      <c r="C42" s="10" t="n">
-        <v>47926</v>
-      </c>
       <c r="D42" s="23" t="n">
-        <v>95.48999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="E42" s="15">
         <f>(100-D42)/100</f>
         <v/>
       </c>
       <c r="F42" s="24" t="n">
-        <v>6.51</v>
+        <v>5.8</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.0450998</v>
+        <v>0.0449948</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>-0.002</v>
+        <v>-0.052</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>117178</v>
+        <v>149147</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 31</t>
+          <t>SR3 DEC 30</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
+        <v>47835</v>
+      </c>
+      <c r="C43" s="10" t="n">
         <v>47926</v>
       </c>
-      <c r="C43" s="10" t="n">
-        <v>48017</v>
-      </c>
       <c r="D43" s="23" t="n">
-        <v>95.47</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="E43" s="15">
         <f>(100-D43)/100</f>
         <v/>
       </c>
       <c r="F43" s="24" t="n">
-        <v>7.23</v>
+        <v>6.5</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.0452999</v>
+        <v>0.0451038</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>-0.001</v>
+        <v>0.038</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>86402</v>
+        <v>117631</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 31</t>
+          <t>SR3 MAR 31</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
+        <v>47926</v>
+      </c>
+      <c r="C44" s="10" t="n">
         <v>48017</v>
       </c>
-      <c r="C44" s="10" t="n">
-        <v>48108</v>
-      </c>
       <c r="D44" s="23" t="n">
-        <v>95.44499999999999</v>
+        <v>95.47</v>
       </c>
       <c r="E44" s="15">
         <f>(100-D44)/100</f>
         <v/>
       </c>
       <c r="F44" s="24" t="n">
-        <v>8</v>
+        <v>7.23</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.0455509</v>
+        <v>0.0452981</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.019</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>72371</v>
+        <v>86768</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 31</t>
+          <t>SR3 JUN 31</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
+        <v>48017</v>
+      </c>
+      <c r="C45" s="10" t="n">
         <v>48108</v>
       </c>
-      <c r="C45" s="10" t="n">
-        <v>48199</v>
-      </c>
       <c r="D45" s="23" t="n">
-        <v>95.41500000000001</v>
+        <v>95.44499999999999</v>
       </c>
       <c r="E45" s="15">
         <f>(100-D45)/100</f>
         <v/>
       </c>
       <c r="F45" s="24" t="n">
-        <v>8.789999999999999</v>
+        <v>7.99</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.045849</v>
+        <v>0.0455515</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>-0.01</v>
+        <v>0.015</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>38653</v>
+        <v>73328</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 31</t>
+          <t>SR3 SEP 31</t>
         </is>
       </c>
       <c r="B46" s="10" t="n">
+        <v>48108</v>
+      </c>
+      <c r="C46" s="10" t="n">
         <v>48199</v>
       </c>
-      <c r="C46" s="10" t="n">
-        <v>48290</v>
-      </c>
       <c r="D46" s="23" t="n">
-        <v>95.38500000000001</v>
+        <v>95.41500000000001</v>
       </c>
       <c r="E46" s="15">
         <f>(100-D46)/100</f>
         <v/>
       </c>
       <c r="F46" s="24" t="n">
-        <v>9.619999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.0461503</v>
+        <v>0.0458489</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>0.003</v>
+        <v>-0.011</v>
       </c>
       <c r="I46" s="25" t="n">
-        <v>7521</v>
+        <v>38487</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 32</t>
+          <t>SR3 DEC 31</t>
         </is>
       </c>
       <c r="B47" s="10" t="n">
+        <v>48199</v>
+      </c>
+      <c r="C47" s="10" t="n">
         <v>48290</v>
       </c>
-      <c r="C47" s="10" t="n">
-        <v>48381</v>
-      </c>
       <c r="D47" s="23" t="n">
-        <v>95.355</v>
+        <v>95.38500000000001</v>
       </c>
       <c r="E47" s="15">
         <f>(100-D47)/100</f>
         <v/>
       </c>
       <c r="F47" s="24" t="n">
-        <v>10.47</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.0464495</v>
+        <v>0.0461503</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>-0.005</v>
+        <v>0.003</v>
       </c>
       <c r="I47" s="25" t="n">
-        <v>2784</v>
+        <v>7911</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 32</t>
+          <t>SR3 MAR 32</t>
         </is>
       </c>
       <c r="B48" s="10" t="n">
+        <v>48290</v>
+      </c>
+      <c r="C48" s="10" t="n">
         <v>48381</v>
       </c>
-      <c r="C48" s="10" t="n">
-        <v>48472</v>
-      </c>
       <c r="D48" s="23" t="n">
-        <v>95.325</v>
+        <v>95.355</v>
       </c>
       <c r="E48" s="15">
         <f>(100-D48)/100</f>
         <v/>
       </c>
       <c r="F48" s="24" t="n">
-        <v>11.36</v>
+        <v>10.46</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.0467518</v>
+        <v>0.04645</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="I48" s="25" t="n">
-        <v>722</v>
+        <v>4065</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 32</t>
+          <t>SR3 JUN 32</t>
         </is>
       </c>
       <c r="B49" s="10" t="n">
+        <v>48381</v>
+      </c>
+      <c r="C49" s="10" t="n">
         <v>48472</v>
       </c>
-      <c r="C49" s="10" t="n">
-        <v>48563</v>
-      </c>
       <c r="D49" s="23" t="n">
-        <v>95.295</v>
+        <v>95.325</v>
       </c>
       <c r="E49" s="15">
         <f>(100-D49)/100</f>
         <v/>
       </c>
       <c r="F49" s="24" t="n">
-        <v>12.27</v>
+        <v>11.35</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.047046</v>
+        <v>0.04675</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="I49" s="25" t="n">
-        <v>434</v>
+        <v>790</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 32</t>
+          <t>SR3 SEP 32</t>
         </is>
       </c>
       <c r="B50" s="10" t="n">
+        <v>48472</v>
+      </c>
+      <c r="C50" s="10" t="n">
         <v>48563</v>
       </c>
-      <c r="C50" s="10" t="n">
-        <v>48654</v>
-      </c>
       <c r="D50" s="23" t="n">
-        <v>95.27</v>
+        <v>95.295</v>
       </c>
       <c r="E50" s="15">
         <f>(100-D50)/100</f>
         <v/>
       </c>
       <c r="F50" s="24" t="n">
-        <v>13.21</v>
+        <v>12.26</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.0473055</v>
+        <v>0.0470496</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>0.055</v>
+        <v>-0.004</v>
       </c>
       <c r="I50" s="25" t="n">
-        <v>164</v>
+        <v>441</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 33</t>
+          <t>SR3 DEC 32</t>
         </is>
       </c>
       <c r="B51" s="10" t="n">
+        <v>48563</v>
+      </c>
+      <c r="C51" s="10" t="n">
         <v>48654</v>
       </c>
-      <c r="C51" s="10" t="n">
-        <v>48745</v>
-      </c>
       <c r="D51" s="23" t="n">
-        <v>95.23999999999999</v>
+        <v>95.265</v>
       </c>
       <c r="E51" s="15">
         <f>(100-D51)/100</f>
         <v/>
       </c>
       <c r="F51" s="24" t="n">
-        <v>14.18</v>
+        <v>13.2</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.0475949</v>
+        <v>0.047352</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>-0.051</v>
+        <v>0.02</v>
       </c>
       <c r="I51" s="25" t="n">
-        <v>35</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 33</t>
+          <t>SR3 MAR 33</t>
         </is>
       </c>
       <c r="B52" s="10" t="n">
+        <v>48654</v>
+      </c>
+      <c r="C52" s="10" t="n">
         <v>48745</v>
       </c>
-      <c r="C52" s="10" t="n">
-        <v>48843</v>
-      </c>
       <c r="D52" s="23" t="n">
-        <v>95.215</v>
+        <v>95.235</v>
       </c>
       <c r="E52" s="15">
         <f>(100-D52)/100</f>
         <v/>
       </c>
       <c r="F52" s="24" t="n">
-        <v>15.22</v>
+        <v>14.17</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.0478516</v>
+        <v>0.0476467</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>0.016</v>
+        <v>-0.033</v>
       </c>
       <c r="I52" s="25" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 33</t>
+          <t>SR3 JUN 33</t>
         </is>
       </c>
       <c r="B53" s="10" t="n">
+        <v>48745</v>
+      </c>
+      <c r="C53" s="10" t="n">
         <v>48843</v>
       </c>
-      <c r="C53" s="10" t="n">
-        <v>48934</v>
-      </c>
       <c r="D53" s="23" t="n">
-        <v>95.19</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="E53" s="15">
         <f>(100-D53)/100</f>
         <v/>
       </c>
       <c r="F53" s="24" t="n">
-        <v>16.28</v>
+        <v>15.2</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.0481063</v>
+        <v>0.0479011</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>0.063</v>
+        <v>0.011</v>
       </c>
       <c r="I53" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 33</t>
+          <t>SR3 SEP 33</t>
         </is>
       </c>
       <c r="B54" s="10" t="n">
+        <v>48843</v>
+      </c>
+      <c r="C54" s="10" t="n">
         <v>48934</v>
       </c>
-      <c r="C54" s="10" t="n">
-        <v>49018</v>
-      </c>
       <c r="D54" s="23" t="n">
-        <v>95.16500000000001</v>
+        <v>95.185</v>
       </c>
       <c r="E54" s="15">
         <f>(100-D54)/100</f>
         <v/>
       </c>
       <c r="F54" s="24" t="n">
-        <v>17.29</v>
+        <v>16.27</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.048334</v>
+        <v>0.0481565</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>-0.16</v>
+        <v>0.065</v>
       </c>
       <c r="I54" s="25" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 34</t>
+          <t>SR3 DEC 33</t>
         </is>
       </c>
       <c r="B55" s="10" t="n">
+        <v>48934</v>
+      </c>
+      <c r="C55" s="10" t="n">
         <v>49018</v>
       </c>
-      <c r="C55" s="10" t="n">
-        <v>49116</v>
-      </c>
       <c r="D55" s="23" t="n">
-        <v>95.15000000000001</v>
+        <v>95.16</v>
       </c>
       <c r="E55" s="15">
         <f>(100-D55)/100</f>
         <v/>
       </c>
       <c r="F55" s="24" t="n">
-        <v>18.36</v>
+        <v>17.28</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.0485227</v>
+        <v>0.048384</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>0.227</v>
+        <v>-0.16</v>
       </c>
       <c r="I55" s="25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 34</t>
+          <t>SR3 MAR 34</t>
         </is>
       </c>
       <c r="B56" s="10" t="n">
+        <v>49018</v>
+      </c>
+      <c r="C56" s="10" t="n">
         <v>49116</v>
       </c>
-      <c r="C56" s="10" t="n">
-        <v>49207</v>
-      </c>
       <c r="D56" s="23" t="n">
-        <v>95.12</v>
+        <v>95.145</v>
       </c>
       <c r="E56" s="15">
         <f>(100-D56)/100</f>
         <v/>
       </c>
       <c r="F56" s="24" t="n">
-        <v>19.5</v>
+        <v>18.35</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.0487716</v>
+        <v>0.0485727</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>-0.284</v>
+        <v>0.227</v>
       </c>
       <c r="I56" s="25" t="n">
         <v>0</v>
@@ -7250,30 +7250,30 @@
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 34</t>
+          <t>SR3 JUN 34</t>
         </is>
       </c>
       <c r="B57" s="10" t="n">
+        <v>49116</v>
+      </c>
+      <c r="C57" s="10" t="n">
         <v>49207</v>
       </c>
-      <c r="C57" s="10" t="n">
-        <v>49298</v>
-      </c>
       <c r="D57" s="23" t="n">
-        <v>95.11</v>
+        <v>95.11499999999999</v>
       </c>
       <c r="E57" s="15">
         <f>(100-D57)/100</f>
         <v/>
       </c>
       <c r="F57" s="24" t="n">
-        <v>20.62</v>
+        <v>19.49</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.0489337</v>
+        <v>0.0488216</v>
       </c>
       <c r="H57" s="24" t="n">
-        <v>0.337</v>
+        <v>-0.284</v>
       </c>
       <c r="I57" s="25" t="n">
         <v>0</v>
@@ -7282,30 +7282,30 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 34</t>
+          <t>SR3 SEP 34</t>
         </is>
       </c>
       <c r="B58" s="10" t="n">
+        <v>49207</v>
+      </c>
+      <c r="C58" s="10" t="n">
         <v>49298</v>
       </c>
-      <c r="C58" s="10" t="n">
-        <v>49389</v>
-      </c>
       <c r="D58" s="23" t="n">
-        <v>95.065</v>
+        <v>95.105</v>
       </c>
       <c r="E58" s="15">
         <f>(100-D58)/100</f>
         <v/>
       </c>
       <c r="F58" s="24" t="n">
-        <v>21.77</v>
+        <v>20.61</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.0493186</v>
+        <v>0.0489837</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>-0.314</v>
+        <v>0.337</v>
       </c>
       <c r="I58" s="25" t="n">
         <v>0</v>
@@ -7314,30 +7314,30 @@
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 35</t>
+          <t>SR3 DEC 34</t>
         </is>
       </c>
       <c r="B59" s="10" t="n">
+        <v>49298</v>
+      </c>
+      <c r="C59" s="10" t="n">
         <v>49389</v>
       </c>
-      <c r="C59" s="10" t="n">
-        <v>49480</v>
-      </c>
       <c r="D59" s="23" t="n">
-        <v>95.05500000000001</v>
+        <v>95.06</v>
       </c>
       <c r="E59" s="15">
         <f>(100-D59)/100</f>
         <v/>
       </c>
       <c r="F59" s="24" t="n">
-        <v>22.93</v>
+        <v>21.75</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.0494718</v>
+        <v>0.04936860000000001</v>
       </c>
       <c r="H59" s="24" t="n">
-        <v>0.218</v>
+        <v>-0.314</v>
       </c>
       <c r="I59" s="25" t="n">
         <v>0</v>
@@ -7346,30 +7346,30 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>SR3 JUN 35</t>
+          <t>SR3 MAR 35</t>
         </is>
       </c>
       <c r="B60" s="10" t="n">
+        <v>49389</v>
+      </c>
+      <c r="C60" s="10" t="n">
         <v>49480</v>
       </c>
-      <c r="C60" s="10" t="n">
-        <v>49571</v>
-      </c>
       <c r="D60" s="23" t="n">
-        <v>95.03</v>
+        <v>95.05</v>
       </c>
       <c r="E60" s="15">
         <f>(100-D60)/100</f>
         <v/>
       </c>
       <c r="F60" s="24" t="n">
-        <v>24.12</v>
+        <v>22.92</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.0496842</v>
+        <v>0.0495218</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>-0.158</v>
+        <v>0.218</v>
       </c>
       <c r="I60" s="25" t="n">
         <v>0</v>
@@ -7378,30 +7378,30 @@
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
         <is>
-          <t>SR3 SEP 35</t>
+          <t>SR3 JUN 35</t>
         </is>
       </c>
       <c r="B61" s="10" t="n">
+        <v>49480</v>
+      </c>
+      <c r="C61" s="10" t="n">
         <v>49571</v>
       </c>
-      <c r="C61" s="10" t="n">
-        <v>49662</v>
-      </c>
       <c r="D61" s="23" t="n">
-        <v>95.005</v>
+        <v>95.02500000000001</v>
       </c>
       <c r="E61" s="15">
         <f>(100-D61)/100</f>
         <v/>
       </c>
       <c r="F61" s="24" t="n">
-        <v>25.33</v>
+        <v>24.11</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.0499687</v>
+        <v>0.0497342</v>
       </c>
       <c r="H61" s="24" t="n">
-        <v>0.187</v>
+        <v>-0.158</v>
       </c>
       <c r="I61" s="25" t="n">
         <v>0</v>
@@ -7410,30 +7410,30 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>SR3 DEC 35</t>
+          <t>SR3 SEP 35</t>
         </is>
       </c>
       <c r="B62" s="10" t="n">
+        <v>49571</v>
+      </c>
+      <c r="C62" s="10" t="n">
         <v>49662</v>
       </c>
-      <c r="C62" s="10" t="n">
-        <v>49753</v>
-      </c>
       <c r="D62" s="23" t="n">
-        <v>94.95999999999999</v>
+        <v>95</v>
       </c>
       <c r="E62" s="15">
         <f>(100-D62)/100</f>
         <v/>
       </c>
       <c r="F62" s="24" t="n">
-        <v>26.56</v>
+        <v>25.31</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.0503833</v>
+        <v>0.0500187</v>
       </c>
       <c r="H62" s="24" t="n">
-        <v>-0.167</v>
+        <v>0.187</v>
       </c>
       <c r="I62" s="25" t="n">
         <v>0</v>
@@ -7442,39 +7442,71 @@
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
         <is>
-          <t>SR3 MAR 36</t>
+          <t>SR3 DEC 35</t>
         </is>
       </c>
       <c r="B63" s="10" t="n">
+        <v>49662</v>
+      </c>
+      <c r="C63" s="10" t="n">
         <v>49753</v>
       </c>
-      <c r="C63" s="10" t="n">
-        <v>49844</v>
-      </c>
       <c r="D63" s="23" t="n">
-        <v>94.95</v>
+        <v>94.955</v>
       </c>
       <c r="E63" s="15">
         <f>(100-D63)/100</f>
         <v/>
       </c>
       <c r="F63" s="24" t="n">
-        <v>27.8</v>
+        <v>26.54</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.0505058</v>
+        <v>0.0504333</v>
       </c>
       <c r="H63" s="24" t="n">
-        <v>0.058</v>
+        <v>-0.167</v>
       </c>
       <c r="I63" s="25" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>Fit: 60 contracts, RMS residual 0.193 bp, max 0.697 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>SR3 MAR 36</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n">
+        <v>49753</v>
+      </c>
+      <c r="C64" s="10" t="n">
+        <v>49844</v>
+      </c>
+      <c r="D64" s="23" t="n">
+        <v>94.94499999999999</v>
+      </c>
+      <c r="E64" s="15">
+        <f>(100-D64)/100</f>
+        <v/>
+      </c>
+      <c r="F64" s="24" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0.0505558</v>
+      </c>
+      <c r="H64" s="24" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I64" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Fit: 61 contracts, RMS residual 0.228 bp, max 0.781 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7517,39 +7549,39 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B4" s="26" t="n">
-        <v>0.0393</v>
+        <v>0.0395</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>0.0392</v>
+        <v>0.0393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B8" s="26" t="n">
         <v>0.0388</v>
@@ -7557,55 +7589,55 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B9" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B10" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B11" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B12" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B13" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B14" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B15" s="26" t="n">
         <v>0.0387</v>
@@ -7613,71 +7645,71 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B16" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B17" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B18" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B19" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B20" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B21" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B22" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B23" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B24" s="26" t="n">
         <v>0.039</v>
@@ -7685,23 +7717,23 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B25" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B26" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B27" s="26" t="n">
         <v>0.0387</v>
@@ -7709,15 +7741,15 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B28" s="26" t="n">
-        <v>0.0385</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B29" s="26" t="n">
         <v>0.0385</v>
@@ -7725,7 +7757,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B30" s="26" t="n">
         <v>0.0385</v>
@@ -7733,31 +7765,31 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B31" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B32" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B33" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B34" s="26" t="n">
         <v>0.0362</v>
@@ -7765,7 +7797,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B35" s="26" t="n">
         <v>0.0362</v>
@@ -7773,15 +7805,15 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B36" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B37" s="26" t="n">
         <v>0.0364</v>
@@ -7789,63 +7821,63 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B38" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B39" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B40" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B41" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B42" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B43" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B44" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B45" s="26" t="n">
         <v>0.0364</v>
@@ -7853,23 +7885,23 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B48" s="26" t="n">
         <v>0.0365</v>
@@ -7877,47 +7909,47 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B49" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B50" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B51" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B52" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B53" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B54" s="26" t="n">
         <v>0.0362</v>
@@ -7925,7 +7957,7 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B55" s="26" t="n">
         <v>0.0362</v>
@@ -7933,79 +7965,79 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B56" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B57" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B58" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B59" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B60" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B61" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B62" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B63" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B64" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B65" s="26" t="n">
         <v>0.0365</v>
@@ -8013,7 +8045,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B66" s="26" t="n">
         <v>0.0365</v>
@@ -8021,15 +8053,15 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B67" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B68" s="26" t="n">
         <v>0.0364</v>
@@ -8037,7 +8069,7 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B69" s="26" t="n">
         <v>0.0364</v>
@@ -8045,143 +8077,143 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B70" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B71" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B72" s="26" t="n">
-        <v>0.0357</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B73" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.0357</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B74" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B75" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B76" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B77" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B78" s="26" t="n">
-        <v>0.0355</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B79" s="26" t="n">
-        <v>0.0353</v>
+        <v>0.0355</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B80" s="26" t="n">
-        <v>0.0358</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B81" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B82" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B83" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B84" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B85" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B86" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B87" s="26" t="n">
         <v>0.0362</v>
@@ -8189,23 +8221,23 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B88" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B89" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B90" s="26" t="n">
         <v>0.0362</v>
@@ -8213,31 +8245,31 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B91" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B92" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B93" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B94" s="26" t="n">
         <v>0.0363</v>
@@ -8245,55 +8277,55 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B95" s="26" t="n">
-        <v>0.0369</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B96" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B97" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B98" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B99" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B100" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B101" s="26" t="n">
         <v>0.0363</v>
@@ -8301,33 +8333,41 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B102" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B103" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B104" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B105" s="26" t="n">
+        <v>0.0363</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n">
         <v>46174</v>
       </c>
-      <c r="B105" s="26" t="n">
+      <c r="B106" s="26" t="n">
         <v>0.0365</v>
       </c>
     </row>

--- a/output/downloads/sofr-forward-curve.xlsx
+++ b/output/downloads/sofr-forward-curve.xlsx
@@ -236,7 +236,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SOFR forward curve, 2026-10-27</a:t>
+              <a:t>SOFR forward curve, 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="3">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.0395</v>
+        <v>0.0394</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>on 2026-10-27 (NY Fed)</t>
+          <t>on 2026-10-28 (NY Fed)</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28 18:52 UTC</t>
+          <t>2026-10-29 18:57 UTC</t>
         </is>
       </c>
     </row>
@@ -855,13 +855,13 @@
         <v>31</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.0389578</v>
+        <v>0.0389817</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>0.0388969</v>
+        <v>0.0389207</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>0.0389577</v>
+        <v>0.0389817</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0</v>
@@ -891,13 +891,13 @@
         <v>30</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.0392515</v>
+        <v>0.0391067</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.0391915</v>
+        <v>0.0390472</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>0.0392513</v>
+        <v>0.0391065</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.0407753</v>
+        <v>0.04067630000000001</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>0.0407084</v>
+        <v>0.0406097</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0.0407759</v>
+        <v>0.0406769</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>0.01</v>
@@ -963,13 +963,13 @@
         <v>31</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.0415104</v>
+        <v>0.0414265</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.0414416</v>
+        <v>0.0413579</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>0.0415118</v>
+        <v>0.0414278</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>0.01</v>
@@ -999,13 +999,13 @@
         <v>28</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.042266</v>
+        <v>0.0421572</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.0422018</v>
+        <v>0.04209329999999999</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0.0422694</v>
+        <v>0.0421605</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>0.03</v>
@@ -1035,13 +1035,13 @@
         <v>31</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.0430513</v>
+        <v>0.0428979</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.0429768</v>
+        <v>0.04282390000000001</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0.0430568</v>
+        <v>0.0429033</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>0.05</v>
@@ -1071,13 +1071,13 @@
         <v>30</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.0440598</v>
+        <v>0.04384420000000001</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>0.0439839</v>
+        <v>0.0437691</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>0.0440679</v>
+        <v>0.0438523</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>0.08</v>
@@ -1107,13 +1107,13 @@
         <v>31</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.0449906</v>
+        <v>0.0446604</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.0449094</v>
+        <v>0.0445803</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.04500200000000001</v>
+        <v>0.0446716</v>
       </c>
       <c r="G19" s="13" t="n">
         <v>0.11</v>
@@ -1143,16 +1143,16 @@
         <v>30</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.04571310000000001</v>
+        <v>0.0454242</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>0.045632</v>
+        <v>0.0453442</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0.0457297</v>
+        <v>0.04544069999999999</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
@@ -1179,16 +1179,16 @@
         <v>31</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.0460596</v>
+        <v>0.045792</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.0459744</v>
+        <v>0.0457078</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.0460791</v>
+        <v>0.0458113</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
@@ -1215,13 +1215,13 @@
         <v>31</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.0463663</v>
+        <v>0.04613229999999999</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.04627919999999999</v>
+        <v>0.0460462</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0.046392</v>
+        <v>0.04615789999999999</v>
       </c>
       <c r="G22" s="13" t="n">
         <v>0.26</v>
@@ -1251,13 +1251,13 @@
         <v>30</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.0465441</v>
+        <v>0.04636999999999999</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.04646</v>
+        <v>0.0462866</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.0465748</v>
+        <v>0.0464005</v>
       </c>
       <c r="G23" s="13" t="n">
         <v>0.31</v>
@@ -1287,13 +1287,13 @@
         <v>31</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.0467213</v>
+        <v>0.0466116</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>0.0466341</v>
+        <v>0.0465248</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0.04675799999999999</v>
+        <v>0.0466481</v>
       </c>
       <c r="G24" s="13" t="n">
         <v>0.37</v>
@@ -1323,13 +1323,13 @@
         <v>30</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.0466737</v>
+        <v>0.0465944</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.0465889</v>
+        <v>0.04651</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0.0467166</v>
+        <v>0.0466371</v>
       </c>
       <c r="G25" s="13" t="n">
         <v>0.43</v>
@@ -1359,13 +1359,13 @@
         <v>31</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.0465657</v>
+        <v>0.0464514</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.0464785</v>
+        <v>0.0463646</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0.0466179</v>
+        <v>0.0465033</v>
       </c>
       <c r="G26" s="13" t="n">
         <v>0.52</v>
@@ -1395,13 +1395,13 @@
         <v>31</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.0464957</v>
+        <v>0.0464321</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>0.0464089</v>
+        <v>0.04634559999999999</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0.0465525</v>
+        <v>0.04648869999999999</v>
       </c>
       <c r="G27" s="13" t="n">
         <v>0.57</v>
@@ -1431,16 +1431,16 @@
         <v>29</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.046327</v>
+        <v>0.0465908</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>0.0462468</v>
+        <v>0.0465097</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>0.0463918</v>
+        <v>0.0466553</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
@@ -1467,13 +1467,13 @@
         <v>31</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.04619239999999999</v>
+        <v>0.0464179</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>0.046106</v>
+        <v>0.0463307</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.0462639</v>
+        <v>0.0464891</v>
       </c>
       <c r="G29" s="13" t="n">
         <v>0.71</v>
@@ -1503,13 +1503,13 @@
         <v>30</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>0.04607770000000001</v>
+        <v>0.0463127</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>0.0459956</v>
+        <v>0.0462296</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0.0461591</v>
+        <v>0.0463937</v>
       </c>
       <c r="G30" s="13" t="n">
         <v>0.8100000000000001</v>
@@ -1539,13 +1539,13 @@
         <v>31</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>0.0459587</v>
+        <v>0.0462226</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0.04587379999999999</v>
+        <v>0.0461367</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.0460512</v>
+        <v>0.0463148</v>
       </c>
       <c r="G31" s="13" t="n">
         <v>0.92</v>
@@ -1575,16 +1575,16 @@
         <v>30</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.0458494</v>
+        <v>0.0461622</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>0.0457678</v>
+        <v>0.04607960000000001</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0.045952</v>
+        <v>0.0462645</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
@@ -1611,13 +1611,13 @@
         <v>31</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.0457632</v>
+        <v>0.0461282</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>0.0456788</v>
+        <v>0.0460424</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0.0458755</v>
+        <v>0.0462401</v>
       </c>
       <c r="G33" s="13" t="n">
         <v>1.12</v>
@@ -1647,16 +1647,16 @@
         <v>31</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.04567350000000001</v>
+        <v>0.0460849</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>0.0455891</v>
+        <v>0.045999</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0.04579710000000001</v>
+        <v>0.0462082</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
@@ -1683,16 +1683,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.0455941</v>
+        <v>0.0460286</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>0.0455137</v>
+        <v>0.0459466</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0.045729</v>
+        <v>0.04616310000000001</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
@@ -1719,13 +1719,13 @@
         <v>31</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>0.0455246</v>
+        <v>0.0459688</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>0.0454413</v>
+        <v>0.0458838</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0.04567109999999999</v>
+        <v>0.0461148</v>
       </c>
       <c r="G36" s="13" t="n">
         <v>1.46</v>
@@ -1755,13 +1755,13 @@
         <v>30</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.04543700000000001</v>
+        <v>0.0458903</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>0.0453565</v>
+        <v>0.0458083</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0.0455962</v>
+        <v>0.0460492</v>
       </c>
       <c r="G37" s="13" t="n">
         <v>1.59</v>
@@ -1791,13 +1791,13 @@
         <v>31</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>0.0453463</v>
+        <v>0.0458133</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>0.0452641</v>
+        <v>0.0457295</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0.0455184</v>
+        <v>0.0459851</v>
       </c>
       <c r="G38" s="13" t="n">
         <v>1.72</v>
@@ -1827,13 +1827,13 @@
         <v>31</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0.0452504</v>
+        <v>0.0457345</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0.0451681</v>
+        <v>0.0456504</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0.0454354</v>
+        <v>0.0459191</v>
       </c>
       <c r="G39" s="13" t="n">
         <v>1.85</v>
@@ -1863,16 +1863,16 @@
         <v>28</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>0.04513760000000001</v>
+        <v>0.0456398</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>0.0450644</v>
+        <v>0.0455649</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0.04533649999999999</v>
+        <v>0.0458382</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>31</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.0450471</v>
+        <v>0.04556619999999999</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.0449655</v>
+        <v>0.04548269999999999</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0.04525999999999999</v>
+        <v>0.0457786</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
@@ -1935,16 +1935,16 @@
         <v>30</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>0.0449508</v>
+        <v>0.0454861</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>0.0448718</v>
+        <v>0.0454052</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0.04517769999999999</v>
+        <v>0.0457125</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
@@ -1971,13 +1971,13 @@
         <v>31</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.04485459999999999</v>
+        <v>0.0454092</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.0447737</v>
+        <v>0.0453263</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.0450971</v>
+        <v>0.0456512</v>
       </c>
       <c r="G43" s="13" t="n">
         <v>2.42</v>
@@ -2007,13 +2007,13 @@
         <v>30</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.0447613</v>
+        <v>0.0453355</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>0.04468340000000001</v>
+        <v>0.04525559999999999</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0.0450195</v>
+        <v>0.04559319999999999</v>
       </c>
       <c r="G44" s="13" t="n">
         <v>2.58</v>
@@ -2043,16 +2043,16 @@
         <v>31</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.0446868</v>
+        <v>0.0452771</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.0446062</v>
+        <v>0.0451943</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0.0449608</v>
+        <v>0.0455506</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
@@ -2079,13 +2079,13 @@
         <v>31</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.04462</v>
+        <v>0.04522</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>0.0445394</v>
+        <v>0.0451372</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0.0449111</v>
+        <v>0.0455105</v>
       </c>
       <c r="G46" s="13" t="n">
         <v>2.91</v>
@@ -2115,13 +2115,13 @@
         <v>30</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.0445711</v>
+        <v>0.0451722</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.044494</v>
+        <v>0.04509299999999999</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.04487720000000001</v>
+        <v>0.04547780000000001</v>
       </c>
       <c r="G47" s="13" t="n">
         <v>3.06</v>
@@ -2151,16 +2151,16 @@
         <v>31</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.0445226</v>
+        <v>0.0451214</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>0.04444289999999999</v>
+        <v>0.0450395</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0.0448477</v>
+        <v>0.0454458</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
@@ -2187,16 +2187,16 @@
         <v>30</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.0444685</v>
+        <v>0.0450652</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>0.04439199999999999</v>
+        <v>0.0449866</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0.0448111</v>
+        <v>0.0454071</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
@@ -2223,13 +2223,13 @@
         <v>31</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.0444194</v>
+        <v>0.0450159</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>0.0443398</v>
+        <v>0.04493420000000001</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0.0447788</v>
+        <v>0.0453747</v>
       </c>
       <c r="G50" s="13" t="n">
         <v>3.59</v>
@@ -2259,13 +2259,13 @@
         <v>31</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.0443661</v>
+        <v>0.0449621</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>0.0442869</v>
+        <v>0.0448808</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>0.0447445</v>
+        <v>0.0453399</v>
       </c>
       <c r="G51" s="13" t="n">
         <v>3.78</v>
@@ -2295,16 +2295,16 @@
         <v>28</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.0443195</v>
+        <v>0.0449125</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>0.04424890000000001</v>
+        <v>0.04484</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0.0447171</v>
+        <v>0.0453095</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
@@ -2331,16 +2331,16 @@
         <v>31</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.04430659999999999</v>
+        <v>0.0448965</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.04422760000000001</v>
+        <v>0.0448154</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.0447235</v>
+        <v>0.0453128</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
@@ -2367,16 +2367,16 @@
         <v>30</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>0.0442889</v>
+        <v>0.0448799</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>0.0442128</v>
+        <v>0.0448018</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>0.04472540000000001</v>
+        <v>0.0453158</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>4.37</v>
+        <v>4.36</v>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
@@ -2403,16 +2403,16 @@
         <v>31</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>0.0442726</v>
+        <v>0.0448744</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.0441937</v>
+        <v>0.0447934</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.0447292</v>
+        <v>0.0453304</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>4.57</v>
+        <v>4.56</v>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
@@ -2439,16 +2439,16 @@
         <v>30</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>0.0442469</v>
+        <v>0.0448662</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>0.0441708</v>
+        <v>0.0447879</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>0.04472279999999999</v>
+        <v>0.0453414</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>4.76</v>
+        <v>4.75</v>
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
@@ -2475,13 +2475,13 @@
         <v>31</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>0.0442274</v>
+        <v>0.0448664</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.0441484</v>
+        <v>0.0447851</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.0447258</v>
+        <v>0.045364</v>
       </c>
       <c r="G57" s="13" t="n">
         <v>4.98</v>
@@ -2511,16 +2511,16 @@
         <v>31</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>0.0442212</v>
+        <v>0.0448694</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>0.0441422</v>
+        <v>0.04478799999999999</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0.0447408</v>
+        <v>0.0453883</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
@@ -2547,16 +2547,16 @@
         <v>30</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>0.0442272</v>
+        <v>0.0448745</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.0441509</v>
+        <v>0.044796</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.0447669</v>
+        <v>0.0454135</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>5.4</v>
+        <v>5.39</v>
       </c>
       <c r="H59" s="14" t="inlineStr">
         <is>
@@ -2583,13 +2583,13 @@
         <v>31</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.044246</v>
+        <v>0.0448905</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>0.0441673</v>
+        <v>0.04480940000000001</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0.0448095</v>
+        <v>0.0454531</v>
       </c>
       <c r="G60" s="13" t="n">
         <v>5.63</v>
@@ -2619,16 +2619,16 @@
         <v>30</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>0.044255</v>
+        <v>0.0449033</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>0.0441793</v>
+        <v>0.0448254</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0.0448411</v>
+        <v>0.0454887</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
@@ -2655,16 +2655,16 @@
         <v>31</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>0.0442654</v>
+        <v>0.0449275</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>0.0441863</v>
+        <v>0.0448459</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0.0448743</v>
+        <v>0.04553550000000001</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
@@ -2691,13 +2691,13 @@
         <v>31</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>0.0442749</v>
+        <v>0.0449579</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>0.044196</v>
+        <v>0.0448766</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0.0449074</v>
+        <v>0.0455896</v>
       </c>
       <c r="G63" s="13" t="n">
         <v>6.32</v>
@@ -2727,16 +2727,16 @@
         <v>28</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>0.0442874</v>
+        <v>0.0449923</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>0.0442165</v>
+        <v>0.0449191</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>0.0449422</v>
+        <v>0.0456462</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>6.55</v>
+        <v>6.54</v>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
@@ -2763,16 +2763,16 @@
         <v>31</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>0.04433119999999999</v>
+        <v>0.0450571</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>0.0442518</v>
+        <v>0.0449751</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0.0450097</v>
+        <v>0.0457348</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>6.79</v>
+        <v>6.78</v>
       </c>
       <c r="H65" s="14" t="inlineStr">
         <is>
@@ -2799,16 +2799,16 @@
         <v>30</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>0.0443773</v>
+        <v>0.0451191</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>0.0443009</v>
+        <v>0.0450402</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0.0450809</v>
+        <v>0.0458218</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>7.04</v>
+        <v>7.03</v>
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
@@ -2835,16 +2835,16 @@
         <v>31</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>0.0444324</v>
+        <v>0.04518150000000001</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>0.0443532</v>
+        <v>0.0450996</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>0.0451603</v>
+        <v>0.0459085</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>7.28</v>
+        <v>7.27</v>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
@@ -2871,16 +2871,16 @@
         <v>30</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>0.044484</v>
+        <v>0.0452337</v>
       </c>
       <c r="E68" s="12" t="n">
-        <v>0.0444069</v>
+        <v>0.0451539</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0.045236</v>
+        <v>0.04598480000000001</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>7.52</v>
+        <v>7.51</v>
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
@@ -2907,16 +2907,16 @@
         <v>31</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>0.0445488</v>
+        <v>0.0452962</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>0.044469</v>
+        <v>0.0452137</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0.0453274</v>
+        <v>0.04607389999999999</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>7.79</v>
+        <v>7.78</v>
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
@@ -2943,16 +2943,16 @@
         <v>31</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>0.0446159</v>
+        <v>0.0453617</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>0.0445359</v>
+        <v>0.045279</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>0.0454207</v>
+        <v>0.0461655</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>8.050000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
@@ -2979,16 +2979,16 @@
         <v>30</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>0.0446844</v>
+        <v>0.0454301</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>0.0446064</v>
+        <v>0.0453495</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0.0455146</v>
+        <v>0.0462593</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>8.300000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H71" s="14" t="inlineStr">
         <is>
@@ -3015,16 +3015,16 @@
         <v>31</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>0.0447654</v>
+        <v>0.0455105</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>0.0446848</v>
+        <v>0.0454272</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0.04562330000000001</v>
+        <v>0.0463674</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>8.58</v>
+        <v>8.57</v>
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
@@ -3051,16 +3051,16 @@
         <v>30</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>0.0448332</v>
+        <v>0.0455753</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>0.0447552</v>
+        <v>0.04549470000000001</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0.0457161</v>
+        <v>0.04645730000000001</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>8.83</v>
+        <v>8.82</v>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
@@ -3087,16 +3087,16 @@
         <v>31</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>0.0449151</v>
+        <v>0.0456537</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>0.0448336</v>
+        <v>0.0455695</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0.04582729999999999</v>
+        <v>0.046565</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
@@ -3123,16 +3123,16 @@
         <v>31</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>0.044984</v>
+        <v>0.04572440000000001</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>0.0449028</v>
+        <v>0.0456405</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0.045923</v>
+        <v>0.0466623</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>9.390000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
@@ -3159,16 +3159,16 @@
         <v>29</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>0.0450493</v>
+        <v>0.0458003</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>0.0449734</v>
+        <v>0.0457219</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>0.0460157</v>
+        <v>0.0467657</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
@@ -3195,16 +3195,16 @@
         <v>31</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>0.0451283</v>
+        <v>0.0458986</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>0.0450464</v>
+        <v>0.0458139</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0.04612409999999999</v>
+        <v>0.0468933</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>9.960000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="H77" s="14" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
         <v>30</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>0.0451967</v>
+        <v>0.0459856</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>0.04511689999999999</v>
+        <v>0.045903</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0.04622080000000001</v>
+        <v>0.0470086</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
@@ -3267,16 +3267,16 @@
         <v>31</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>0.04526500000000001</v>
+        <v>0.0460642</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0.0451828</v>
+        <v>0.04597909999999999</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0.0463161</v>
+        <v>0.0471143</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>10.51</v>
+        <v>10.5</v>
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
@@ -3303,16 +3303,16 @@
         <v>30</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>0.0453373</v>
+        <v>0.0461388</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>0.04525750000000001</v>
+        <v>0.0460562</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0.0464194</v>
+        <v>0.0472197</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>10.82</v>
+        <v>10.81</v>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
@@ -3339,16 +3339,16 @@
         <v>31</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>0.0454103</v>
+        <v>0.0462082</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>0.0453275</v>
+        <v>0.0461225</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0.04652199999999999</v>
+        <v>0.0473188</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>11.12</v>
+        <v>11.11</v>
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
@@ -3375,16 +3375,16 @@
         <v>31</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>0.0454786</v>
+        <v>0.0462732</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>0.04539489999999999</v>
+        <v>0.0461865</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0.0466193</v>
+        <v>0.0474127</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>11.41</v>
+        <v>11.4</v>
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
@@ -3411,16 +3411,16 @@
         <v>30</v>
       </c>
       <c r="D83" s="12" t="n">
-        <v>0.0455467</v>
+        <v>0.04634000000000001</v>
       </c>
       <c r="E83" s="12" t="n">
-        <v>0.0454662</v>
+        <v>0.0462567</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0.0467183</v>
+        <v>0.04751039999999999</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>11.72</v>
+        <v>11.7</v>
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
@@ -3447,16 +3447,16 @@
         <v>31</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>0.0456178</v>
+        <v>0.0464118</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>0.0455346</v>
+        <v>0.0463257</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0.0468199</v>
+        <v>0.0476128</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>12.02</v>
+        <v>12.01</v>
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
@@ -3483,16 +3483,16 @@
         <v>30</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>0.0456836</v>
+        <v>0.0464784</v>
       </c>
       <c r="E85" s="12" t="n">
-        <v>0.0456024</v>
+        <v>0.0463944</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>0.04691670000000001</v>
+        <v>0.0477103</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         <v>31</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>0.0457548</v>
+        <v>0.04655</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>0.0456706</v>
+        <v>0.04646289999999999</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>0.0470195</v>
+        <v>0.04781349999999999</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>12.65</v>
+        <v>12.64</v>
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
@@ -3555,16 +3555,16 @@
         <v>31</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>0.0458205</v>
+        <v>0.0466157</v>
       </c>
       <c r="E87" s="12" t="n">
-        <v>0.04573629999999999</v>
+        <v>0.0465285</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0.0471149</v>
+        <v>0.04790879999999999</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>12.94</v>
+        <v>12.93</v>
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
@@ -3591,16 +3591,16 @@
         <v>28</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>0.0458887</v>
+        <v>0.0466834</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>0.045813</v>
+        <v>0.0466051</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0.0472162</v>
+        <v>0.0480097</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>13.28</v>
+        <v>13.26</v>
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>31</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>0.0459696</v>
+        <v>0.0467646</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>0.0458841</v>
+        <v>0.0466761</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>0.0473293</v>
+        <v>0.0481231</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>13.6</v>
+        <v>13.58</v>
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
@@ -3663,16 +3663,16 @@
         <v>30</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>0.0460297</v>
+        <v>0.04682450000000001</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>0.04594769999999999</v>
+        <v>0.0467396</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0.0474208</v>
+        <v>0.0482144</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>13.91</v>
+        <v>13.9</v>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
@@ -3699,16 +3699,16 @@
         <v>31</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>0.0460827</v>
+        <v>0.0468775</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>0.0459973</v>
+        <v>0.0467891</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>0.04750479999999999</v>
+        <v>0.0482984</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>14.22</v>
+        <v>14.21</v>
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
@@ -3735,16 +3735,16 @@
         <v>30</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>0.0461212</v>
+        <v>0.0469156</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>0.0460386</v>
+        <v>0.0468302</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>0.0475764</v>
+        <v>0.0483695</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>14.55</v>
+        <v>14.54</v>
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
@@ -3771,16 +3771,16 @@
         <v>31</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>0.0461582</v>
+        <v>0.04695249999999999</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>0.0460731</v>
+        <v>0.0468644</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>0.0476464</v>
+        <v>0.0484393</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>14.88</v>
+        <v>14.87</v>
       </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
@@ -3807,16 +3807,16 @@
         <v>31</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>0.0461967</v>
+        <v>0.0469909</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>0.04611030000000001</v>
+        <v>0.0469015</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>0.0477186</v>
+        <v>0.0485114</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>15.22</v>
+        <v>15.21</v>
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
@@ -3843,16 +3843,16 @@
         <v>30</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>0.0462395</v>
+        <v>0.0470337</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>0.0461565</v>
+        <v>0.0469479</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>0.0477955</v>
+        <v>0.0485884</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>15.56</v>
+        <v>15.55</v>
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
@@ -3879,16 +3879,16 @@
         <v>31</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>0.0462984</v>
+        <v>0.047093</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>0.0462124</v>
+        <v>0.047004</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>0.0478875</v>
+        <v>0.0486808</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>15.89</v>
+        <v>15.88</v>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
@@ -3915,16 +3915,16 @@
         <v>30</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>0.0463716</v>
+        <v>0.0471666</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>0.0462884</v>
+        <v>0.0470805</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>0.0479985</v>
+        <v>0.0487922</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>16.27</v>
+        <v>16.26</v>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
@@ -3951,16 +3951,16 @@
         <v>31</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>0.0464481</v>
+        <v>0.04724370000000001</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>0.0463616</v>
+        <v>0.0471542</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>0.0481111</v>
+        <v>0.0489053</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>16.63</v>
+        <v>16.62</v>
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
@@ -3987,16 +3987,16 @@
         <v>31</v>
       </c>
       <c r="D99" s="12" t="n">
-        <v>0.046497</v>
+        <v>0.0472928</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>0.04641029999999999</v>
+        <v>0.047203</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>0.0481929</v>
+        <v>0.0489873</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>16.96</v>
+        <v>16.95</v>
       </c>
       <c r="H99" s="14" t="inlineStr">
         <is>
@@ -4023,16 +4023,16 @@
         <v>28</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>0.0465053</v>
+        <v>0.0473005</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>0.0464276</v>
+        <v>0.0472202</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>0.0482371</v>
+        <v>0.0490309</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>17.32</v>
+        <v>17.3</v>
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
@@ -4059,16 +4059,16 @@
         <v>31</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>0.0465022</v>
+        <v>0.0472972</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>0.0464147</v>
+        <v>0.04720659999999999</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>0.0482683</v>
+        <v>0.0490619</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>17.66</v>
+        <v>17.65</v>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         <v>30</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>0.0464967</v>
+        <v>0.0472911</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>0.0464131</v>
+        <v>0.0472045</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>0.0482942</v>
+        <v>0.0490871</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>17.97</v>
+        <v>17.96</v>
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
         <v>31</v>
       </c>
       <c r="D103" s="12" t="n">
-        <v>0.046539</v>
+        <v>0.0473331</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>0.0464519</v>
+        <v>0.04724300000000001</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>0.0483743</v>
+        <v>0.049167</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>18.35</v>
+        <v>18.34</v>
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
@@ -4167,16 +4167,16 @@
         <v>30</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>0.0466123</v>
+        <v>0.0474065</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>0.046528</v>
+        <v>0.0473193</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>0.0484841</v>
+        <v>0.0492768</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>18.72</v>
+        <v>18.7</v>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
@@ -4203,16 +4203,16 @@
         <v>31</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>0.0466847</v>
+        <v>0.0474794</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>0.0465969</v>
+        <v>0.0473886</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>0.048592</v>
+        <v>0.0493853</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>19.07</v>
+        <v>19.06</v>
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
@@ -4239,16 +4239,16 @@
         <v>31</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>0.0467169</v>
+        <v>0.047512</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>0.0466286</v>
+        <v>0.04742060000000001</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>0.0486644</v>
+        <v>0.049458</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>19.47</v>
+        <v>19.46</v>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         <v>30</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>0.046695</v>
+        <v>0.04749</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>0.0466106</v>
+        <v>0.0474027</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>0.0486793</v>
+        <v>0.0494729</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>19.84</v>
+        <v>19.83</v>
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
@@ -4311,16 +4311,16 @@
         <v>31</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>0.0466864</v>
+        <v>0.0474814</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>0.0465987</v>
+        <v>0.0473908</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>0.0487069</v>
+        <v>0.0495005</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>20.21</v>
+        <v>20.19</v>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
@@ -4347,16 +4347,16 @@
         <v>30</v>
       </c>
       <c r="D109" s="12" t="n">
-        <v>0.0467352</v>
+        <v>0.0475301</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>0.04665</v>
+        <v>0.04744200000000001</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>0.0487941</v>
+        <v>0.0495875</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>20.59</v>
+        <v>20.57</v>
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
@@ -4383,16 +4383,16 @@
         <v>31</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>0.0468556</v>
+        <v>0.0476505</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>0.04676789999999999</v>
+        <v>0.0475598</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>0.0489525</v>
+        <v>0.049746</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>20.97</v>
+        <v>20.95</v>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
@@ -4419,16 +4419,16 @@
         <v>31</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0.0469825</v>
+        <v>0.0477774</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>0.0468937</v>
+        <v>0.0476856</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>0.04911629999999999</v>
+        <v>0.0499097</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>21.34</v>
+        <v>21.32</v>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
@@ -4455,16 +4455,16 @@
         <v>28</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0.0470527</v>
+        <v>0.04784740000000001</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>0.04697320000000001</v>
+        <v>0.04776519999999999</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>0.0492248</v>
+        <v>0.0500179</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>21.72</v>
+        <v>21.71</v>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
@@ -4491,16 +4491,16 @@
         <v>31</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.0470682</v>
+        <v>0.0478632</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>0.0469793</v>
+        <v>0.0477713</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>0.0492791</v>
+        <v>0.05007259999999999</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>22.11</v>
+        <v>22.09</v>
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>30</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0.0470381</v>
+        <v>0.04783299999999999</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>0.0469516</v>
+        <v>0.0477436</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>0.0492858</v>
+        <v>0.0500791</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>22.48</v>
+        <v>22.46</v>
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
@@ -4563,16 +4563,16 @@
         <v>31</v>
       </c>
       <c r="D115" s="12" t="n">
-        <v>0.0470311</v>
+        <v>0.0478261</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>0.0469421</v>
+        <v>0.0477341</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>0.0493193</v>
+        <v>0.0501127</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>22.88</v>
+        <v>22.87</v>
       </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
@@ -4599,16 +4599,16 @@
         <v>30</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>0.0470594</v>
+        <v>0.0478542</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>0.04697320000000001</v>
+        <v>0.04776519999999999</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>0.0493872</v>
+        <v>0.0501804</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
@@ -4635,16 +4635,16 @@
         <v>31</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>0.0471142</v>
+        <v>0.0479092</v>
       </c>
       <c r="E117" s="12" t="n">
-        <v>0.0470245</v>
+        <v>0.0478165</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>0.0494813</v>
+        <v>0.0502747</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>23.67</v>
+        <v>23.65</v>
       </c>
       <c r="H117" s="14" t="inlineStr">
         <is>
@@ -4671,16 +4671,16 @@
         <v>31</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>0.04716090000000001</v>
+        <v>0.0479559</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>0.0470709</v>
+        <v>0.0478628</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>0.04956940000000001</v>
+        <v>0.0503628</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>24.08</v>
+        <v>24.07</v>
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
@@ -4707,16 +4707,16 @@
         <v>30</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>0.0471864</v>
+        <v>0.0479813</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>0.0471</v>
+        <v>0.047892</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>0.0496303</v>
+        <v>0.0504235</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>24.44</v>
+        <v>24.42</v>
       </c>
       <c r="H119" s="14" t="inlineStr">
         <is>
@@ -4743,16 +4743,16 @@
         <v>31</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>0.0472392</v>
+        <v>0.0480342</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>0.0471495</v>
+        <v>0.0479414</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>0.0497273</v>
+        <v>0.05052069999999999</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>24.88</v>
+        <v>24.86</v>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
@@ -4779,16 +4779,16 @@
         <v>30</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>0.0473231</v>
+        <v>0.048118</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>0.0472364</v>
+        <v>0.0480284</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>0.0498511</v>
+        <v>0.0506443</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>25.28</v>
+        <v>25.26</v>
       </c>
       <c r="H121" s="14" t="inlineStr">
         <is>
@@ -4815,16 +4815,16 @@
         <v>31</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.04744139999999999</v>
+        <v>0.04823649999999999</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>0.0473507</v>
+        <v>0.0481427</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>0.0500082</v>
+        <v>0.0508015</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>25.67</v>
+        <v>25.65</v>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
@@ -4851,16 +4851,16 @@
         <v>31</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>0.0475646</v>
+        <v>0.0483596</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>0.0474736</v>
+        <v>0.0482655</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>0.0501738</v>
+        <v>0.0509671</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>26.09</v>
+        <v>26.08</v>
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
@@ -4887,16 +4887,16 @@
         <v>29</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>0.04763530000000001</v>
+        <v>0.04843</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>0.0475505</v>
+        <v>0.0483424</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>0.0502863</v>
+        <v>0.05107929999999999</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>26.51</v>
+        <v>26.49</v>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
@@ -4923,16 +4923,16 @@
         <v>31</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>0.0476543</v>
+        <v>0.0484493</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>0.0475626</v>
+        <v>0.04835449999999999</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>0.05034449999999999</v>
+        <v>0.0511378</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>26.9</v>
+        <v>26.88</v>
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>30</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>0.0476185</v>
+        <v>0.0484134</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>0.0475306</v>
+        <v>0.0483225</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>0.0503518</v>
+        <v>0.051145</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>27.33</v>
+        <v>27.32</v>
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
@@ -4995,16 +4995,16 @@
         <v>31</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>0.047568</v>
+        <v>0.048363</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>0.0474772</v>
+        <v>0.0482691</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>0.0503424</v>
+        <v>0.0511357</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>27.74</v>
+        <v>27.73</v>
       </c>
       <c r="H127" s="14" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>30</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>0.0475085</v>
+        <v>0.0483034</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>0.0474205</v>
+        <v>0.0482125</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>0.0503221</v>
+        <v>0.0511152</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>28.14</v>
+        <v>28.12</v>
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
@@ -5067,16 +5067,16 @@
         <v>31</v>
       </c>
       <c r="D129" s="18" t="n">
-        <v>0.0475094</v>
+        <v>0.0483044</v>
       </c>
       <c r="E129" s="18" t="n">
-        <v>0.0474186</v>
+        <v>0.0482106</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.0503246</v>
+        <v>0.0511179</v>
       </c>
       <c r="G129" s="19" t="n">
-        <v>28.15</v>
+        <v>28.13</v>
       </c>
       <c r="H129" s="20" t="inlineStr">
         <is>
@@ -5103,16 +5103,16 @@
         <v>31</v>
       </c>
       <c r="D130" s="18" t="n">
-        <v>0.0475094</v>
+        <v>0.0483044</v>
       </c>
       <c r="E130" s="18" t="n">
-        <v>0.0474186</v>
+        <v>0.0482106</v>
       </c>
       <c r="F130" s="18" t="n">
-        <v>0.0503246</v>
+        <v>0.0511179</v>
       </c>
       <c r="G130" s="19" t="n">
-        <v>28.15</v>
+        <v>28.13</v>
       </c>
       <c r="H130" s="20" t="inlineStr">
         <is>
@@ -5139,16 +5139,16 @@
         <v>30</v>
       </c>
       <c r="D131" s="18" t="n">
-        <v>0.0475068</v>
+        <v>0.0483017</v>
       </c>
       <c r="E131" s="18" t="n">
-        <v>0.0474186</v>
+        <v>0.0482106</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.0503217</v>
+        <v>0.0511149</v>
       </c>
       <c r="G131" s="19" t="n">
-        <v>28.15</v>
+        <v>28.13</v>
       </c>
       <c r="H131" s="20" t="inlineStr">
         <is>
@@ -5175,16 +5175,16 @@
         <v>31</v>
       </c>
       <c r="D132" s="18" t="n">
-        <v>0.0475094</v>
+        <v>0.0483044</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>0.0474186</v>
+        <v>0.0482106</v>
       </c>
       <c r="F132" s="18" t="n">
-        <v>0.0503246</v>
+        <v>0.0511179</v>
       </c>
       <c r="G132" s="19" t="n">
-        <v>28.15</v>
+        <v>28.13</v>
       </c>
       <c r="H132" s="20" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-27)</t>
+          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-28)</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
         <v>46344</v>
       </c>
       <c r="D4" s="23" t="n">
-        <v>96.16249999999999</v>
+        <v>96.17</v>
       </c>
       <c r="E4" s="15">
         <f>(100-D4)/100</f>
@@ -5574,13 +5574,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.0383217</v>
+        <v>0.0383026</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>-0.533</v>
+        <v>0.026</v>
       </c>
       <c r="I4" s="25" t="n">
-        <v>7844</v>
+        <v>8075</v>
       </c>
     </row>
     <row r="5">
@@ -5596,7 +5596,7 @@
         <v>46372</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>96.065</v>
+        <v>96.075</v>
       </c>
       <c r="E5" s="15">
         <f>(100-D5)/100</f>
@@ -5606,13 +5606,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.0393212</v>
+        <v>0.0392616</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>-0.288</v>
+        <v>0.116</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>1308389</v>
+        <v>1341462</v>
       </c>
     </row>
     <row r="6">
@@ -5638,13 +5638,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.0388969</v>
+        <v>0.0389207</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>-0.781</v>
+        <v>-0.543</v>
       </c>
       <c r="I6" s="25" t="n">
-        <v>339910</v>
+        <v>343550</v>
       </c>
     </row>
     <row r="7">
@@ -5660,7 +5660,7 @@
         <v>46407</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>95.965</v>
+        <v>95.97499999999999</v>
       </c>
       <c r="E7" s="15">
         <f>(100-D7)/100</f>
@@ -5670,13 +5670,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.040342</v>
+        <v>0.0402513</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>-0.08</v>
+        <v>0.013</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>7722</v>
+        <v>7932</v>
       </c>
     </row>
     <row r="8">
@@ -5692,7 +5692,7 @@
         <v>46357</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>96.08499999999999</v>
+        <v>96.095</v>
       </c>
       <c r="E8" s="15">
         <f>(100-D8)/100</f>
@@ -5702,13 +5702,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.0391916</v>
+        <v>0.0390472</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>0.416</v>
+        <v>-0.028</v>
       </c>
       <c r="I8" s="25" t="n">
-        <v>315657</v>
+        <v>336795</v>
       </c>
     </row>
     <row r="9">
@@ -5724,7 +5724,7 @@
         <v>46435</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>95.88</v>
+        <v>95.89</v>
       </c>
       <c r="E9" s="15">
         <f>(100-D9)/100</f>
@@ -5734,10 +5734,10 @@
         <v>0.01</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.041213</v>
+        <v>0.0411101</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>0.13</v>
+        <v>0.101</v>
       </c>
       <c r="I9" s="25" t="n">
         <v>1478</v>
@@ -5756,7 +5756,7 @@
         <v>46388</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>95.93000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="E10" s="15">
         <f>(100-D10)/100</f>
@@ -5766,13 +5766,13 @@
         <v>0.01</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.0407091</v>
+        <v>0.0406104</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0.091</v>
+        <v>0.104</v>
       </c>
       <c r="I10" s="25" t="n">
-        <v>244021</v>
+        <v>243331</v>
       </c>
     </row>
     <row r="11">
@@ -5788,7 +5788,7 @@
         <v>46463</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>95.795</v>
+        <v>95.81</v>
       </c>
       <c r="E11" s="15">
         <f>(100-D11)/100</f>
@@ -5798,13 +5798,13 @@
         <v>0.02</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.0420078</v>
+        <v>0.0419117</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.422</v>
+        <v>0.117</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>1596096</v>
+        <v>1637028</v>
       </c>
     </row>
     <row r="12">
@@ -5820,7 +5820,7 @@
         <v>46419</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>95.855</v>
+        <v>95.86</v>
       </c>
       <c r="E12" s="15">
         <f>(100-D12)/100</f>
@@ -5830,13 +5830,13 @@
         <v>0.02</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.0414435</v>
+        <v>0.0413598</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.065</v>
+        <v>-0.402</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>193502</v>
+        <v>193414</v>
       </c>
     </row>
     <row r="13">
@@ -5852,7 +5852,7 @@
         <v>46498</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>95.705</v>
+        <v>95.72</v>
       </c>
       <c r="E13" s="15">
         <f>(100-D13)/100</f>
@@ -5862,13 +5862,13 @@
         <v>0.04</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.0429976</v>
+        <v>0.0428533</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.476</v>
+        <v>0.533</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>1258</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="14">
@@ -5884,7 +5884,7 @@
         <v>46447</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>95.78</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="E14" s="15">
         <f>(100-D14)/100</f>
@@ -5894,13 +5894,13 @@
         <v>0.04</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.0422055</v>
+        <v>0.0420969</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.055</v>
+        <v>-0.031</v>
       </c>
       <c r="I14" s="25" t="n">
-        <v>111680</v>
+        <v>126859</v>
       </c>
     </row>
     <row r="15">
@@ -5916,7 +5916,7 @@
         <v>46526</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>95.62</v>
+        <v>95.63500000000001</v>
       </c>
       <c r="E15" s="15">
         <f>(100-D15)/100</f>
@@ -5926,13 +5926,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.0438317</v>
+        <v>0.0436271</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>0.317</v>
+        <v>-0.229</v>
       </c>
       <c r="I15" s="25" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="16">
@@ -5948,7 +5948,7 @@
         <v>46478</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>95.7</v>
+        <v>95.715</v>
       </c>
       <c r="E16" s="15">
         <f>(100-D16)/100</f>
@@ -5958,13 +5958,13 @@
         <v>0.06</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.0429826</v>
+        <v>0.0428297</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.174</v>
+        <v>-0.203</v>
       </c>
       <c r="I16" s="25" t="n">
-        <v>36442</v>
+        <v>36816</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>46554</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>95.52</v>
+        <v>95.55500000000001</v>
       </c>
       <c r="E17" s="15">
         <f>(100-D17)/100</f>
@@ -5990,13 +5990,13 @@
         <v>0.1</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.0447454</v>
+        <v>0.0444761</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>-0.546</v>
+        <v>0.261</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>1311471</v>
+        <v>1304793</v>
       </c>
     </row>
     <row r="18">
@@ -6012,7 +6012,7 @@
         <v>46508</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>95.59999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="E18" s="15">
         <f>(100-D18)/100</f>
@@ -6022,13 +6022,13 @@
         <v>0.09</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.0439926</v>
+        <v>0.0437777</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>-0.074</v>
+        <v>-0.223</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>70063</v>
+        <v>70984</v>
       </c>
     </row>
     <row r="19">
@@ -6044,7 +6044,7 @@
         <v>46589</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>95.44499999999999</v>
+        <v>95.47499999999999</v>
       </c>
       <c r="E19" s="15">
         <f>(100-D19)/100</f>
@@ -6054,10 +6054,10 @@
         <v>0.14</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.0455556</v>
+        <v>0.0452604</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>0.056</v>
+        <v>0.104</v>
       </c>
       <c r="I19" s="25" t="n">
         <v>200</v>
@@ -6076,7 +6076,7 @@
         <v>46539</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>95.51000000000001</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="E20" s="15">
         <f>(100-D20)/100</f>
@@ -6086,13 +6086,13 @@
         <v>0.12</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.0449214</v>
+        <v>0.0445923</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>0.214</v>
+        <v>-0.077</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>71981</v>
+        <v>71496</v>
       </c>
     </row>
     <row r="21">
@@ -6108,7 +6108,7 @@
         <v>46569</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>95.435</v>
+        <v>95.465</v>
       </c>
       <c r="E21" s="15">
         <f>(100-D21)/100</f>
@@ -6118,13 +6118,13 @@
         <v>0.16</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.045648</v>
+        <v>0.04536</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>-0.02</v>
+        <v>0.1</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>21197</v>
+        <v>21036</v>
       </c>
     </row>
     <row r="22">
@@ -6140,7 +6140,7 @@
         <v>46645</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>95.36</v>
+        <v>95.38500000000001</v>
       </c>
       <c r="E22" s="15">
         <f>(100-D22)/100</f>
@@ -6150,13 +6150,13 @@
         <v>0.22</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.0464058</v>
+        <v>0.0461521</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>0.058</v>
+        <v>0.021</v>
       </c>
       <c r="I22" s="25" t="n">
-        <v>1244193</v>
+        <v>1248283</v>
       </c>
     </row>
     <row r="23">
@@ -6172,7 +6172,7 @@
         <v>46600</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>95.40000000000001</v>
+        <v>95.425</v>
       </c>
       <c r="E23" s="15">
         <f>(100-D23)/100</f>
@@ -6182,13 +6182,13 @@
         <v>0.2</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.0459948</v>
+        <v>0.04572809999999999</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>-0.052</v>
+        <v>-0.219</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>38111</v>
+        <v>38129</v>
       </c>
     </row>
     <row r="24">
@@ -6204,7 +6204,7 @@
         <v>46631</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>95.37</v>
+        <v>95.395</v>
       </c>
       <c r="E24" s="15">
         <f>(100-D24)/100</f>
@@ -6214,13 +6214,13 @@
         <v>0.25</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.0463047</v>
+        <v>0.0460715</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>0.047</v>
+        <v>0.215</v>
       </c>
       <c r="I24" s="25" t="n">
-        <v>20521</v>
+        <v>20628</v>
       </c>
     </row>
     <row r="25">
@@ -6236,7 +6236,7 @@
         <v>46661</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>95.34999999999999</v>
+        <v>95.36499999999999</v>
       </c>
       <c r="E25" s="15">
         <f>(100-D25)/100</f>
@@ -6246,13 +6246,13 @@
         <v>0.31</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.046491</v>
+        <v>0.04631739999999999</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>-0.09</v>
+        <v>-0.326</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>5161</v>
+        <v>5195</v>
       </c>
     </row>
     <row r="26">
@@ -6268,7 +6268,7 @@
         <v>46736</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>95.315</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E26" s="15">
         <f>(100-D26)/100</f>
@@ -6278,13 +6278,13 @@
         <v>0.39</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.04690859999999999</v>
+        <v>0.0468074</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>0.586</v>
+        <v>0.074</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>1076373</v>
+        <v>1067970</v>
       </c>
     </row>
     <row r="27">
@@ -6300,7 +6300,7 @@
         <v>46692</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>95.33</v>
+        <v>95.345</v>
       </c>
       <c r="E27" s="15">
         <f>(100-D27)/100</f>
@@ -6310,13 +6310,13 @@
         <v>0.37</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.0466711</v>
+        <v>0.0465616</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>-0.289</v>
+        <v>0.116</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>8027</v>
+        <v>8460</v>
       </c>
     </row>
     <row r="28">
@@ -6332,23 +6332,23 @@
         <v>46722</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>95.33499999999999</v>
+        <v>95.345</v>
       </c>
       <c r="E28" s="15">
         <f>(100-D28)/100</f>
         <v/>
       </c>
       <c r="F28" s="24" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.04663249999999999</v>
+        <v>0.0465533</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>-0.175</v>
+        <v>0.033</v>
       </c>
       <c r="I28" s="25" t="n">
-        <v>1743</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="29">
@@ -6364,20 +6364,20 @@
         <v>46753</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>95.345</v>
+        <v>95.355</v>
       </c>
       <c r="E29" s="15">
         <f>(100-D29)/100</f>
         <v/>
       </c>
       <c r="F29" s="24" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.0465291</v>
+        <v>0.046415</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>-0.209</v>
+        <v>-0.35</v>
       </c>
       <c r="I29" s="25" t="n">
         <v>20</v>
@@ -6396,7 +6396,7 @@
         <v>46827</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>95.33499999999999</v>
+        <v>95.325</v>
       </c>
       <c r="E30" s="15">
         <f>(100-D30)/100</f>
@@ -6406,13 +6406,13 @@
         <v>0.61</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.0466436</v>
+        <v>0.0467175</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>-0.064</v>
+        <v>-0.325</v>
       </c>
       <c r="I30" s="25" t="n">
-        <v>1608233</v>
+        <v>1611473</v>
       </c>
     </row>
     <row r="31">
@@ -6428,7 +6428,7 @@
         <v>46784</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>95.355</v>
+        <v>95.36499999999999</v>
       </c>
       <c r="E31" s="15">
         <f>(100-D31)/100</f>
@@ -6438,10 +6438,10 @@
         <v>0.58</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.0464673</v>
+        <v>0.0464037</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>0.173</v>
+        <v>0.537</v>
       </c>
       <c r="I31" s="25" t="n">
         <v>1</v>
@@ -6460,7 +6460,7 @@
         <v>46925</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>95.37</v>
+        <v>95.345</v>
       </c>
       <c r="E32" s="15">
         <f>(100-D32)/100</f>
@@ -6470,13 +6470,13 @@
         <v>0.88</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.0463004</v>
+        <v>0.0465607</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>0.004</v>
+        <v>0.107</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>833821</v>
+        <v>826525</v>
       </c>
     </row>
     <row r="33">
@@ -6492,23 +6492,23 @@
         <v>47016</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>95.40000000000001</v>
+        <v>95.36</v>
       </c>
       <c r="E33" s="15">
         <f>(100-D33)/100</f>
         <v/>
       </c>
       <c r="F33" s="24" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.0460025</v>
+        <v>0.0463947</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>0.025</v>
+        <v>-0.053</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>646762</v>
+        <v>635167</v>
       </c>
     </row>
     <row r="34">
@@ -6524,23 +6524,23 @@
         <v>47107</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>95.42</v>
+        <v>95.375</v>
       </c>
       <c r="E34" s="15">
         <f>(100-D34)/100</f>
         <v/>
       </c>
       <c r="F34" s="24" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.04579659999999999</v>
+        <v>0.0462505</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>-0.034</v>
+        <v>0.005</v>
       </c>
       <c r="I34" s="25" t="n">
-        <v>672641</v>
+        <v>671748</v>
       </c>
     </row>
     <row r="35">
@@ -6556,7 +6556,7 @@
         <v>47198</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>95.44499999999999</v>
+        <v>95.395</v>
       </c>
       <c r="E35" s="15">
         <f>(100-D35)/100</f>
@@ -6566,13 +6566,13 @@
         <v>1.95</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.0455516</v>
+        <v>0.0460501</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>0.016</v>
+        <v>0.001</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>551465</v>
+        <v>546311</v>
       </c>
     </row>
     <row r="36">
@@ -6588,23 +6588,23 @@
         <v>47289</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>95.47</v>
+        <v>95.41500000000001</v>
       </c>
       <c r="E36" s="15">
         <f>(100-D36)/100</f>
         <v/>
       </c>
       <c r="F36" s="24" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.0452982</v>
+        <v>0.04584990000000001</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>-0.018</v>
+        <v>-0.001</v>
       </c>
       <c r="I36" s="25" t="n">
-        <v>385342</v>
+        <v>392725</v>
       </c>
     </row>
     <row r="37">
@@ -6620,7 +6620,7 @@
         <v>47380</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>95.48999999999999</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="E37" s="15">
         <f>(100-D37)/100</f>
@@ -6630,13 +6630,13 @@
         <v>2.86</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.0451041</v>
+        <v>0.04570179999999999</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>0.041</v>
+        <v>0.018</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>391038</v>
+        <v>390544</v>
       </c>
     </row>
     <row r="38">
@@ -6652,23 +6652,23 @@
         <v>47471</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>95.5</v>
+        <v>95.44</v>
       </c>
       <c r="E38" s="15">
         <f>(100-D38)/100</f>
         <v/>
       </c>
       <c r="F38" s="24" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.0449946</v>
+        <v>0.04559650000000001</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>-0.054</v>
+        <v>-0.035</v>
       </c>
       <c r="I38" s="25" t="n">
-        <v>309038</v>
+        <v>315412</v>
       </c>
     </row>
     <row r="39">
@@ -6684,23 +6684,23 @@
         <v>47562</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>95.51000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="E39" s="15">
         <f>(100-D39)/100</f>
         <v/>
       </c>
       <c r="F39" s="24" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.0449057</v>
+        <v>0.0455035</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>0.057</v>
+        <v>0.035</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>250351</v>
+        <v>251891</v>
       </c>
     </row>
     <row r="40">
@@ -6716,23 +6716,23 @@
         <v>47653</v>
       </c>
       <c r="D40" s="23" t="n">
-        <v>95.51000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="E40" s="15">
         <f>(100-D40)/100</f>
         <v/>
       </c>
       <c r="F40" s="24" t="n">
-        <v>4.52</v>
+        <v>4.51</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.0448943</v>
+        <v>0.0454981</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>-0.057</v>
+        <v>-0.019</v>
       </c>
       <c r="I40" s="25" t="n">
-        <v>181620</v>
+        <v>182290</v>
       </c>
     </row>
     <row r="41">
@@ -6748,7 +6748,7 @@
         <v>47744</v>
       </c>
       <c r="D41" s="23" t="n">
-        <v>95.51000000000001</v>
+        <v>95.44499999999999</v>
       </c>
       <c r="E41" s="15">
         <f>(100-D41)/100</f>
@@ -6758,13 +6758,13 @@
         <v>5.14</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.0449056</v>
+        <v>0.0455509</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>0.056</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>157168</v>
+        <v>157147</v>
       </c>
     </row>
     <row r="42">
@@ -6780,7 +6780,7 @@
         <v>47835</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>95.5</v>
+        <v>95.435</v>
       </c>
       <c r="E42" s="15">
         <f>(100-D42)/100</f>
@@ -6790,13 +6790,13 @@
         <v>5.8</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.0449948</v>
+        <v>0.0456483</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>-0.052</v>
+        <v>-0.017</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>149147</v>
+        <v>149004</v>
       </c>
     </row>
     <row r="43">
@@ -6812,23 +6812,23 @@
         <v>47926</v>
       </c>
       <c r="D43" s="23" t="n">
-        <v>95.48999999999999</v>
+        <v>95.42</v>
       </c>
       <c r="E43" s="15">
         <f>(100-D43)/100</f>
         <v/>
       </c>
       <c r="F43" s="24" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.0451038</v>
+        <v>0.0458031</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>0.038</v>
+        <v>0.031</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>117631</v>
+        <v>116569</v>
       </c>
     </row>
     <row r="44">
@@ -6844,23 +6844,23 @@
         <v>48017</v>
       </c>
       <c r="D44" s="23" t="n">
-        <v>95.47</v>
+        <v>95.395</v>
       </c>
       <c r="E44" s="15">
         <f>(100-D44)/100</f>
         <v/>
       </c>
       <c r="F44" s="24" t="n">
-        <v>7.23</v>
+        <v>7.22</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.0452981</v>
+        <v>0.0460465</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>-0.019</v>
+        <v>-0.035</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>86768</v>
+        <v>86256</v>
       </c>
     </row>
     <row r="45">
@@ -6876,23 +6876,23 @@
         <v>48108</v>
       </c>
       <c r="D45" s="23" t="n">
-        <v>95.44499999999999</v>
+        <v>95.37</v>
       </c>
       <c r="E45" s="15">
         <f>(100-D45)/100</f>
         <v/>
       </c>
       <c r="F45" s="24" t="n">
-        <v>7.99</v>
+        <v>7.98</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.0455515</v>
+        <v>0.0463031</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>0.015</v>
+        <v>0.031</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>73328</v>
+        <v>73439</v>
       </c>
     </row>
     <row r="46">
@@ -6908,23 +6908,23 @@
         <v>48199</v>
       </c>
       <c r="D46" s="23" t="n">
-        <v>95.41500000000001</v>
+        <v>95.34</v>
       </c>
       <c r="E46" s="15">
         <f>(100-D46)/100</f>
         <v/>
       </c>
       <c r="F46" s="24" t="n">
-        <v>8.779999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.0458489</v>
+        <v>0.0465967</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>-0.011</v>
+        <v>-0.033</v>
       </c>
       <c r="I46" s="25" t="n">
-        <v>38487</v>
+        <v>39145</v>
       </c>
     </row>
     <row r="47">
@@ -6940,23 +6940,23 @@
         <v>48290</v>
       </c>
       <c r="D47" s="23" t="n">
-        <v>95.38500000000001</v>
+        <v>95.31</v>
       </c>
       <c r="E47" s="15">
         <f>(100-D47)/100</f>
         <v/>
       </c>
       <c r="F47" s="24" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.0461503</v>
+        <v>0.0469038</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>0.003</v>
+        <v>0.038</v>
       </c>
       <c r="I47" s="25" t="n">
-        <v>7911</v>
+        <v>7991</v>
       </c>
     </row>
     <row r="48">
@@ -6972,23 +6972,23 @@
         <v>48381</v>
       </c>
       <c r="D48" s="23" t="n">
-        <v>95.355</v>
+        <v>95.27500000000001</v>
       </c>
       <c r="E48" s="15">
         <f>(100-D48)/100</f>
         <v/>
       </c>
       <c r="F48" s="24" t="n">
-        <v>10.46</v>
+        <v>10.45</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.04645</v>
+        <v>0.0472465</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>0</v>
+        <v>-0.035</v>
       </c>
       <c r="I48" s="25" t="n">
-        <v>4065</v>
+        <v>4139</v>
       </c>
     </row>
     <row r="49">
@@ -7004,23 +7004,23 @@
         <v>48472</v>
       </c>
       <c r="D49" s="23" t="n">
-        <v>95.325</v>
+        <v>95.245</v>
       </c>
       <c r="E49" s="15">
         <f>(100-D49)/100</f>
         <v/>
       </c>
       <c r="F49" s="24" t="n">
-        <v>11.35</v>
+        <v>11.34</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.04675</v>
+        <v>0.04755180000000001</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="I49" s="25" t="n">
-        <v>790</v>
+        <v>997</v>
       </c>
     </row>
     <row r="50">
@@ -7036,23 +7036,23 @@
         <v>48563</v>
       </c>
       <c r="D50" s="23" t="n">
-        <v>95.295</v>
+        <v>95.215</v>
       </c>
       <c r="E50" s="15">
         <f>(100-D50)/100</f>
         <v/>
       </c>
       <c r="F50" s="24" t="n">
-        <v>12.26</v>
+        <v>12.25</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.0470496</v>
+        <v>0.047849</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>-0.004</v>
+        <v>-0.01</v>
       </c>
       <c r="I50" s="25" t="n">
-        <v>441</v>
+        <v>486</v>
       </c>
     </row>
     <row r="51">
@@ -7068,23 +7068,23 @@
         <v>48654</v>
       </c>
       <c r="D51" s="23" t="n">
-        <v>95.265</v>
+        <v>95.185</v>
       </c>
       <c r="E51" s="15">
         <f>(100-D51)/100</f>
         <v/>
       </c>
       <c r="F51" s="24" t="n">
-        <v>13.2</v>
+        <v>13.19</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.047352</v>
+        <v>0.0481521</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="I51" s="25" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52">
@@ -7100,20 +7100,20 @@
         <v>48745</v>
       </c>
       <c r="D52" s="23" t="n">
-        <v>95.235</v>
+        <v>95.155</v>
       </c>
       <c r="E52" s="15">
         <f>(100-D52)/100</f>
         <v/>
       </c>
       <c r="F52" s="24" t="n">
-        <v>14.17</v>
+        <v>14.16</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.0476467</v>
+        <v>0.0484466</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>-0.033</v>
+        <v>-0.034</v>
       </c>
       <c r="I52" s="25" t="n">
         <v>35</v>
@@ -7132,23 +7132,23 @@
         <v>48843</v>
       </c>
       <c r="D53" s="23" t="n">
-        <v>95.20999999999999</v>
+        <v>95.13</v>
       </c>
       <c r="E53" s="15">
         <f>(100-D53)/100</f>
         <v/>
       </c>
       <c r="F53" s="24" t="n">
-        <v>15.2</v>
+        <v>15.19</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.0479011</v>
+        <v>0.0487012</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="I53" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -7164,17 +7164,17 @@
         <v>48934</v>
       </c>
       <c r="D54" s="23" t="n">
-        <v>95.185</v>
+        <v>95.105</v>
       </c>
       <c r="E54" s="15">
         <f>(100-D54)/100</f>
         <v/>
       </c>
       <c r="F54" s="24" t="n">
-        <v>16.27</v>
+        <v>16.26</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.0481565</v>
+        <v>0.0489565</v>
       </c>
       <c r="H54" s="24" t="n">
         <v>0.065</v>
@@ -7196,20 +7196,20 @@
         <v>49018</v>
       </c>
       <c r="D55" s="23" t="n">
-        <v>95.16</v>
+        <v>95.08</v>
       </c>
       <c r="E55" s="15">
         <f>(100-D55)/100</f>
         <v/>
       </c>
       <c r="F55" s="24" t="n">
-        <v>17.28</v>
+        <v>17.27</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.048384</v>
+        <v>0.0491838</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>-0.16</v>
+        <v>-0.162</v>
       </c>
       <c r="I55" s="25" t="n">
         <v>11</v>
@@ -7228,20 +7228,20 @@
         <v>49116</v>
       </c>
       <c r="D56" s="23" t="n">
-        <v>95.145</v>
+        <v>95.065</v>
       </c>
       <c r="E56" s="15">
         <f>(100-D56)/100</f>
         <v/>
       </c>
       <c r="F56" s="24" t="n">
-        <v>18.35</v>
+        <v>18.34</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.0485727</v>
+        <v>0.0493728</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>0.227</v>
+        <v>0.228</v>
       </c>
       <c r="I56" s="25" t="n">
         <v>0</v>
@@ -7260,20 +7260,20 @@
         <v>49207</v>
       </c>
       <c r="D57" s="23" t="n">
-        <v>95.11499999999999</v>
+        <v>95.035</v>
       </c>
       <c r="E57" s="15">
         <f>(100-D57)/100</f>
         <v/>
       </c>
       <c r="F57" s="24" t="n">
-        <v>19.49</v>
+        <v>19.48</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.0488216</v>
+        <v>0.04962150000000001</v>
       </c>
       <c r="H57" s="24" t="n">
-        <v>-0.284</v>
+        <v>-0.285</v>
       </c>
       <c r="I57" s="25" t="n">
         <v>0</v>
@@ -7292,17 +7292,17 @@
         <v>49298</v>
       </c>
       <c r="D58" s="23" t="n">
-        <v>95.105</v>
+        <v>95.02500000000001</v>
       </c>
       <c r="E58" s="15">
         <f>(100-D58)/100</f>
         <v/>
       </c>
       <c r="F58" s="24" t="n">
-        <v>20.61</v>
+        <v>20.6</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.0489837</v>
+        <v>0.0497837</v>
       </c>
       <c r="H58" s="24" t="n">
         <v>0.337</v>
@@ -7324,17 +7324,17 @@
         <v>49389</v>
       </c>
       <c r="D59" s="23" t="n">
-        <v>95.06</v>
+        <v>94.98</v>
       </c>
       <c r="E59" s="15">
         <f>(100-D59)/100</f>
         <v/>
       </c>
       <c r="F59" s="24" t="n">
-        <v>21.75</v>
+        <v>21.74</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.04936860000000001</v>
+        <v>0.0501686</v>
       </c>
       <c r="H59" s="24" t="n">
         <v>-0.314</v>
@@ -7356,17 +7356,17 @@
         <v>49480</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>95.05</v>
+        <v>94.97</v>
       </c>
       <c r="E60" s="15">
         <f>(100-D60)/100</f>
         <v/>
       </c>
       <c r="F60" s="24" t="n">
-        <v>22.92</v>
+        <v>22.91</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.0495218</v>
+        <v>0.0503218</v>
       </c>
       <c r="H60" s="24" t="n">
         <v>0.218</v>
@@ -7388,17 +7388,17 @@
         <v>49571</v>
       </c>
       <c r="D61" s="23" t="n">
-        <v>95.02500000000001</v>
+        <v>94.94499999999999</v>
       </c>
       <c r="E61" s="15">
         <f>(100-D61)/100</f>
         <v/>
       </c>
       <c r="F61" s="24" t="n">
-        <v>24.11</v>
+        <v>24.09</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.0497342</v>
+        <v>0.0505342</v>
       </c>
       <c r="H61" s="24" t="n">
         <v>-0.158</v>
@@ -7420,17 +7420,17 @@
         <v>49662</v>
       </c>
       <c r="D62" s="23" t="n">
-        <v>95</v>
+        <v>94.92</v>
       </c>
       <c r="E62" s="15">
         <f>(100-D62)/100</f>
         <v/>
       </c>
       <c r="F62" s="24" t="n">
-        <v>25.31</v>
+        <v>25.3</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.0500187</v>
+        <v>0.0508187</v>
       </c>
       <c r="H62" s="24" t="n">
         <v>0.187</v>
@@ -7452,17 +7452,17 @@
         <v>49753</v>
       </c>
       <c r="D63" s="23" t="n">
-        <v>94.955</v>
+        <v>94.875</v>
       </c>
       <c r="E63" s="15">
         <f>(100-D63)/100</f>
         <v/>
       </c>
       <c r="F63" s="24" t="n">
-        <v>26.54</v>
+        <v>26.53</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.0504333</v>
+        <v>0.0512333</v>
       </c>
       <c r="H63" s="24" t="n">
         <v>-0.167</v>
@@ -7484,17 +7484,17 @@
         <v>49844</v>
       </c>
       <c r="D64" s="23" t="n">
-        <v>94.94499999999999</v>
+        <v>94.86499999999999</v>
       </c>
       <c r="E64" s="15">
         <f>(100-D64)/100</f>
         <v/>
       </c>
       <c r="F64" s="24" t="n">
-        <v>27.79</v>
+        <v>27.78</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.0505558</v>
+        <v>0.0513558</v>
       </c>
       <c r="H64" s="24" t="n">
         <v>0.058</v>
@@ -7506,7 +7506,7 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Fit: 61 contracts, RMS residual 0.228 bp, max 0.781 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
+          <t>Fit: 61 contracts, RMS residual 0.195 bp, max 0.543 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
         </is>
       </c>
     </row>
@@ -7521,7 +7521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7549,47 +7549,47 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="B4" s="26" t="n">
-        <v>0.0395</v>
+        <v>0.0394</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>0.0393</v>
+        <v>0.0395</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.0392</v>
+        <v>0.0393</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B8" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B9" s="26" t="n">
         <v>0.0388</v>
@@ -7597,55 +7597,55 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B10" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B11" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B12" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B13" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B14" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B15" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B16" s="26" t="n">
         <v>0.0387</v>
@@ -7653,71 +7653,71 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B17" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B18" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B19" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B20" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B21" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B22" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B23" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B24" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B25" s="26" t="n">
         <v>0.039</v>
@@ -7725,23 +7725,23 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B26" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B27" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B28" s="26" t="n">
         <v>0.0387</v>
@@ -7749,15 +7749,15 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B29" s="26" t="n">
-        <v>0.0385</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B30" s="26" t="n">
         <v>0.0385</v>
@@ -7765,7 +7765,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B31" s="26" t="n">
         <v>0.0385</v>
@@ -7773,31 +7773,31 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B32" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B33" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B34" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B35" s="26" t="n">
         <v>0.0362</v>
@@ -7805,7 +7805,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B36" s="26" t="n">
         <v>0.0362</v>
@@ -7813,15 +7813,15 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B37" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B38" s="26" t="n">
         <v>0.0364</v>
@@ -7829,63 +7829,63 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B39" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B40" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B41" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B42" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B43" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B44" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B45" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B46" s="26" t="n">
         <v>0.0364</v>
@@ -7893,23 +7893,23 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B47" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B48" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B49" s="26" t="n">
         <v>0.0365</v>
@@ -7917,47 +7917,47 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B50" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B51" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B52" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B53" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B54" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B55" s="26" t="n">
         <v>0.0362</v>
@@ -7965,7 +7965,7 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B56" s="26" t="n">
         <v>0.0362</v>
@@ -7973,79 +7973,79 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B57" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B58" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B59" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B60" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B61" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B62" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B63" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B64" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B65" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B66" s="26" t="n">
         <v>0.0365</v>
@@ -8053,7 +8053,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B67" s="26" t="n">
         <v>0.0365</v>
@@ -8061,15 +8061,15 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B68" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B69" s="26" t="n">
         <v>0.0364</v>
@@ -8077,7 +8077,7 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B70" s="26" t="n">
         <v>0.0364</v>
@@ -8085,143 +8085,143 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B71" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B72" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B73" s="26" t="n">
-        <v>0.0357</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B74" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.0357</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B75" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B76" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B77" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B78" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B79" s="26" t="n">
-        <v>0.0355</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B80" s="26" t="n">
-        <v>0.0353</v>
+        <v>0.0355</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B81" s="26" t="n">
-        <v>0.0358</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B82" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B83" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B84" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B85" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B86" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B87" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B88" s="26" t="n">
         <v>0.0362</v>
@@ -8229,23 +8229,23 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B89" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B90" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B91" s="26" t="n">
         <v>0.0362</v>
@@ -8253,31 +8253,31 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B92" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B93" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B94" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B95" s="26" t="n">
         <v>0.0363</v>
@@ -8285,55 +8285,55 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B96" s="26" t="n">
-        <v>0.0369</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B97" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B98" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B99" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B100" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B101" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B102" s="26" t="n">
         <v>0.0363</v>
@@ -8341,33 +8341,41 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B103" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B104" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B105" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B106" s="26" t="n">
+        <v>0.0363</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
         <v>46174</v>
       </c>
-      <c r="B106" s="26" t="n">
+      <c r="B107" s="26" t="n">
         <v>0.0365</v>
       </c>
     </row>

--- a/output/downloads/sofr-forward-curve.xlsx
+++ b/output/downloads/sofr-forward-curve.xlsx
@@ -236,7 +236,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SOFR forward curve, 2026-10-28</a:t>
+              <a:t>SOFR forward curve, 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="3">
@@ -731,7 +731,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>on 2026-10-28 (NY Fed)</t>
+          <t>on 2026-10-29 (NY Fed)</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29 18:57 UTC</t>
+          <t>2026-10-30 18:38 UTC</t>
         </is>
       </c>
     </row>
@@ -855,13 +855,13 @@
         <v>31</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.0389817</v>
+        <v>0.0389879</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>0.0389207</v>
+        <v>0.0389269</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>0.0389817</v>
+        <v>0.0389879</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0</v>
@@ -891,13 +891,13 @@
         <v>30</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.0391067</v>
+        <v>0.0390258</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.0390472</v>
+        <v>0.0389666</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>0.0391065</v>
+        <v>0.0390256</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.04067630000000001</v>
+        <v>0.0405161</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>0.0406097</v>
+        <v>0.0404501</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0.0406769</v>
+        <v>0.0405168</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>0.01</v>
@@ -963,13 +963,13 @@
         <v>31</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.0414265</v>
+        <v>0.04121909999999999</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.0413579</v>
+        <v>0.0411512</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>0.0414278</v>
+        <v>0.04122029999999999</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>0.01</v>
@@ -999,13 +999,13 @@
         <v>28</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.0421572</v>
+        <v>0.04184980000000001</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.04209329999999999</v>
+        <v>0.04178689999999999</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0.0421605</v>
+        <v>0.0418531</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>0.03</v>
@@ -1035,13 +1035,13 @@
         <v>31</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.0428979</v>
+        <v>0.0425061</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.04282390000000001</v>
+        <v>0.0424334</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0.0429033</v>
+        <v>0.0425113</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>0.05</v>
@@ -1071,13 +1071,13 @@
         <v>30</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.04384420000000001</v>
+        <v>0.043342</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>0.0437691</v>
+        <v>0.0432686</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>0.0438523</v>
+        <v>0.04335</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>0.08</v>
@@ -1107,13 +1107,13 @@
         <v>31</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.0446604</v>
+        <v>0.04404759999999999</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.0445803</v>
+        <v>0.0439698</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.0446716</v>
+        <v>0.0440588</v>
       </c>
       <c r="G19" s="13" t="n">
         <v>0.11</v>
@@ -1143,13 +1143,13 @@
         <v>30</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.0454242</v>
+        <v>0.0446961</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>0.0453442</v>
+        <v>0.04461859999999999</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0.04544069999999999</v>
+        <v>0.0447124</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>0.16</v>
@@ -1179,13 +1179,13 @@
         <v>31</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.045792</v>
+        <v>0.0450052</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.0457078</v>
+        <v>0.0449239</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.0458113</v>
+        <v>0.0450244</v>
       </c>
       <c r="G21" s="13" t="n">
         <v>0.19</v>
@@ -1215,16 +1215,16 @@
         <v>31</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.04613229999999999</v>
+        <v>0.045261</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.0460462</v>
+        <v>0.045178</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0.04615789999999999</v>
+        <v>0.04528629999999999</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
@@ -1251,16 +1251,16 @@
         <v>30</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.04636999999999999</v>
+        <v>0.0454312</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.0462866</v>
+        <v>0.0453512</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.0464005</v>
+        <v>0.0454616</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
@@ -1287,16 +1287,16 @@
         <v>31</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.0466116</v>
+        <v>0.045606</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>0.0465248</v>
+        <v>0.04552290000000001</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0.0466481</v>
+        <v>0.0456423</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
@@ -1323,13 +1323,13 @@
         <v>30</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.0465944</v>
+        <v>0.0455943</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.04651</v>
+        <v>0.0455134</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0.0466371</v>
+        <v>0.0456368</v>
       </c>
       <c r="G25" s="13" t="n">
         <v>0.43</v>
@@ -1359,13 +1359,13 @@
         <v>31</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.0464514</v>
+        <v>0.0454526</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.0463646</v>
+        <v>0.0453695</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0.0465033</v>
+        <v>0.0455043</v>
       </c>
       <c r="G26" s="13" t="n">
         <v>0.52</v>
@@ -1395,16 +1395,16 @@
         <v>31</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.0464321</v>
+        <v>0.0454217</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>0.04634559999999999</v>
+        <v>0.0453389</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0.04648869999999999</v>
+        <v>0.0454781</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
@@ -1431,13 +1431,13 @@
         <v>29</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.0465908</v>
+        <v>0.0455176</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>0.0465097</v>
+        <v>0.0454402</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>0.0466553</v>
+        <v>0.04558189999999999</v>
       </c>
       <c r="G28" s="13" t="n">
         <v>0.64</v>
@@ -1467,13 +1467,13 @@
         <v>31</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.0464179</v>
+        <v>0.0453502</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>0.0463307</v>
+        <v>0.04526690000000001</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.0464891</v>
+        <v>0.0454211</v>
       </c>
       <c r="G29" s="13" t="n">
         <v>0.71</v>
@@ -1503,13 +1503,13 @@
         <v>30</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>0.0463127</v>
+        <v>0.0452615</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>0.0462296</v>
+        <v>0.04518220000000001</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0.0463937</v>
+        <v>0.0453423</v>
       </c>
       <c r="G30" s="13" t="n">
         <v>0.8100000000000001</v>
@@ -1539,13 +1539,13 @@
         <v>31</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>0.0462226</v>
+        <v>0.0451877</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0.0461367</v>
+        <v>0.0451055</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.0463148</v>
+        <v>0.0452795</v>
       </c>
       <c r="G31" s="13" t="n">
         <v>0.92</v>
@@ -1575,13 +1575,13 @@
         <v>30</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.0461622</v>
+        <v>0.0451406</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>0.04607960000000001</v>
+        <v>0.0450615</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0.0462645</v>
+        <v>0.0452426</v>
       </c>
       <c r="G32" s="13" t="n">
         <v>1.02</v>
@@ -1611,13 +1611,13 @@
         <v>31</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.0461282</v>
+        <v>0.04512069999999999</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>0.0460424</v>
+        <v>0.04503860000000001</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0.0462401</v>
+        <v>0.0452322</v>
       </c>
       <c r="G33" s="13" t="n">
         <v>1.12</v>
@@ -1647,13 +1647,13 @@
         <v>31</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.0460849</v>
+        <v>0.04510049999999999</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>0.045999</v>
+        <v>0.0450181</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0.0462082</v>
+        <v>0.0452233</v>
       </c>
       <c r="G34" s="13" t="n">
         <v>1.23</v>
@@ -1683,13 +1683,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.0460286</v>
+        <v>0.0450748</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>0.0459466</v>
+        <v>0.0449961</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0.04616310000000001</v>
+        <v>0.0452089</v>
       </c>
       <c r="G35" s="13" t="n">
         <v>1.34</v>
@@ -1719,13 +1719,13 @@
         <v>31</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>0.0459688</v>
+        <v>0.0450505</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>0.0458838</v>
+        <v>0.0449689</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0.0461148</v>
+        <v>0.0451962</v>
       </c>
       <c r="G36" s="13" t="n">
         <v>1.46</v>
@@ -1755,16 +1755,16 @@
         <v>30</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.0458903</v>
+        <v>0.0450127</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>0.0458083</v>
+        <v>0.04493369999999999</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0.0460492</v>
+        <v>0.0451711</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
@@ -1791,16 +1791,16 @@
         <v>31</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>0.0458133</v>
+        <v>0.0449733</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>0.0457295</v>
+        <v>0.0448925</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0.0459851</v>
+        <v>0.0451446</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
@@ -1827,16 +1827,16 @@
         <v>31</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0.0457345</v>
+        <v>0.0449259</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0.0456504</v>
+        <v>0.0448447</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0.0459191</v>
+        <v>0.04511</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
@@ -1863,13 +1863,13 @@
         <v>28</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>0.0456398</v>
+        <v>0.0448573</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>0.0455649</v>
+        <v>0.04478500000000001</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0.0458382</v>
+        <v>0.0450553</v>
       </c>
       <c r="G40" s="13" t="n">
         <v>1.98</v>
@@ -1899,13 +1899,13 @@
         <v>31</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.04556619999999999</v>
+        <v>0.044801</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.04548269999999999</v>
+        <v>0.0447203</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0.0457786</v>
+        <v>0.045013</v>
       </c>
       <c r="G41" s="13" t="n">
         <v>2.12</v>
@@ -1935,13 +1935,13 @@
         <v>30</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>0.0454861</v>
+        <v>0.04473410000000001</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>0.0454052</v>
+        <v>0.0446559</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0.0457125</v>
+        <v>0.04496000000000001</v>
       </c>
       <c r="G42" s="13" t="n">
         <v>2.26</v>
@@ -1971,16 +1971,16 @@
         <v>31</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.0454092</v>
+        <v>0.0446713</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.0453263</v>
+        <v>0.0445911</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.0456512</v>
+        <v>0.0449128</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
@@ -2007,16 +2007,16 @@
         <v>30</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.0453355</v>
+        <v>0.0446134</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>0.04525559999999999</v>
+        <v>0.044536</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0.04559319999999999</v>
+        <v>0.0448706</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
@@ -2043,13 +2043,13 @@
         <v>31</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.0452771</v>
+        <v>0.0445719</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.0451943</v>
+        <v>0.0444916</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0.0455506</v>
+        <v>0.0448448</v>
       </c>
       <c r="G45" s="13" t="n">
         <v>2.73</v>
@@ -2079,16 +2079,16 @@
         <v>31</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.04522</v>
+        <v>0.0445331</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>0.0451372</v>
+        <v>0.0444528</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0.0455105</v>
+        <v>0.0448231</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
@@ -2115,16 +2115,16 @@
         <v>30</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.0451722</v>
+        <v>0.0445007</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.04509299999999999</v>
+        <v>0.0444239</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.04547780000000001</v>
+        <v>0.0448058</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
@@ -2151,13 +2151,13 @@
         <v>31</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.0451214</v>
+        <v>0.0444677</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>0.0450395</v>
+        <v>0.0443881</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0.0454458</v>
+        <v>0.0447915</v>
       </c>
       <c r="G48" s="13" t="n">
         <v>3.24</v>
@@ -2187,16 +2187,16 @@
         <v>30</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.0450652</v>
+        <v>0.0444269</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>0.0449866</v>
+        <v>0.0443505</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0.0454071</v>
+        <v>0.0447683</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
@@ -2223,16 +2223,16 @@
         <v>31</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.0450159</v>
+        <v>0.0443922</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>0.04493420000000001</v>
+        <v>0.0443128</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0.0453747</v>
+        <v>0.04475050000000001</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
@@ -2259,16 +2259,16 @@
         <v>31</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.0449621</v>
+        <v>0.0443565</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>0.0448808</v>
+        <v>0.04427730000000001</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>0.0453399</v>
+        <v>0.0447337</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
@@ -2295,16 +2295,16 @@
         <v>28</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.0449125</v>
+        <v>0.0443278</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>0.04484</v>
+        <v>0.04425709999999999</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0.0453095</v>
+        <v>0.0447242</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
@@ -2331,13 +2331,13 @@
         <v>31</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.0448965</v>
+        <v>0.04433169999999999</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.0448154</v>
+        <v>0.0442526</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.0453128</v>
+        <v>0.0447474</v>
       </c>
       <c r="G53" s="13" t="n">
         <v>4.16</v>
@@ -2367,16 +2367,16 @@
         <v>30</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>0.0448799</v>
+        <v>0.0443304</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>0.0448018</v>
+        <v>0.0442542</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>0.0453158</v>
+        <v>0.0447656</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
@@ -2403,16 +2403,16 @@
         <v>31</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>0.0448744</v>
+        <v>0.04433049999999999</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.0447934</v>
+        <v>0.0442514</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.0453304</v>
+        <v>0.0447858</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>4.56</v>
+        <v>4.55</v>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
@@ -2439,13 +2439,13 @@
         <v>30</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>0.0448662</v>
+        <v>0.0443203</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>0.0447879</v>
+        <v>0.0442439</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>0.0453414</v>
+        <v>0.0447949</v>
       </c>
       <c r="G56" s="13" t="n">
         <v>4.75</v>
@@ -2475,16 +2475,16 @@
         <v>31</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>0.0448664</v>
+        <v>0.0443187</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.0447851</v>
+        <v>0.0442393</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.045364</v>
+        <v>0.0448156</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
@@ -2511,16 +2511,16 @@
         <v>31</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>0.0448694</v>
+        <v>0.0443291</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>0.04478799999999999</v>
+        <v>0.0442497</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0.0453883</v>
+        <v>0.0448473</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
@@ -2547,16 +2547,16 @@
         <v>30</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>0.0448745</v>
+        <v>0.0443506</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.044796</v>
+        <v>0.0442739</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.0454135</v>
+        <v>0.0448889</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="H59" s="14" t="inlineStr">
         <is>
@@ -2583,16 +2583,16 @@
         <v>31</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.0448905</v>
+        <v>0.0443872</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>0.04480940000000001</v>
+        <v>0.04430799999999999</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0.0454531</v>
+        <v>0.04494919999999999</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>5.63</v>
+        <v>5.62</v>
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>30</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>0.0449033</v>
+        <v>0.04441290000000001</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>0.0448254</v>
+        <v>0.0443368</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0.0454887</v>
+        <v>0.0449976</v>
       </c>
       <c r="G61" s="13" t="n">
         <v>5.85</v>
@@ -2655,16 +2655,16 @@
         <v>31</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>0.0449275</v>
+        <v>0.0444398</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>0.0448459</v>
+        <v>0.04436</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0.04553550000000001</v>
+        <v>0.0450472</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
@@ -2691,16 +2691,16 @@
         <v>31</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>0.0449579</v>
+        <v>0.0444662</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>0.0448766</v>
+        <v>0.0443867</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0.0455896</v>
+        <v>0.0450972</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>6.32</v>
+        <v>6.31</v>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
@@ -2727,16 +2727,16 @@
         <v>28</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>0.0449923</v>
+        <v>0.0444948</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>0.0449191</v>
+        <v>0.0444232</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>0.0456462</v>
+        <v>0.045148</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
@@ -2763,16 +2763,16 @@
         <v>31</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>0.0450571</v>
+        <v>0.0445551</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>0.0449751</v>
+        <v>0.0444749</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0.0457348</v>
+        <v>0.045232</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>6.78</v>
+        <v>6.77</v>
       </c>
       <c r="H65" s="14" t="inlineStr">
         <is>
@@ -2799,16 +2799,16 @@
         <v>30</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>0.0451191</v>
+        <v>0.044618</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>0.0450402</v>
+        <v>0.04454080000000001</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0.0458218</v>
+        <v>0.0453199</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>7.03</v>
+        <v>7.02</v>
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
@@ -2835,16 +2835,16 @@
         <v>31</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>0.04518150000000001</v>
+        <v>0.0446885</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>0.0450996</v>
+        <v>0.0446084</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>0.0459085</v>
+        <v>0.0454147</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>7.27</v>
+        <v>7.26</v>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
@@ -2871,16 +2871,16 @@
         <v>30</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>0.0452337</v>
+        <v>0.04475539999999999</v>
       </c>
       <c r="E68" s="12" t="n">
-        <v>0.0451539</v>
+        <v>0.0446773</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0.04598480000000001</v>
+        <v>0.0455058</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>7.51</v>
+        <v>7.5</v>
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
@@ -2907,16 +2907,16 @@
         <v>31</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>0.0452962</v>
+        <v>0.0448387</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>0.0452137</v>
+        <v>0.0447578</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0.04607389999999999</v>
+        <v>0.0456156</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>7.78</v>
+        <v>7.77</v>
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
@@ -2943,16 +2943,16 @@
         <v>31</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>0.0453617</v>
+        <v>0.0449263</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>0.045279</v>
+        <v>0.0448451</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>0.0461655</v>
+        <v>0.0457293</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>8.039999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
@@ -2979,16 +2979,16 @@
         <v>30</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>0.0454301</v>
+        <v>0.0450147</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>0.0453495</v>
+        <v>0.04493560000000001</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0.0462593</v>
+        <v>0.0458431</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>8.289999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="H71" s="14" t="inlineStr">
         <is>
@@ -3015,16 +3015,16 @@
         <v>31</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>0.0455105</v>
+        <v>0.0451112</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>0.0454272</v>
+        <v>0.0450294</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0.0463674</v>
+        <v>0.0459673</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>8.57</v>
+        <v>8.56</v>
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
@@ -3051,16 +3051,16 @@
         <v>30</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>0.0455753</v>
+        <v>0.0451832</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>0.04549470000000001</v>
+        <v>0.045104</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0.04645730000000001</v>
+        <v>0.0460644</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>8.82</v>
+        <v>8.81</v>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
@@ -3087,16 +3087,16 @@
         <v>31</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>0.0456537</v>
+        <v>0.0452628</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>0.0455695</v>
+        <v>0.04518</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0.046565</v>
+        <v>0.0461732</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
@@ -3123,16 +3123,16 @@
         <v>31</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>0.04572440000000001</v>
+        <v>0.0453306</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>0.0456405</v>
+        <v>0.0452482</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0.0466623</v>
+        <v>0.04626769999999999</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>9.380000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
@@ -3159,13 +3159,13 @@
         <v>29</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>0.0458003</v>
+        <v>0.045404</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>0.0457219</v>
+        <v>0.045327</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>0.0467657</v>
+        <v>0.0463686</v>
       </c>
       <c r="G76" s="13" t="n">
         <v>9.65</v>
@@ -3195,16 +3195,16 @@
         <v>31</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>0.0458986</v>
+        <v>0.0455013</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>0.0458139</v>
+        <v>0.045418</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0.0468933</v>
+        <v>0.0464952</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>9.949999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="H77" s="14" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
         <v>30</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>0.0459856</v>
+        <v>0.045589</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>0.045903</v>
+        <v>0.04550779999999999</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0.0470086</v>
+        <v>0.0466111</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>10.23</v>
+        <v>10.22</v>
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
@@ -3267,16 +3267,16 @@
         <v>31</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>0.0460642</v>
+        <v>0.0456682</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0.04597909999999999</v>
+        <v>0.0455845</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0.0471143</v>
+        <v>0.0467174</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>10.5</v>
+        <v>10.49</v>
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
@@ -3303,16 +3303,16 @@
         <v>30</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>0.0461388</v>
+        <v>0.04574309999999999</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>0.0460562</v>
+        <v>0.0456619</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0.0472197</v>
+        <v>0.0468232</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>10.81</v>
+        <v>10.8</v>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
@@ -3339,16 +3339,16 @@
         <v>31</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>0.0462082</v>
+        <v>0.0458124</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>0.0461225</v>
+        <v>0.0457282</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0.0473188</v>
+        <v>0.0469221</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
@@ -3375,16 +3375,16 @@
         <v>31</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>0.0462732</v>
+        <v>0.0458772</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>0.0461865</v>
+        <v>0.045792</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0.0474127</v>
+        <v>0.0470158</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>11.4</v>
+        <v>11.39</v>
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
@@ -3411,16 +3411,16 @@
         <v>30</v>
       </c>
       <c r="D83" s="12" t="n">
-        <v>0.04634000000000001</v>
+        <v>0.04594400000000001</v>
       </c>
       <c r="E83" s="12" t="n">
-        <v>0.0462567</v>
+        <v>0.0458621</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0.04751039999999999</v>
+        <v>0.0471135</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>11.7</v>
+        <v>11.69</v>
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
@@ -3447,16 +3447,16 @@
         <v>31</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>0.0464118</v>
+        <v>0.0460158</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>0.0463257</v>
+        <v>0.0459312</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0.0476128</v>
+        <v>0.0472159</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>12.01</v>
+        <v>12</v>
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
@@ -3483,16 +3483,16 @@
         <v>30</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>0.0464784</v>
+        <v>0.0460825</v>
       </c>
       <c r="E85" s="12" t="n">
-        <v>0.0463944</v>
+        <v>0.046</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>0.0477103</v>
+        <v>0.0473135</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>12.32</v>
+        <v>12.31</v>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         <v>31</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>0.04655</v>
+        <v>0.0461541</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>0.04646289999999999</v>
+        <v>0.0460685</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>0.04781349999999999</v>
+        <v>0.0474167</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>12.64</v>
+        <v>12.63</v>
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
@@ -3555,16 +3555,16 @@
         <v>31</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>0.0466157</v>
+        <v>0.0462198</v>
       </c>
       <c r="E87" s="12" t="n">
-        <v>0.0465285</v>
+        <v>0.0461341</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0.04790879999999999</v>
+        <v>0.0475119</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>12.93</v>
+        <v>12.92</v>
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
@@ -3591,16 +3591,16 @@
         <v>28</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>0.0466834</v>
+        <v>0.0462876</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>0.0466051</v>
+        <v>0.0462106</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0.0480097</v>
+        <v>0.047613</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>13.26</v>
+        <v>13.25</v>
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
@@ -3627,13 +3627,13 @@
         <v>31</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>0.0467646</v>
+        <v>0.0463687</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>0.0466761</v>
+        <v>0.04628160000000001</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>0.0481231</v>
+        <v>0.0477262</v>
       </c>
       <c r="G89" s="13" t="n">
         <v>13.58</v>
@@ -3663,16 +3663,16 @@
         <v>30</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>0.04682450000000001</v>
+        <v>0.0464287</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>0.0467396</v>
+        <v>0.0463452</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0.0482144</v>
+        <v>0.0478176</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>13.9</v>
+        <v>13.89</v>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
@@ -3699,16 +3699,16 @@
         <v>31</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>0.0468775</v>
+        <v>0.0464817</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>0.0467891</v>
+        <v>0.0463948</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>0.0482984</v>
+        <v>0.0479016</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>14.21</v>
+        <v>14.2</v>
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
@@ -3735,16 +3735,16 @@
         <v>30</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>0.0469156</v>
+        <v>0.04652</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>0.0468302</v>
+        <v>0.0464361</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>0.0483695</v>
+        <v>0.04797290000000001</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>14.54</v>
+        <v>14.53</v>
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
@@ -3771,16 +3771,16 @@
         <v>31</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>0.04695249999999999</v>
+        <v>0.046557</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>0.0468644</v>
+        <v>0.0464704</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>0.0484393</v>
+        <v>0.0480429</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>14.87</v>
+        <v>14.86</v>
       </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
@@ -3807,16 +3807,16 @@
         <v>31</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>0.0469909</v>
+        <v>0.0465955</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>0.0469015</v>
+        <v>0.0465076</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>0.0485114</v>
+        <v>0.048115</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>15.21</v>
+        <v>15.2</v>
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
@@ -3843,16 +3843,16 @@
         <v>30</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>0.0470337</v>
+        <v>0.0466383</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>0.0469479</v>
+        <v>0.0465539</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>0.0485884</v>
+        <v>0.04819200000000001</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>15.55</v>
+        <v>15.54</v>
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
@@ -3879,16 +3879,16 @@
         <v>31</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>0.047093</v>
+        <v>0.0466974</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>0.047004</v>
+        <v>0.0466099</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>0.0486808</v>
+        <v>0.04828420000000001</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>15.88</v>
+        <v>15.87</v>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
@@ -3915,16 +3915,16 @@
         <v>30</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>0.0471666</v>
+        <v>0.0467708</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>0.0470805</v>
+        <v>0.0466862</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>0.0487922</v>
+        <v>0.04839540000000001</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>16.26</v>
+        <v>16.25</v>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
@@ -3951,16 +3951,16 @@
         <v>31</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>0.04724370000000001</v>
+        <v>0.04684770000000001</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>0.0471542</v>
+        <v>0.0467596</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>0.0489053</v>
+        <v>0.04850819999999999</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>16.62</v>
+        <v>16.61</v>
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
@@ -3987,16 +3987,16 @@
         <v>31</v>
       </c>
       <c r="D99" s="12" t="n">
-        <v>0.0472928</v>
+        <v>0.0468966</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>0.047203</v>
+        <v>0.0468084</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>0.0489873</v>
+        <v>0.0485901</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>16.95</v>
+        <v>16.94</v>
       </c>
       <c r="H99" s="14" t="inlineStr">
         <is>
@@ -4023,16 +4023,16 @@
         <v>28</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>0.0473005</v>
+        <v>0.0469047</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>0.0472202</v>
+        <v>0.0468256</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>0.0490309</v>
+        <v>0.048634</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>17.3</v>
+        <v>17.29</v>
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
@@ -4059,16 +4059,16 @@
         <v>31</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>0.0472972</v>
+        <v>0.0469015</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>0.04720659999999999</v>
+        <v>0.0468124</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>0.0490619</v>
+        <v>0.0486651</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>17.65</v>
+        <v>17.64</v>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         <v>30</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>0.0472911</v>
+        <v>0.0468957</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>0.0472045</v>
+        <v>0.04681060000000001</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>0.0490871</v>
+        <v>0.0486907</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>17.96</v>
+        <v>17.95</v>
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
         <v>31</v>
       </c>
       <c r="D103" s="12" t="n">
-        <v>0.0473331</v>
+        <v>0.0469378</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>0.04724300000000001</v>
+        <v>0.0468492</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>0.049167</v>
+        <v>0.0487706</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>18.34</v>
+        <v>18.33</v>
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
@@ -4167,16 +4167,16 @@
         <v>30</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>0.0474065</v>
+        <v>0.0470112</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>0.0473193</v>
+        <v>0.04692549999999999</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>0.0492768</v>
+        <v>0.0488805</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>18.7</v>
+        <v>18.69</v>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
@@ -4203,16 +4203,16 @@
         <v>31</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>0.0474794</v>
+        <v>0.0470839</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>0.0473886</v>
+        <v>0.04699449999999999</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>0.0493853</v>
+        <v>0.0489887</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>19.06</v>
+        <v>19.05</v>
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
@@ -4239,16 +4239,16 @@
         <v>31</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>0.047512</v>
+        <v>0.04711630000000001</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>0.04742060000000001</v>
+        <v>0.0470264</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>0.049458</v>
+        <v>0.0490612</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>19.46</v>
+        <v>19.45</v>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         <v>30</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>0.04749</v>
+        <v>0.04709430000000001</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>0.0474027</v>
+        <v>0.0470085</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>0.0494729</v>
+        <v>0.0490761</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>19.83</v>
+        <v>19.82</v>
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
@@ -4311,16 +4311,16 @@
         <v>31</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>0.0474814</v>
+        <v>0.0470858</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>0.0473908</v>
+        <v>0.0469966</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>0.0495005</v>
+        <v>0.0491037</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>20.19</v>
+        <v>20.18</v>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
@@ -4347,16 +4347,16 @@
         <v>30</v>
       </c>
       <c r="D109" s="12" t="n">
-        <v>0.0475301</v>
+        <v>0.0471345</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>0.04744200000000001</v>
+        <v>0.0470479</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>0.0495875</v>
+        <v>0.0491908</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>20.57</v>
+        <v>20.56</v>
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
@@ -4383,16 +4383,16 @@
         <v>31</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>0.0476505</v>
+        <v>0.0472549</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>0.0475598</v>
+        <v>0.0471657</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>0.049746</v>
+        <v>0.0493493</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>20.95</v>
+        <v>20.94</v>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
@@ -4419,16 +4419,16 @@
         <v>31</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0.0477774</v>
+        <v>0.0473818</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>0.0476856</v>
+        <v>0.0472916</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>0.0499097</v>
+        <v>0.049513</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>21.32</v>
+        <v>21.31</v>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
@@ -4455,16 +4455,16 @@
         <v>28</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0.04784740000000001</v>
+        <v>0.04745199999999999</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>0.04776519999999999</v>
+        <v>0.04737110000000001</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>0.0500179</v>
+        <v>0.0496214</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>21.71</v>
+        <v>21.69</v>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
@@ -4491,16 +4491,16 @@
         <v>31</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.0478632</v>
+        <v>0.0474676</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>0.0477713</v>
+        <v>0.0473772</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>0.05007259999999999</v>
+        <v>0.0496759</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>22.09</v>
+        <v>22.08</v>
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>30</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0.04783299999999999</v>
+        <v>0.0474375</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>0.0477436</v>
+        <v>0.0473496</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>0.0500791</v>
+        <v>0.04968239999999999</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>22.46</v>
+        <v>22.45</v>
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
@@ -4563,16 +4563,16 @@
         <v>31</v>
       </c>
       <c r="D115" s="12" t="n">
-        <v>0.0478261</v>
+        <v>0.0474305</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>0.0477341</v>
+        <v>0.04734</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>0.0501127</v>
+        <v>0.049716</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>22.87</v>
+        <v>22.86</v>
       </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
@@ -4599,16 +4599,16 @@
         <v>30</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>0.0478542</v>
+        <v>0.0474588</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>0.04776519999999999</v>
+        <v>0.0473712</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>0.0501804</v>
+        <v>0.0497838</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>23.26</v>
+        <v>23.25</v>
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
@@ -4635,16 +4635,16 @@
         <v>31</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>0.0479092</v>
+        <v>0.0475137</v>
       </c>
       <c r="E117" s="12" t="n">
-        <v>0.0478165</v>
+        <v>0.04742250000000001</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>0.0502747</v>
+        <v>0.049878</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>23.65</v>
+        <v>23.64</v>
       </c>
       <c r="H117" s="14" t="inlineStr">
         <is>
@@ -4671,16 +4671,16 @@
         <v>31</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>0.0479559</v>
+        <v>0.0475604</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>0.0478628</v>
+        <v>0.0474688</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>0.0503628</v>
+        <v>0.04996610000000001</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>24.07</v>
+        <v>24.06</v>
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
@@ -4707,16 +4707,16 @@
         <v>30</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>0.0479813</v>
+        <v>0.0475858</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>0.047892</v>
+        <v>0.047498</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>0.0504235</v>
+        <v>0.05002690000000001</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>24.42</v>
+        <v>24.41</v>
       </c>
       <c r="H119" s="14" t="inlineStr">
         <is>
@@ -4743,16 +4743,16 @@
         <v>31</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>0.0480342</v>
+        <v>0.0476387</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>0.0479414</v>
+        <v>0.04754749999999999</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>0.05052069999999999</v>
+        <v>0.050124</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>24.86</v>
+        <v>24.85</v>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
@@ -4779,16 +4779,16 @@
         <v>30</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>0.048118</v>
+        <v>0.04772249999999999</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>0.0480284</v>
+        <v>0.0476344</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>0.0506443</v>
+        <v>0.0502477</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>25.26</v>
+        <v>25.25</v>
       </c>
       <c r="H121" s="14" t="inlineStr">
         <is>
@@ -4815,16 +4815,16 @@
         <v>31</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.04823649999999999</v>
+        <v>0.04784099999999999</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>0.0481427</v>
+        <v>0.0477487</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>0.0508015</v>
+        <v>0.0504048</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>25.65</v>
+        <v>25.64</v>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
@@ -4851,16 +4851,16 @@
         <v>31</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>0.0483596</v>
+        <v>0.0479641</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>0.0482655</v>
+        <v>0.0478716</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>0.0509671</v>
+        <v>0.0505705</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>26.08</v>
+        <v>26.06</v>
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
@@ -4887,16 +4887,16 @@
         <v>29</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>0.04843</v>
+        <v>0.0480347</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>0.0483424</v>
+        <v>0.04794850000000001</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>0.05107929999999999</v>
+        <v>0.0506828</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>26.49</v>
+        <v>26.48</v>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
@@ -4923,16 +4923,16 @@
         <v>31</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>0.0484493</v>
+        <v>0.0480539</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>0.04835449999999999</v>
+        <v>0.0479606</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>0.0511378</v>
+        <v>0.0507412</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>26.88</v>
+        <v>26.87</v>
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>30</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>0.0484134</v>
+        <v>0.04801809999999999</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>0.0483225</v>
+        <v>0.0479286</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>0.051145</v>
+        <v>0.0507484</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>27.32</v>
+        <v>27.3</v>
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
@@ -4995,16 +4995,16 @@
         <v>31</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>0.048363</v>
+        <v>0.0479675</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>0.0482691</v>
+        <v>0.0478752</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>0.0511357</v>
+        <v>0.050739</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>27.73</v>
+        <v>27.72</v>
       </c>
       <c r="H127" s="14" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>30</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>0.0483034</v>
+        <v>0.0479081</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>0.0482125</v>
+        <v>0.0478186</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>0.0511152</v>
+        <v>0.0507186</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>28.12</v>
+        <v>28.11</v>
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
@@ -5067,16 +5067,16 @@
         <v>31</v>
       </c>
       <c r="D129" s="18" t="n">
-        <v>0.0483044</v>
+        <v>0.047909</v>
       </c>
       <c r="E129" s="18" t="n">
-        <v>0.0482106</v>
+        <v>0.0478167</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.0511179</v>
+        <v>0.0507213</v>
       </c>
       <c r="G129" s="19" t="n">
-        <v>28.13</v>
+        <v>28.12</v>
       </c>
       <c r="H129" s="20" t="inlineStr">
         <is>
@@ -5103,16 +5103,16 @@
         <v>31</v>
       </c>
       <c r="D130" s="18" t="n">
-        <v>0.0483044</v>
+        <v>0.047909</v>
       </c>
       <c r="E130" s="18" t="n">
-        <v>0.0482106</v>
+        <v>0.0478167</v>
       </c>
       <c r="F130" s="18" t="n">
-        <v>0.0511179</v>
+        <v>0.0507213</v>
       </c>
       <c r="G130" s="19" t="n">
-        <v>28.13</v>
+        <v>28.12</v>
       </c>
       <c r="H130" s="20" t="inlineStr">
         <is>
@@ -5139,16 +5139,16 @@
         <v>30</v>
       </c>
       <c r="D131" s="18" t="n">
-        <v>0.0483017</v>
+        <v>0.0479063</v>
       </c>
       <c r="E131" s="18" t="n">
-        <v>0.0482106</v>
+        <v>0.0478167</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.0511149</v>
+        <v>0.0507183</v>
       </c>
       <c r="G131" s="19" t="n">
-        <v>28.13</v>
+        <v>28.12</v>
       </c>
       <c r="H131" s="20" t="inlineStr">
         <is>
@@ -5175,16 +5175,16 @@
         <v>31</v>
       </c>
       <c r="D132" s="18" t="n">
-        <v>0.0483044</v>
+        <v>0.047909</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>0.0482106</v>
+        <v>0.0478167</v>
       </c>
       <c r="F132" s="18" t="n">
-        <v>0.0511179</v>
+        <v>0.0507213</v>
       </c>
       <c r="G132" s="19" t="n">
-        <v>28.13</v>
+        <v>28.12</v>
       </c>
       <c r="H132" s="20" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-28)</t>
+          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -5574,13 +5574,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.0383026</v>
+        <v>0.0382896</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>0.026</v>
+        <v>-0.104</v>
       </c>
       <c r="I4" s="25" t="n">
-        <v>8075</v>
+        <v>8372</v>
       </c>
     </row>
     <row r="5">
@@ -5596,7 +5596,7 @@
         <v>46372</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>96.075</v>
+        <v>96.0775</v>
       </c>
       <c r="E5" s="15">
         <f>(100-D5)/100</f>
@@ -5606,13 +5606,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.0392616</v>
+        <v>0.0392161</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>0.116</v>
+        <v>-0.089</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>1341462</v>
+        <v>1334862</v>
       </c>
     </row>
     <row r="6">
@@ -5628,7 +5628,7 @@
         <v>46327</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>96.10250000000001</v>
+        <v>96.105</v>
       </c>
       <c r="E6" s="15">
         <f>(100-D6)/100</f>
@@ -5638,13 +5638,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.0389207</v>
+        <v>0.0389269</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>-0.543</v>
+        <v>-0.231</v>
       </c>
       <c r="I6" s="25" t="n">
-        <v>343550</v>
+        <v>342903</v>
       </c>
     </row>
     <row r="7">
@@ -5660,7 +5660,7 @@
         <v>46407</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>95.97499999999999</v>
+        <v>95.9875</v>
       </c>
       <c r="E7" s="15">
         <f>(100-D7)/100</f>
@@ -5670,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.0402513</v>
+        <v>0.0401312</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>0.013</v>
+        <v>0.062</v>
       </c>
       <c r="I7" s="25" t="n">
         <v>7932</v>
@@ -5692,7 +5692,7 @@
         <v>46357</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>96.095</v>
+        <v>96.105</v>
       </c>
       <c r="E8" s="15">
         <f>(100-D8)/100</f>
@@ -5702,13 +5702,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.0390472</v>
+        <v>0.0389666</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>-0.028</v>
+        <v>0.166</v>
       </c>
       <c r="I8" s="25" t="n">
-        <v>336795</v>
+        <v>359808</v>
       </c>
     </row>
     <row r="9">
@@ -5724,7 +5724,7 @@
         <v>46435</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>95.89</v>
+        <v>95.905</v>
       </c>
       <c r="E9" s="15">
         <f>(100-D9)/100</f>
@@ -5734,13 +5734,13 @@
         <v>0.01</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.0411101</v>
+        <v>0.04091789999999999</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>0.101</v>
+        <v>-0.321</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>1478</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="10">
@@ -5756,7 +5756,7 @@
         <v>46388</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>95.94</v>
+        <v>95.955</v>
       </c>
       <c r="E10" s="15">
         <f>(100-D10)/100</f>
@@ -5766,13 +5766,13 @@
         <v>0.01</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.0406104</v>
+        <v>0.0404508</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0.104</v>
+        <v>0.008</v>
       </c>
       <c r="I10" s="25" t="n">
-        <v>243331</v>
+        <v>254452</v>
       </c>
     </row>
     <row r="11">
@@ -5788,7 +5788,7 @@
         <v>46463</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>95.81</v>
+        <v>95.83499999999999</v>
       </c>
       <c r="E11" s="15">
         <f>(100-D11)/100</f>
@@ -5798,13 +5798,13 @@
         <v>0.02</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.0419117</v>
+        <v>0.0416567</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>0.117</v>
+        <v>0.067</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>1637028</v>
+        <v>1666309</v>
       </c>
     </row>
     <row r="12">
@@ -5820,7 +5820,7 @@
         <v>46419</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>95.86</v>
+        <v>95.88500000000001</v>
       </c>
       <c r="E12" s="15">
         <f>(100-D12)/100</f>
@@ -5830,13 +5830,13 @@
         <v>0.02</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.0413598</v>
+        <v>0.041153</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.402</v>
+        <v>0.03</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>193414</v>
+        <v>189410</v>
       </c>
     </row>
     <row r="13">
@@ -5852,7 +5852,7 @@
         <v>46498</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>95.72</v>
+        <v>95.75</v>
       </c>
       <c r="E13" s="15">
         <f>(100-D13)/100</f>
@@ -5862,13 +5862,13 @@
         <v>0.04</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.0428533</v>
+        <v>0.0424834</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.533</v>
+        <v>-0.166</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>1280</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="14">
@@ -5884,7 +5884,7 @@
         <v>46447</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>95.79000000000001</v>
+        <v>95.825</v>
       </c>
       <c r="E14" s="15">
         <f>(100-D14)/100</f>
@@ -5894,13 +5894,13 @@
         <v>0.04</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.0420969</v>
+        <v>0.0417904</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>-0.031</v>
+        <v>0.404</v>
       </c>
       <c r="I14" s="25" t="n">
-        <v>126859</v>
+        <v>125324</v>
       </c>
     </row>
     <row r="15">
@@ -5916,7 +5916,7 @@
         <v>46526</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>95.63500000000001</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="E15" s="15">
         <f>(100-D15)/100</f>
@@ -5926,10 +5926,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.0436271</v>
+        <v>0.0431629</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.229</v>
+        <v>-0.371</v>
       </c>
       <c r="I15" s="25" t="n">
         <v>556</v>
@@ -5948,7 +5948,7 @@
         <v>46478</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>95.715</v>
+        <v>95.755</v>
       </c>
       <c r="E16" s="15">
         <f>(100-D16)/100</f>
@@ -5958,13 +5958,13 @@
         <v>0.06</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.0428297</v>
+        <v>0.04243909999999999</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.203</v>
+        <v>-0.109</v>
       </c>
       <c r="I16" s="25" t="n">
-        <v>36816</v>
+        <v>36032</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>46554</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>95.55500000000001</v>
+        <v>95.61</v>
       </c>
       <c r="E17" s="15">
         <f>(100-D17)/100</f>
@@ -5990,13 +5990,13 @@
         <v>0.1</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.0444761</v>
+        <v>0.0439062</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.261</v>
+        <v>0.062</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>1304793</v>
+        <v>1267298</v>
       </c>
     </row>
     <row r="18">
@@ -6012,23 +6012,23 @@
         <v>46508</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>95.62</v>
+        <v>95.675</v>
       </c>
       <c r="E18" s="15">
         <f>(100-D18)/100</f>
         <v/>
       </c>
       <c r="F18" s="24" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.0437777</v>
+        <v>0.0432771</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>-0.223</v>
+        <v>0.271</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>70984</v>
+        <v>71299</v>
       </c>
     </row>
     <row r="19">
@@ -6044,7 +6044,7 @@
         <v>46589</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>95.47499999999999</v>
+        <v>95.535</v>
       </c>
       <c r="E19" s="15">
         <f>(100-D19)/100</f>
@@ -6054,10 +6054,10 @@
         <v>0.14</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.0452604</v>
+        <v>0.0445786</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>0.104</v>
+        <v>-0.714</v>
       </c>
       <c r="I19" s="25" t="n">
         <v>200</v>
@@ -6076,7 +6076,7 @@
         <v>46539</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>95.54000000000001</v>
+        <v>95.605</v>
       </c>
       <c r="E20" s="15">
         <f>(100-D20)/100</f>
@@ -6086,13 +6086,13 @@
         <v>0.12</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.0445923</v>
+        <v>0.0439816</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>-0.077</v>
+        <v>0.316</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>71496</v>
+        <v>73691</v>
       </c>
     </row>
     <row r="21">
@@ -6108,7 +6108,7 @@
         <v>46569</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>95.465</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="E21" s="15">
         <f>(100-D21)/100</f>
@@ -6118,13 +6118,13 @@
         <v>0.16</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.04536</v>
+        <v>0.04463429999999999</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>0.1</v>
+        <v>0.343</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>21036</v>
+        <v>24510</v>
       </c>
     </row>
     <row r="22">
@@ -6140,7 +6140,7 @@
         <v>46645</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>95.38500000000001</v>
+        <v>95.47</v>
       </c>
       <c r="E22" s="15">
         <f>(100-D22)/100</f>
@@ -6150,13 +6150,13 @@
         <v>0.22</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.0461521</v>
+        <v>0.0453186</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>0.021</v>
+        <v>0.186</v>
       </c>
       <c r="I22" s="25" t="n">
-        <v>1248283</v>
+        <v>1227598</v>
       </c>
     </row>
     <row r="23">
@@ -6172,7 +6172,7 @@
         <v>46600</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>95.425</v>
+        <v>95.505</v>
       </c>
       <c r="E23" s="15">
         <f>(100-D23)/100</f>
@@ -6182,13 +6182,13 @@
         <v>0.2</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.04572809999999999</v>
+        <v>0.044944</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>-0.219</v>
+        <v>-0.06</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>38129</v>
+        <v>39070</v>
       </c>
     </row>
     <row r="24">
@@ -6204,7 +6204,7 @@
         <v>46631</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>95.395</v>
+        <v>95.48</v>
       </c>
       <c r="E24" s="15">
         <f>(100-D24)/100</f>
@@ -6214,13 +6214,13 @@
         <v>0.25</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.0460715</v>
+        <v>0.0452032</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>0.215</v>
+        <v>0.032</v>
       </c>
       <c r="I24" s="25" t="n">
-        <v>20628</v>
+        <v>22056</v>
       </c>
     </row>
     <row r="25">
@@ -6236,7 +6236,7 @@
         <v>46661</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>95.36499999999999</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="E25" s="15">
         <f>(100-D25)/100</f>
@@ -6246,13 +6246,13 @@
         <v>0.31</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.04631739999999999</v>
+        <v>0.0453818</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>-0.326</v>
+        <v>-0.182</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>5195</v>
+        <v>5249</v>
       </c>
     </row>
     <row r="26">
@@ -6268,7 +6268,7 @@
         <v>46736</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>95.31999999999999</v>
+        <v>95.42</v>
       </c>
       <c r="E26" s="15">
         <f>(100-D26)/100</f>
@@ -6278,13 +6278,13 @@
         <v>0.39</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.0468074</v>
+        <v>0.0457979</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>0.074</v>
+        <v>-0.021</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>1067970</v>
+        <v>1083838</v>
       </c>
     </row>
     <row r="27">
@@ -6300,7 +6300,7 @@
         <v>46692</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>95.345</v>
+        <v>95.44499999999999</v>
       </c>
       <c r="E27" s="15">
         <f>(100-D27)/100</f>
@@ -6310,13 +6310,13 @@
         <v>0.37</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.0465616</v>
+        <v>0.0455595</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>0.116</v>
+        <v>0.095</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>8460</v>
+        <v>9006</v>
       </c>
     </row>
     <row r="28">
@@ -6332,7 +6332,7 @@
         <v>46722</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>95.345</v>
+        <v>95.44499999999999</v>
       </c>
       <c r="E28" s="15">
         <f>(100-D28)/100</f>
@@ -6342,13 +6342,13 @@
         <v>0.43</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.0465533</v>
+        <v>0.0455566</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>0.033</v>
+        <v>0.066</v>
       </c>
       <c r="I28" s="25" t="n">
-        <v>1745</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="29">
@@ -6364,7 +6364,7 @@
         <v>46753</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>95.355</v>
+        <v>95.455</v>
       </c>
       <c r="E29" s="15">
         <f>(100-D29)/100</f>
@@ -6374,10 +6374,10 @@
         <v>0.5</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.046415</v>
+        <v>0.0454197</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>-0.35</v>
+        <v>-0.303</v>
       </c>
       <c r="I29" s="25" t="n">
         <v>20</v>
@@ -6396,7 +6396,7 @@
         <v>46827</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>95.325</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="E30" s="15">
         <f>(100-D30)/100</f>
@@ -6406,13 +6406,13 @@
         <v>0.61</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.0467175</v>
+        <v>0.0456722</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>-0.325</v>
+        <v>-0.278</v>
       </c>
       <c r="I30" s="25" t="n">
-        <v>1611473</v>
+        <v>1583949</v>
       </c>
     </row>
     <row r="31">
@@ -6428,7 +6428,7 @@
         <v>46784</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>95.36499999999999</v>
+        <v>95.465</v>
       </c>
       <c r="E31" s="15">
         <f>(100-D31)/100</f>
@@ -6438,10 +6438,10 @@
         <v>0.58</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.0464037</v>
+        <v>0.04539679999999999</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>0.537</v>
+        <v>0.468</v>
       </c>
       <c r="I31" s="25" t="n">
         <v>1</v>
@@ -6460,7 +6460,7 @@
         <v>46925</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>95.345</v>
+        <v>95.45</v>
       </c>
       <c r="E32" s="15">
         <f>(100-D32)/100</f>
@@ -6470,13 +6470,13 @@
         <v>0.88</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.0465607</v>
+        <v>0.04550849999999999</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>0.107</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>826525</v>
+        <v>826836</v>
       </c>
     </row>
     <row r="33">
@@ -6492,7 +6492,7 @@
         <v>47016</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>95.36</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="E33" s="15">
         <f>(100-D33)/100</f>
@@ -6502,13 +6502,13 @@
         <v>1.2</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.0463947</v>
+        <v>0.04539679999999999</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>-0.053</v>
+        <v>-0.032</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>635167</v>
+        <v>643693</v>
       </c>
     </row>
     <row r="34">
@@ -6524,7 +6524,7 @@
         <v>47107</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>95.375</v>
+        <v>95.465</v>
       </c>
       <c r="E34" s="15">
         <f>(100-D34)/100</f>
@@ -6534,13 +6534,13 @@
         <v>1.55</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.0462505</v>
+        <v>0.04535040000000001</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="I34" s="25" t="n">
-        <v>671748</v>
+        <v>670131</v>
       </c>
     </row>
     <row r="35">
@@ -6556,23 +6556,23 @@
         <v>47198</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>95.395</v>
+        <v>95.47499999999999</v>
       </c>
       <c r="E35" s="15">
         <f>(100-D35)/100</f>
         <v/>
       </c>
       <c r="F35" s="24" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.0460501</v>
+        <v>0.0452483</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>0.001</v>
+        <v>-0.017</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>546311</v>
+        <v>550192</v>
       </c>
     </row>
     <row r="36">
@@ -6588,7 +6588,7 @@
         <v>47289</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>95.41500000000001</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="E36" s="15">
         <f>(100-D36)/100</f>
@@ -6598,13 +6598,13 @@
         <v>2.38</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.04584990000000001</v>
+        <v>0.0451013</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>-0.001</v>
+        <v>0.013</v>
       </c>
       <c r="I36" s="25" t="n">
-        <v>392725</v>
+        <v>395341</v>
       </c>
     </row>
     <row r="37">
@@ -6620,23 +6620,23 @@
         <v>47380</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>95.43000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="E37" s="15">
         <f>(100-D37)/100</f>
         <v/>
       </c>
       <c r="F37" s="24" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.04570179999999999</v>
+        <v>0.0450014</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>390544</v>
+        <v>389747</v>
       </c>
     </row>
     <row r="38">
@@ -6652,23 +6652,23 @@
         <v>47471</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>95.44</v>
+        <v>95.505</v>
       </c>
       <c r="E38" s="15">
         <f>(100-D38)/100</f>
         <v/>
       </c>
       <c r="F38" s="24" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.04559650000000001</v>
+        <v>0.0449461</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>-0.035</v>
+        <v>-0.039</v>
       </c>
       <c r="I38" s="25" t="n">
-        <v>315412</v>
+        <v>310179</v>
       </c>
     </row>
     <row r="39">
@@ -6684,7 +6684,7 @@
         <v>47562</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>95.45</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="E39" s="15">
         <f>(100-D39)/100</f>
@@ -6694,13 +6694,13 @@
         <v>3.92</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.0455035</v>
+        <v>0.0449053</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>0.035</v>
+        <v>0.053</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>251891</v>
+        <v>250890</v>
       </c>
     </row>
     <row r="40">
@@ -6716,23 +6716,23 @@
         <v>47653</v>
       </c>
       <c r="D40" s="23" t="n">
-        <v>95.45</v>
+        <v>95.505</v>
       </c>
       <c r="E40" s="15">
         <f>(100-D40)/100</f>
         <v/>
       </c>
       <c r="F40" s="24" t="n">
-        <v>4.51</v>
+        <v>4.5</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.0454981</v>
+        <v>0.0449444</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>-0.019</v>
+        <v>-0.056</v>
       </c>
       <c r="I40" s="25" t="n">
-        <v>182290</v>
+        <v>185443</v>
       </c>
     </row>
     <row r="41">
@@ -6748,23 +6748,23 @@
         <v>47744</v>
       </c>
       <c r="D41" s="23" t="n">
-        <v>95.44499999999999</v>
+        <v>95.5</v>
       </c>
       <c r="E41" s="15">
         <f>(100-D41)/100</f>
         <v/>
       </c>
       <c r="F41" s="24" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.0455509</v>
+        <v>0.0450055</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.055</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>157147</v>
+        <v>159838</v>
       </c>
     </row>
     <row r="42">
@@ -6780,23 +6780,23 @@
         <v>47835</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>95.435</v>
+        <v>95.485</v>
       </c>
       <c r="E42" s="15">
         <f>(100-D42)/100</f>
         <v/>
       </c>
       <c r="F42" s="24" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.0456483</v>
+        <v>0.0451449</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>-0.017</v>
+        <v>-0.051</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>149004</v>
+        <v>148941</v>
       </c>
     </row>
     <row r="43">
@@ -6812,23 +6812,23 @@
         <v>47926</v>
       </c>
       <c r="D43" s="23" t="n">
-        <v>95.42</v>
+        <v>95.47</v>
       </c>
       <c r="E43" s="15">
         <f>(100-D43)/100</f>
         <v/>
       </c>
       <c r="F43" s="24" t="n">
-        <v>6.49</v>
+        <v>6.48</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.0458031</v>
+        <v>0.0453037</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>0.031</v>
+        <v>0.037</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>116569</v>
+        <v>117196</v>
       </c>
     </row>
     <row r="44">
@@ -6844,23 +6844,23 @@
         <v>48017</v>
       </c>
       <c r="D44" s="23" t="n">
-        <v>95.395</v>
+        <v>95.44499999999999</v>
       </c>
       <c r="E44" s="15">
         <f>(100-D44)/100</f>
         <v/>
       </c>
       <c r="F44" s="24" t="n">
-        <v>7.22</v>
+        <v>7.21</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.0460465</v>
+        <v>0.0455476</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>-0.035</v>
+        <v>-0.024</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>86256</v>
+        <v>86510</v>
       </c>
     </row>
     <row r="45">
@@ -6876,23 +6876,23 @@
         <v>48108</v>
       </c>
       <c r="D45" s="23" t="n">
-        <v>95.37</v>
+        <v>95.41500000000001</v>
       </c>
       <c r="E45" s="15">
         <f>(100-D45)/100</f>
         <v/>
       </c>
       <c r="F45" s="24" t="n">
-        <v>7.98</v>
+        <v>7.97</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.0463031</v>
+        <v>0.0458533</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>0.031</v>
+        <v>0.033</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>73439</v>
+        <v>72445</v>
       </c>
     </row>
     <row r="46">
@@ -6908,23 +6908,23 @@
         <v>48199</v>
       </c>
       <c r="D46" s="23" t="n">
-        <v>95.34</v>
+        <v>95.38</v>
       </c>
       <c r="E46" s="15">
         <f>(100-D46)/100</f>
         <v/>
       </c>
       <c r="F46" s="24" t="n">
-        <v>8.77</v>
+        <v>8.76</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.0465967</v>
+        <v>0.04619500000000001</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>-0.033</v>
+        <v>-0.05</v>
       </c>
       <c r="I46" s="25" t="n">
-        <v>39145</v>
+        <v>40015</v>
       </c>
     </row>
     <row r="47">
@@ -6940,23 +6940,23 @@
         <v>48290</v>
       </c>
       <c r="D47" s="23" t="n">
-        <v>95.31</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="E47" s="15">
         <f>(100-D47)/100</f>
         <v/>
       </c>
       <c r="F47" s="24" t="n">
-        <v>9.6</v>
+        <v>9.59</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.0469038</v>
+        <v>0.04650509999999999</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>0.038</v>
+        <v>0.051</v>
       </c>
       <c r="I47" s="25" t="n">
-        <v>7991</v>
+        <v>8021</v>
       </c>
     </row>
     <row r="48">
@@ -6972,23 +6972,23 @@
         <v>48381</v>
       </c>
       <c r="D48" s="23" t="n">
-        <v>95.27500000000001</v>
+        <v>95.315</v>
       </c>
       <c r="E48" s="15">
         <f>(100-D48)/100</f>
         <v/>
       </c>
       <c r="F48" s="24" t="n">
-        <v>10.45</v>
+        <v>10.44</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.0472465</v>
+        <v>0.0468461</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>-0.035</v>
+        <v>-0.039</v>
       </c>
       <c r="I48" s="25" t="n">
-        <v>4139</v>
+        <v>4147</v>
       </c>
     </row>
     <row r="49">
@@ -7004,23 +7004,23 @@
         <v>48472</v>
       </c>
       <c r="D49" s="23" t="n">
-        <v>95.245</v>
+        <v>95.285</v>
       </c>
       <c r="E49" s="15">
         <f>(100-D49)/100</f>
         <v/>
       </c>
       <c r="F49" s="24" t="n">
-        <v>11.34</v>
+        <v>11.33</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.04755180000000001</v>
+        <v>0.0471519</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="I49" s="25" t="n">
-        <v>997</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="50">
@@ -7036,23 +7036,23 @@
         <v>48563</v>
       </c>
       <c r="D50" s="23" t="n">
-        <v>95.215</v>
+        <v>95.255</v>
       </c>
       <c r="E50" s="15">
         <f>(100-D50)/100</f>
         <v/>
       </c>
       <c r="F50" s="24" t="n">
-        <v>12.25</v>
+        <v>12.24</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.047849</v>
+        <v>0.04744900000000001</v>
       </c>
       <c r="H50" s="24" t="n">
         <v>-0.01</v>
       </c>
       <c r="I50" s="25" t="n">
-        <v>486</v>
+        <v>570</v>
       </c>
     </row>
     <row r="51">
@@ -7068,23 +7068,23 @@
         <v>48654</v>
       </c>
       <c r="D51" s="23" t="n">
-        <v>95.185</v>
+        <v>95.22499999999999</v>
       </c>
       <c r="E51" s="15">
         <f>(100-D51)/100</f>
         <v/>
       </c>
       <c r="F51" s="24" t="n">
-        <v>13.19</v>
+        <v>13.18</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.0481521</v>
+        <v>0.04775210000000001</v>
       </c>
       <c r="H51" s="24" t="n">
         <v>0.021</v>
       </c>
       <c r="I51" s="25" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52">
@@ -7100,23 +7100,23 @@
         <v>48745</v>
       </c>
       <c r="D52" s="23" t="n">
-        <v>95.155</v>
+        <v>95.19499999999999</v>
       </c>
       <c r="E52" s="15">
         <f>(100-D52)/100</f>
         <v/>
       </c>
       <c r="F52" s="24" t="n">
-        <v>14.16</v>
+        <v>14.15</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.0484466</v>
+        <v>0.0480466</v>
       </c>
       <c r="H52" s="24" t="n">
         <v>-0.034</v>
       </c>
       <c r="I52" s="25" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53">
@@ -7132,20 +7132,20 @@
         <v>48843</v>
       </c>
       <c r="D53" s="23" t="n">
-        <v>95.13</v>
+        <v>95.17</v>
       </c>
       <c r="E53" s="15">
         <f>(100-D53)/100</f>
         <v/>
       </c>
       <c r="F53" s="24" t="n">
-        <v>15.19</v>
+        <v>15.18</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.0487012</v>
+        <v>0.04830110000000001</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="I53" s="25" t="n">
         <v>3</v>
@@ -7164,17 +7164,17 @@
         <v>48934</v>
       </c>
       <c r="D54" s="23" t="n">
-        <v>95.105</v>
+        <v>95.145</v>
       </c>
       <c r="E54" s="15">
         <f>(100-D54)/100</f>
         <v/>
       </c>
       <c r="F54" s="24" t="n">
-        <v>16.26</v>
+        <v>16.25</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.0489565</v>
+        <v>0.0485565</v>
       </c>
       <c r="H54" s="24" t="n">
         <v>0.065</v>
@@ -7196,20 +7196,20 @@
         <v>49018</v>
       </c>
       <c r="D55" s="23" t="n">
-        <v>95.08</v>
+        <v>95.12</v>
       </c>
       <c r="E55" s="15">
         <f>(100-D55)/100</f>
         <v/>
       </c>
       <c r="F55" s="24" t="n">
-        <v>17.27</v>
+        <v>17.25</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.0491838</v>
+        <v>0.0487839</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>-0.162</v>
+        <v>-0.161</v>
       </c>
       <c r="I55" s="25" t="n">
         <v>11</v>
@@ -7228,17 +7228,17 @@
         <v>49116</v>
       </c>
       <c r="D56" s="23" t="n">
-        <v>95.065</v>
+        <v>95.105</v>
       </c>
       <c r="E56" s="15">
         <f>(100-D56)/100</f>
         <v/>
       </c>
       <c r="F56" s="24" t="n">
-        <v>18.34</v>
+        <v>18.33</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.0493728</v>
+        <v>0.0489728</v>
       </c>
       <c r="H56" s="24" t="n">
         <v>0.228</v>
@@ -7260,17 +7260,17 @@
         <v>49207</v>
       </c>
       <c r="D57" s="23" t="n">
-        <v>95.035</v>
+        <v>95.075</v>
       </c>
       <c r="E57" s="15">
         <f>(100-D57)/100</f>
         <v/>
       </c>
       <c r="F57" s="24" t="n">
-        <v>19.48</v>
+        <v>19.47</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.04962150000000001</v>
+        <v>0.0492215</v>
       </c>
       <c r="H57" s="24" t="n">
         <v>-0.285</v>
@@ -7292,17 +7292,17 @@
         <v>49298</v>
       </c>
       <c r="D58" s="23" t="n">
-        <v>95.02500000000001</v>
+        <v>95.065</v>
       </c>
       <c r="E58" s="15">
         <f>(100-D58)/100</f>
         <v/>
       </c>
       <c r="F58" s="24" t="n">
-        <v>20.6</v>
+        <v>20.59</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.0497837</v>
+        <v>0.0493837</v>
       </c>
       <c r="H58" s="24" t="n">
         <v>0.337</v>
@@ -7324,17 +7324,17 @@
         <v>49389</v>
       </c>
       <c r="D59" s="23" t="n">
-        <v>94.98</v>
+        <v>95.02</v>
       </c>
       <c r="E59" s="15">
         <f>(100-D59)/100</f>
         <v/>
       </c>
       <c r="F59" s="24" t="n">
-        <v>21.74</v>
+        <v>21.73</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.0501686</v>
+        <v>0.0497686</v>
       </c>
       <c r="H59" s="24" t="n">
         <v>-0.314</v>
@@ -7356,17 +7356,17 @@
         <v>49480</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>94.97</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="E60" s="15">
         <f>(100-D60)/100</f>
         <v/>
       </c>
       <c r="F60" s="24" t="n">
-        <v>22.91</v>
+        <v>22.89</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.0503218</v>
+        <v>0.0499218</v>
       </c>
       <c r="H60" s="24" t="n">
         <v>0.218</v>
@@ -7388,17 +7388,17 @@
         <v>49571</v>
       </c>
       <c r="D61" s="23" t="n">
-        <v>94.94499999999999</v>
+        <v>94.985</v>
       </c>
       <c r="E61" s="15">
         <f>(100-D61)/100</f>
         <v/>
       </c>
       <c r="F61" s="24" t="n">
-        <v>24.09</v>
+        <v>24.08</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.0505342</v>
+        <v>0.0501342</v>
       </c>
       <c r="H61" s="24" t="n">
         <v>-0.158</v>
@@ -7420,17 +7420,17 @@
         <v>49662</v>
       </c>
       <c r="D62" s="23" t="n">
-        <v>94.92</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="E62" s="15">
         <f>(100-D62)/100</f>
         <v/>
       </c>
       <c r="F62" s="24" t="n">
-        <v>25.3</v>
+        <v>25.29</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.0508187</v>
+        <v>0.0504187</v>
       </c>
       <c r="H62" s="24" t="n">
         <v>0.187</v>
@@ -7452,17 +7452,17 @@
         <v>49753</v>
       </c>
       <c r="D63" s="23" t="n">
-        <v>94.875</v>
+        <v>94.91500000000001</v>
       </c>
       <c r="E63" s="15">
         <f>(100-D63)/100</f>
         <v/>
       </c>
       <c r="F63" s="24" t="n">
-        <v>26.53</v>
+        <v>26.52</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.0512333</v>
+        <v>0.0508333</v>
       </c>
       <c r="H63" s="24" t="n">
         <v>-0.167</v>
@@ -7484,17 +7484,17 @@
         <v>49844</v>
       </c>
       <c r="D64" s="23" t="n">
-        <v>94.86499999999999</v>
+        <v>94.905</v>
       </c>
       <c r="E64" s="15">
         <f>(100-D64)/100</f>
         <v/>
       </c>
       <c r="F64" s="24" t="n">
-        <v>27.78</v>
+        <v>27.76</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.0513558</v>
+        <v>0.0509558</v>
       </c>
       <c r="H64" s="24" t="n">
         <v>0.058</v>
@@ -7506,7 +7506,7 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Fit: 61 contracts, RMS residual 0.195 bp, max 0.543 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
+          <t>Fit: 61 contracts, RMS residual 0.197 bp, max 0.714 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B4" s="26" t="n">
         <v>0.0394</v>
@@ -7557,47 +7557,47 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>0.0395</v>
+        <v>0.0394</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.0393</v>
+        <v>0.0395</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0392</v>
+        <v>0.0393</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B8" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B9" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B10" s="26" t="n">
         <v>0.0388</v>
@@ -7605,55 +7605,55 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B11" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B12" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B13" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B14" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B15" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B16" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B17" s="26" t="n">
         <v>0.0387</v>
@@ -7661,71 +7661,71 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B18" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B19" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B20" s="26" t="n">
-        <v>0.0389</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B21" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B22" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B23" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B24" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B25" s="26" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B26" s="26" t="n">
         <v>0.039</v>
@@ -7733,23 +7733,23 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B27" s="26" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B28" s="26" t="n">
-        <v>0.0387</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B29" s="26" t="n">
         <v>0.0387</v>
@@ -7757,15 +7757,15 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B30" s="26" t="n">
-        <v>0.0385</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B31" s="26" t="n">
         <v>0.0385</v>
@@ -7773,7 +7773,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B32" s="26" t="n">
         <v>0.0385</v>
@@ -7781,31 +7781,31 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B33" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B34" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B35" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B36" s="26" t="n">
         <v>0.0362</v>
@@ -7813,7 +7813,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B37" s="26" t="n">
         <v>0.0362</v>
@@ -7821,15 +7821,15 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B38" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B39" s="26" t="n">
         <v>0.0364</v>
@@ -7837,63 +7837,63 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B40" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B41" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B42" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B43" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B44" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B45" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B46" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B47" s="26" t="n">
         <v>0.0364</v>
@@ -7901,23 +7901,23 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B48" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B49" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B50" s="26" t="n">
         <v>0.0365</v>
@@ -7925,47 +7925,47 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B51" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B52" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B53" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B54" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B55" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B56" s="26" t="n">
         <v>0.0362</v>
@@ -7973,7 +7973,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B57" s="26" t="n">
         <v>0.0362</v>
@@ -7981,79 +7981,79 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B58" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B59" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B60" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B61" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B62" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B63" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B64" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B65" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B66" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B67" s="26" t="n">
         <v>0.0365</v>
@@ -8061,7 +8061,7 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B68" s="26" t="n">
         <v>0.0365</v>
@@ -8069,15 +8069,15 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B69" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B70" s="26" t="n">
         <v>0.0364</v>
@@ -8085,7 +8085,7 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B71" s="26" t="n">
         <v>0.0364</v>
@@ -8093,143 +8093,143 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B72" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B73" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B74" s="26" t="n">
-        <v>0.0357</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B75" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.0357</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B76" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B77" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B78" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B79" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B80" s="26" t="n">
-        <v>0.0355</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B81" s="26" t="n">
-        <v>0.0353</v>
+        <v>0.0355</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B82" s="26" t="n">
-        <v>0.0358</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B83" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B84" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B85" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B86" s="26" t="n">
-        <v>0.0366</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B87" s="26" t="n">
-        <v>0.0368</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B88" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B89" s="26" t="n">
         <v>0.0362</v>
@@ -8237,23 +8237,23 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B90" s="26" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B91" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B92" s="26" t="n">
         <v>0.0362</v>
@@ -8261,31 +8261,31 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B93" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B94" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B95" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B96" s="26" t="n">
         <v>0.0363</v>
@@ -8293,55 +8293,55 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B97" s="26" t="n">
-        <v>0.0369</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B98" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B99" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B100" s="26" t="n">
-        <v>0.0359</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B101" s="26" t="n">
-        <v>0.036</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B102" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B103" s="26" t="n">
         <v>0.0363</v>
@@ -8349,34 +8349,34 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B104" s="26" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B105" s="26" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B106" s="26" t="n">
-        <v>0.0363</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B107" s="26" t="n">
-        <v>0.0365</v>
+        <v>0.0363</v>
       </c>
     </row>
   </sheetData>

--- a/output/downloads/sofr-forward-curve.xlsx
+++ b/output/downloads/sofr-forward-curve.xlsx
@@ -236,7 +236,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SOFR forward curve, 2026-10-29</a:t>
+              <a:t>SOFR forward curve, 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="3">
@@ -743,7 +743,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30 18:38 UTC</t>
+          <t>2026-10-31 17:44 UTC</t>
         </is>
       </c>
     </row>
@@ -855,13 +855,13 @@
         <v>31</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.0389879</v>
+        <v>0.038988</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>0.0389269</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>0.0389879</v>
+        <v>0.038988</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0</v>
@@ -891,13 +891,13 @@
         <v>30</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.0390258</v>
+        <v>0.0390269</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.0389666</v>
+        <v>0.0389676</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>0.0390256</v>
+        <v>0.0390266</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.0405161</v>
+        <v>0.0403597</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>0.0404501</v>
+        <v>0.0402942</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0.0405168</v>
+        <v>0.0403603</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>0.01</v>
@@ -963,13 +963,13 @@
         <v>31</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.04121909999999999</v>
+        <v>0.040978</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.0411512</v>
+        <v>0.0409109</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>0.04122029999999999</v>
+        <v>0.0409792</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>0.01</v>
@@ -999,13 +999,13 @@
         <v>28</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.04184980000000001</v>
+        <v>0.04147199999999999</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.04178689999999999</v>
+        <v>0.0414102</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0.0418531</v>
+        <v>0.0414752</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>0.03</v>
@@ -1035,13 +1035,13 @@
         <v>31</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.0425061</v>
+        <v>0.0420452</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.0424334</v>
+        <v>0.04197409999999999</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0.0425113</v>
+        <v>0.0420504</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>0.05</v>
@@ -1071,13 +1071,13 @@
         <v>30</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.043342</v>
+        <v>0.0427726</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>0.0432686</v>
+        <v>0.0427011</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>0.04335</v>
+        <v>0.04278050000000001</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>0.08</v>
@@ -1107,13 +1107,13 @@
         <v>31</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.04404759999999999</v>
+        <v>0.04336909999999999</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.0439698</v>
+        <v>0.0432936</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.0440588</v>
+        <v>0.0433802</v>
       </c>
       <c r="G19" s="13" t="n">
         <v>0.11</v>
@@ -1143,13 +1143,13 @@
         <v>30</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.0446961</v>
+        <v>0.0439651</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>0.04461859999999999</v>
+        <v>0.0438901</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0.0447124</v>
+        <v>0.0439813</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>0.16</v>
@@ -1179,13 +1179,13 @@
         <v>31</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.0450052</v>
+        <v>0.0442462</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.0449239</v>
+        <v>0.0441676</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.0450244</v>
+        <v>0.04426529999999999</v>
       </c>
       <c r="G21" s="13" t="n">
         <v>0.19</v>
@@ -1215,13 +1215,13 @@
         <v>31</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.045261</v>
+        <v>0.0444522</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.045178</v>
+        <v>0.0443722</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0.04528629999999999</v>
+        <v>0.04447739999999999</v>
       </c>
       <c r="G22" s="13" t="n">
         <v>0.25</v>
@@ -1251,13 +1251,13 @@
         <v>30</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.0454312</v>
+        <v>0.04462</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.0453512</v>
+        <v>0.0445427</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.0454616</v>
+        <v>0.04465010000000001</v>
       </c>
       <c r="G23" s="13" t="n">
         <v>0.3</v>
@@ -1287,13 +1287,13 @@
         <v>31</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.045606</v>
+        <v>0.0447917</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>0.04552290000000001</v>
+        <v>0.0447116</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0.0456423</v>
+        <v>0.0448278</v>
       </c>
       <c r="G24" s="13" t="n">
         <v>0.36</v>
@@ -1323,16 +1323,16 @@
         <v>30</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.0455943</v>
+        <v>0.0447783</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.0455134</v>
+        <v>0.04470030000000001</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0.0456368</v>
+        <v>0.0448206</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
@@ -1359,16 +1359,16 @@
         <v>31</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.0454526</v>
+        <v>0.0446556</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.0453695</v>
+        <v>0.0445754</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0.0455043</v>
+        <v>0.044707</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         <v>31</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.0454217</v>
+        <v>0.0446026</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>0.0453389</v>
+        <v>0.0445228</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0.0454781</v>
+        <v>0.0446587</v>
       </c>
       <c r="G27" s="13" t="n">
         <v>0.5600000000000001</v>
@@ -1431,13 +1431,13 @@
         <v>29</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.0455176</v>
+        <v>0.0445493</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>0.0454402</v>
+        <v>0.0444752</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>0.04558189999999999</v>
+        <v>0.0446133</v>
       </c>
       <c r="G28" s="13" t="n">
         <v>0.64</v>
@@ -1467,13 +1467,13 @@
         <v>31</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.0453502</v>
+        <v>0.0444017</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>0.04526690000000001</v>
+        <v>0.0443219</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.0454211</v>
+        <v>0.0444723</v>
       </c>
       <c r="G29" s="13" t="n">
         <v>0.71</v>
@@ -1503,16 +1503,16 @@
         <v>30</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>0.0452615</v>
+        <v>0.0443202</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>0.04518220000000001</v>
+        <v>0.0442442</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0.0453423</v>
+        <v>0.0444007</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
@@ -1539,13 +1539,13 @@
         <v>31</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>0.0451877</v>
+        <v>0.0442455</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0.0451055</v>
+        <v>0.04416680000000001</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.0452795</v>
+        <v>0.044337</v>
       </c>
       <c r="G31" s="13" t="n">
         <v>0.92</v>
@@ -1575,13 +1575,13 @@
         <v>30</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.0451406</v>
+        <v>0.04418560000000001</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>0.0450615</v>
+        <v>0.0441099</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0.0452426</v>
+        <v>0.0442873</v>
       </c>
       <c r="G32" s="13" t="n">
         <v>1.02</v>
@@ -1611,16 +1611,16 @@
         <v>31</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.04512069999999999</v>
+        <v>0.0441455</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>0.04503860000000001</v>
+        <v>0.0440669</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0.0452322</v>
+        <v>0.0442567</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
@@ -1647,13 +1647,13 @@
         <v>31</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.04510049999999999</v>
+        <v>0.0441004</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>0.0450181</v>
+        <v>0.0440216</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0.0452233</v>
+        <v>0.0442229</v>
       </c>
       <c r="G34" s="13" t="n">
         <v>1.23</v>
@@ -1683,13 +1683,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.0450748</v>
+        <v>0.0440538</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>0.0449961</v>
+        <v>0.0439787</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0.0452089</v>
+        <v>0.0441876</v>
       </c>
       <c r="G35" s="13" t="n">
         <v>1.34</v>
@@ -1719,16 +1719,16 @@
         <v>31</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>0.0450505</v>
+        <v>0.0440138</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>0.0449689</v>
+        <v>0.0439358</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0.0451962</v>
+        <v>0.044159</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
@@ -1755,13 +1755,13 @@
         <v>30</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.0450127</v>
+        <v>0.043965</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>0.04493369999999999</v>
+        <v>0.0438897</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0.0451711</v>
+        <v>0.0441231</v>
       </c>
       <c r="G37" s="13" t="n">
         <v>1.58</v>
@@ -1791,13 +1791,13 @@
         <v>31</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>0.0449733</v>
+        <v>0.0439215</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>0.0448925</v>
+        <v>0.0438445</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0.0451446</v>
+        <v>0.0440925</v>
       </c>
       <c r="G38" s="13" t="n">
         <v>1.71</v>
@@ -1827,13 +1827,13 @@
         <v>31</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0.0449259</v>
+        <v>0.0438766</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0.0448447</v>
+        <v>0.0437991</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0.04511</v>
+        <v>0.0440603</v>
       </c>
       <c r="G39" s="13" t="n">
         <v>1.84</v>
@@ -1863,13 +1863,13 @@
         <v>28</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>0.0448573</v>
+        <v>0.0438174</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>0.04478500000000001</v>
+        <v>0.0437484</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0.0450553</v>
+        <v>0.04401500000000001</v>
       </c>
       <c r="G40" s="13" t="n">
         <v>1.98</v>
@@ -1899,13 +1899,13 @@
         <v>31</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.044801</v>
+        <v>0.0437756</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.0447203</v>
+        <v>0.04369849999999999</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0.045013</v>
+        <v>0.0439871</v>
       </c>
       <c r="G41" s="13" t="n">
         <v>2.12</v>
@@ -1935,16 +1935,16 @@
         <v>30</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>0.04473410000000001</v>
+        <v>0.04372810000000001</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>0.0446559</v>
+        <v>0.04365339999999999</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0.04496000000000001</v>
+        <v>0.0439535</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
@@ -1971,13 +1971,13 @@
         <v>31</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.0446713</v>
+        <v>0.0436888</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.0445911</v>
+        <v>0.0436121</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.0449128</v>
+        <v>0.0439299</v>
       </c>
       <c r="G43" s="13" t="n">
         <v>2.41</v>
@@ -2007,13 +2007,13 @@
         <v>30</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.0446134</v>
+        <v>0.043653</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>0.044536</v>
+        <v>0.0435789</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0.0448706</v>
+        <v>0.0439097</v>
       </c>
       <c r="G44" s="13" t="n">
         <v>2.57</v>
@@ -2043,16 +2043,16 @@
         <v>31</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.0445719</v>
+        <v>0.0436255</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.0444916</v>
+        <v>0.04354860000000001</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0.0448448</v>
+        <v>0.0438979</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
@@ -2079,16 +2079,16 @@
         <v>31</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.0445331</v>
+        <v>0.0435898</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>0.0444528</v>
+        <v>0.04351289999999999</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0.0448231</v>
+        <v>0.0438793</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
@@ -2115,13 +2115,13 @@
         <v>30</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.0445007</v>
+        <v>0.0435526</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.0444239</v>
+        <v>0.043479</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.0448058</v>
+        <v>0.0438572</v>
       </c>
       <c r="G47" s="13" t="n">
         <v>3.05</v>
@@ -2151,16 +2151,16 @@
         <v>31</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.0444677</v>
+        <v>0.0435177</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>0.0443881</v>
+        <v>0.0434416</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0.0447915</v>
+        <v>0.04384109999999999</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
@@ -2187,13 +2187,13 @@
         <v>30</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.0444269</v>
+        <v>0.0434927</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>0.0443505</v>
+        <v>0.0434195</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0.0447683</v>
+        <v>0.0438336</v>
       </c>
       <c r="G49" s="13" t="n">
         <v>3.41</v>
@@ -2223,13 +2223,13 @@
         <v>31</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.0443922</v>
+        <v>0.0434887</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>0.0443128</v>
+        <v>0.0434124</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0.04475050000000001</v>
+        <v>0.0438463</v>
       </c>
       <c r="G50" s="13" t="n">
         <v>3.58</v>
@@ -2259,13 +2259,13 @@
         <v>31</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.0443565</v>
+        <v>0.0434923</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>0.04427730000000001</v>
+        <v>0.0434162</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>0.0447337</v>
+        <v>0.0438689</v>
       </c>
       <c r="G51" s="13" t="n">
         <v>3.77</v>
@@ -2295,13 +2295,13 @@
         <v>28</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.0443278</v>
+        <v>0.0434961</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>0.04425709999999999</v>
+        <v>0.0434281</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0.0447242</v>
+        <v>0.0438919</v>
       </c>
       <c r="G52" s="13" t="n">
         <v>3.96</v>
@@ -2331,16 +2331,16 @@
         <v>31</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.04433169999999999</v>
+        <v>0.0435193</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.0442526</v>
+        <v>0.0434431</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.0447474</v>
+        <v>0.0439344</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
@@ -2367,13 +2367,13 @@
         <v>30</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>0.0443304</v>
+        <v>0.0435313</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>0.0442542</v>
+        <v>0.0434578</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>0.0447656</v>
+        <v>0.0439659</v>
       </c>
       <c r="G54" s="13" t="n">
         <v>4.35</v>
@@ -2403,13 +2403,13 @@
         <v>31</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>0.04433049999999999</v>
+        <v>0.0435463</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.0442514</v>
+        <v>0.0434701</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.0447858</v>
+        <v>0.04400109999999999</v>
       </c>
       <c r="G55" s="13" t="n">
         <v>4.55</v>
@@ -2439,16 +2439,16 @@
         <v>30</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>0.0443203</v>
+        <v>0.0435536</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>0.0442439</v>
+        <v>0.0434798</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>0.0447949</v>
+        <v>0.0440275</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
@@ -2475,16 +2475,16 @@
         <v>31</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>0.0443187</v>
+        <v>0.0435694</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.0442393</v>
+        <v>0.0434927</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.0448156</v>
+        <v>0.04406570000000001</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>4.97</v>
+        <v>4.96</v>
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
@@ -2511,13 +2511,13 @@
         <v>31</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>0.0443291</v>
+        <v>0.0435873</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>0.0442497</v>
+        <v>0.0435105</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0.0448473</v>
+        <v>0.0441049</v>
       </c>
       <c r="G58" s="13" t="n">
         <v>5.18</v>
@@ -2547,13 +2547,13 @@
         <v>30</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>0.0443506</v>
+        <v>0.0436077</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.0442739</v>
+        <v>0.0435335</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.0448889</v>
+        <v>0.0441453</v>
       </c>
       <c r="G59" s="13" t="n">
         <v>5.38</v>
@@ -2583,16 +2583,16 @@
         <v>31</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.0443872</v>
+        <v>0.04364150000000001</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>0.04430799999999999</v>
+        <v>0.0435648</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0.04494919999999999</v>
+        <v>0.0442027</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>5.62</v>
+        <v>5.61</v>
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>30</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>0.04441290000000001</v>
+        <v>0.0436715</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>0.0443368</v>
+        <v>0.0435979</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0.0449976</v>
+        <v>0.0442555</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>5.85</v>
+        <v>5.84</v>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
@@ -2655,13 +2655,13 @@
         <v>31</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>0.0444398</v>
+        <v>0.0437119</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>0.04436</v>
+        <v>0.04363470000000001</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0.0450472</v>
+        <v>0.04431860000000001</v>
       </c>
       <c r="G62" s="13" t="n">
         <v>6.07</v>
@@ -2691,16 +2691,16 @@
         <v>31</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>0.0444662</v>
+        <v>0.0437597</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>0.0443867</v>
+        <v>0.0436826</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0.0450972</v>
+        <v>0.0443899</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
@@ -2727,16 +2727,16 @@
         <v>28</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>0.0444948</v>
+        <v>0.0438112</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>0.0444232</v>
+        <v>0.04374189999999999</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>0.045148</v>
+        <v>0.0444637</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
@@ -2763,16 +2763,16 @@
         <v>31</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>0.0445551</v>
+        <v>0.0438928</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>0.0444749</v>
+        <v>0.043815</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0.045232</v>
+        <v>0.044569</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>6.77</v>
+        <v>6.76</v>
       </c>
       <c r="H65" s="14" t="inlineStr">
         <is>
@@ -2799,16 +2799,16 @@
         <v>30</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>0.044618</v>
+        <v>0.04397090000000001</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>0.04454080000000001</v>
+        <v>0.0438959</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0.0453199</v>
+        <v>0.0446721</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>7.02</v>
+        <v>7.01</v>
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
@@ -2835,16 +2835,16 @@
         <v>31</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>0.0446885</v>
+        <v>0.0440452</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>0.0446084</v>
+        <v>0.0439673</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>0.0454147</v>
+        <v>0.0447707</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>7.26</v>
+        <v>7.25</v>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
@@ -2871,13 +2871,13 @@
         <v>30</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>0.04475539999999999</v>
+        <v>0.0441093</v>
       </c>
       <c r="E68" s="12" t="n">
-        <v>0.0446773</v>
+        <v>0.0440334</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0.0455058</v>
+        <v>0.04485890000000001</v>
       </c>
       <c r="G68" s="13" t="n">
         <v>7.5</v>
@@ -2907,16 +2907,16 @@
         <v>31</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>0.0448387</v>
+        <v>0.0441914</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>0.0447578</v>
+        <v>0.04411279999999999</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0.0456156</v>
+        <v>0.04496749999999999</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>7.77</v>
+        <v>7.76</v>
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
@@ -2943,16 +2943,16 @@
         <v>31</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>0.0449263</v>
+        <v>0.0442882</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>0.0448451</v>
+        <v>0.0442093</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>0.0457293</v>
+        <v>0.0450904</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>8.029999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
@@ -2979,13 +2979,13 @@
         <v>30</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>0.0450147</v>
+        <v>0.04439460000000001</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>0.04493560000000001</v>
+        <v>0.0443176</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0.0458431</v>
+        <v>0.0452222</v>
       </c>
       <c r="G71" s="13" t="n">
         <v>8.279999999999999</v>
@@ -3015,16 +3015,16 @@
         <v>31</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>0.0451112</v>
+        <v>0.0445102</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>0.0450294</v>
+        <v>0.0444305</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0.0459673</v>
+        <v>0.04536539999999999</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>8.56</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
@@ -3051,16 +3051,16 @@
         <v>30</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>0.0451832</v>
+        <v>0.0445904</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>0.045104</v>
+        <v>0.0445133</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0.0460644</v>
+        <v>0.04547080000000001</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>8.81</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         <v>31</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>0.0452628</v>
+        <v>0.0446694</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>0.04518</v>
+        <v>0.0445888</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0.0461732</v>
+        <v>0.045579</v>
       </c>
       <c r="G74" s="13" t="n">
         <v>9.1</v>
@@ -3123,16 +3123,16 @@
         <v>31</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>0.0453306</v>
+        <v>0.0447347</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>0.0452482</v>
+        <v>0.0446544</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0.04626769999999999</v>
+        <v>0.045671</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>9.369999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
@@ -3159,16 +3159,16 @@
         <v>29</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>0.045404</v>
+        <v>0.0448129</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>0.045327</v>
+        <v>0.0447379</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>0.0463686</v>
+        <v>0.0457767</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>9.65</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
@@ -3195,16 +3195,16 @@
         <v>31</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>0.0455013</v>
+        <v>0.0449249</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>0.045418</v>
+        <v>0.0448438</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0.0464952</v>
+        <v>0.045918</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>9.94</v>
+        <v>9.93</v>
       </c>
       <c r="H77" s="14" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
         <v>30</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>0.045589</v>
+        <v>0.0450328</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>0.04550779999999999</v>
+        <v>0.0449536</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0.0466111</v>
+        <v>0.0460541</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
@@ -3267,16 +3267,16 @@
         <v>31</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>0.0456682</v>
+        <v>0.0451303</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0.0455845</v>
+        <v>0.0450486</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0.0467174</v>
+        <v>0.0461787</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>10.49</v>
+        <v>10.48</v>
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
@@ -3303,16 +3303,16 @@
         <v>30</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>0.04574309999999999</v>
+        <v>0.0452239</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>0.0456619</v>
+        <v>0.0451445</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0.0468232</v>
+        <v>0.0463031</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>10.8</v>
+        <v>10.79</v>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
@@ -3339,16 +3339,16 @@
         <v>31</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>0.0458124</v>
+        <v>0.0453098</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>0.0457282</v>
+        <v>0.0452274</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0.0469221</v>
+        <v>0.0464187</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
@@ -3375,16 +3375,16 @@
         <v>31</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>0.0458772</v>
+        <v>0.0453925</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>0.045792</v>
+        <v>0.0453091</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0.0470158</v>
+        <v>0.04653019999999999</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>11.39</v>
+        <v>11.38</v>
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
@@ -3411,13 +3411,13 @@
         <v>30</v>
       </c>
       <c r="D83" s="12" t="n">
-        <v>0.04594400000000001</v>
+        <v>0.0454791</v>
       </c>
       <c r="E83" s="12" t="n">
-        <v>0.0458621</v>
+        <v>0.0453989</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0.0471135</v>
+        <v>0.0466477</v>
       </c>
       <c r="G83" s="13" t="n">
         <v>11.69</v>
@@ -3447,16 +3447,16 @@
         <v>31</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>0.0460158</v>
+        <v>0.0455668</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>0.0459312</v>
+        <v>0.0454838</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0.0472159</v>
+        <v>0.046766</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>12</v>
+        <v>11.99</v>
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
@@ -3483,16 +3483,16 @@
         <v>30</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>0.0460825</v>
+        <v>0.0456423</v>
       </c>
       <c r="E85" s="12" t="n">
-        <v>0.046</v>
+        <v>0.0455613</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>0.0473135</v>
+        <v>0.0468724</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>12.31</v>
+        <v>12.3</v>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         <v>31</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>0.0461541</v>
+        <v>0.0457151</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>0.0460685</v>
+        <v>0.045631</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>0.0474167</v>
+        <v>0.0469767</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>12.63</v>
+        <v>12.62</v>
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
@@ -3555,16 +3555,16 @@
         <v>31</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>0.0462198</v>
+        <v>0.045777</v>
       </c>
       <c r="E87" s="12" t="n">
-        <v>0.0461341</v>
+        <v>0.04569289999999999</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0.0475119</v>
+        <v>0.0470682</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>12.92</v>
+        <v>12.91</v>
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
@@ -3591,16 +3591,16 @@
         <v>28</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>0.0462876</v>
+        <v>0.0458394</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>0.0462106</v>
+        <v>0.0457639</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0.047613</v>
+        <v>0.0471638</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>13.25</v>
+        <v>13.24</v>
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>31</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>0.0463687</v>
+        <v>0.0459169</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>0.04628160000000001</v>
+        <v>0.0458315</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>0.0477262</v>
+        <v>0.0472734</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>13.58</v>
+        <v>13.57</v>
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
@@ -3663,16 +3663,16 @@
         <v>30</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>0.0464287</v>
+        <v>0.0459783</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>0.0463452</v>
+        <v>0.0458965</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0.0478176</v>
+        <v>0.0473663</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>13.89</v>
+        <v>13.88</v>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
@@ -3699,16 +3699,16 @@
         <v>31</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>0.0464817</v>
+        <v>0.0460391</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>0.0463948</v>
+        <v>0.0459538</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>0.0479016</v>
+        <v>0.047458</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>14.2</v>
+        <v>14.19</v>
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
@@ -3735,16 +3735,16 @@
         <v>30</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>0.04652</v>
+        <v>0.0460925</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>0.0464361</v>
+        <v>0.0460101</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>0.04797290000000001</v>
+        <v>0.0475445</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>14.53</v>
+        <v>14.52</v>
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
@@ -3771,16 +3771,16 @@
         <v>31</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>0.046557</v>
+        <v>0.0461495</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>0.0464704</v>
+        <v>0.0460644</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>0.0480429</v>
+        <v>0.0476344</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>14.86</v>
+        <v>14.85</v>
       </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
@@ -3807,16 +3807,16 @@
         <v>31</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>0.0465955</v>
+        <v>0.0462104</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>0.0465076</v>
+        <v>0.046124</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>0.048115</v>
+        <v>0.047729</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>15.2</v>
+        <v>15.19</v>
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
@@ -3843,16 +3843,16 @@
         <v>30</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>0.0466383</v>
+        <v>0.04627410000000001</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>0.0465539</v>
+        <v>0.046191</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>0.04819200000000001</v>
+        <v>0.0478268</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>15.54</v>
+        <v>15.53</v>
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
@@ -3879,16 +3879,16 @@
         <v>31</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>0.0466974</v>
+        <v>0.0463467</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>0.0466099</v>
+        <v>0.0462605</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>0.04828420000000001</v>
+        <v>0.0479324</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>15.87</v>
+        <v>15.86</v>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
@@ -3915,16 +3915,16 @@
         <v>30</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>0.0467708</v>
+        <v>0.0464258</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>0.0466862</v>
+        <v>0.0463423</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>0.04839540000000001</v>
+        <v>0.0480493</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>16.25</v>
+        <v>16.24</v>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
@@ -3951,16 +3951,16 @@
         <v>31</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>0.04684770000000001</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>0.0467596</v>
+        <v>0.0464133</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>0.04850819999999999</v>
+        <v>0.0481595</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>16.61</v>
+        <v>16.59</v>
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
@@ -3987,16 +3987,16 @@
         <v>31</v>
       </c>
       <c r="D99" s="12" t="n">
-        <v>0.0468966</v>
+        <v>0.0465477</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>0.0468084</v>
+        <v>0.0464608</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>0.0485901</v>
+        <v>0.0482402</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>16.94</v>
+        <v>16.92</v>
       </c>
       <c r="H99" s="14" t="inlineStr">
         <is>
@@ -4023,16 +4023,16 @@
         <v>28</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>0.0469047</v>
+        <v>0.0465641</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>0.0468256</v>
+        <v>0.04648620000000001</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>0.048634</v>
+        <v>0.04829240000000001</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>17.29</v>
+        <v>17.28</v>
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
@@ -4059,16 +4059,16 @@
         <v>31</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>0.0469015</v>
+        <v>0.0465788</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>0.0468124</v>
+        <v>0.0464909</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>0.0486651</v>
+        <v>0.0483413</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>17.64</v>
+        <v>17.63</v>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         <v>30</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>0.0468957</v>
+        <v>0.0465912</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>0.04681060000000001</v>
+        <v>0.0465071</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>0.0486907</v>
+        <v>0.0483851</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>17.95</v>
+        <v>17.94</v>
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
         <v>31</v>
       </c>
       <c r="D103" s="12" t="n">
-        <v>0.0469378</v>
+        <v>0.046647</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>0.0468492</v>
+        <v>0.0465594</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>0.0487706</v>
+        <v>0.04847870000000001</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>18.33</v>
+        <v>18.32</v>
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
@@ -4167,16 +4167,16 @@
         <v>30</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>0.0470112</v>
+        <v>0.04672279999999999</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>0.04692549999999999</v>
+        <v>0.0466382</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>0.0488805</v>
+        <v>0.04859110000000001</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>18.69</v>
+        <v>18.68</v>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
@@ -4203,16 +4203,16 @@
         <v>31</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>0.0470839</v>
+        <v>0.04679179999999999</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>0.04699449999999999</v>
+        <v>0.0467035</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>0.0489887</v>
+        <v>0.0486955</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>19.05</v>
+        <v>19.04</v>
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
@@ -4239,16 +4239,16 @@
         <v>31</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>0.04711630000000001</v>
+        <v>0.0468196</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>0.0470264</v>
+        <v>0.0467309</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>0.0490612</v>
+        <v>0.0487634</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>19.45</v>
+        <v>19.44</v>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         <v>30</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>0.04709430000000001</v>
+        <v>0.046796</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>0.0470085</v>
+        <v>0.0467113</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>0.0490761</v>
+        <v>0.0487767</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>19.82</v>
+        <v>19.81</v>
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
@@ -4311,16 +4311,16 @@
         <v>31</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>0.0470858</v>
+        <v>0.04678810000000001</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>0.0469966</v>
+        <v>0.0467001</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>0.0491037</v>
+        <v>0.04880499999999999</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>20.18</v>
+        <v>20.17</v>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
@@ -4347,16 +4347,16 @@
         <v>30</v>
       </c>
       <c r="D109" s="12" t="n">
-        <v>0.0471345</v>
+        <v>0.046838</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>0.0470479</v>
+        <v>0.0467525</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>0.0491908</v>
+        <v>0.0488932</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>20.56</v>
+        <v>20.55</v>
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
@@ -4383,16 +4383,16 @@
         <v>31</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>0.0472549</v>
+        <v>0.0469589</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>0.0471657</v>
+        <v>0.04687090000000001</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>0.0493493</v>
+        <v>0.0490521</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>20.94</v>
+        <v>20.93</v>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
@@ -4419,16 +4419,16 @@
         <v>31</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0.0473818</v>
+        <v>0.0470857</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>0.0472916</v>
+        <v>0.0469966</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>0.049513</v>
+        <v>0.0492157</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>21.31</v>
+        <v>21.3</v>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
@@ -4455,16 +4455,16 @@
         <v>28</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0.04745199999999999</v>
+        <v>0.04715569999999999</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>0.04737110000000001</v>
+        <v>0.0470758</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>0.0496214</v>
+        <v>0.04932400000000001</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>21.69</v>
+        <v>21.68</v>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
@@ -4491,16 +4491,16 @@
         <v>31</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.0474676</v>
+        <v>0.0471712</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>0.0473772</v>
+        <v>0.0470819</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>0.0496759</v>
+        <v>0.0493782</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>22.08</v>
+        <v>22.07</v>
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>30</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0.0474375</v>
+        <v>0.0471411</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>0.0473496</v>
+        <v>0.0470542</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>0.04968239999999999</v>
+        <v>0.0493849</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>22.45</v>
+        <v>22.44</v>
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
@@ -4563,16 +4563,16 @@
         <v>31</v>
       </c>
       <c r="D115" s="12" t="n">
-        <v>0.0474305</v>
+        <v>0.0471341</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>0.04734</v>
+        <v>0.0470448</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>0.049716</v>
+        <v>0.0494185</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>22.86</v>
+        <v>22.84</v>
       </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
@@ -4599,16 +4599,16 @@
         <v>30</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>0.0474588</v>
+        <v>0.0471625</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>0.0473712</v>
+        <v>0.047076</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>0.0497838</v>
+        <v>0.0494863</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>23.25</v>
+        <v>23.24</v>
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
@@ -4635,16 +4635,16 @@
         <v>31</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>0.0475137</v>
+        <v>0.04721739999999999</v>
       </c>
       <c r="E117" s="12" t="n">
-        <v>0.04742250000000001</v>
+        <v>0.0471273</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>0.049878</v>
+        <v>0.0495805</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>23.64</v>
+        <v>23.63</v>
       </c>
       <c r="H117" s="14" t="inlineStr">
         <is>
@@ -4671,16 +4671,16 @@
         <v>31</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>0.0475604</v>
+        <v>0.0472641</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>0.0474688</v>
+        <v>0.0471736</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>0.04996610000000001</v>
+        <v>0.04966859999999999</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>24.06</v>
+        <v>24.04</v>
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
@@ -4707,16 +4707,16 @@
         <v>30</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>0.0475858</v>
+        <v>0.04728950000000001</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>0.047498</v>
+        <v>0.0472028</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>0.05002690000000001</v>
+        <v>0.04972940000000001</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>24.41</v>
+        <v>24.4</v>
       </c>
       <c r="H119" s="14" t="inlineStr">
         <is>
@@ -4743,16 +4743,16 @@
         <v>31</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>0.0476387</v>
+        <v>0.0473424</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>0.04754749999999999</v>
+        <v>0.0472523</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>0.050124</v>
+        <v>0.0498265</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>24.85</v>
+        <v>24.84</v>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
@@ -4779,16 +4779,16 @@
         <v>30</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>0.04772249999999999</v>
+        <v>0.0474263</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>0.0476344</v>
+        <v>0.0473392</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>0.0502477</v>
+        <v>0.0499503</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>25.25</v>
+        <v>25.24</v>
       </c>
       <c r="H121" s="14" t="inlineStr">
         <is>
@@ -4815,16 +4815,16 @@
         <v>31</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.04784099999999999</v>
+        <v>0.0475447</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>0.0477487</v>
+        <v>0.0474536</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>0.0504048</v>
+        <v>0.05010729999999999</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>25.64</v>
+        <v>25.63</v>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
@@ -4851,16 +4851,16 @@
         <v>31</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>0.0479641</v>
+        <v>0.0476678</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>0.0478716</v>
+        <v>0.0475764</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>0.0505705</v>
+        <v>0.05027300000000001</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>26.06</v>
+        <v>26.05</v>
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
@@ -4887,16 +4887,16 @@
         <v>29</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>0.0480347</v>
+        <v>0.0477385</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>0.04794850000000001</v>
+        <v>0.0476534</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>0.0506828</v>
+        <v>0.0503854</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>26.48</v>
+        <v>26.47</v>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
@@ -4923,16 +4923,16 @@
         <v>31</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>0.0480539</v>
+        <v>0.0477576</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>0.0479606</v>
+        <v>0.0476655</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>0.0507412</v>
+        <v>0.0504437</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>26.87</v>
+        <v>26.86</v>
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>30</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>0.04801809999999999</v>
+        <v>0.04772179999999999</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>0.0479286</v>
+        <v>0.0476335</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>0.0507484</v>
+        <v>0.050451</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>27.3</v>
+        <v>27.29</v>
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
@@ -4995,16 +4995,16 @@
         <v>31</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>0.0479675</v>
+        <v>0.0476713</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>0.0478752</v>
+        <v>0.04758009999999999</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>0.050739</v>
+        <v>0.0504416</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>27.72</v>
+        <v>27.7</v>
       </c>
       <c r="H127" s="14" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>30</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>0.0479081</v>
+        <v>0.0476119</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>0.0478186</v>
+        <v>0.0475235</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>0.0507186</v>
+        <v>0.0504212</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>28.11</v>
+        <v>28.09</v>
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
@@ -5067,16 +5067,16 @@
         <v>31</v>
       </c>
       <c r="D129" s="18" t="n">
-        <v>0.047909</v>
+        <v>0.04761269999999999</v>
       </c>
       <c r="E129" s="18" t="n">
-        <v>0.0478167</v>
+        <v>0.0475215</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.0507213</v>
+        <v>0.0504238</v>
       </c>
       <c r="G129" s="19" t="n">
-        <v>28.12</v>
+        <v>28.11</v>
       </c>
       <c r="H129" s="20" t="inlineStr">
         <is>
@@ -5103,16 +5103,16 @@
         <v>31</v>
       </c>
       <c r="D130" s="18" t="n">
-        <v>0.047909</v>
+        <v>0.04761269999999999</v>
       </c>
       <c r="E130" s="18" t="n">
-        <v>0.0478167</v>
+        <v>0.0475215</v>
       </c>
       <c r="F130" s="18" t="n">
-        <v>0.0507213</v>
+        <v>0.0504238</v>
       </c>
       <c r="G130" s="19" t="n">
-        <v>28.12</v>
+        <v>28.11</v>
       </c>
       <c r="H130" s="20" t="inlineStr">
         <is>
@@ -5139,16 +5139,16 @@
         <v>30</v>
       </c>
       <c r="D131" s="18" t="n">
-        <v>0.0479063</v>
+        <v>0.0476101</v>
       </c>
       <c r="E131" s="18" t="n">
-        <v>0.0478167</v>
+        <v>0.0475215</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.0507183</v>
+        <v>0.0504208</v>
       </c>
       <c r="G131" s="19" t="n">
-        <v>28.12</v>
+        <v>28.11</v>
       </c>
       <c r="H131" s="20" t="inlineStr">
         <is>
@@ -5175,16 +5175,16 @@
         <v>31</v>
       </c>
       <c r="D132" s="18" t="n">
-        <v>0.047909</v>
+        <v>0.04761269999999999</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>0.0478167</v>
+        <v>0.0475215</v>
       </c>
       <c r="F132" s="18" t="n">
-        <v>0.0507213</v>
+        <v>0.0504238</v>
       </c>
       <c r="G132" s="19" t="n">
-        <v>28.12</v>
+        <v>28.11</v>
       </c>
       <c r="H132" s="20" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-29)</t>
+          <t>CME SOFR futures settlements used in the fit (trade date 2026-10-30)</t>
         </is>
       </c>
     </row>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.0382896</v>
+        <v>0.0382898</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>-0.104</v>
+        <v>-0.102</v>
       </c>
       <c r="I4" s="25" t="n">
         <v>8372</v>
@@ -5596,7 +5596,7 @@
         <v>46372</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>96.0775</v>
+        <v>96.08</v>
       </c>
       <c r="E5" s="15">
         <f>(100-D5)/100</f>
@@ -5606,13 +5606,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.0392161</v>
+        <v>0.0392019</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>-0.089</v>
+        <v>0.019</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>1334862</v>
+        <v>1301830</v>
       </c>
     </row>
     <row r="6">
@@ -5628,7 +5628,7 @@
         <v>46327</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>96.105</v>
+        <v>96.10250000000001</v>
       </c>
       <c r="E6" s="15">
         <f>(100-D6)/100</f>
@@ -5641,10 +5641,10 @@
         <v>0.0389269</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>-0.231</v>
+        <v>-0.481</v>
       </c>
       <c r="I6" s="25" t="n">
-        <v>342903</v>
+        <v>343523</v>
       </c>
     </row>
     <row r="7">
@@ -5660,7 +5660,7 @@
         <v>46407</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>95.9875</v>
+        <v>96.0025</v>
       </c>
       <c r="E7" s="15">
         <f>(100-D7)/100</f>
@@ -5670,13 +5670,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.0401312</v>
+        <v>0.0400316</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>0.062</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>7932</v>
+        <v>7949</v>
       </c>
     </row>
     <row r="8">
@@ -5692,7 +5692,7 @@
         <v>46357</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>96.105</v>
+        <v>96.10250000000001</v>
       </c>
       <c r="E8" s="15">
         <f>(100-D8)/100</f>
@@ -5702,13 +5702,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.0389666</v>
+        <v>0.0389676</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>0.166</v>
+        <v>-0.074</v>
       </c>
       <c r="I8" s="25" t="n">
-        <v>359808</v>
+        <v>360072</v>
       </c>
     </row>
     <row r="9">
@@ -5724,7 +5724,7 @@
         <v>46435</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>95.905</v>
+        <v>95.925</v>
       </c>
       <c r="E9" s="15">
         <f>(100-D9)/100</f>
@@ -5734,10 +5734,10 @@
         <v>0.01</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.04091789999999999</v>
+        <v>0.0407148</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.321</v>
+        <v>-0.352</v>
       </c>
       <c r="I9" s="25" t="n">
         <v>1414</v>
@@ -5756,7 +5756,7 @@
         <v>46388</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>95.955</v>
+        <v>95.97</v>
       </c>
       <c r="E10" s="15">
         <f>(100-D10)/100</f>
@@ -5766,13 +5766,13 @@
         <v>0.01</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.0404508</v>
+        <v>0.04029480000000001</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0.008</v>
+        <v>-0.052</v>
       </c>
       <c r="I10" s="25" t="n">
-        <v>254452</v>
+        <v>254192</v>
       </c>
     </row>
     <row r="11">
@@ -5788,7 +5788,7 @@
         <v>46463</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>95.83499999999999</v>
+        <v>95.87</v>
       </c>
       <c r="E11" s="15">
         <f>(100-D11)/100</f>
@@ -5798,13 +5798,13 @@
         <v>0.02</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.0416567</v>
+        <v>0.0413509</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>0.067</v>
+        <v>0.509</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>1666309</v>
+        <v>1641255</v>
       </c>
     </row>
     <row r="12">
@@ -5820,7 +5820,7 @@
         <v>46419</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>95.88500000000001</v>
+        <v>95.905</v>
       </c>
       <c r="E12" s="15">
         <f>(100-D12)/100</f>
@@ -5830,13 +5830,13 @@
         <v>0.02</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.041153</v>
+        <v>0.0409127</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>0.03</v>
+        <v>-0.373</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>189410</v>
+        <v>203226</v>
       </c>
     </row>
     <row r="13">
@@ -5852,7 +5852,7 @@
         <v>46498</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>95.75</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="E13" s="15">
         <f>(100-D13)/100</f>
@@ -5862,13 +5862,13 @@
         <v>0.04</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.0424834</v>
+        <v>0.0420476</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>-0.166</v>
+        <v>-0.524</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>1380</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="14">
@@ -5884,23 +5884,23 @@
         <v>46447</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>95.825</v>
+        <v>95.86</v>
       </c>
       <c r="E14" s="15">
         <f>(100-D14)/100</f>
         <v/>
       </c>
       <c r="F14" s="24" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.0417904</v>
+        <v>0.04141359999999999</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.404</v>
+        <v>0.136</v>
       </c>
       <c r="I14" s="25" t="n">
-        <v>125324</v>
+        <v>124427</v>
       </c>
     </row>
     <row r="15">
@@ -5916,7 +5916,7 @@
         <v>46526</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>95.68000000000001</v>
+        <v>95.735</v>
       </c>
       <c r="E15" s="15">
         <f>(100-D15)/100</f>
@@ -5926,13 +5926,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.0431629</v>
+        <v>0.0426302</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.371</v>
+        <v>-0.198</v>
       </c>
       <c r="I15" s="25" t="n">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="16">
@@ -5948,7 +5948,7 @@
         <v>46478</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>95.755</v>
+        <v>95.80500000000001</v>
       </c>
       <c r="E16" s="15">
         <f>(100-D16)/100</f>
@@ -5958,13 +5958,13 @@
         <v>0.06</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.04243909999999999</v>
+        <v>0.04197969999999999</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.109</v>
+        <v>0.297</v>
       </c>
       <c r="I16" s="25" t="n">
-        <v>36032</v>
+        <v>34131</v>
       </c>
     </row>
     <row r="17">
@@ -5980,23 +5980,23 @@
         <v>46554</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>95.61</v>
+        <v>95.675</v>
       </c>
       <c r="E17" s="15">
         <f>(100-D17)/100</f>
         <v/>
       </c>
       <c r="F17" s="24" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.0439062</v>
+        <v>0.0432753</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.062</v>
+        <v>0.253</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>1267298</v>
+        <v>1286636</v>
       </c>
     </row>
     <row r="18">
@@ -6012,7 +6012,7 @@
         <v>46508</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>95.675</v>
+        <v>95.73</v>
       </c>
       <c r="E18" s="15">
         <f>(100-D18)/100</f>
@@ -6022,13 +6022,13 @@
         <v>0.08</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.0432771</v>
+        <v>0.0427095</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>0.271</v>
+        <v>0.095</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>71299</v>
+        <v>71664</v>
       </c>
     </row>
     <row r="19">
@@ -6044,7 +6044,7 @@
         <v>46589</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>95.535</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="E19" s="15">
         <f>(100-D19)/100</f>
@@ -6054,10 +6054,10 @@
         <v>0.14</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.0445786</v>
+        <v>0.04387120000000001</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>-0.714</v>
+        <v>-1.288</v>
       </c>
       <c r="I19" s="25" t="n">
         <v>200</v>
@@ -6076,7 +6076,7 @@
         <v>46539</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>95.605</v>
+        <v>95.675</v>
       </c>
       <c r="E20" s="15">
         <f>(100-D20)/100</f>
@@ -6086,13 +6086,13 @@
         <v>0.12</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.0439816</v>
+        <v>0.0433053</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>0.316</v>
+        <v>0.553</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>73691</v>
+        <v>72982</v>
       </c>
     </row>
     <row r="21">
@@ -6108,7 +6108,7 @@
         <v>46569</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>95.54000000000001</v>
+        <v>95.61</v>
       </c>
       <c r="E21" s="15">
         <f>(100-D21)/100</f>
@@ -6118,13 +6118,13 @@
         <v>0.16</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.04463429999999999</v>
+        <v>0.04390570000000001</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>0.343</v>
+        <v>0.057</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>24510</v>
+        <v>24696</v>
       </c>
     </row>
     <row r="22">
@@ -6140,7 +6140,7 @@
         <v>46645</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>95.47</v>
+        <v>95.55</v>
       </c>
       <c r="E22" s="15">
         <f>(100-D22)/100</f>
@@ -6150,13 +6150,13 @@
         <v>0.22</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.0453186</v>
+        <v>0.0445299</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>0.186</v>
+        <v>0.299</v>
       </c>
       <c r="I22" s="25" t="n">
-        <v>1227598</v>
+        <v>1221462</v>
       </c>
     </row>
     <row r="23">
@@ -6172,7 +6172,7 @@
         <v>46600</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>95.505</v>
+        <v>95.58499999999999</v>
       </c>
       <c r="E23" s="15">
         <f>(100-D23)/100</f>
@@ -6182,13 +6182,13 @@
         <v>0.2</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.044944</v>
+        <v>0.0441876</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>-0.06</v>
+        <v>0.376</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>39070</v>
+        <v>39612</v>
       </c>
     </row>
     <row r="24">
@@ -6204,7 +6204,7 @@
         <v>46631</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>95.48</v>
+        <v>95.56</v>
       </c>
       <c r="E24" s="15">
         <f>(100-D24)/100</f>
@@ -6214,13 +6214,13 @@
         <v>0.25</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.0452032</v>
+        <v>0.0443972</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>0.032</v>
+        <v>-0.028</v>
       </c>
       <c r="I24" s="25" t="n">
-        <v>22056</v>
+        <v>22492</v>
       </c>
     </row>
     <row r="25">
@@ -6236,23 +6236,23 @@
         <v>46661</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>95.45999999999999</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="E25" s="15">
         <f>(100-D25)/100</f>
         <v/>
       </c>
       <c r="F25" s="24" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.0453818</v>
+        <v>0.0445732</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>-0.182</v>
+        <v>-0.268</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>5249</v>
+        <v>5506</v>
       </c>
     </row>
     <row r="26">
@@ -6268,7 +6268,7 @@
         <v>46736</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>95.42</v>
+        <v>95.505</v>
       </c>
       <c r="E26" s="15">
         <f>(100-D26)/100</f>
@@ -6278,13 +6278,13 @@
         <v>0.39</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.0457979</v>
+        <v>0.0449782</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>-0.021</v>
+        <v>0.282</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>1083838</v>
+        <v>1077449</v>
       </c>
     </row>
     <row r="27">
@@ -6300,23 +6300,23 @@
         <v>46692</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>95.44499999999999</v>
+        <v>95.52500000000001</v>
       </c>
       <c r="E27" s="15">
         <f>(100-D27)/100</f>
         <v/>
       </c>
       <c r="F27" s="24" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.0455595</v>
+        <v>0.044748</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>0.095</v>
+        <v>-0.02</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>9006</v>
+        <v>9745</v>
       </c>
     </row>
     <row r="28">
@@ -6332,7 +6332,7 @@
         <v>46722</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>95.44499999999999</v>
+        <v>95.52500000000001</v>
       </c>
       <c r="E28" s="15">
         <f>(100-D28)/100</f>
@@ -6342,10 +6342,10 @@
         <v>0.43</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.0455566</v>
+        <v>0.0447433</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>0.066</v>
+        <v>-0.067</v>
       </c>
       <c r="I28" s="25" t="n">
         <v>2499</v>
@@ -6364,7 +6364,7 @@
         <v>46753</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>95.455</v>
+        <v>95.535</v>
       </c>
       <c r="E29" s="15">
         <f>(100-D29)/100</f>
@@ -6374,10 +6374,10 @@
         <v>0.5</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.0454197</v>
+        <v>0.0446253</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>-0.303</v>
+        <v>-0.247</v>
       </c>
       <c r="I29" s="25" t="n">
         <v>20</v>
@@ -6396,23 +6396,23 @@
         <v>46827</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>95.43000000000001</v>
+        <v>95.52</v>
       </c>
       <c r="E30" s="15">
         <f>(100-D30)/100</f>
         <v/>
       </c>
       <c r="F30" s="24" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.0456722</v>
+        <v>0.0447841</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>-0.278</v>
+        <v>-0.159</v>
       </c>
       <c r="I30" s="25" t="n">
-        <v>1583949</v>
+        <v>1573107</v>
       </c>
     </row>
     <row r="31">
@@ -6428,7 +6428,7 @@
         <v>46784</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>95.465</v>
+        <v>95.545</v>
       </c>
       <c r="E31" s="15">
         <f>(100-D31)/100</f>
@@ -6438,10 +6438,10 @@
         <v>0.58</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.04539679999999999</v>
+        <v>0.04458039999999999</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>0.468</v>
+        <v>0.304</v>
       </c>
       <c r="I31" s="25" t="n">
         <v>1</v>
@@ -6460,23 +6460,23 @@
         <v>46925</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>95.45</v>
+        <v>95.545</v>
       </c>
       <c r="E32" s="15">
         <f>(100-D32)/100</f>
         <v/>
       </c>
       <c r="F32" s="24" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.04550849999999999</v>
+        <v>0.0445547</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.047</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>826836</v>
+        <v>836589</v>
       </c>
     </row>
     <row r="33">
@@ -6492,23 +6492,23 @@
         <v>47016</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>95.45999999999999</v>
+        <v>95.56</v>
       </c>
       <c r="E33" s="15">
         <f>(100-D33)/100</f>
         <v/>
       </c>
       <c r="F33" s="24" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.04539679999999999</v>
+        <v>0.044398</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>-0.032</v>
+        <v>-0.02</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>643693</v>
+        <v>641652</v>
       </c>
     </row>
     <row r="34">
@@ -6524,7 +6524,7 @@
         <v>47107</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>95.465</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="E34" s="15">
         <f>(100-D34)/100</f>
@@ -6534,13 +6534,13 @@
         <v>1.55</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.04535040000000001</v>
+        <v>0.0443006</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="I34" s="25" t="n">
-        <v>670131</v>
+        <v>665784</v>
       </c>
     </row>
     <row r="35">
@@ -6556,7 +6556,7 @@
         <v>47198</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>95.47499999999999</v>
+        <v>95.58</v>
       </c>
       <c r="E35" s="15">
         <f>(100-D35)/100</f>
@@ -6566,13 +6566,13 @@
         <v>1.94</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.0452483</v>
+        <v>0.0441986</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>-0.017</v>
+        <v>-0.014</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>550192</v>
+        <v>550207</v>
       </c>
     </row>
     <row r="36">
@@ -6588,23 +6588,23 @@
         <v>47289</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>95.48999999999999</v>
+        <v>95.59</v>
       </c>
       <c r="E36" s="15">
         <f>(100-D36)/100</f>
         <v/>
       </c>
       <c r="F36" s="24" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.0451013</v>
+        <v>0.0441026</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>0.013</v>
+        <v>0.026</v>
       </c>
       <c r="I36" s="25" t="n">
-        <v>395341</v>
+        <v>395795</v>
       </c>
     </row>
     <row r="37">
@@ -6620,7 +6620,7 @@
         <v>47380</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>95.5</v>
+        <v>95.595</v>
       </c>
       <c r="E37" s="15">
         <f>(100-D37)/100</f>
@@ -6630,13 +6630,13 @@
         <v>2.85</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.0450014</v>
+        <v>0.0440466</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>0.014</v>
+        <v>-0.034</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>389747</v>
+        <v>393238</v>
       </c>
     </row>
     <row r="38">
@@ -6652,7 +6652,7 @@
         <v>47471</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>95.505</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="E38" s="15">
         <f>(100-D38)/100</f>
@@ -6662,13 +6662,13 @@
         <v>3.36</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.0449461</v>
+        <v>0.0440029</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>-0.039</v>
+        <v>0.029</v>
       </c>
       <c r="I38" s="25" t="n">
-        <v>310179</v>
+        <v>305317</v>
       </c>
     </row>
     <row r="39">
@@ -6684,23 +6684,23 @@
         <v>47562</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>95.51000000000001</v>
+        <v>95.595</v>
       </c>
       <c r="E39" s="15">
         <f>(100-D39)/100</f>
         <v/>
       </c>
       <c r="F39" s="24" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.0449053</v>
+        <v>0.0440496</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>0.053</v>
+        <v>-0.004</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>250890</v>
+        <v>248123</v>
       </c>
     </row>
     <row r="40">
@@ -6716,7 +6716,7 @@
         <v>47653</v>
       </c>
       <c r="D40" s="23" t="n">
-        <v>95.505</v>
+        <v>95.58499999999999</v>
       </c>
       <c r="E40" s="15">
         <f>(100-D40)/100</f>
@@ -6726,13 +6726,13 @@
         <v>4.5</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.0449444</v>
+        <v>0.0441484</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>-0.056</v>
+        <v>-0.016</v>
       </c>
       <c r="I40" s="25" t="n">
-        <v>185443</v>
+        <v>183983</v>
       </c>
     </row>
     <row r="41">
@@ -6748,23 +6748,23 @@
         <v>47744</v>
       </c>
       <c r="D41" s="23" t="n">
-        <v>95.5</v>
+        <v>95.575</v>
       </c>
       <c r="E41" s="15">
         <f>(100-D41)/100</f>
         <v/>
       </c>
       <c r="F41" s="24" t="n">
-        <v>5.13</v>
+        <v>5.12</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.0450055</v>
+        <v>0.0442516</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>0.055</v>
+        <v>0.016</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>159838</v>
+        <v>156079</v>
       </c>
     </row>
     <row r="42">
@@ -6780,23 +6780,23 @@
         <v>47835</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>95.485</v>
+        <v>95.56</v>
       </c>
       <c r="E42" s="15">
         <f>(100-D42)/100</f>
         <v/>
       </c>
       <c r="F42" s="24" t="n">
-        <v>5.79</v>
+        <v>5.78</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.0451449</v>
+        <v>0.044398</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>-0.051</v>
+        <v>-0.02</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>148941</v>
+        <v>148761</v>
       </c>
     </row>
     <row r="43">
@@ -6812,23 +6812,23 @@
         <v>47926</v>
       </c>
       <c r="D43" s="23" t="n">
-        <v>95.47</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="E43" s="15">
         <f>(100-D43)/100</f>
         <v/>
       </c>
       <c r="F43" s="24" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.0453037</v>
+        <v>0.0446037</v>
       </c>
       <c r="H43" s="24" t="n">
         <v>0.037</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>117196</v>
+        <v>115701</v>
       </c>
     </row>
     <row r="44">
@@ -6844,23 +6844,23 @@
         <v>48017</v>
       </c>
       <c r="D44" s="23" t="n">
-        <v>95.44499999999999</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="E44" s="15">
         <f>(100-D44)/100</f>
         <v/>
       </c>
       <c r="F44" s="24" t="n">
-        <v>7.21</v>
+        <v>7.2</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.0455476</v>
+        <v>0.0448944</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>-0.024</v>
+        <v>-0.056</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>86510</v>
+        <v>85661</v>
       </c>
     </row>
     <row r="45">
@@ -6876,23 +6876,23 @@
         <v>48108</v>
       </c>
       <c r="D45" s="23" t="n">
-        <v>95.41500000000001</v>
+        <v>95.48</v>
       </c>
       <c r="E45" s="15">
         <f>(100-D45)/100</f>
         <v/>
       </c>
       <c r="F45" s="24" t="n">
-        <v>7.97</v>
+        <v>7.96</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.0458533</v>
+        <v>0.0452083</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>0.033</v>
+        <v>0.083</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>72445</v>
+        <v>70849</v>
       </c>
     </row>
     <row r="46">
@@ -6908,7 +6908,7 @@
         <v>48199</v>
       </c>
       <c r="D46" s="23" t="n">
-        <v>95.38</v>
+        <v>95.44</v>
       </c>
       <c r="E46" s="15">
         <f>(100-D46)/100</f>
@@ -6918,13 +6918,13 @@
         <v>8.76</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.04619500000000001</v>
+        <v>0.0455897</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>-0.05</v>
+        <v>-0.103</v>
       </c>
       <c r="I46" s="25" t="n">
-        <v>40015</v>
+        <v>39261</v>
       </c>
     </row>
     <row r="47">
@@ -6940,23 +6940,23 @@
         <v>48290</v>
       </c>
       <c r="D47" s="23" t="n">
-        <v>95.34999999999999</v>
+        <v>95.41</v>
       </c>
       <c r="E47" s="15">
         <f>(100-D47)/100</f>
         <v/>
       </c>
       <c r="F47" s="24" t="n">
-        <v>9.59</v>
+        <v>9.58</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.04650509999999999</v>
+        <v>0.0459092</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>0.051</v>
+        <v>0.092</v>
       </c>
       <c r="I47" s="25" t="n">
-        <v>8021</v>
+        <v>8219</v>
       </c>
     </row>
     <row r="48">
@@ -6972,23 +6972,23 @@
         <v>48381</v>
       </c>
       <c r="D48" s="23" t="n">
-        <v>95.315</v>
+        <v>95.37</v>
       </c>
       <c r="E48" s="15">
         <f>(100-D48)/100</f>
         <v/>
       </c>
       <c r="F48" s="24" t="n">
-        <v>10.44</v>
+        <v>10.43</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.0468461</v>
+        <v>0.0462939</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>-0.039</v>
+        <v>-0.061</v>
       </c>
       <c r="I48" s="25" t="n">
-        <v>4147</v>
+        <v>4826</v>
       </c>
     </row>
     <row r="49">
@@ -7004,23 +7004,23 @@
         <v>48472</v>
       </c>
       <c r="D49" s="23" t="n">
-        <v>95.285</v>
+        <v>95.33499999999999</v>
       </c>
       <c r="E49" s="15">
         <f>(100-D49)/100</f>
         <v/>
       </c>
       <c r="F49" s="24" t="n">
-        <v>11.33</v>
+        <v>11.32</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.0471519</v>
+        <v>0.0466537</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>0.019</v>
+        <v>0.037</v>
       </c>
       <c r="I49" s="25" t="n">
-        <v>1113</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="50">
@@ -7036,23 +7036,23 @@
         <v>48563</v>
       </c>
       <c r="D50" s="23" t="n">
-        <v>95.255</v>
+        <v>95.3</v>
       </c>
       <c r="E50" s="15">
         <f>(100-D50)/100</f>
         <v/>
       </c>
       <c r="F50" s="24" t="n">
-        <v>12.24</v>
+        <v>12.23</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.04744900000000001</v>
+        <v>0.0469972</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>-0.01</v>
+        <v>-0.028</v>
       </c>
       <c r="I50" s="25" t="n">
-        <v>570</v>
+        <v>716</v>
       </c>
     </row>
     <row r="51">
@@ -7068,20 +7068,20 @@
         <v>48654</v>
       </c>
       <c r="D51" s="23" t="n">
-        <v>95.22499999999999</v>
+        <v>95.27</v>
       </c>
       <c r="E51" s="15">
         <f>(100-D51)/100</f>
         <v/>
       </c>
       <c r="F51" s="24" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.04775210000000001</v>
+        <v>0.0473023</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="I51" s="25" t="n">
         <v>161</v>
@@ -7100,20 +7100,20 @@
         <v>48745</v>
       </c>
       <c r="D52" s="23" t="n">
-        <v>95.19499999999999</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="E52" s="15">
         <f>(100-D52)/100</f>
         <v/>
       </c>
       <c r="F52" s="24" t="n">
-        <v>14.15</v>
+        <v>14.14</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.0480466</v>
+        <v>0.0475976</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.024</v>
       </c>
       <c r="I52" s="25" t="n">
         <v>36</v>
@@ -7132,20 +7132,20 @@
         <v>48843</v>
       </c>
       <c r="D53" s="23" t="n">
-        <v>95.17</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="E53" s="15">
         <f>(100-D53)/100</f>
         <v/>
       </c>
       <c r="F53" s="24" t="n">
-        <v>15.18</v>
+        <v>15.17</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.04830110000000001</v>
+        <v>0.0479018</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
       <c r="I53" s="25" t="n">
         <v>3</v>
@@ -7164,20 +7164,20 @@
         <v>48934</v>
       </c>
       <c r="D54" s="23" t="n">
-        <v>95.145</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="E54" s="15">
         <f>(100-D54)/100</f>
         <v/>
       </c>
       <c r="F54" s="24" t="n">
-        <v>16.25</v>
+        <v>16.23</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.0485565</v>
+        <v>0.048203</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>0.065</v>
+        <v>0.03</v>
       </c>
       <c r="I54" s="25" t="n">
         <v>0</v>
@@ -7196,20 +7196,20 @@
         <v>49018</v>
       </c>
       <c r="D55" s="23" t="n">
-        <v>95.12</v>
+        <v>95.155</v>
       </c>
       <c r="E55" s="15">
         <f>(100-D55)/100</f>
         <v/>
       </c>
       <c r="F55" s="24" t="n">
-        <v>17.25</v>
+        <v>17.24</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.0487839</v>
+        <v>0.0484387</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>-0.161</v>
+        <v>-0.113</v>
       </c>
       <c r="I55" s="25" t="n">
         <v>11</v>
@@ -7228,20 +7228,20 @@
         <v>49116</v>
       </c>
       <c r="D56" s="23" t="n">
-        <v>95.105</v>
+        <v>95.13500000000001</v>
       </c>
       <c r="E56" s="15">
         <f>(100-D56)/100</f>
         <v/>
       </c>
       <c r="F56" s="24" t="n">
-        <v>18.33</v>
+        <v>18.31</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.0489728</v>
+        <v>0.04866889999999999</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>0.228</v>
+        <v>0.189</v>
       </c>
       <c r="I56" s="25" t="n">
         <v>0</v>
@@ -7260,20 +7260,20 @@
         <v>49207</v>
       </c>
       <c r="D57" s="23" t="n">
-        <v>95.075</v>
+        <v>95.105</v>
       </c>
       <c r="E57" s="15">
         <f>(100-D57)/100</f>
         <v/>
       </c>
       <c r="F57" s="24" t="n">
-        <v>19.47</v>
+        <v>19.45</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.0492215</v>
+        <v>0.0489234</v>
       </c>
       <c r="H57" s="24" t="n">
-        <v>-0.285</v>
+        <v>-0.266</v>
       </c>
       <c r="I57" s="25" t="n">
         <v>0</v>
@@ -7292,20 +7292,20 @@
         <v>49298</v>
       </c>
       <c r="D58" s="23" t="n">
-        <v>95.065</v>
+        <v>95.095</v>
       </c>
       <c r="E58" s="15">
         <f>(100-D58)/100</f>
         <v/>
       </c>
       <c r="F58" s="24" t="n">
-        <v>20.59</v>
+        <v>20.57</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.0493837</v>
+        <v>0.0490831</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>0.337</v>
+        <v>0.331</v>
       </c>
       <c r="I58" s="25" t="n">
         <v>0</v>
@@ -7324,20 +7324,20 @@
         <v>49389</v>
       </c>
       <c r="D59" s="23" t="n">
-        <v>95.02</v>
+        <v>95.05</v>
       </c>
       <c r="E59" s="15">
         <f>(100-D59)/100</f>
         <v/>
       </c>
       <c r="F59" s="24" t="n">
-        <v>21.73</v>
+        <v>21.72</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.0497686</v>
+        <v>0.0494687</v>
       </c>
       <c r="H59" s="24" t="n">
-        <v>-0.314</v>
+        <v>-0.313</v>
       </c>
       <c r="I59" s="25" t="n">
         <v>0</v>
@@ -7356,20 +7356,20 @@
         <v>49480</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>95.01000000000001</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="E60" s="15">
         <f>(100-D60)/100</f>
         <v/>
       </c>
       <c r="F60" s="24" t="n">
-        <v>22.89</v>
+        <v>22.88</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.0499218</v>
+        <v>0.0496217</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>0.218</v>
+        <v>0.217</v>
       </c>
       <c r="I60" s="25" t="n">
         <v>0</v>
@@ -7388,17 +7388,17 @@
         <v>49571</v>
       </c>
       <c r="D61" s="23" t="n">
-        <v>94.985</v>
+        <v>95.015</v>
       </c>
       <c r="E61" s="15">
         <f>(100-D61)/100</f>
         <v/>
       </c>
       <c r="F61" s="24" t="n">
-        <v>24.08</v>
+        <v>24.07</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.0501342</v>
+        <v>0.0498342</v>
       </c>
       <c r="H61" s="24" t="n">
         <v>-0.158</v>
@@ -7420,17 +7420,17 @@
         <v>49662</v>
       </c>
       <c r="D62" s="23" t="n">
-        <v>94.95999999999999</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="E62" s="15">
         <f>(100-D62)/100</f>
         <v/>
       </c>
       <c r="F62" s="24" t="n">
-        <v>25.29</v>
+        <v>25.27</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.0504187</v>
+        <v>0.0501187</v>
       </c>
       <c r="H62" s="24" t="n">
         <v>0.187</v>
@@ -7452,17 +7452,17 @@
         <v>49753</v>
       </c>
       <c r="D63" s="23" t="n">
-        <v>94.91500000000001</v>
+        <v>94.94499999999999</v>
       </c>
       <c r="E63" s="15">
         <f>(100-D63)/100</f>
         <v/>
       </c>
       <c r="F63" s="24" t="n">
-        <v>26.52</v>
+        <v>26.5</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.0508333</v>
+        <v>0.0505333</v>
       </c>
       <c r="H63" s="24" t="n">
         <v>-0.167</v>
@@ -7484,17 +7484,17 @@
         <v>49844</v>
       </c>
       <c r="D64" s="23" t="n">
-        <v>94.905</v>
+        <v>94.935</v>
       </c>
       <c r="E64" s="15">
         <f>(100-D64)/100</f>
         <v/>
       </c>
       <c r="F64" s="24" t="n">
-        <v>27.76</v>
+        <v>27.75</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.0509558</v>
+        <v>0.0506558</v>
       </c>
       <c r="H64" s="24" t="n">
         <v>0.058</v>
@@ -7506,7 +7506,7 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Fit: 61 contracts, RMS residual 0.197 bp, max 0.714 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
+          <t>Fit: 61 contracts, RMS residual 0.275 bp, max 1.288 bp. Residual = model futures rate - market rate. Source: CME Group daily settlements (SR3, SR1).</t>
         </is>
       </c>
     </row>
@@ -7521,7 +7521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8369,14 +8369,6 @@
       </c>
       <c r="B106" s="26" t="n">
         <v>0.0361</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="n">
-        <v>46175</v>
-      </c>
-      <c r="B107" s="26" t="n">
-        <v>0.0363</v>
       </c>
     </row>
   </sheetData>
